--- a/data/tags/מוזיקה לועזית חדשה/sites/apple-music-playlist/2026-05-week01/titles.xlsx
+++ b/data/tags/מוזיקה לועזית חדשה/sites/apple-music-playlist/2026-05-week01/titles.xlsx
@@ -445,7 +445,7 @@
         <v>https://music.apple.com/us/song/eurosummer-girls-trip/1894058279</v>
       </c>
       <c r="D2" t="str">
-        <v>2026-05-01</v>
+        <v>2026-05-02</v>
       </c>
       <c r="E2" t="str">
         <v/>
@@ -483,7 +483,7 @@
         <v>https://music.apple.com/us/song/shape-of-a-woman/6764429252</v>
       </c>
       <c r="D3" t="str">
-        <v>2026-05-01</v>
+        <v>2026-05-02</v>
       </c>
       <c r="E3" t="str">
         <v/>
@@ -521,7 +521,7 @@
         <v>https://music.apple.com/us/song/bring-your-love/1892545227</v>
       </c>
       <c r="D4" t="str">
-        <v>2026-05-01</v>
+        <v>2026-05-02</v>
       </c>
       <c r="E4" t="str">
         <v/>
@@ -559,7 +559,7 @@
         <v>https://music.apple.com/us/song/horses-and-divorces/1883177267</v>
       </c>
       <c r="D5" t="str">
-        <v>2026-05-01</v>
+        <v>2026-05-02</v>
       </c>
       <c r="E5" t="str">
         <v/>
@@ -597,7 +597,7 @@
         <v>https://music.apple.com/us/song/staying-still/6762758806</v>
       </c>
       <c r="D6" t="str">
-        <v>2026-05-01</v>
+        <v>2026-05-02</v>
       </c>
       <c r="E6" t="str">
         <v/>
@@ -635,7 +635,7 @@
         <v>https://music.apple.com/us/song/fine-place-to-die/6764686279</v>
       </c>
       <c r="D7" t="str">
-        <v>2026-05-01</v>
+        <v>2026-05-02</v>
       </c>
       <c r="E7" t="str">
         <v/>
@@ -673,7 +673,7 @@
         <v>https://music.apple.com/us/song/mutt/6763145178</v>
       </c>
       <c r="D8" t="str">
-        <v>2026-05-01</v>
+        <v>2026-05-02</v>
       </c>
       <c r="E8" t="str">
         <v/>
@@ -711,7 +711,7 @@
         <v>https://music.apple.com/us/song/fire-away-feat-slayyyter/1892422570</v>
       </c>
       <c r="D9" t="str">
-        <v>2026-05-01</v>
+        <v>2026-05-02</v>
       </c>
       <c r="E9" t="str">
         <v/>
@@ -749,7 +749,7 @@
         <v>https://music.apple.com/us/song/lioness/1878649397</v>
       </c>
       <c r="D10" t="str">
-        <v>2026-05-01</v>
+        <v>2026-05-02</v>
       </c>
       <c r="E10" t="str">
         <v/>
@@ -787,7 +787,7 @@
         <v>https://music.apple.com/us/song/its-ok/6763134121</v>
       </c>
       <c r="D11" t="str">
-        <v>2026-05-01</v>
+        <v>2026-05-02</v>
       </c>
       <c r="E11" t="str">
         <v/>
@@ -825,7 +825,7 @@
         <v>https://music.apple.com/us/song/promise/6763162287</v>
       </c>
       <c r="D12" t="str">
-        <v>2026-05-01</v>
+        <v>2026-05-02</v>
       </c>
       <c r="E12" t="str">
         <v/>
@@ -863,7 +863,7 @@
         <v>https://music.apple.com/us/song/cool-buzz/1880470657</v>
       </c>
       <c r="D13" t="str">
-        <v>2026-05-01</v>
+        <v>2026-05-02</v>
       </c>
       <c r="E13" t="str">
         <v/>
@@ -901,7 +901,7 @@
         <v>https://music.apple.com/us/song/material-lover/6764429256</v>
       </c>
       <c r="D14" t="str">
-        <v>2026-05-01</v>
+        <v>2026-05-02</v>
       </c>
       <c r="E14" t="str">
         <v/>
@@ -939,7 +939,7 @@
         <v>https://music.apple.com/us/song/fallin-feat-leon-thomas/6764419265</v>
       </c>
       <c r="D15" t="str">
-        <v>2026-05-01</v>
+        <v>2026-05-02</v>
       </c>
       <c r="E15" t="str">
         <v/>
@@ -977,7 +977,7 @@
         <v>https://music.apple.com/us/song/echo/6763379683</v>
       </c>
       <c r="D16" t="str">
-        <v>2026-05-01</v>
+        <v>2026-05-02</v>
       </c>
       <c r="E16" t="str">
         <v/>
@@ -1015,7 +1015,7 @@
         <v>https://music.apple.com/us/song/blackberry-marmalade/1887627837</v>
       </c>
       <c r="D17" t="str">
-        <v>2026-05-01</v>
+        <v>2026-05-02</v>
       </c>
       <c r="E17" t="str">
         <v/>
@@ -1053,7 +1053,7 @@
         <v>https://music.apple.com/us/song/ricky-bobby/6764406571</v>
       </c>
       <c r="D18" t="str">
-        <v>2026-05-01</v>
+        <v>2026-05-02</v>
       </c>
       <c r="E18" t="str">
         <v/>
@@ -1091,7 +1091,7 @@
         <v>https://music.apple.com/us/song/te-entiendo-remix/6763665638</v>
       </c>
       <c r="D19" t="str">
-        <v>2026-05-01</v>
+        <v>2026-05-02</v>
       </c>
       <c r="E19" t="str">
         <v/>
@@ -1129,7 +1129,7 @@
         <v>https://music.apple.com/us/song/dont-worry-baby/1894294411</v>
       </c>
       <c r="D20" t="str">
-        <v>2026-05-01</v>
+        <v>2026-05-02</v>
       </c>
       <c r="E20" t="str">
         <v/>
@@ -1167,7 +1167,7 @@
         <v>https://music.apple.com/us/song/bitch/6763622110</v>
       </c>
       <c r="D21" t="str">
-        <v>2026-05-01</v>
+        <v>2026-05-02</v>
       </c>
       <c r="E21" t="str">
         <v/>
@@ -1205,7 +1205,7 @@
         <v>https://music.apple.com/us/song/just-wanna-cry/6763414703</v>
       </c>
       <c r="D22" t="str">
-        <v>2026-05-01</v>
+        <v>2026-05-02</v>
       </c>
       <c r="E22" t="str">
         <v/>
@@ -1243,7 +1243,7 @@
         <v>https://music.apple.com/us/song/carry-the-weight/6763611647</v>
       </c>
       <c r="D23" t="str">
-        <v>2026-05-01</v>
+        <v>2026-05-02</v>
       </c>
       <c r="E23" t="str">
         <v/>
@@ -1281,7 +1281,7 @@
         <v>https://music.apple.com/us/song/prostitute/1894092341</v>
       </c>
       <c r="D24" t="str">
-        <v>2026-05-01</v>
+        <v>2026-05-02</v>
       </c>
       <c r="E24" t="str">
         <v/>
@@ -1319,7 +1319,7 @@
         <v>https://music.apple.com/us/song/im-not-joking/1872842623</v>
       </c>
       <c r="D25" t="str">
-        <v>2026-05-01</v>
+        <v>2026-05-02</v>
       </c>
       <c r="E25" t="str">
         <v/>
@@ -1357,7 +1357,7 @@
         <v>https://music.apple.com/us/song/ruca/6763671002</v>
       </c>
       <c r="D26" t="str">
-        <v>2026-05-01</v>
+        <v>2026-05-02</v>
       </c>
       <c r="E26" t="str">
         <v/>
@@ -1395,7 +1395,7 @@
         <v>https://music.apple.com/us/song/make-you-fight/1892332386</v>
       </c>
       <c r="D27" t="str">
-        <v>2026-05-01</v>
+        <v>2026-05-02</v>
       </c>
       <c r="E27" t="str">
         <v/>
@@ -1433,7 +1433,7 @@
         <v>https://music.apple.com/us/song/n0rth4evr/6763302230</v>
       </c>
       <c r="D28" t="str">
-        <v>2026-05-01</v>
+        <v>2026-05-02</v>
       </c>
       <c r="E28" t="str">
         <v/>
@@ -1471,7 +1471,7 @@
         <v>https://music.apple.com/us/song/boy-in-red/1892543110</v>
       </c>
       <c r="D29" t="str">
-        <v>2026-05-01</v>
+        <v>2026-05-02</v>
       </c>
       <c r="E29" t="str">
         <v/>
@@ -1509,7 +1509,7 @@
         <v>https://music.apple.com/us/song/ea-ea-ea/6763438376</v>
       </c>
       <c r="D30" t="str">
-        <v>2026-05-01</v>
+        <v>2026-05-02</v>
       </c>
       <c r="E30" t="str">
         <v/>
@@ -1547,7 +1547,7 @@
         <v>https://music.apple.com/us/song/just-a-man/6762944365</v>
       </c>
       <c r="D31" t="str">
-        <v>2026-05-01</v>
+        <v>2026-05-02</v>
       </c>
       <c r="E31" t="str">
         <v/>
@@ -1585,7 +1585,7 @@
         <v>https://music.apple.com/us/song/the-observer/1891982314</v>
       </c>
       <c r="D32" t="str">
-        <v>2026-05-01</v>
+        <v>2026-05-02</v>
       </c>
       <c r="E32" t="str">
         <v/>
@@ -1623,7 +1623,7 @@
         <v>https://music.apple.com/us/song/heroine/6762693177</v>
       </c>
       <c r="D33" t="str">
-        <v>2026-05-01</v>
+        <v>2026-05-02</v>
       </c>
       <c r="E33" t="str">
         <v/>
@@ -1661,7 +1661,7 @@
         <v>https://music.apple.com/us/song/do-me-right/6764667658</v>
       </c>
       <c r="D34" t="str">
-        <v>2026-05-01</v>
+        <v>2026-05-02</v>
       </c>
       <c r="E34" t="str">
         <v/>
@@ -1699,7 +1699,7 @@
         <v>https://music.apple.com/us/song/its-me/1887194026</v>
       </c>
       <c r="D35" t="str">
-        <v>2026-05-01</v>
+        <v>2026-05-02</v>
       </c>
       <c r="E35" t="str">
         <v/>
@@ -1737,7 +1737,7 @@
         <v>https://music.apple.com/us/song/the-precipice/1891830326</v>
       </c>
       <c r="D36" t="str">
-        <v>2026-05-01</v>
+        <v>2026-05-02</v>
       </c>
       <c r="E36" t="str">
         <v/>
@@ -1775,7 +1775,7 @@
         <v>https://music.apple.com/us/song/hello-lonesome/1892466003</v>
       </c>
       <c r="D37" t="str">
-        <v>2026-05-01</v>
+        <v>2026-05-02</v>
       </c>
       <c r="E37" t="str">
         <v/>
@@ -1813,7 +1813,7 @@
         <v>https://music.apple.com/us/song/trippin-opera-edit/6764648776</v>
       </c>
       <c r="D38" t="str">
-        <v>2026-05-01</v>
+        <v>2026-05-02</v>
       </c>
       <c r="E38" t="str">
         <v/>
@@ -1851,7 +1851,7 @@
         <v>https://music.apple.com/us/song/the-mandalorian-and-grogu-boys-noize-remix-from-star/6764131630</v>
       </c>
       <c r="D39" t="str">
-        <v>2026-05-01</v>
+        <v>2026-05-02</v>
       </c>
       <c r="E39" t="str">
         <v/>
@@ -1889,7 +1889,7 @@
         <v>https://music.apple.com/us/song/blow-my-mind-ca7riel-paco-amoroso-version/1894344140</v>
       </c>
       <c r="D40" t="str">
-        <v>2026-05-01</v>
+        <v>2026-05-02</v>
       </c>
       <c r="E40" t="str">
         <v/>
@@ -1927,7 +1927,7 @@
         <v>https://music.apple.com/us/song/bring-that-body/6764009310</v>
       </c>
       <c r="D41" t="str">
-        <v>2026-05-01</v>
+        <v>2026-05-02</v>
       </c>
       <c r="E41" t="str">
         <v/>
@@ -1965,7 +1965,7 @@
         <v>https://music.apple.com/us/song/star/1891845608</v>
       </c>
       <c r="D42" t="str">
-        <v>2026-05-01</v>
+        <v>2026-05-02</v>
       </c>
       <c r="E42" t="str">
         <v/>
@@ -2003,7 +2003,7 @@
         <v>https://music.apple.com/us/song/whats-a-little-rain/1885061171</v>
       </c>
       <c r="D43" t="str">
-        <v>2026-05-01</v>
+        <v>2026-05-02</v>
       </c>
       <c r="E43" t="str">
         <v/>
@@ -2041,7 +2041,7 @@
         <v>https://music.apple.com/us/song/evergreen/1866700315</v>
       </c>
       <c r="D44" t="str">
-        <v>2026-05-01</v>
+        <v>2026-05-02</v>
       </c>
       <c r="E44" t="str">
         <v/>
@@ -2079,7 +2079,7 @@
         <v>https://music.apple.com/us/song/she-does-it-right/1873477957</v>
       </c>
       <c r="D45" t="str">
-        <v>2026-05-01</v>
+        <v>2026-05-02</v>
       </c>
       <c r="E45" t="str">
         <v/>
@@ -2117,7 +2117,7 @@
         <v>https://music.apple.com/us/song/punching-the-flowers/1878362636</v>
       </c>
       <c r="D46" t="str">
-        <v>2026-05-01</v>
+        <v>2026-05-02</v>
       </c>
       <c r="E46" t="str">
         <v/>
@@ -2155,7 +2155,7 @@
         <v>https://music.apple.com/us/song/how-did-you-know/1888553137</v>
       </c>
       <c r="D47" t="str">
-        <v>2026-05-01</v>
+        <v>2026-05-02</v>
       </c>
       <c r="E47" t="str">
         <v/>
@@ -2193,7 +2193,7 @@
         <v>https://music.apple.com/us/song/summer-breeze/6763360727</v>
       </c>
       <c r="D48" t="str">
-        <v>2026-05-01</v>
+        <v>2026-05-02</v>
       </c>
       <c r="E48" t="str">
         <v/>
@@ -2231,7 +2231,7 @@
         <v>https://music.apple.com/us/song/sound-of-a-woman/1859763367</v>
       </c>
       <c r="D49" t="str">
-        <v>2026-05-01</v>
+        <v>2026-05-02</v>
       </c>
       <c r="E49" t="str">
         <v/>
@@ -2269,7 +2269,7 @@
         <v>https://music.apple.com/us/song/my-life/1893157347</v>
       </c>
       <c r="D50" t="str">
-        <v>2026-05-01</v>
+        <v>2026-05-02</v>
       </c>
       <c r="E50" t="str">
         <v/>
@@ -2307,7 +2307,7 @@
         <v>https://music.apple.com/us/song/ribcage/1893155593</v>
       </c>
       <c r="D51" t="str">
-        <v>2026-05-01</v>
+        <v>2026-05-02</v>
       </c>
       <c r="E51" t="str">
         <v/>
@@ -2345,7 +2345,7 @@
         <v>https://music.apple.com/us/song/i-loved-you-then/1878232821</v>
       </c>
       <c r="D52" t="str">
-        <v>2026-05-01</v>
+        <v>2026-05-02</v>
       </c>
       <c r="E52" t="str">
         <v/>
@@ -2383,7 +2383,7 @@
         <v>https://music.apple.com/us/song/ill-let-you-finish/1891844342</v>
       </c>
       <c r="D53" t="str">
-        <v>2026-05-01</v>
+        <v>2026-05-02</v>
       </c>
       <c r="E53" t="str">
         <v/>
@@ -2421,7 +2421,7 @@
         <v>https://music.apple.com/us/song/it-gets-me-through/1884798927</v>
       </c>
       <c r="D54" t="str">
-        <v>2026-05-01</v>
+        <v>2026-05-02</v>
       </c>
       <c r="E54" t="str">
         <v/>
@@ -2459,7 +2459,7 @@
         <v>https://music.apple.com/us/song/the-author/6763327641</v>
       </c>
       <c r="D55" t="str">
-        <v>2026-05-01</v>
+        <v>2026-05-02</v>
       </c>
       <c r="E55" t="str">
         <v/>
@@ -2497,7 +2497,7 @@
         <v>https://music.apple.com/us/song/want-me-back-feat-tors/1889370756</v>
       </c>
       <c r="D56" t="str">
-        <v>2026-05-01</v>
+        <v>2026-05-02</v>
       </c>
       <c r="E56" t="str">
         <v/>
@@ -2535,7 +2535,7 @@
         <v>https://music.apple.com/us/song/ruin/1886537117</v>
       </c>
       <c r="D57" t="str">
-        <v>2026-05-01</v>
+        <v>2026-05-02</v>
       </c>
       <c r="E57" t="str">
         <v/>
@@ -2573,7 +2573,7 @@
         <v>https://music.apple.com/us/song/i-know-i-know/1894354139</v>
       </c>
       <c r="D58" t="str">
-        <v>2026-05-01</v>
+        <v>2026-05-02</v>
       </c>
       <c r="E58" t="str">
         <v/>
@@ -2611,7 +2611,7 @@
         <v>https://music.apple.com/us/song/drive-all-night/6763189759</v>
       </c>
       <c r="D59" t="str">
-        <v>2026-05-01</v>
+        <v>2026-05-02</v>
       </c>
       <c r="E59" t="str">
         <v/>
@@ -2649,7 +2649,7 @@
         <v>https://music.apple.com/us/song/aint-u-tired/6763115235</v>
       </c>
       <c r="D60" t="str">
-        <v>2026-05-01</v>
+        <v>2026-05-02</v>
       </c>
       <c r="E60" t="str">
         <v/>
@@ -2687,7 +2687,7 @@
         <v>https://music.apple.com/us/song/boys-in-blue/1892436920</v>
       </c>
       <c r="D61" t="str">
-        <v>2026-05-01</v>
+        <v>2026-05-02</v>
       </c>
       <c r="E61" t="str">
         <v/>
@@ -2725,7 +2725,7 @@
         <v>https://music.apple.com/us/song/salma-hayek/1891815286</v>
       </c>
       <c r="D62" t="str">
-        <v>2026-05-01</v>
+        <v>2026-05-02</v>
       </c>
       <c r="E62" t="str">
         <v/>
@@ -2763,7 +2763,7 @@
         <v>https://music.apple.com/us/song/stubborn-mouth/1893194800</v>
       </c>
       <c r="D63" t="str">
-        <v>2026-05-01</v>
+        <v>2026-05-02</v>
       </c>
       <c r="E63" t="str">
         <v/>
@@ -2801,7 +2801,7 @@
         <v>https://music.apple.com/us/song/hallucination/6764110976</v>
       </c>
       <c r="D64" t="str">
-        <v>2026-05-01</v>
+        <v>2026-05-02</v>
       </c>
       <c r="E64" t="str">
         <v/>
@@ -2839,7 +2839,7 @@
         <v>https://music.apple.com/us/song/in-da-jungle/1891136400</v>
       </c>
       <c r="D65" t="str">
-        <v>2026-05-01</v>
+        <v>2026-05-02</v>
       </c>
       <c r="E65" t="str">
         <v/>
@@ -2877,7 +2877,7 @@
         <v>https://music.apple.com/us/song/fall-short/1894662749</v>
       </c>
       <c r="D66" t="str">
-        <v>2026-05-01</v>
+        <v>2026-05-02</v>
       </c>
       <c r="E66" t="str">
         <v/>
@@ -2915,7 +2915,7 @@
         <v>https://music.apple.com/us/song/irish-goodbye-feat-kae-tempest/1862224205</v>
       </c>
       <c r="D67" t="str">
-        <v>2026-05-01</v>
+        <v>2026-05-02</v>
       </c>
       <c r="E67" t="str">
         <v/>
@@ -2953,7 +2953,7 @@
         <v>https://music.apple.com/us/song/1989/1893089382</v>
       </c>
       <c r="D68" t="str">
-        <v>2026-05-01</v>
+        <v>2026-05-02</v>
       </c>
       <c r="E68" t="str">
         <v/>
@@ -2991,7 +2991,7 @@
         <v>https://music.apple.com/us/song/no-more-regrets/1893191803</v>
       </c>
       <c r="D69" t="str">
-        <v>2026-05-01</v>
+        <v>2026-05-02</v>
       </c>
       <c r="E69" t="str">
         <v/>
@@ -3029,7 +3029,7 @@
         <v>https://music.apple.com/us/song/drum-machine/1840517102</v>
       </c>
       <c r="D70" t="str">
-        <v>2026-05-01</v>
+        <v>2026-05-02</v>
       </c>
       <c r="E70" t="str">
         <v/>
@@ -3067,7 +3067,7 @@
         <v>https://music.apple.com/us/song/im-perfect/1893181359</v>
       </c>
       <c r="D71" t="str">
-        <v>2026-05-01</v>
+        <v>2026-05-02</v>
       </c>
       <c r="E71" t="str">
         <v/>
@@ -3105,7 +3105,7 @@
         <v>https://music.apple.com/us/song/theme-for-a-train-journey/1880699785</v>
       </c>
       <c r="D72" t="str">
-        <v>2026-05-01</v>
+        <v>2026-05-02</v>
       </c>
       <c r="E72" t="str">
         <v/>
@@ -3143,7 +3143,7 @@
         <v>https://music.apple.com/us/song/bitch-you-weird/6763395875</v>
       </c>
       <c r="D73" t="str">
-        <v>2026-05-01</v>
+        <v>2026-05-02</v>
       </c>
       <c r="E73" t="str">
         <v/>
@@ -3181,7 +3181,7 @@
         <v>https://music.apple.com/us/song/blackbird-rising/1887166611</v>
       </c>
       <c r="D74" t="str">
-        <v>2026-05-01</v>
+        <v>2026-05-02</v>
       </c>
       <c r="E74" t="str">
         <v/>
@@ -3219,7 +3219,7 @@
         <v>https://music.apple.com/us/song/usher-in-the-spirit/6763373678</v>
       </c>
       <c r="D75" t="str">
-        <v>2026-05-01</v>
+        <v>2026-05-02</v>
       </c>
       <c r="E75" t="str">
         <v/>
@@ -3257,7 +3257,7 @@
         <v>https://music.apple.com/us/song/moonlight/1892950791</v>
       </c>
       <c r="D76" t="str">
-        <v>2026-05-01</v>
+        <v>2026-05-02</v>
       </c>
       <c r="E76" t="str">
         <v/>
@@ -3295,7 +3295,7 @@
         <v>https://music.apple.com/us/song/hands-on-me/1893960365</v>
       </c>
       <c r="D77" t="str">
-        <v>2026-05-01</v>
+        <v>2026-05-02</v>
       </c>
       <c r="E77" t="str">
         <v/>
@@ -3333,7 +3333,7 @@
         <v>https://music.apple.com/us/song/closure/1892418294</v>
       </c>
       <c r="D78" t="str">
-        <v>2026-05-01</v>
+        <v>2026-05-02</v>
       </c>
       <c r="E78" t="str">
         <v/>
@@ -3371,7 +3371,7 @@
         <v>https://music.apple.com/us/song/hots-4-u/1891478541</v>
       </c>
       <c r="D79" t="str">
-        <v>2026-05-01</v>
+        <v>2026-05-02</v>
       </c>
       <c r="E79" t="str">
         <v/>
@@ -3409,7 +3409,7 @@
         <v>https://music.apple.com/us/song/cule-poco-sirena-besarico-coste%C3%B1a/1893480200</v>
       </c>
       <c r="D80" t="str">
-        <v>2026-05-01</v>
+        <v>2026-05-02</v>
       </c>
       <c r="E80" t="str">
         <v/>
@@ -3447,7 +3447,7 @@
         <v>https://music.apple.com/us/song/the-coin-toss/1894872115</v>
       </c>
       <c r="D81" t="str">
-        <v>2026-05-01</v>
+        <v>2026-05-02</v>
       </c>
       <c r="E81" t="str">
         <v/>
@@ -3485,7 +3485,7 @@
         <v>https://music.apple.com/us/song/bottles-lights/6763041153</v>
       </c>
       <c r="D82" t="str">
-        <v>2026-05-01</v>
+        <v>2026-05-02</v>
       </c>
       <c r="E82" t="str">
         <v/>
@@ -3523,7 +3523,7 @@
         <v>https://music.apple.com/us/song/perfect-for-me/6762879981</v>
       </c>
       <c r="D83" t="str">
-        <v>2026-05-01</v>
+        <v>2026-05-02</v>
       </c>
       <c r="E83" t="str">
         <v/>
@@ -3561,7 +3561,7 @@
         <v>https://music.apple.com/us/song/so/1893162424</v>
       </c>
       <c r="D84" t="str">
-        <v>2026-05-01</v>
+        <v>2026-05-02</v>
       </c>
       <c r="E84" t="str">
         <v/>
@@ -3599,7 +3599,7 @@
         <v>https://music.apple.com/us/song/pase-y-pase/1894076490</v>
       </c>
       <c r="D85" t="str">
-        <v>2026-05-01</v>
+        <v>2026-05-02</v>
       </c>
       <c r="E85" t="str">
         <v/>
@@ -3637,7 +3637,7 @@
         <v>https://music.apple.com/us/song/agou%C3%A9-dambala-yanvalou-1/1888242486</v>
       </c>
       <c r="D86" t="str">
-        <v>2026-05-01</v>
+        <v>2026-05-02</v>
       </c>
       <c r="E86" t="str">
         <v/>
@@ -3675,7 +3675,7 @@
         <v>https://music.apple.com/us/song/aljahalat/1889267983</v>
       </c>
       <c r="D87" t="str">
-        <v>2026-05-01</v>
+        <v>2026-05-02</v>
       </c>
       <c r="E87" t="str">
         <v/>
@@ -3713,7 +3713,7 @@
         <v>https://music.apple.com/us/song/puleza/1893765840</v>
       </c>
       <c r="D88" t="str">
-        <v>2026-05-01</v>
+        <v>2026-05-02</v>
       </c>
       <c r="E88" t="str">
         <v/>
@@ -3751,7 +3751,7 @@
         <v>https://music.apple.com/us/song/bastards/6762403102</v>
       </c>
       <c r="D89" t="str">
-        <v>2026-05-01</v>
+        <v>2026-05-02</v>
       </c>
       <c r="E89" t="str">
         <v/>
@@ -3789,7 +3789,7 @@
         <v>https://music.apple.com/us/song/crutch/6763345020</v>
       </c>
       <c r="D90" t="str">
-        <v>2026-05-01</v>
+        <v>2026-05-02</v>
       </c>
       <c r="E90" t="str">
         <v/>
@@ -3827,7 +3827,7 @@
         <v>https://music.apple.com/us/song/just-a-man/1893736206</v>
       </c>
       <c r="D91" t="str">
-        <v>2026-05-01</v>
+        <v>2026-05-02</v>
       </c>
       <c r="E91" t="str">
         <v/>
@@ -3865,7 +3865,7 @@
         <v>https://music.apple.com/us/song/take-care-of-you/6762283983</v>
       </c>
       <c r="D92" t="str">
-        <v>2026-05-01</v>
+        <v>2026-05-02</v>
       </c>
       <c r="E92" t="str">
         <v/>
@@ -3903,7 +3903,7 @@
         <v>https://music.apple.com/us/song/love-you-more/1889686330</v>
       </c>
       <c r="D93" t="str">
-        <v>2026-05-01</v>
+        <v>2026-05-02</v>
       </c>
       <c r="E93" t="str">
         <v/>
@@ -3941,7 +3941,7 @@
         <v>https://music.apple.com/us/song/construct/1869323374</v>
       </c>
       <c r="D94" t="str">
-        <v>2026-05-01</v>
+        <v>2026-05-02</v>
       </c>
       <c r="E94" t="str">
         <v/>
@@ -3979,7 +3979,7 @@
         <v>https://music.apple.com/us/song/as-above-so-below/1872651422</v>
       </c>
       <c r="D95" t="str">
-        <v>2026-05-01</v>
+        <v>2026-05-02</v>
       </c>
       <c r="E95" t="str">
         <v/>
@@ -4017,7 +4017,7 @@
         <v>https://music.apple.com/us/song/revenant/6763148056</v>
       </c>
       <c r="D96" t="str">
-        <v>2026-05-01</v>
+        <v>2026-05-02</v>
       </c>
       <c r="E96" t="str">
         <v/>
@@ -4055,7 +4055,7 @@
         <v>https://music.apple.com/us/song/black-box-feat-joe-duplantier-the-mystery-of/6762312582</v>
       </c>
       <c r="D97" t="str">
-        <v>2026-05-01</v>
+        <v>2026-05-02</v>
       </c>
       <c r="E97" t="str">
         <v/>
@@ -4093,7 +4093,7 @@
         <v>https://music.apple.com/us/song/power-4/6763647813</v>
       </c>
       <c r="D98" t="str">
-        <v>2026-05-01</v>
+        <v>2026-05-02</v>
       </c>
       <c r="E98" t="str">
         <v/>
@@ -4131,7 +4131,7 @@
         <v>https://music.apple.com/us/song/too-easy/1893814702</v>
       </c>
       <c r="D99" t="str">
-        <v>2026-05-01</v>
+        <v>2026-05-02</v>
       </c>
       <c r="E99" t="str">
         <v/>
@@ -4169,7 +4169,7 @@
         <v>https://music.apple.com/us/song/if-you-want-it/1892503347</v>
       </c>
       <c r="D100" t="str">
-        <v>2026-05-01</v>
+        <v>2026-05-02</v>
       </c>
       <c r="E100" t="str">
         <v/>
@@ -4207,7 +4207,7 @@
         <v>https://music.apple.com/us/song/shoplifting/1852812659</v>
       </c>
       <c r="D101" t="str">
-        <v>2026-05-01</v>
+        <v>2026-05-02</v>
       </c>
       <c r="E101" t="str">
         <v/>
@@ -4245,7 +4245,7 @@
         <v>https://music.apple.com/us/song/endlessly-feat-bea1991/1876022833</v>
       </c>
       <c r="D102" t="str">
-        <v>2026-05-01</v>
+        <v>2026-05-02</v>
       </c>
       <c r="E102" t="str">
         <v/>

--- a/data/tags/מוזיקה לועזית חדשה/sites/apple-music-playlist/2026-05-week01/titles.xlsx
+++ b/data/tags/מוזיקה לועזית חדשה/sites/apple-music-playlist/2026-05-week01/titles.xlsx
@@ -445,7 +445,7 @@
         <v>https://music.apple.com/us/song/eurosummer-girls-trip/1894058279</v>
       </c>
       <c r="D2" t="str">
-        <v>2026-05-02</v>
+        <v>2026-05-03</v>
       </c>
       <c r="E2" t="str">
         <v/>
@@ -483,7 +483,7 @@
         <v>https://music.apple.com/us/song/shape-of-a-woman/6764429252</v>
       </c>
       <c r="D3" t="str">
-        <v>2026-05-02</v>
+        <v>2026-05-03</v>
       </c>
       <c r="E3" t="str">
         <v/>
@@ -521,7 +521,7 @@
         <v>https://music.apple.com/us/song/bring-your-love/1892545227</v>
       </c>
       <c r="D4" t="str">
-        <v>2026-05-02</v>
+        <v>2026-05-03</v>
       </c>
       <c r="E4" t="str">
         <v/>
@@ -559,7 +559,7 @@
         <v>https://music.apple.com/us/song/horses-and-divorces/1883177267</v>
       </c>
       <c r="D5" t="str">
-        <v>2026-05-02</v>
+        <v>2026-05-03</v>
       </c>
       <c r="E5" t="str">
         <v/>
@@ -597,7 +597,7 @@
         <v>https://music.apple.com/us/song/staying-still/6762758806</v>
       </c>
       <c r="D6" t="str">
-        <v>2026-05-02</v>
+        <v>2026-05-03</v>
       </c>
       <c r="E6" t="str">
         <v/>
@@ -635,7 +635,7 @@
         <v>https://music.apple.com/us/song/fine-place-to-die/6764686279</v>
       </c>
       <c r="D7" t="str">
-        <v>2026-05-02</v>
+        <v>2026-05-03</v>
       </c>
       <c r="E7" t="str">
         <v/>
@@ -673,7 +673,7 @@
         <v>https://music.apple.com/us/song/mutt/6763145178</v>
       </c>
       <c r="D8" t="str">
-        <v>2026-05-02</v>
+        <v>2026-05-03</v>
       </c>
       <c r="E8" t="str">
         <v/>
@@ -711,7 +711,7 @@
         <v>https://music.apple.com/us/song/fire-away-feat-slayyyter/1892422570</v>
       </c>
       <c r="D9" t="str">
-        <v>2026-05-02</v>
+        <v>2026-05-03</v>
       </c>
       <c r="E9" t="str">
         <v/>
@@ -749,7 +749,7 @@
         <v>https://music.apple.com/us/song/lioness/1878649397</v>
       </c>
       <c r="D10" t="str">
-        <v>2026-05-02</v>
+        <v>2026-05-03</v>
       </c>
       <c r="E10" t="str">
         <v/>
@@ -787,7 +787,7 @@
         <v>https://music.apple.com/us/song/its-ok/6763134121</v>
       </c>
       <c r="D11" t="str">
-        <v>2026-05-02</v>
+        <v>2026-05-03</v>
       </c>
       <c r="E11" t="str">
         <v/>
@@ -825,7 +825,7 @@
         <v>https://music.apple.com/us/song/promise/6763162287</v>
       </c>
       <c r="D12" t="str">
-        <v>2026-05-02</v>
+        <v>2026-05-03</v>
       </c>
       <c r="E12" t="str">
         <v/>
@@ -863,7 +863,7 @@
         <v>https://music.apple.com/us/song/cool-buzz/1880470657</v>
       </c>
       <c r="D13" t="str">
-        <v>2026-05-02</v>
+        <v>2026-05-03</v>
       </c>
       <c r="E13" t="str">
         <v/>
@@ -901,7 +901,7 @@
         <v>https://music.apple.com/us/song/material-lover/6764429256</v>
       </c>
       <c r="D14" t="str">
-        <v>2026-05-02</v>
+        <v>2026-05-03</v>
       </c>
       <c r="E14" t="str">
         <v/>
@@ -939,7 +939,7 @@
         <v>https://music.apple.com/us/song/fallin-feat-leon-thomas/6764419265</v>
       </c>
       <c r="D15" t="str">
-        <v>2026-05-02</v>
+        <v>2026-05-03</v>
       </c>
       <c r="E15" t="str">
         <v/>
@@ -977,7 +977,7 @@
         <v>https://music.apple.com/us/song/echo/6763379683</v>
       </c>
       <c r="D16" t="str">
-        <v>2026-05-02</v>
+        <v>2026-05-03</v>
       </c>
       <c r="E16" t="str">
         <v/>
@@ -1015,7 +1015,7 @@
         <v>https://music.apple.com/us/song/blackberry-marmalade/1887627837</v>
       </c>
       <c r="D17" t="str">
-        <v>2026-05-02</v>
+        <v>2026-05-03</v>
       </c>
       <c r="E17" t="str">
         <v/>
@@ -1053,7 +1053,7 @@
         <v>https://music.apple.com/us/song/ricky-bobby/6764406571</v>
       </c>
       <c r="D18" t="str">
-        <v>2026-05-02</v>
+        <v>2026-05-03</v>
       </c>
       <c r="E18" t="str">
         <v/>
@@ -1091,7 +1091,7 @@
         <v>https://music.apple.com/us/song/te-entiendo-remix/6763665638</v>
       </c>
       <c r="D19" t="str">
-        <v>2026-05-02</v>
+        <v>2026-05-03</v>
       </c>
       <c r="E19" t="str">
         <v/>
@@ -1129,7 +1129,7 @@
         <v>https://music.apple.com/us/song/dont-worry-baby/1894294411</v>
       </c>
       <c r="D20" t="str">
-        <v>2026-05-02</v>
+        <v>2026-05-03</v>
       </c>
       <c r="E20" t="str">
         <v/>
@@ -1167,7 +1167,7 @@
         <v>https://music.apple.com/us/song/bitch/6763622110</v>
       </c>
       <c r="D21" t="str">
-        <v>2026-05-02</v>
+        <v>2026-05-03</v>
       </c>
       <c r="E21" t="str">
         <v/>
@@ -1205,7 +1205,7 @@
         <v>https://music.apple.com/us/song/just-wanna-cry/6763414703</v>
       </c>
       <c r="D22" t="str">
-        <v>2026-05-02</v>
+        <v>2026-05-03</v>
       </c>
       <c r="E22" t="str">
         <v/>
@@ -1243,7 +1243,7 @@
         <v>https://music.apple.com/us/song/carry-the-weight/6763611647</v>
       </c>
       <c r="D23" t="str">
-        <v>2026-05-02</v>
+        <v>2026-05-03</v>
       </c>
       <c r="E23" t="str">
         <v/>
@@ -1281,7 +1281,7 @@
         <v>https://music.apple.com/us/song/prostitute/1894092341</v>
       </c>
       <c r="D24" t="str">
-        <v>2026-05-02</v>
+        <v>2026-05-03</v>
       </c>
       <c r="E24" t="str">
         <v/>
@@ -1319,7 +1319,7 @@
         <v>https://music.apple.com/us/song/im-not-joking/1872842623</v>
       </c>
       <c r="D25" t="str">
-        <v>2026-05-02</v>
+        <v>2026-05-03</v>
       </c>
       <c r="E25" t="str">
         <v/>
@@ -1357,7 +1357,7 @@
         <v>https://music.apple.com/us/song/ruca/6763671002</v>
       </c>
       <c r="D26" t="str">
-        <v>2026-05-02</v>
+        <v>2026-05-03</v>
       </c>
       <c r="E26" t="str">
         <v/>
@@ -1395,7 +1395,7 @@
         <v>https://music.apple.com/us/song/make-you-fight/1892332386</v>
       </c>
       <c r="D27" t="str">
-        <v>2026-05-02</v>
+        <v>2026-05-03</v>
       </c>
       <c r="E27" t="str">
         <v/>
@@ -1433,7 +1433,7 @@
         <v>https://music.apple.com/us/song/n0rth4evr/6763302230</v>
       </c>
       <c r="D28" t="str">
-        <v>2026-05-02</v>
+        <v>2026-05-03</v>
       </c>
       <c r="E28" t="str">
         <v/>
@@ -1471,7 +1471,7 @@
         <v>https://music.apple.com/us/song/boy-in-red/1892543110</v>
       </c>
       <c r="D29" t="str">
-        <v>2026-05-02</v>
+        <v>2026-05-03</v>
       </c>
       <c r="E29" t="str">
         <v/>
@@ -1509,7 +1509,7 @@
         <v>https://music.apple.com/us/song/ea-ea-ea/6763438376</v>
       </c>
       <c r="D30" t="str">
-        <v>2026-05-02</v>
+        <v>2026-05-03</v>
       </c>
       <c r="E30" t="str">
         <v/>
@@ -1547,7 +1547,7 @@
         <v>https://music.apple.com/us/song/just-a-man/6762944365</v>
       </c>
       <c r="D31" t="str">
-        <v>2026-05-02</v>
+        <v>2026-05-03</v>
       </c>
       <c r="E31" t="str">
         <v/>
@@ -1585,7 +1585,7 @@
         <v>https://music.apple.com/us/song/the-observer/1891982314</v>
       </c>
       <c r="D32" t="str">
-        <v>2026-05-02</v>
+        <v>2026-05-03</v>
       </c>
       <c r="E32" t="str">
         <v/>
@@ -1623,7 +1623,7 @@
         <v>https://music.apple.com/us/song/heroine/6762693177</v>
       </c>
       <c r="D33" t="str">
-        <v>2026-05-02</v>
+        <v>2026-05-03</v>
       </c>
       <c r="E33" t="str">
         <v/>
@@ -1661,7 +1661,7 @@
         <v>https://music.apple.com/us/song/do-me-right/6764667658</v>
       </c>
       <c r="D34" t="str">
-        <v>2026-05-02</v>
+        <v>2026-05-03</v>
       </c>
       <c r="E34" t="str">
         <v/>
@@ -1699,7 +1699,7 @@
         <v>https://music.apple.com/us/song/its-me/1887194026</v>
       </c>
       <c r="D35" t="str">
-        <v>2026-05-02</v>
+        <v>2026-05-03</v>
       </c>
       <c r="E35" t="str">
         <v/>
@@ -1737,7 +1737,7 @@
         <v>https://music.apple.com/us/song/the-precipice/1891830326</v>
       </c>
       <c r="D36" t="str">
-        <v>2026-05-02</v>
+        <v>2026-05-03</v>
       </c>
       <c r="E36" t="str">
         <v/>
@@ -1775,7 +1775,7 @@
         <v>https://music.apple.com/us/song/hello-lonesome/1892466003</v>
       </c>
       <c r="D37" t="str">
-        <v>2026-05-02</v>
+        <v>2026-05-03</v>
       </c>
       <c r="E37" t="str">
         <v/>
@@ -1813,7 +1813,7 @@
         <v>https://music.apple.com/us/song/trippin-opera-edit/6764648776</v>
       </c>
       <c r="D38" t="str">
-        <v>2026-05-02</v>
+        <v>2026-05-03</v>
       </c>
       <c r="E38" t="str">
         <v/>
@@ -1851,7 +1851,7 @@
         <v>https://music.apple.com/us/song/the-mandalorian-and-grogu-boys-noize-remix-from-star/6764131630</v>
       </c>
       <c r="D39" t="str">
-        <v>2026-05-02</v>
+        <v>2026-05-03</v>
       </c>
       <c r="E39" t="str">
         <v/>
@@ -1889,7 +1889,7 @@
         <v>https://music.apple.com/us/song/blow-my-mind-ca7riel-paco-amoroso-version/1894344140</v>
       </c>
       <c r="D40" t="str">
-        <v>2026-05-02</v>
+        <v>2026-05-03</v>
       </c>
       <c r="E40" t="str">
         <v/>
@@ -1927,7 +1927,7 @@
         <v>https://music.apple.com/us/song/bring-that-body/6764009310</v>
       </c>
       <c r="D41" t="str">
-        <v>2026-05-02</v>
+        <v>2026-05-03</v>
       </c>
       <c r="E41" t="str">
         <v/>
@@ -1965,7 +1965,7 @@
         <v>https://music.apple.com/us/song/star/1891845608</v>
       </c>
       <c r="D42" t="str">
-        <v>2026-05-02</v>
+        <v>2026-05-03</v>
       </c>
       <c r="E42" t="str">
         <v/>
@@ -2003,7 +2003,7 @@
         <v>https://music.apple.com/us/song/whats-a-little-rain/1885061171</v>
       </c>
       <c r="D43" t="str">
-        <v>2026-05-02</v>
+        <v>2026-05-03</v>
       </c>
       <c r="E43" t="str">
         <v/>
@@ -2041,7 +2041,7 @@
         <v>https://music.apple.com/us/song/evergreen/1866700315</v>
       </c>
       <c r="D44" t="str">
-        <v>2026-05-02</v>
+        <v>2026-05-03</v>
       </c>
       <c r="E44" t="str">
         <v/>
@@ -2079,7 +2079,7 @@
         <v>https://music.apple.com/us/song/she-does-it-right/1873477957</v>
       </c>
       <c r="D45" t="str">
-        <v>2026-05-02</v>
+        <v>2026-05-03</v>
       </c>
       <c r="E45" t="str">
         <v/>
@@ -2117,7 +2117,7 @@
         <v>https://music.apple.com/us/song/punching-the-flowers/1878362636</v>
       </c>
       <c r="D46" t="str">
-        <v>2026-05-02</v>
+        <v>2026-05-03</v>
       </c>
       <c r="E46" t="str">
         <v/>
@@ -2155,7 +2155,7 @@
         <v>https://music.apple.com/us/song/how-did-you-know/1888553137</v>
       </c>
       <c r="D47" t="str">
-        <v>2026-05-02</v>
+        <v>2026-05-03</v>
       </c>
       <c r="E47" t="str">
         <v/>
@@ -2193,7 +2193,7 @@
         <v>https://music.apple.com/us/song/summer-breeze/6763360727</v>
       </c>
       <c r="D48" t="str">
-        <v>2026-05-02</v>
+        <v>2026-05-03</v>
       </c>
       <c r="E48" t="str">
         <v/>
@@ -2231,7 +2231,7 @@
         <v>https://music.apple.com/us/song/sound-of-a-woman/1859763367</v>
       </c>
       <c r="D49" t="str">
-        <v>2026-05-02</v>
+        <v>2026-05-03</v>
       </c>
       <c r="E49" t="str">
         <v/>
@@ -2269,7 +2269,7 @@
         <v>https://music.apple.com/us/song/my-life/1893157347</v>
       </c>
       <c r="D50" t="str">
-        <v>2026-05-02</v>
+        <v>2026-05-03</v>
       </c>
       <c r="E50" t="str">
         <v/>
@@ -2307,7 +2307,7 @@
         <v>https://music.apple.com/us/song/ribcage/1893155593</v>
       </c>
       <c r="D51" t="str">
-        <v>2026-05-02</v>
+        <v>2026-05-03</v>
       </c>
       <c r="E51" t="str">
         <v/>
@@ -2345,7 +2345,7 @@
         <v>https://music.apple.com/us/song/i-loved-you-then/1878232821</v>
       </c>
       <c r="D52" t="str">
-        <v>2026-05-02</v>
+        <v>2026-05-03</v>
       </c>
       <c r="E52" t="str">
         <v/>
@@ -2383,7 +2383,7 @@
         <v>https://music.apple.com/us/song/ill-let-you-finish/1891844342</v>
       </c>
       <c r="D53" t="str">
-        <v>2026-05-02</v>
+        <v>2026-05-03</v>
       </c>
       <c r="E53" t="str">
         <v/>
@@ -2421,7 +2421,7 @@
         <v>https://music.apple.com/us/song/it-gets-me-through/1884798927</v>
       </c>
       <c r="D54" t="str">
-        <v>2026-05-02</v>
+        <v>2026-05-03</v>
       </c>
       <c r="E54" t="str">
         <v/>
@@ -2459,7 +2459,7 @@
         <v>https://music.apple.com/us/song/the-author/6763327641</v>
       </c>
       <c r="D55" t="str">
-        <v>2026-05-02</v>
+        <v>2026-05-03</v>
       </c>
       <c r="E55" t="str">
         <v/>
@@ -2497,7 +2497,7 @@
         <v>https://music.apple.com/us/song/want-me-back-feat-tors/1889370756</v>
       </c>
       <c r="D56" t="str">
-        <v>2026-05-02</v>
+        <v>2026-05-03</v>
       </c>
       <c r="E56" t="str">
         <v/>
@@ -2535,7 +2535,7 @@
         <v>https://music.apple.com/us/song/ruin/1886537117</v>
       </c>
       <c r="D57" t="str">
-        <v>2026-05-02</v>
+        <v>2026-05-03</v>
       </c>
       <c r="E57" t="str">
         <v/>
@@ -2573,7 +2573,7 @@
         <v>https://music.apple.com/us/song/i-know-i-know/1894354139</v>
       </c>
       <c r="D58" t="str">
-        <v>2026-05-02</v>
+        <v>2026-05-03</v>
       </c>
       <c r="E58" t="str">
         <v/>
@@ -2611,7 +2611,7 @@
         <v>https://music.apple.com/us/song/drive-all-night/6763189759</v>
       </c>
       <c r="D59" t="str">
-        <v>2026-05-02</v>
+        <v>2026-05-03</v>
       </c>
       <c r="E59" t="str">
         <v/>
@@ -2649,7 +2649,7 @@
         <v>https://music.apple.com/us/song/aint-u-tired/6763115235</v>
       </c>
       <c r="D60" t="str">
-        <v>2026-05-02</v>
+        <v>2026-05-03</v>
       </c>
       <c r="E60" t="str">
         <v/>
@@ -2687,7 +2687,7 @@
         <v>https://music.apple.com/us/song/boys-in-blue/1892436920</v>
       </c>
       <c r="D61" t="str">
-        <v>2026-05-02</v>
+        <v>2026-05-03</v>
       </c>
       <c r="E61" t="str">
         <v/>
@@ -2725,7 +2725,7 @@
         <v>https://music.apple.com/us/song/salma-hayek/1891815286</v>
       </c>
       <c r="D62" t="str">
-        <v>2026-05-02</v>
+        <v>2026-05-03</v>
       </c>
       <c r="E62" t="str">
         <v/>
@@ -2763,7 +2763,7 @@
         <v>https://music.apple.com/us/song/stubborn-mouth/1893194800</v>
       </c>
       <c r="D63" t="str">
-        <v>2026-05-02</v>
+        <v>2026-05-03</v>
       </c>
       <c r="E63" t="str">
         <v/>
@@ -2801,7 +2801,7 @@
         <v>https://music.apple.com/us/song/hallucination/6764110976</v>
       </c>
       <c r="D64" t="str">
-        <v>2026-05-02</v>
+        <v>2026-05-03</v>
       </c>
       <c r="E64" t="str">
         <v/>
@@ -2839,7 +2839,7 @@
         <v>https://music.apple.com/us/song/in-da-jungle/1891136400</v>
       </c>
       <c r="D65" t="str">
-        <v>2026-05-02</v>
+        <v>2026-05-03</v>
       </c>
       <c r="E65" t="str">
         <v/>
@@ -2877,7 +2877,7 @@
         <v>https://music.apple.com/us/song/fall-short/1894662749</v>
       </c>
       <c r="D66" t="str">
-        <v>2026-05-02</v>
+        <v>2026-05-03</v>
       </c>
       <c r="E66" t="str">
         <v/>
@@ -2915,7 +2915,7 @@
         <v>https://music.apple.com/us/song/irish-goodbye-feat-kae-tempest/1862224205</v>
       </c>
       <c r="D67" t="str">
-        <v>2026-05-02</v>
+        <v>2026-05-03</v>
       </c>
       <c r="E67" t="str">
         <v/>
@@ -2953,7 +2953,7 @@
         <v>https://music.apple.com/us/song/1989/1893089382</v>
       </c>
       <c r="D68" t="str">
-        <v>2026-05-02</v>
+        <v>2026-05-03</v>
       </c>
       <c r="E68" t="str">
         <v/>
@@ -2991,7 +2991,7 @@
         <v>https://music.apple.com/us/song/no-more-regrets/1893191803</v>
       </c>
       <c r="D69" t="str">
-        <v>2026-05-02</v>
+        <v>2026-05-03</v>
       </c>
       <c r="E69" t="str">
         <v/>
@@ -3029,7 +3029,7 @@
         <v>https://music.apple.com/us/song/drum-machine/1840517102</v>
       </c>
       <c r="D70" t="str">
-        <v>2026-05-02</v>
+        <v>2026-05-03</v>
       </c>
       <c r="E70" t="str">
         <v/>
@@ -3067,7 +3067,7 @@
         <v>https://music.apple.com/us/song/im-perfect/1893181359</v>
       </c>
       <c r="D71" t="str">
-        <v>2026-05-02</v>
+        <v>2026-05-03</v>
       </c>
       <c r="E71" t="str">
         <v/>
@@ -3105,7 +3105,7 @@
         <v>https://music.apple.com/us/song/theme-for-a-train-journey/1880699785</v>
       </c>
       <c r="D72" t="str">
-        <v>2026-05-02</v>
+        <v>2026-05-03</v>
       </c>
       <c r="E72" t="str">
         <v/>
@@ -3143,7 +3143,7 @@
         <v>https://music.apple.com/us/song/bitch-you-weird/6763395875</v>
       </c>
       <c r="D73" t="str">
-        <v>2026-05-02</v>
+        <v>2026-05-03</v>
       </c>
       <c r="E73" t="str">
         <v/>
@@ -3181,7 +3181,7 @@
         <v>https://music.apple.com/us/song/blackbird-rising/1887166611</v>
       </c>
       <c r="D74" t="str">
-        <v>2026-05-02</v>
+        <v>2026-05-03</v>
       </c>
       <c r="E74" t="str">
         <v/>
@@ -3219,7 +3219,7 @@
         <v>https://music.apple.com/us/song/usher-in-the-spirit/6763373678</v>
       </c>
       <c r="D75" t="str">
-        <v>2026-05-02</v>
+        <v>2026-05-03</v>
       </c>
       <c r="E75" t="str">
         <v/>
@@ -3257,7 +3257,7 @@
         <v>https://music.apple.com/us/song/moonlight/1892950791</v>
       </c>
       <c r="D76" t="str">
-        <v>2026-05-02</v>
+        <v>2026-05-03</v>
       </c>
       <c r="E76" t="str">
         <v/>
@@ -3295,7 +3295,7 @@
         <v>https://music.apple.com/us/song/hands-on-me/1893960365</v>
       </c>
       <c r="D77" t="str">
-        <v>2026-05-02</v>
+        <v>2026-05-03</v>
       </c>
       <c r="E77" t="str">
         <v/>
@@ -3333,7 +3333,7 @@
         <v>https://music.apple.com/us/song/closure/1892418294</v>
       </c>
       <c r="D78" t="str">
-        <v>2026-05-02</v>
+        <v>2026-05-03</v>
       </c>
       <c r="E78" t="str">
         <v/>
@@ -3371,7 +3371,7 @@
         <v>https://music.apple.com/us/song/hots-4-u/1891478541</v>
       </c>
       <c r="D79" t="str">
-        <v>2026-05-02</v>
+        <v>2026-05-03</v>
       </c>
       <c r="E79" t="str">
         <v/>
@@ -3409,7 +3409,7 @@
         <v>https://music.apple.com/us/song/cule-poco-sirena-besarico-coste%C3%B1a/1893480200</v>
       </c>
       <c r="D80" t="str">
-        <v>2026-05-02</v>
+        <v>2026-05-03</v>
       </c>
       <c r="E80" t="str">
         <v/>
@@ -3447,7 +3447,7 @@
         <v>https://music.apple.com/us/song/the-coin-toss/1894872115</v>
       </c>
       <c r="D81" t="str">
-        <v>2026-05-02</v>
+        <v>2026-05-03</v>
       </c>
       <c r="E81" t="str">
         <v/>
@@ -3485,7 +3485,7 @@
         <v>https://music.apple.com/us/song/bottles-lights/6763041153</v>
       </c>
       <c r="D82" t="str">
-        <v>2026-05-02</v>
+        <v>2026-05-03</v>
       </c>
       <c r="E82" t="str">
         <v/>
@@ -3523,7 +3523,7 @@
         <v>https://music.apple.com/us/song/perfect-for-me/6762879981</v>
       </c>
       <c r="D83" t="str">
-        <v>2026-05-02</v>
+        <v>2026-05-03</v>
       </c>
       <c r="E83" t="str">
         <v/>
@@ -3561,7 +3561,7 @@
         <v>https://music.apple.com/us/song/so/1893162424</v>
       </c>
       <c r="D84" t="str">
-        <v>2026-05-02</v>
+        <v>2026-05-03</v>
       </c>
       <c r="E84" t="str">
         <v/>
@@ -3599,7 +3599,7 @@
         <v>https://music.apple.com/us/song/pase-y-pase/1894076490</v>
       </c>
       <c r="D85" t="str">
-        <v>2026-05-02</v>
+        <v>2026-05-03</v>
       </c>
       <c r="E85" t="str">
         <v/>
@@ -3637,7 +3637,7 @@
         <v>https://music.apple.com/us/song/agou%C3%A9-dambala-yanvalou-1/1888242486</v>
       </c>
       <c r="D86" t="str">
-        <v>2026-05-02</v>
+        <v>2026-05-03</v>
       </c>
       <c r="E86" t="str">
         <v/>
@@ -3675,7 +3675,7 @@
         <v>https://music.apple.com/us/song/aljahalat/1889267983</v>
       </c>
       <c r="D87" t="str">
-        <v>2026-05-02</v>
+        <v>2026-05-03</v>
       </c>
       <c r="E87" t="str">
         <v/>
@@ -3713,7 +3713,7 @@
         <v>https://music.apple.com/us/song/puleza/1893765840</v>
       </c>
       <c r="D88" t="str">
-        <v>2026-05-02</v>
+        <v>2026-05-03</v>
       </c>
       <c r="E88" t="str">
         <v/>
@@ -3751,7 +3751,7 @@
         <v>https://music.apple.com/us/song/bastards/6762403102</v>
       </c>
       <c r="D89" t="str">
-        <v>2026-05-02</v>
+        <v>2026-05-03</v>
       </c>
       <c r="E89" t="str">
         <v/>
@@ -3789,7 +3789,7 @@
         <v>https://music.apple.com/us/song/crutch/6763345020</v>
       </c>
       <c r="D90" t="str">
-        <v>2026-05-02</v>
+        <v>2026-05-03</v>
       </c>
       <c r="E90" t="str">
         <v/>
@@ -3827,7 +3827,7 @@
         <v>https://music.apple.com/us/song/just-a-man/1893736206</v>
       </c>
       <c r="D91" t="str">
-        <v>2026-05-02</v>
+        <v>2026-05-03</v>
       </c>
       <c r="E91" t="str">
         <v/>
@@ -3865,7 +3865,7 @@
         <v>https://music.apple.com/us/song/take-care-of-you/6762283983</v>
       </c>
       <c r="D92" t="str">
-        <v>2026-05-02</v>
+        <v>2026-05-03</v>
       </c>
       <c r="E92" t="str">
         <v/>
@@ -3903,7 +3903,7 @@
         <v>https://music.apple.com/us/song/love-you-more/1889686330</v>
       </c>
       <c r="D93" t="str">
-        <v>2026-05-02</v>
+        <v>2026-05-03</v>
       </c>
       <c r="E93" t="str">
         <v/>
@@ -3941,7 +3941,7 @@
         <v>https://music.apple.com/us/song/construct/1869323374</v>
       </c>
       <c r="D94" t="str">
-        <v>2026-05-02</v>
+        <v>2026-05-03</v>
       </c>
       <c r="E94" t="str">
         <v/>
@@ -3979,7 +3979,7 @@
         <v>https://music.apple.com/us/song/as-above-so-below/1872651422</v>
       </c>
       <c r="D95" t="str">
-        <v>2026-05-02</v>
+        <v>2026-05-03</v>
       </c>
       <c r="E95" t="str">
         <v/>
@@ -4017,7 +4017,7 @@
         <v>https://music.apple.com/us/song/revenant/6763148056</v>
       </c>
       <c r="D96" t="str">
-        <v>2026-05-02</v>
+        <v>2026-05-03</v>
       </c>
       <c r="E96" t="str">
         <v/>
@@ -4055,7 +4055,7 @@
         <v>https://music.apple.com/us/song/black-box-feat-joe-duplantier-the-mystery-of/6762312582</v>
       </c>
       <c r="D97" t="str">
-        <v>2026-05-02</v>
+        <v>2026-05-03</v>
       </c>
       <c r="E97" t="str">
         <v/>
@@ -4093,7 +4093,7 @@
         <v>https://music.apple.com/us/song/power-4/6763647813</v>
       </c>
       <c r="D98" t="str">
-        <v>2026-05-02</v>
+        <v>2026-05-03</v>
       </c>
       <c r="E98" t="str">
         <v/>
@@ -4131,7 +4131,7 @@
         <v>https://music.apple.com/us/song/too-easy/1893814702</v>
       </c>
       <c r="D99" t="str">
-        <v>2026-05-02</v>
+        <v>2026-05-03</v>
       </c>
       <c r="E99" t="str">
         <v/>
@@ -4169,7 +4169,7 @@
         <v>https://music.apple.com/us/song/if-you-want-it/1892503347</v>
       </c>
       <c r="D100" t="str">
-        <v>2026-05-02</v>
+        <v>2026-05-03</v>
       </c>
       <c r="E100" t="str">
         <v/>
@@ -4207,7 +4207,7 @@
         <v>https://music.apple.com/us/song/shoplifting/1852812659</v>
       </c>
       <c r="D101" t="str">
-        <v>2026-05-02</v>
+        <v>2026-05-03</v>
       </c>
       <c r="E101" t="str">
         <v/>
@@ -4245,7 +4245,7 @@
         <v>https://music.apple.com/us/song/endlessly-feat-bea1991/1876022833</v>
       </c>
       <c r="D102" t="str">
-        <v>2026-05-02</v>
+        <v>2026-05-03</v>
       </c>
       <c r="E102" t="str">
         <v/>

--- a/data/tags/מוזיקה לועזית חדשה/sites/apple-music-playlist/2026-05-week01/titles.xlsx
+++ b/data/tags/מוזיקה לועזית חדשה/sites/apple-music-playlist/2026-05-week01/titles.xlsx
@@ -445,7 +445,7 @@
         <v>https://music.apple.com/us/song/eurosummer-girls-trip/1894058279</v>
       </c>
       <c r="D2" t="str">
-        <v>2026-05-03</v>
+        <v>2026-05-04</v>
       </c>
       <c r="E2" t="str">
         <v/>
@@ -483,7 +483,7 @@
         <v>https://music.apple.com/us/song/shape-of-a-woman/6764429252</v>
       </c>
       <c r="D3" t="str">
-        <v>2026-05-03</v>
+        <v>2026-05-04</v>
       </c>
       <c r="E3" t="str">
         <v/>
@@ -521,7 +521,7 @@
         <v>https://music.apple.com/us/song/bring-your-love/1892545227</v>
       </c>
       <c r="D4" t="str">
-        <v>2026-05-03</v>
+        <v>2026-05-04</v>
       </c>
       <c r="E4" t="str">
         <v/>
@@ -559,7 +559,7 @@
         <v>https://music.apple.com/us/song/horses-and-divorces/1883177267</v>
       </c>
       <c r="D5" t="str">
-        <v>2026-05-03</v>
+        <v>2026-05-04</v>
       </c>
       <c r="E5" t="str">
         <v/>
@@ -597,7 +597,7 @@
         <v>https://music.apple.com/us/song/staying-still/6762758806</v>
       </c>
       <c r="D6" t="str">
-        <v>2026-05-03</v>
+        <v>2026-05-04</v>
       </c>
       <c r="E6" t="str">
         <v/>
@@ -635,7 +635,7 @@
         <v>https://music.apple.com/us/song/fine-place-to-die/6764686279</v>
       </c>
       <c r="D7" t="str">
-        <v>2026-05-03</v>
+        <v>2026-05-04</v>
       </c>
       <c r="E7" t="str">
         <v/>
@@ -673,7 +673,7 @@
         <v>https://music.apple.com/us/song/mutt/6763145178</v>
       </c>
       <c r="D8" t="str">
-        <v>2026-05-03</v>
+        <v>2026-05-04</v>
       </c>
       <c r="E8" t="str">
         <v/>
@@ -711,7 +711,7 @@
         <v>https://music.apple.com/us/song/fire-away-feat-slayyyter/1892422570</v>
       </c>
       <c r="D9" t="str">
-        <v>2026-05-03</v>
+        <v>2026-05-04</v>
       </c>
       <c r="E9" t="str">
         <v/>
@@ -749,7 +749,7 @@
         <v>https://music.apple.com/us/song/lioness/1878649397</v>
       </c>
       <c r="D10" t="str">
-        <v>2026-05-03</v>
+        <v>2026-05-04</v>
       </c>
       <c r="E10" t="str">
         <v/>
@@ -787,7 +787,7 @@
         <v>https://music.apple.com/us/song/its-ok/6763134121</v>
       </c>
       <c r="D11" t="str">
-        <v>2026-05-03</v>
+        <v>2026-05-04</v>
       </c>
       <c r="E11" t="str">
         <v/>
@@ -825,7 +825,7 @@
         <v>https://music.apple.com/us/song/promise/6763162287</v>
       </c>
       <c r="D12" t="str">
-        <v>2026-05-03</v>
+        <v>2026-05-04</v>
       </c>
       <c r="E12" t="str">
         <v/>
@@ -863,7 +863,7 @@
         <v>https://music.apple.com/us/song/cool-buzz/1880470657</v>
       </c>
       <c r="D13" t="str">
-        <v>2026-05-03</v>
+        <v>2026-05-04</v>
       </c>
       <c r="E13" t="str">
         <v/>
@@ -901,7 +901,7 @@
         <v>https://music.apple.com/us/song/material-lover/6764429256</v>
       </c>
       <c r="D14" t="str">
-        <v>2026-05-03</v>
+        <v>2026-05-04</v>
       </c>
       <c r="E14" t="str">
         <v/>
@@ -939,7 +939,7 @@
         <v>https://music.apple.com/us/song/fallin-feat-leon-thomas/6764419265</v>
       </c>
       <c r="D15" t="str">
-        <v>2026-05-03</v>
+        <v>2026-05-04</v>
       </c>
       <c r="E15" t="str">
         <v/>
@@ -977,7 +977,7 @@
         <v>https://music.apple.com/us/song/echo/6763379683</v>
       </c>
       <c r="D16" t="str">
-        <v>2026-05-03</v>
+        <v>2026-05-04</v>
       </c>
       <c r="E16" t="str">
         <v/>
@@ -1015,7 +1015,7 @@
         <v>https://music.apple.com/us/song/blackberry-marmalade/1887627837</v>
       </c>
       <c r="D17" t="str">
-        <v>2026-05-03</v>
+        <v>2026-05-04</v>
       </c>
       <c r="E17" t="str">
         <v/>
@@ -1053,7 +1053,7 @@
         <v>https://music.apple.com/us/song/ricky-bobby/6764406571</v>
       </c>
       <c r="D18" t="str">
-        <v>2026-05-03</v>
+        <v>2026-05-04</v>
       </c>
       <c r="E18" t="str">
         <v/>
@@ -1091,7 +1091,7 @@
         <v>https://music.apple.com/us/song/te-entiendo-remix/6763665638</v>
       </c>
       <c r="D19" t="str">
-        <v>2026-05-03</v>
+        <v>2026-05-04</v>
       </c>
       <c r="E19" t="str">
         <v/>
@@ -1129,7 +1129,7 @@
         <v>https://music.apple.com/us/song/dont-worry-baby/1894294411</v>
       </c>
       <c r="D20" t="str">
-        <v>2026-05-03</v>
+        <v>2026-05-04</v>
       </c>
       <c r="E20" t="str">
         <v/>
@@ -1167,7 +1167,7 @@
         <v>https://music.apple.com/us/song/bitch/6763622110</v>
       </c>
       <c r="D21" t="str">
-        <v>2026-05-03</v>
+        <v>2026-05-04</v>
       </c>
       <c r="E21" t="str">
         <v/>
@@ -1205,7 +1205,7 @@
         <v>https://music.apple.com/us/song/just-wanna-cry/6763414703</v>
       </c>
       <c r="D22" t="str">
-        <v>2026-05-03</v>
+        <v>2026-05-04</v>
       </c>
       <c r="E22" t="str">
         <v/>
@@ -1243,7 +1243,7 @@
         <v>https://music.apple.com/us/song/carry-the-weight/6763611647</v>
       </c>
       <c r="D23" t="str">
-        <v>2026-05-03</v>
+        <v>2026-05-04</v>
       </c>
       <c r="E23" t="str">
         <v/>
@@ -1281,7 +1281,7 @@
         <v>https://music.apple.com/us/song/prostitute/1894092341</v>
       </c>
       <c r="D24" t="str">
-        <v>2026-05-03</v>
+        <v>2026-05-04</v>
       </c>
       <c r="E24" t="str">
         <v/>
@@ -1319,7 +1319,7 @@
         <v>https://music.apple.com/us/song/im-not-joking/1872842623</v>
       </c>
       <c r="D25" t="str">
-        <v>2026-05-03</v>
+        <v>2026-05-04</v>
       </c>
       <c r="E25" t="str">
         <v/>
@@ -1357,7 +1357,7 @@
         <v>https://music.apple.com/us/song/ruca/6763671002</v>
       </c>
       <c r="D26" t="str">
-        <v>2026-05-03</v>
+        <v>2026-05-04</v>
       </c>
       <c r="E26" t="str">
         <v/>
@@ -1395,7 +1395,7 @@
         <v>https://music.apple.com/us/song/make-you-fight/1892332386</v>
       </c>
       <c r="D27" t="str">
-        <v>2026-05-03</v>
+        <v>2026-05-04</v>
       </c>
       <c r="E27" t="str">
         <v/>
@@ -1433,7 +1433,7 @@
         <v>https://music.apple.com/us/song/n0rth4evr/6763302230</v>
       </c>
       <c r="D28" t="str">
-        <v>2026-05-03</v>
+        <v>2026-05-04</v>
       </c>
       <c r="E28" t="str">
         <v/>
@@ -1471,7 +1471,7 @@
         <v>https://music.apple.com/us/song/boy-in-red/1892543110</v>
       </c>
       <c r="D29" t="str">
-        <v>2026-05-03</v>
+        <v>2026-05-04</v>
       </c>
       <c r="E29" t="str">
         <v/>
@@ -1509,7 +1509,7 @@
         <v>https://music.apple.com/us/song/ea-ea-ea/6763438376</v>
       </c>
       <c r="D30" t="str">
-        <v>2026-05-03</v>
+        <v>2026-05-04</v>
       </c>
       <c r="E30" t="str">
         <v/>
@@ -1547,7 +1547,7 @@
         <v>https://music.apple.com/us/song/just-a-man/6762944365</v>
       </c>
       <c r="D31" t="str">
-        <v>2026-05-03</v>
+        <v>2026-05-04</v>
       </c>
       <c r="E31" t="str">
         <v/>
@@ -1585,7 +1585,7 @@
         <v>https://music.apple.com/us/song/the-observer/1891982314</v>
       </c>
       <c r="D32" t="str">
-        <v>2026-05-03</v>
+        <v>2026-05-04</v>
       </c>
       <c r="E32" t="str">
         <v/>
@@ -1623,7 +1623,7 @@
         <v>https://music.apple.com/us/song/heroine/6762693177</v>
       </c>
       <c r="D33" t="str">
-        <v>2026-05-03</v>
+        <v>2026-05-04</v>
       </c>
       <c r="E33" t="str">
         <v/>
@@ -1661,7 +1661,7 @@
         <v>https://music.apple.com/us/song/do-me-right/6764667658</v>
       </c>
       <c r="D34" t="str">
-        <v>2026-05-03</v>
+        <v>2026-05-04</v>
       </c>
       <c r="E34" t="str">
         <v/>
@@ -1699,7 +1699,7 @@
         <v>https://music.apple.com/us/song/its-me/1887194026</v>
       </c>
       <c r="D35" t="str">
-        <v>2026-05-03</v>
+        <v>2026-05-04</v>
       </c>
       <c r="E35" t="str">
         <v/>
@@ -1737,7 +1737,7 @@
         <v>https://music.apple.com/us/song/the-precipice/1891830326</v>
       </c>
       <c r="D36" t="str">
-        <v>2026-05-03</v>
+        <v>2026-05-04</v>
       </c>
       <c r="E36" t="str">
         <v/>
@@ -1775,7 +1775,7 @@
         <v>https://music.apple.com/us/song/hello-lonesome/1892466003</v>
       </c>
       <c r="D37" t="str">
-        <v>2026-05-03</v>
+        <v>2026-05-04</v>
       </c>
       <c r="E37" t="str">
         <v/>
@@ -1813,7 +1813,7 @@
         <v>https://music.apple.com/us/song/trippin-opera-edit/6764648776</v>
       </c>
       <c r="D38" t="str">
-        <v>2026-05-03</v>
+        <v>2026-05-04</v>
       </c>
       <c r="E38" t="str">
         <v/>
@@ -1851,7 +1851,7 @@
         <v>https://music.apple.com/us/song/the-mandalorian-and-grogu-boys-noize-remix-from-star/6764131630</v>
       </c>
       <c r="D39" t="str">
-        <v>2026-05-03</v>
+        <v>2026-05-04</v>
       </c>
       <c r="E39" t="str">
         <v/>
@@ -1889,7 +1889,7 @@
         <v>https://music.apple.com/us/song/blow-my-mind-ca7riel-paco-amoroso-version/1894344140</v>
       </c>
       <c r="D40" t="str">
-        <v>2026-05-03</v>
+        <v>2026-05-04</v>
       </c>
       <c r="E40" t="str">
         <v/>
@@ -1927,7 +1927,7 @@
         <v>https://music.apple.com/us/song/bring-that-body/6764009310</v>
       </c>
       <c r="D41" t="str">
-        <v>2026-05-03</v>
+        <v>2026-05-04</v>
       </c>
       <c r="E41" t="str">
         <v/>
@@ -1965,7 +1965,7 @@
         <v>https://music.apple.com/us/song/star/1891845608</v>
       </c>
       <c r="D42" t="str">
-        <v>2026-05-03</v>
+        <v>2026-05-04</v>
       </c>
       <c r="E42" t="str">
         <v/>
@@ -2003,7 +2003,7 @@
         <v>https://music.apple.com/us/song/whats-a-little-rain/1885061171</v>
       </c>
       <c r="D43" t="str">
-        <v>2026-05-03</v>
+        <v>2026-05-04</v>
       </c>
       <c r="E43" t="str">
         <v/>
@@ -2041,7 +2041,7 @@
         <v>https://music.apple.com/us/song/evergreen/1866700315</v>
       </c>
       <c r="D44" t="str">
-        <v>2026-05-03</v>
+        <v>2026-05-04</v>
       </c>
       <c r="E44" t="str">
         <v/>
@@ -2079,7 +2079,7 @@
         <v>https://music.apple.com/us/song/she-does-it-right/1873477957</v>
       </c>
       <c r="D45" t="str">
-        <v>2026-05-03</v>
+        <v>2026-05-04</v>
       </c>
       <c r="E45" t="str">
         <v/>
@@ -2117,7 +2117,7 @@
         <v>https://music.apple.com/us/song/punching-the-flowers/1878362636</v>
       </c>
       <c r="D46" t="str">
-        <v>2026-05-03</v>
+        <v>2026-05-04</v>
       </c>
       <c r="E46" t="str">
         <v/>
@@ -2155,7 +2155,7 @@
         <v>https://music.apple.com/us/song/how-did-you-know/1888553137</v>
       </c>
       <c r="D47" t="str">
-        <v>2026-05-03</v>
+        <v>2026-05-04</v>
       </c>
       <c r="E47" t="str">
         <v/>
@@ -2193,7 +2193,7 @@
         <v>https://music.apple.com/us/song/summer-breeze/6763360727</v>
       </c>
       <c r="D48" t="str">
-        <v>2026-05-03</v>
+        <v>2026-05-04</v>
       </c>
       <c r="E48" t="str">
         <v/>
@@ -2231,7 +2231,7 @@
         <v>https://music.apple.com/us/song/sound-of-a-woman/1859763367</v>
       </c>
       <c r="D49" t="str">
-        <v>2026-05-03</v>
+        <v>2026-05-04</v>
       </c>
       <c r="E49" t="str">
         <v/>
@@ -2269,7 +2269,7 @@
         <v>https://music.apple.com/us/song/my-life/1893157347</v>
       </c>
       <c r="D50" t="str">
-        <v>2026-05-03</v>
+        <v>2026-05-04</v>
       </c>
       <c r="E50" t="str">
         <v/>
@@ -2307,7 +2307,7 @@
         <v>https://music.apple.com/us/song/ribcage/1893155593</v>
       </c>
       <c r="D51" t="str">
-        <v>2026-05-03</v>
+        <v>2026-05-04</v>
       </c>
       <c r="E51" t="str">
         <v/>
@@ -2345,7 +2345,7 @@
         <v>https://music.apple.com/us/song/i-loved-you-then/1878232821</v>
       </c>
       <c r="D52" t="str">
-        <v>2026-05-03</v>
+        <v>2026-05-04</v>
       </c>
       <c r="E52" t="str">
         <v/>
@@ -2383,7 +2383,7 @@
         <v>https://music.apple.com/us/song/ill-let-you-finish/1891844342</v>
       </c>
       <c r="D53" t="str">
-        <v>2026-05-03</v>
+        <v>2026-05-04</v>
       </c>
       <c r="E53" t="str">
         <v/>
@@ -2421,7 +2421,7 @@
         <v>https://music.apple.com/us/song/it-gets-me-through/1884798927</v>
       </c>
       <c r="D54" t="str">
-        <v>2026-05-03</v>
+        <v>2026-05-04</v>
       </c>
       <c r="E54" t="str">
         <v/>
@@ -2459,7 +2459,7 @@
         <v>https://music.apple.com/us/song/the-author/6763327641</v>
       </c>
       <c r="D55" t="str">
-        <v>2026-05-03</v>
+        <v>2026-05-04</v>
       </c>
       <c r="E55" t="str">
         <v/>
@@ -2497,7 +2497,7 @@
         <v>https://music.apple.com/us/song/want-me-back-feat-tors/1889370756</v>
       </c>
       <c r="D56" t="str">
-        <v>2026-05-03</v>
+        <v>2026-05-04</v>
       </c>
       <c r="E56" t="str">
         <v/>
@@ -2535,7 +2535,7 @@
         <v>https://music.apple.com/us/song/ruin/1886537117</v>
       </c>
       <c r="D57" t="str">
-        <v>2026-05-03</v>
+        <v>2026-05-04</v>
       </c>
       <c r="E57" t="str">
         <v/>
@@ -2573,7 +2573,7 @@
         <v>https://music.apple.com/us/song/i-know-i-know/1894354139</v>
       </c>
       <c r="D58" t="str">
-        <v>2026-05-03</v>
+        <v>2026-05-04</v>
       </c>
       <c r="E58" t="str">
         <v/>
@@ -2611,7 +2611,7 @@
         <v>https://music.apple.com/us/song/drive-all-night/6763189759</v>
       </c>
       <c r="D59" t="str">
-        <v>2026-05-03</v>
+        <v>2026-05-04</v>
       </c>
       <c r="E59" t="str">
         <v/>
@@ -2649,7 +2649,7 @@
         <v>https://music.apple.com/us/song/aint-u-tired/6763115235</v>
       </c>
       <c r="D60" t="str">
-        <v>2026-05-03</v>
+        <v>2026-05-04</v>
       </c>
       <c r="E60" t="str">
         <v/>
@@ -2687,7 +2687,7 @@
         <v>https://music.apple.com/us/song/boys-in-blue/1892436920</v>
       </c>
       <c r="D61" t="str">
-        <v>2026-05-03</v>
+        <v>2026-05-04</v>
       </c>
       <c r="E61" t="str">
         <v/>
@@ -2725,7 +2725,7 @@
         <v>https://music.apple.com/us/song/salma-hayek/1891815286</v>
       </c>
       <c r="D62" t="str">
-        <v>2026-05-03</v>
+        <v>2026-05-04</v>
       </c>
       <c r="E62" t="str">
         <v/>
@@ -2763,7 +2763,7 @@
         <v>https://music.apple.com/us/song/stubborn-mouth/1893194800</v>
       </c>
       <c r="D63" t="str">
-        <v>2026-05-03</v>
+        <v>2026-05-04</v>
       </c>
       <c r="E63" t="str">
         <v/>
@@ -2801,7 +2801,7 @@
         <v>https://music.apple.com/us/song/hallucination/6764110976</v>
       </c>
       <c r="D64" t="str">
-        <v>2026-05-03</v>
+        <v>2026-05-04</v>
       </c>
       <c r="E64" t="str">
         <v/>
@@ -2839,7 +2839,7 @@
         <v>https://music.apple.com/us/song/in-da-jungle/1891136400</v>
       </c>
       <c r="D65" t="str">
-        <v>2026-05-03</v>
+        <v>2026-05-04</v>
       </c>
       <c r="E65" t="str">
         <v/>
@@ -2877,7 +2877,7 @@
         <v>https://music.apple.com/us/song/fall-short/1894662749</v>
       </c>
       <c r="D66" t="str">
-        <v>2026-05-03</v>
+        <v>2026-05-04</v>
       </c>
       <c r="E66" t="str">
         <v/>
@@ -2915,7 +2915,7 @@
         <v>https://music.apple.com/us/song/irish-goodbye-feat-kae-tempest/1862224205</v>
       </c>
       <c r="D67" t="str">
-        <v>2026-05-03</v>
+        <v>2026-05-04</v>
       </c>
       <c r="E67" t="str">
         <v/>
@@ -2953,7 +2953,7 @@
         <v>https://music.apple.com/us/song/1989/1893089382</v>
       </c>
       <c r="D68" t="str">
-        <v>2026-05-03</v>
+        <v>2026-05-04</v>
       </c>
       <c r="E68" t="str">
         <v/>
@@ -2991,7 +2991,7 @@
         <v>https://music.apple.com/us/song/no-more-regrets/1893191803</v>
       </c>
       <c r="D69" t="str">
-        <v>2026-05-03</v>
+        <v>2026-05-04</v>
       </c>
       <c r="E69" t="str">
         <v/>
@@ -3029,7 +3029,7 @@
         <v>https://music.apple.com/us/song/drum-machine/1840517102</v>
       </c>
       <c r="D70" t="str">
-        <v>2026-05-03</v>
+        <v>2026-05-04</v>
       </c>
       <c r="E70" t="str">
         <v/>
@@ -3067,7 +3067,7 @@
         <v>https://music.apple.com/us/song/im-perfect/1893181359</v>
       </c>
       <c r="D71" t="str">
-        <v>2026-05-03</v>
+        <v>2026-05-04</v>
       </c>
       <c r="E71" t="str">
         <v/>
@@ -3105,7 +3105,7 @@
         <v>https://music.apple.com/us/song/theme-for-a-train-journey/1880699785</v>
       </c>
       <c r="D72" t="str">
-        <v>2026-05-03</v>
+        <v>2026-05-04</v>
       </c>
       <c r="E72" t="str">
         <v/>
@@ -3143,7 +3143,7 @@
         <v>https://music.apple.com/us/song/bitch-you-weird/6763395875</v>
       </c>
       <c r="D73" t="str">
-        <v>2026-05-03</v>
+        <v>2026-05-04</v>
       </c>
       <c r="E73" t="str">
         <v/>
@@ -3181,7 +3181,7 @@
         <v>https://music.apple.com/us/song/blackbird-rising/1887166611</v>
       </c>
       <c r="D74" t="str">
-        <v>2026-05-03</v>
+        <v>2026-05-04</v>
       </c>
       <c r="E74" t="str">
         <v/>
@@ -3219,7 +3219,7 @@
         <v>https://music.apple.com/us/song/usher-in-the-spirit/6763373678</v>
       </c>
       <c r="D75" t="str">
-        <v>2026-05-03</v>
+        <v>2026-05-04</v>
       </c>
       <c r="E75" t="str">
         <v/>
@@ -3257,7 +3257,7 @@
         <v>https://music.apple.com/us/song/moonlight/1892950791</v>
       </c>
       <c r="D76" t="str">
-        <v>2026-05-03</v>
+        <v>2026-05-04</v>
       </c>
       <c r="E76" t="str">
         <v/>
@@ -3295,7 +3295,7 @@
         <v>https://music.apple.com/us/song/hands-on-me/1893960365</v>
       </c>
       <c r="D77" t="str">
-        <v>2026-05-03</v>
+        <v>2026-05-04</v>
       </c>
       <c r="E77" t="str">
         <v/>
@@ -3333,7 +3333,7 @@
         <v>https://music.apple.com/us/song/closure/1892418294</v>
       </c>
       <c r="D78" t="str">
-        <v>2026-05-03</v>
+        <v>2026-05-04</v>
       </c>
       <c r="E78" t="str">
         <v/>
@@ -3371,7 +3371,7 @@
         <v>https://music.apple.com/us/song/hots-4-u/1891478541</v>
       </c>
       <c r="D79" t="str">
-        <v>2026-05-03</v>
+        <v>2026-05-04</v>
       </c>
       <c r="E79" t="str">
         <v/>
@@ -3409,7 +3409,7 @@
         <v>https://music.apple.com/us/song/cule-poco-sirena-besarico-coste%C3%B1a/1893480200</v>
       </c>
       <c r="D80" t="str">
-        <v>2026-05-03</v>
+        <v>2026-05-04</v>
       </c>
       <c r="E80" t="str">
         <v/>
@@ -3447,7 +3447,7 @@
         <v>https://music.apple.com/us/song/the-coin-toss/1894872115</v>
       </c>
       <c r="D81" t="str">
-        <v>2026-05-03</v>
+        <v>2026-05-04</v>
       </c>
       <c r="E81" t="str">
         <v/>
@@ -3485,7 +3485,7 @@
         <v>https://music.apple.com/us/song/bottles-lights/6763041153</v>
       </c>
       <c r="D82" t="str">
-        <v>2026-05-03</v>
+        <v>2026-05-04</v>
       </c>
       <c r="E82" t="str">
         <v/>
@@ -3523,7 +3523,7 @@
         <v>https://music.apple.com/us/song/perfect-for-me/6762879981</v>
       </c>
       <c r="D83" t="str">
-        <v>2026-05-03</v>
+        <v>2026-05-04</v>
       </c>
       <c r="E83" t="str">
         <v/>
@@ -3561,7 +3561,7 @@
         <v>https://music.apple.com/us/song/so/1893162424</v>
       </c>
       <c r="D84" t="str">
-        <v>2026-05-03</v>
+        <v>2026-05-04</v>
       </c>
       <c r="E84" t="str">
         <v/>
@@ -3599,7 +3599,7 @@
         <v>https://music.apple.com/us/song/pase-y-pase/1894076490</v>
       </c>
       <c r="D85" t="str">
-        <v>2026-05-03</v>
+        <v>2026-05-04</v>
       </c>
       <c r="E85" t="str">
         <v/>
@@ -3637,7 +3637,7 @@
         <v>https://music.apple.com/us/song/agou%C3%A9-dambala-yanvalou-1/1888242486</v>
       </c>
       <c r="D86" t="str">
-        <v>2026-05-03</v>
+        <v>2026-05-04</v>
       </c>
       <c r="E86" t="str">
         <v/>
@@ -3675,7 +3675,7 @@
         <v>https://music.apple.com/us/song/aljahalat/1889267983</v>
       </c>
       <c r="D87" t="str">
-        <v>2026-05-03</v>
+        <v>2026-05-04</v>
       </c>
       <c r="E87" t="str">
         <v/>
@@ -3713,7 +3713,7 @@
         <v>https://music.apple.com/us/song/puleza/1893765840</v>
       </c>
       <c r="D88" t="str">
-        <v>2026-05-03</v>
+        <v>2026-05-04</v>
       </c>
       <c r="E88" t="str">
         <v/>
@@ -3751,7 +3751,7 @@
         <v>https://music.apple.com/us/song/bastards/6762403102</v>
       </c>
       <c r="D89" t="str">
-        <v>2026-05-03</v>
+        <v>2026-05-04</v>
       </c>
       <c r="E89" t="str">
         <v/>
@@ -3789,7 +3789,7 @@
         <v>https://music.apple.com/us/song/crutch/6763345020</v>
       </c>
       <c r="D90" t="str">
-        <v>2026-05-03</v>
+        <v>2026-05-04</v>
       </c>
       <c r="E90" t="str">
         <v/>
@@ -3827,7 +3827,7 @@
         <v>https://music.apple.com/us/song/just-a-man/1893736206</v>
       </c>
       <c r="D91" t="str">
-        <v>2026-05-03</v>
+        <v>2026-05-04</v>
       </c>
       <c r="E91" t="str">
         <v/>
@@ -3865,7 +3865,7 @@
         <v>https://music.apple.com/us/song/take-care-of-you/6762283983</v>
       </c>
       <c r="D92" t="str">
-        <v>2026-05-03</v>
+        <v>2026-05-04</v>
       </c>
       <c r="E92" t="str">
         <v/>
@@ -3903,7 +3903,7 @@
         <v>https://music.apple.com/us/song/love-you-more/1889686330</v>
       </c>
       <c r="D93" t="str">
-        <v>2026-05-03</v>
+        <v>2026-05-04</v>
       </c>
       <c r="E93" t="str">
         <v/>
@@ -3941,7 +3941,7 @@
         <v>https://music.apple.com/us/song/construct/1869323374</v>
       </c>
       <c r="D94" t="str">
-        <v>2026-05-03</v>
+        <v>2026-05-04</v>
       </c>
       <c r="E94" t="str">
         <v/>
@@ -3979,7 +3979,7 @@
         <v>https://music.apple.com/us/song/as-above-so-below/1872651422</v>
       </c>
       <c r="D95" t="str">
-        <v>2026-05-03</v>
+        <v>2026-05-04</v>
       </c>
       <c r="E95" t="str">
         <v/>
@@ -4017,7 +4017,7 @@
         <v>https://music.apple.com/us/song/revenant/6763148056</v>
       </c>
       <c r="D96" t="str">
-        <v>2026-05-03</v>
+        <v>2026-05-04</v>
       </c>
       <c r="E96" t="str">
         <v/>
@@ -4055,7 +4055,7 @@
         <v>https://music.apple.com/us/song/black-box-feat-joe-duplantier-the-mystery-of/6762312582</v>
       </c>
       <c r="D97" t="str">
-        <v>2026-05-03</v>
+        <v>2026-05-04</v>
       </c>
       <c r="E97" t="str">
         <v/>
@@ -4093,7 +4093,7 @@
         <v>https://music.apple.com/us/song/power-4/6763647813</v>
       </c>
       <c r="D98" t="str">
-        <v>2026-05-03</v>
+        <v>2026-05-04</v>
       </c>
       <c r="E98" t="str">
         <v/>
@@ -4131,7 +4131,7 @@
         <v>https://music.apple.com/us/song/too-easy/1893814702</v>
       </c>
       <c r="D99" t="str">
-        <v>2026-05-03</v>
+        <v>2026-05-04</v>
       </c>
       <c r="E99" t="str">
         <v/>
@@ -4169,7 +4169,7 @@
         <v>https://music.apple.com/us/song/if-you-want-it/1892503347</v>
       </c>
       <c r="D100" t="str">
-        <v>2026-05-03</v>
+        <v>2026-05-04</v>
       </c>
       <c r="E100" t="str">
         <v/>
@@ -4207,7 +4207,7 @@
         <v>https://music.apple.com/us/song/shoplifting/1852812659</v>
       </c>
       <c r="D101" t="str">
-        <v>2026-05-03</v>
+        <v>2026-05-04</v>
       </c>
       <c r="E101" t="str">
         <v/>
@@ -4245,7 +4245,7 @@
         <v>https://music.apple.com/us/song/endlessly-feat-bea1991/1876022833</v>
       </c>
       <c r="D102" t="str">
-        <v>2026-05-03</v>
+        <v>2026-05-04</v>
       </c>
       <c r="E102" t="str">
         <v/>

--- a/data/tags/מוזיקה לועזית חדשה/sites/apple-music-playlist/2026-05-week01/titles.xlsx
+++ b/data/tags/מוזיקה לועזית חדשה/sites/apple-music-playlist/2026-05-week01/titles.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L102"/>
+  <dimension ref="A1:L103"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -436,13 +436,13 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>Eurosummer (Girls Trip)</v>
+        <v>Robotic Love</v>
       </c>
       <c r="B2" t="str">
         <v/>
       </c>
       <c r="C2" t="str">
-        <v>https://music.apple.com/us/song/eurosummer-girls-trip/1894058279</v>
+        <v>https://music.apple.com/us/song/robotic-love/6763638857</v>
       </c>
       <c r="D2" t="str">
         <v>2026-05-04</v>
@@ -451,36 +451,36 @@
         <v/>
       </c>
       <c r="F2" t="str">
-        <v>Midnight Sun: Girls Trip</v>
+        <v>Robotic Love - Single</v>
       </c>
       <c r="G2" t="str">
-        <v>2:50</v>
+        <v>3:25</v>
       </c>
       <c r="H2" t="str">
-        <v>Zara Larsson</v>
+        <v>elkan</v>
       </c>
       <c r="I2" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J2" t="str">
-        <v>https://music.apple.com/us/artist/zara-larsson/570372593</v>
+        <v>https://music.apple.com/us/artist/elkan/1805013361</v>
       </c>
       <c r="K2" t="str">
-        <v>https://music.apple.com/us/album/eurosummer-girls-trip/1894058251</v>
+        <v>https://music.apple.com/us/album/robotic-love/1895412608</v>
       </c>
       <c r="L2" t="str">
-        <v>Eurosummer (Girls Trip) - Zara Larsson</v>
+        <v>Robotic Love - elkan</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>Shape of a Woman</v>
+        <v>Eurosummer (Girls Trip)</v>
       </c>
       <c r="B3" t="str">
         <v/>
       </c>
       <c r="C3" t="str">
-        <v>https://music.apple.com/us/song/shape-of-a-woman/6764429252</v>
+        <v>https://music.apple.com/us/song/eurosummer-girls-trip/1894058279</v>
       </c>
       <c r="D3" t="str">
         <v>2026-05-04</v>
@@ -489,36 +489,36 @@
         <v/>
       </c>
       <c r="F3" t="str">
-        <v>The Devil Wears Prada 2 (Music From The Motion Picture)</v>
+        <v>Midnight Sun: Girls Trip</v>
       </c>
       <c r="G3" t="str">
-        <v>3:29</v>
+        <v>2:50</v>
       </c>
       <c r="H3" t="str">
-        <v>Lady Gaga</v>
+        <v>Zara Larsson</v>
       </c>
       <c r="I3" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J3" t="str">
-        <v>https://music.apple.com/us/artist/lady-gaga/277293880</v>
+        <v>https://music.apple.com/us/artist/zara-larsson/570372593</v>
       </c>
       <c r="K3" t="str">
-        <v>https://music.apple.com/us/album/shape-of-a-woman/1895776688</v>
+        <v>https://music.apple.com/us/album/eurosummer-girls-trip/1894058251</v>
       </c>
       <c r="L3" t="str">
-        <v>Shape of a Woman - Lady Gaga</v>
+        <v>Eurosummer (Girls Trip) - Zara Larsson</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>Bring Your Love</v>
+        <v>Shape of a Woman</v>
       </c>
       <c r="B4" t="str">
         <v/>
       </c>
       <c r="C4" t="str">
-        <v>https://music.apple.com/us/song/bring-your-love/1892545227</v>
+        <v>https://music.apple.com/us/song/shape-of-a-woman/6764429252</v>
       </c>
       <c r="D4" t="str">
         <v>2026-05-04</v>
@@ -527,36 +527,36 @@
         <v/>
       </c>
       <c r="F4" t="str">
-        <v>CONFESSIONS II</v>
+        <v>The Devil Wears Prada 2 (Music From The Motion Picture)</v>
       </c>
       <c r="G4" t="str">
-        <v>3:36</v>
+        <v>3:29</v>
       </c>
       <c r="H4" t="str">
-        <v>Madonna</v>
+        <v>Lady Gaga</v>
       </c>
       <c r="I4" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J4" t="str">
-        <v>https://music.apple.com/us/artist/madonna/20044</v>
+        <v>https://music.apple.com/us/artist/lady-gaga/277293880</v>
       </c>
       <c r="K4" t="str">
-        <v>https://music.apple.com/us/album/bring-your-love/1892545087</v>
+        <v>https://music.apple.com/us/album/shape-of-a-woman/1895776688</v>
       </c>
       <c r="L4" t="str">
-        <v>Bring Your Love - Madonna</v>
+        <v>Shape of a Woman - Lady Gaga</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>Horses and Divorces</v>
+        <v>Bring Your Love</v>
       </c>
       <c r="B5" t="str">
         <v/>
       </c>
       <c r="C5" t="str">
-        <v>https://music.apple.com/us/song/horses-and-divorces/1883177267</v>
+        <v>https://music.apple.com/us/song/bring-your-love/1892545227</v>
       </c>
       <c r="D5" t="str">
         <v>2026-05-04</v>
@@ -565,36 +565,36 @@
         <v/>
       </c>
       <c r="F5" t="str">
-        <v>Middle of Nowhere</v>
+        <v>CONFESSIONS II</v>
       </c>
       <c r="G5" t="str">
-        <v>2:43</v>
+        <v>3:36</v>
       </c>
       <c r="H5" t="str">
-        <v>Kacey Musgraves</v>
+        <v>Madonna</v>
       </c>
       <c r="I5" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J5" t="str">
-        <v>https://music.apple.com/us/artist/kacey-musgraves/466044182</v>
+        <v>https://music.apple.com/us/artist/madonna/20044</v>
       </c>
       <c r="K5" t="str">
-        <v>https://music.apple.com/us/album/horses-and-divorces/1883176984</v>
+        <v>https://music.apple.com/us/album/bring-your-love/1892545087</v>
       </c>
       <c r="L5" t="str">
-        <v>Horses and Divorces - Kacey Musgraves</v>
+        <v>Bring Your Love - Madonna</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>Staying Still</v>
+        <v>Horses and Divorces</v>
       </c>
       <c r="B6" t="str">
         <v/>
       </c>
       <c r="C6" t="str">
-        <v>https://music.apple.com/us/song/staying-still/6762758806</v>
+        <v>https://music.apple.com/us/song/horses-and-divorces/1883177267</v>
       </c>
       <c r="D6" t="str">
         <v>2026-05-04</v>
@@ -603,36 +603,36 @@
         <v/>
       </c>
       <c r="F6" t="str">
-        <v>The Great Divide: The Last Of The Bugs</v>
+        <v>Middle of Nowhere</v>
       </c>
       <c r="G6" t="str">
-        <v>4:28</v>
+        <v>2:43</v>
       </c>
       <c r="H6" t="str">
-        <v>Noah Kahan</v>
+        <v>Kacey Musgraves</v>
       </c>
       <c r="I6" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J6" t="str">
-        <v>https://music.apple.com/us/artist/noah-kahan/328583953</v>
+        <v>https://music.apple.com/us/artist/kacey-musgraves/466044182</v>
       </c>
       <c r="K6" t="str">
-        <v>https://music.apple.com/us/album/staying-still/1894998012</v>
+        <v>https://music.apple.com/us/album/horses-and-divorces/1883176984</v>
       </c>
       <c r="L6" t="str">
-        <v>Staying Still - Noah Kahan</v>
+        <v>Horses and Divorces - Kacey Musgraves</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>FINE PLACE TO DIE</v>
+        <v>Staying Still</v>
       </c>
       <c r="B7" t="str">
         <v/>
       </c>
       <c r="C7" t="str">
-        <v>https://music.apple.com/us/song/fine-place-to-die/6764686279</v>
+        <v>https://music.apple.com/us/song/staying-still/6762758806</v>
       </c>
       <c r="D7" t="str">
         <v>2026-05-04</v>
@@ -641,36 +641,36 @@
         <v/>
       </c>
       <c r="F7" t="str">
-        <v>FINE PLACE TO DIE - Single</v>
+        <v>The Great Divide: The Last Of The Bugs</v>
       </c>
       <c r="G7" t="str">
-        <v>3:07</v>
+        <v>4:28</v>
       </c>
       <c r="H7" t="str">
-        <v>Alex Warren</v>
+        <v>Noah Kahan</v>
       </c>
       <c r="I7" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J7" t="str">
-        <v>https://music.apple.com/us/artist/alex-warren/1572671688</v>
+        <v>https://music.apple.com/us/artist/noah-kahan/328583953</v>
       </c>
       <c r="K7" t="str">
-        <v>https://music.apple.com/us/album/fine-place-to-die/1895878798</v>
+        <v>https://music.apple.com/us/album/staying-still/1894998012</v>
       </c>
       <c r="L7" t="str">
-        <v>FINE PLACE TO DIE - Alex Warren</v>
+        <v>Staying Still - Noah Kahan</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>MUTT</v>
+        <v>FINE PLACE TO DIE</v>
       </c>
       <c r="B8" t="str">
         <v/>
       </c>
       <c r="C8" t="str">
-        <v>https://music.apple.com/us/song/mutt/6763145178</v>
+        <v>https://music.apple.com/us/song/fine-place-to-die/6764686279</v>
       </c>
       <c r="D8" t="str">
         <v>2026-05-04</v>
@@ -679,36 +679,36 @@
         <v/>
       </c>
       <c r="F8" t="str">
-        <v>MUTT - Single</v>
+        <v>FINE PLACE TO DIE - Single</v>
       </c>
       <c r="G8" t="str">
-        <v>1:59</v>
+        <v>3:07</v>
       </c>
       <c r="H8" t="str">
-        <v>NAV</v>
+        <v>Alex Warren</v>
       </c>
       <c r="I8" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J8" t="str">
-        <v>https://music.apple.com/us/artist/nav/1200089113</v>
+        <v>https://music.apple.com/us/artist/alex-warren/1572671688</v>
       </c>
       <c r="K8" t="str">
-        <v>https://music.apple.com/us/album/mutt/1895183429</v>
+        <v>https://music.apple.com/us/album/fine-place-to-die/1895878798</v>
       </c>
       <c r="L8" t="str">
-        <v>MUTT - NAV</v>
+        <v>FINE PLACE TO DIE - Alex Warren</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>Fire Away (feat. Slayyyter)</v>
+        <v>MUTT</v>
       </c>
       <c r="B9" t="str">
         <v/>
       </c>
       <c r="C9" t="str">
-        <v>https://music.apple.com/us/song/fire-away-feat-slayyyter/1892422570</v>
+        <v>https://music.apple.com/us/song/mutt/6763145178</v>
       </c>
       <c r="D9" t="str">
         <v>2026-05-04</v>
@@ -717,36 +717,36 @@
         <v/>
       </c>
       <c r="F9" t="str">
-        <v>Victory</v>
+        <v>MUTT - Single</v>
       </c>
       <c r="G9" t="str">
-        <v>3:27</v>
+        <v>1:59</v>
       </c>
       <c r="H9" t="str">
-        <v>Madeon</v>
+        <v>NAV</v>
       </c>
       <c r="I9" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J9" t="str">
-        <v>https://music.apple.com/us/artist/madeon/371199302</v>
+        <v>https://music.apple.com/us/artist/nav/1200089113</v>
       </c>
       <c r="K9" t="str">
-        <v>https://music.apple.com/us/album/fire-away-feat-slayyyter/1892422364</v>
+        <v>https://music.apple.com/us/album/mutt/1895183429</v>
       </c>
       <c r="L9" t="str">
-        <v>Fire Away (feat. Slayyyter) - Madeon</v>
+        <v>MUTT - NAV</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v>Lioness</v>
+        <v>Fire Away (feat. Slayyyter)</v>
       </c>
       <c r="B10" t="str">
         <v/>
       </c>
       <c r="C10" t="str">
-        <v>https://music.apple.com/us/song/lioness/1878649397</v>
+        <v>https://music.apple.com/us/song/fire-away-feat-slayyyter/1892422570</v>
       </c>
       <c r="D10" t="str">
         <v>2026-05-04</v>
@@ -755,36 +755,36 @@
         <v/>
       </c>
       <c r="F10" t="str">
-        <v>MAITREYA CORSO</v>
+        <v>Victory</v>
       </c>
       <c r="G10" t="str">
-        <v>3:32</v>
+        <v>3:27</v>
       </c>
       <c r="H10" t="str">
-        <v>Maya Hawke</v>
+        <v>Madeon</v>
       </c>
       <c r="I10" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J10" t="str">
-        <v>https://music.apple.com/us/artist/maya-hawke/1473393677</v>
+        <v>https://music.apple.com/us/artist/madeon/371199302</v>
       </c>
       <c r="K10" t="str">
-        <v>https://music.apple.com/us/album/lioness/1878649394</v>
+        <v>https://music.apple.com/us/album/fire-away-feat-slayyyter/1892422364</v>
       </c>
       <c r="L10" t="str">
-        <v>Lioness - Maya Hawke</v>
+        <v>Fire Away (feat. Slayyyter) - Madeon</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="str">
-        <v>IT'S OK</v>
+        <v>Lioness</v>
       </c>
       <c r="B11" t="str">
         <v/>
       </c>
       <c r="C11" t="str">
-        <v>https://music.apple.com/us/song/its-ok/6763134121</v>
+        <v>https://music.apple.com/us/song/lioness/1878649397</v>
       </c>
       <c r="D11" t="str">
         <v>2026-05-04</v>
@@ -793,36 +793,36 @@
         <v/>
       </c>
       <c r="F11" t="str">
-        <v>IT'S OK - Single</v>
+        <v>MAITREYA CORSO</v>
       </c>
       <c r="G11" t="str">
-        <v>2:19</v>
+        <v>3:32</v>
       </c>
       <c r="H11" t="str">
-        <v>Bryson Tiller</v>
+        <v>Maya Hawke</v>
       </c>
       <c r="I11" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J11" t="str">
-        <v>https://music.apple.com/us/artist/bryson-tiller/642591128</v>
+        <v>https://music.apple.com/us/artist/maya-hawke/1473393677</v>
       </c>
       <c r="K11" t="str">
-        <v>https://music.apple.com/us/album/its-ok/1895176998</v>
+        <v>https://music.apple.com/us/album/lioness/1878649394</v>
       </c>
       <c r="L11" t="str">
-        <v>IT'S OK - Bryson Tiller</v>
+        <v>Lioness - Maya Hawke</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="str">
-        <v>Promise?</v>
+        <v>IT'S OK</v>
       </c>
       <c r="B12" t="str">
         <v/>
       </c>
       <c r="C12" t="str">
-        <v>https://music.apple.com/us/song/promise/6763162287</v>
+        <v>https://music.apple.com/us/song/its-ok/6763134121</v>
       </c>
       <c r="D12" t="str">
         <v>2026-05-04</v>
@@ -831,36 +831,36 @@
         <v/>
       </c>
       <c r="F12" t="str">
-        <v>Promise? - Single</v>
+        <v>IT'S OK - Single</v>
       </c>
       <c r="G12" t="str">
-        <v>3:12</v>
+        <v>2:19</v>
       </c>
       <c r="H12" t="str">
-        <v>Bella Kay</v>
+        <v>Bryson Tiller</v>
       </c>
       <c r="I12" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J12" t="str">
-        <v>https://music.apple.com/us/artist/bella-kay/1706434165</v>
+        <v>https://music.apple.com/us/artist/bryson-tiller/642591128</v>
       </c>
       <c r="K12" t="str">
-        <v>https://music.apple.com/us/album/promise/1895191463</v>
+        <v>https://music.apple.com/us/album/its-ok/1895176998</v>
       </c>
       <c r="L12" t="str">
-        <v>Promise? - Bella Kay</v>
+        <v>IT'S OK - Bryson Tiller</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="str">
-        <v>Cool Buzz</v>
+        <v>Promise?</v>
       </c>
       <c r="B13" t="str">
         <v/>
       </c>
       <c r="C13" t="str">
-        <v>https://music.apple.com/us/song/cool-buzz/1880470657</v>
+        <v>https://music.apple.com/us/song/promise/6763162287</v>
       </c>
       <c r="D13" t="str">
         <v>2026-05-04</v>
@@ -869,36 +869,36 @@
         <v/>
       </c>
       <c r="F13" t="str">
-        <v>Be Sweet To Me</v>
+        <v>Promise? - Single</v>
       </c>
       <c r="G13" t="str">
-        <v>2:32</v>
+        <v>3:12</v>
       </c>
       <c r="H13" t="str">
-        <v>Violet Grohl</v>
+        <v>Bella Kay</v>
       </c>
       <c r="I13" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J13" t="str">
-        <v>https://music.apple.com/us/artist/violet-grohl/1538671509</v>
+        <v>https://music.apple.com/us/artist/bella-kay/1706434165</v>
       </c>
       <c r="K13" t="str">
-        <v>https://music.apple.com/us/album/cool-buzz/1880470537</v>
+        <v>https://music.apple.com/us/album/promise/1895191463</v>
       </c>
       <c r="L13" t="str">
-        <v>Cool Buzz - Violet Grohl</v>
+        <v>Promise? - Bella Kay</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="str">
-        <v>Material Lover</v>
+        <v>Cool Buzz</v>
       </c>
       <c r="B14" t="str">
         <v/>
       </c>
       <c r="C14" t="str">
-        <v>https://music.apple.com/us/song/material-lover/6764429256</v>
+        <v>https://music.apple.com/us/song/cool-buzz/1880470657</v>
       </c>
       <c r="D14" t="str">
         <v>2026-05-04</v>
@@ -907,36 +907,36 @@
         <v/>
       </c>
       <c r="F14" t="str">
-        <v>The Devil Wears Prada 2 (Music From The Motion Picture)</v>
+        <v>Be Sweet To Me</v>
       </c>
       <c r="G14" t="str">
-        <v>2:58</v>
+        <v>2:32</v>
       </c>
       <c r="H14" t="str">
-        <v>SIENNA SPIRO</v>
+        <v>Violet Grohl</v>
       </c>
       <c r="I14" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J14" t="str">
-        <v>https://music.apple.com/us/artist/sienna-spiro/1745678083</v>
+        <v>https://music.apple.com/us/artist/violet-grohl/1538671509</v>
       </c>
       <c r="K14" t="str">
-        <v>https://music.apple.com/us/album/material-lover/1895776688</v>
+        <v>https://music.apple.com/us/album/cool-buzz/1880470537</v>
       </c>
       <c r="L14" t="str">
-        <v>Material Lover - SIENNA SPIRO</v>
+        <v>Cool Buzz - Violet Grohl</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="str">
-        <v>Fallin' (feat. Leon Thomas)</v>
+        <v>Material Lover</v>
       </c>
       <c r="B15" t="str">
         <v/>
       </c>
       <c r="C15" t="str">
-        <v>https://music.apple.com/us/song/fallin-feat-leon-thomas/6764419265</v>
+        <v>https://music.apple.com/us/song/material-lover/6764429256</v>
       </c>
       <c r="D15" t="str">
         <v>2026-05-04</v>
@@ -945,36 +945,36 @@
         <v/>
       </c>
       <c r="F15" t="str">
-        <v>BROWN</v>
+        <v>The Devil Wears Prada 2 (Music From The Motion Picture)</v>
       </c>
       <c r="G15" t="str">
-        <v>4:26</v>
+        <v>2:58</v>
       </c>
       <c r="H15" t="str">
-        <v>Chris Brown</v>
+        <v>SIENNA SPIRO</v>
       </c>
       <c r="I15" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J15" t="str">
-        <v>https://music.apple.com/us/artist/chris-brown/95705522</v>
+        <v>https://music.apple.com/us/artist/sienna-spiro/1745678083</v>
       </c>
       <c r="K15" t="str">
-        <v>https://music.apple.com/us/album/fallin-feat-leon-thomas/1895772091</v>
+        <v>https://music.apple.com/us/album/material-lover/1895776688</v>
       </c>
       <c r="L15" t="str">
-        <v>Fallin' (feat. Leon Thomas) - Chris Brown</v>
+        <v>Material Lover - SIENNA SPIRO</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="str">
-        <v>Echo</v>
+        <v>Fallin' (feat. Leon Thomas)</v>
       </c>
       <c r="B16" t="str">
         <v/>
       </c>
       <c r="C16" t="str">
-        <v>https://music.apple.com/us/song/echo/6763379683</v>
+        <v>https://music.apple.com/us/song/fallin-feat-leon-thomas/6764419265</v>
       </c>
       <c r="D16" t="str">
         <v>2026-05-04</v>
@@ -983,36 +983,36 @@
         <v/>
       </c>
       <c r="F16" t="str">
-        <v>Echo (FIFA World Cup 2026™) - Single</v>
+        <v>BROWN</v>
       </c>
       <c r="G16" t="str">
-        <v>2:15</v>
+        <v>4:26</v>
       </c>
       <c r="H16" t="str">
-        <v>Daddy Yankee</v>
+        <v>Chris Brown</v>
       </c>
       <c r="I16" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J16" t="str">
-        <v>https://music.apple.com/us/artist/daddy-yankee/25514958</v>
+        <v>https://music.apple.com/us/artist/chris-brown/95705522</v>
       </c>
       <c r="K16" t="str">
-        <v>https://music.apple.com/us/album/echo/1895288918</v>
+        <v>https://music.apple.com/us/album/fallin-feat-leon-thomas/1895772091</v>
       </c>
       <c r="L16" t="str">
-        <v>Echo - Daddy Yankee</v>
+        <v>Fallin' (feat. Leon Thomas) - Chris Brown</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="str">
-        <v>Blackberry Marmalade</v>
+        <v>Echo</v>
       </c>
       <c r="B17" t="str">
         <v/>
       </c>
       <c r="C17" t="str">
-        <v>https://music.apple.com/us/song/blackberry-marmalade/1887627837</v>
+        <v>https://music.apple.com/us/song/echo/6763379683</v>
       </c>
       <c r="D17" t="str">
         <v>2026-05-04</v>
@@ -1021,36 +1021,36 @@
         <v/>
       </c>
       <c r="F17" t="str">
-        <v>Cry Baby</v>
+        <v>Echo (FIFA World Cup 2026™) - Single</v>
       </c>
       <c r="G17" t="str">
-        <v>3:52</v>
+        <v>2:15</v>
       </c>
       <c r="H17" t="str">
-        <v>Vince Staples</v>
+        <v>Daddy Yankee</v>
       </c>
       <c r="I17" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J17" t="str">
-        <v>https://music.apple.com/us/artist/vince-staples/566639154</v>
+        <v>https://music.apple.com/us/artist/daddy-yankee/25514958</v>
       </c>
       <c r="K17" t="str">
-        <v>https://music.apple.com/us/album/blackberry-marmalade/1887627836</v>
+        <v>https://music.apple.com/us/album/echo/1895288918</v>
       </c>
       <c r="L17" t="str">
-        <v>Blackberry Marmalade - Vince Staples</v>
+        <v>Echo - Daddy Yankee</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="str">
-        <v>Ricky Bobby</v>
+        <v>Blackberry Marmalade</v>
       </c>
       <c r="B18" t="str">
         <v/>
       </c>
       <c r="C18" t="str">
-        <v>https://music.apple.com/us/song/ricky-bobby/6764406571</v>
+        <v>https://music.apple.com/us/song/blackberry-marmalade/1887627837</v>
       </c>
       <c r="D18" t="str">
         <v>2026-05-04</v>
@@ -1059,36 +1059,36 @@
         <v/>
       </c>
       <c r="F18" t="str">
-        <v>CORSA</v>
+        <v>Cry Baby</v>
       </c>
       <c r="G18" t="str">
-        <v>2:55</v>
+        <v>3:52</v>
       </c>
       <c r="H18" t="str">
-        <v>Eladio Carrión</v>
+        <v>Vince Staples</v>
       </c>
       <c r="I18" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J18" t="str">
-        <v>https://music.apple.com/us/artist/eladio-carri%C3%B3n/1024801206</v>
+        <v>https://music.apple.com/us/artist/vince-staples/566639154</v>
       </c>
       <c r="K18" t="str">
-        <v>https://music.apple.com/us/album/ricky-bobby/1895766650</v>
+        <v>https://music.apple.com/us/album/blackberry-marmalade/1887627836</v>
       </c>
       <c r="L18" t="str">
-        <v>Ricky Bobby - Eladio Carrión</v>
+        <v>Blackberry Marmalade - Vince Staples</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="str">
-        <v>Te Entiendo (Remix)</v>
+        <v>Ricky Bobby</v>
       </c>
       <c r="B19" t="str">
         <v/>
       </c>
       <c r="C19" t="str">
-        <v>https://music.apple.com/us/song/te-entiendo-remix/6763665638</v>
+        <v>https://music.apple.com/us/song/ricky-bobby/6764406571</v>
       </c>
       <c r="D19" t="str">
         <v>2026-05-04</v>
@@ -1097,36 +1097,36 @@
         <v/>
       </c>
       <c r="F19" t="str">
-        <v>Te Entiendo (Remix) - Single</v>
+        <v>CORSA</v>
       </c>
       <c r="G19" t="str">
-        <v>5:35</v>
+        <v>2:55</v>
       </c>
       <c r="H19" t="str">
-        <v>Maisak</v>
+        <v>Eladio Carrión</v>
       </c>
       <c r="I19" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J19" t="str">
-        <v>https://music.apple.com/us/artist/maisak/1610652984</v>
+        <v>https://music.apple.com/us/artist/eladio-carri%C3%B3n/1024801206</v>
       </c>
       <c r="K19" t="str">
-        <v>https://music.apple.com/us/album/te-entiendo-remix/1895426152</v>
+        <v>https://music.apple.com/us/album/ricky-bobby/1895766650</v>
       </c>
       <c r="L19" t="str">
-        <v>Te Entiendo (Remix) - Maisak</v>
+        <v>Ricky Bobby - Eladio Carrión</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="str">
-        <v>Don't Worry Baby</v>
+        <v>Te Entiendo (Remix)</v>
       </c>
       <c r="B20" t="str">
         <v/>
       </c>
       <c r="C20" t="str">
-        <v>https://music.apple.com/us/song/dont-worry-baby/1894294411</v>
+        <v>https://music.apple.com/us/song/te-entiendo-remix/6763665638</v>
       </c>
       <c r="D20" t="str">
         <v>2026-05-04</v>
@@ -1135,36 +1135,36 @@
         <v/>
       </c>
       <c r="F20" t="str">
-        <v>Don't Worry Baby - Single</v>
+        <v>Te Entiendo (Remix) - Single</v>
       </c>
       <c r="G20" t="str">
-        <v>3:27</v>
+        <v>5:35</v>
       </c>
       <c r="H20" t="str">
-        <v>Dom Dolla</v>
+        <v>Maisak</v>
       </c>
       <c r="I20" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J20" t="str">
-        <v>https://music.apple.com/us/artist/dom-dolla/555348065</v>
+        <v>https://music.apple.com/us/artist/maisak/1610652984</v>
       </c>
       <c r="K20" t="str">
-        <v>https://music.apple.com/us/album/dont-worry-baby/1894294408</v>
+        <v>https://music.apple.com/us/album/te-entiendo-remix/1895426152</v>
       </c>
       <c r="L20" t="str">
-        <v>Don't Worry Baby - Dom Dolla</v>
+        <v>Te Entiendo (Remix) - Maisak</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="str">
-        <v>BITCH</v>
+        <v>Don't Worry Baby</v>
       </c>
       <c r="B21" t="str">
         <v/>
       </c>
       <c r="C21" t="str">
-        <v>https://music.apple.com/us/song/bitch/6763622110</v>
+        <v>https://music.apple.com/us/song/dont-worry-baby/1894294411</v>
       </c>
       <c r="D21" t="str">
         <v>2026-05-04</v>
@@ -1173,36 +1173,36 @@
         <v/>
       </c>
       <c r="F21" t="str">
-        <v>BITCH</v>
+        <v>Don't Worry Baby - Single</v>
       </c>
       <c r="G21" t="str">
-        <v>2:42</v>
+        <v>3:27</v>
       </c>
       <c r="H21" t="str">
-        <v>Lizzo</v>
+        <v>Dom Dolla</v>
       </c>
       <c r="I21" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J21" t="str">
-        <v>https://music.apple.com/us/artist/lizzo/472949623</v>
+        <v>https://music.apple.com/us/artist/dom-dolla/555348065</v>
       </c>
       <c r="K21" t="str">
-        <v>https://music.apple.com/us/album/bitch/1895402771</v>
+        <v>https://music.apple.com/us/album/dont-worry-baby/1894294408</v>
       </c>
       <c r="L21" t="str">
-        <v>BITCH - Lizzo</v>
+        <v>Don't Worry Baby - Dom Dolla</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="str">
-        <v>Just Wanna Cry</v>
+        <v>BITCH</v>
       </c>
       <c r="B22" t="str">
         <v/>
       </c>
       <c r="C22" t="str">
-        <v>https://music.apple.com/us/song/just-wanna-cry/6763414703</v>
+        <v>https://music.apple.com/us/song/bitch/6763622110</v>
       </c>
       <c r="D22" t="str">
         <v>2026-05-04</v>
@@ -1211,36 +1211,36 @@
         <v/>
       </c>
       <c r="F22" t="str">
-        <v>Toy With Me (Deluxe)</v>
+        <v>BITCH</v>
       </c>
       <c r="G22" t="str">
-        <v>2:27</v>
+        <v>2:42</v>
       </c>
       <c r="H22" t="str">
-        <v>Meghan Trainor</v>
+        <v>Lizzo</v>
       </c>
       <c r="I22" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J22" t="str">
-        <v>https://music.apple.com/us/artist/meghan-trainor/348580754</v>
+        <v>https://music.apple.com/us/artist/lizzo/472949623</v>
       </c>
       <c r="K22" t="str">
-        <v>https://music.apple.com/us/album/just-wanna-cry/1895303290</v>
+        <v>https://music.apple.com/us/album/bitch/1895402771</v>
       </c>
       <c r="L22" t="str">
-        <v>Just Wanna Cry - Meghan Trainor</v>
+        <v>BITCH - Lizzo</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="str">
-        <v>Carry the Weight</v>
+        <v>Just Wanna Cry</v>
       </c>
       <c r="B23" t="str">
         <v/>
       </c>
       <c r="C23" t="str">
-        <v>https://music.apple.com/us/song/carry-the-weight/6763611647</v>
+        <v>https://music.apple.com/us/song/just-wanna-cry/6763414703</v>
       </c>
       <c r="D23" t="str">
         <v>2026-05-04</v>
@@ -1249,36 +1249,36 @@
         <v/>
       </c>
       <c r="F23" t="str">
-        <v>The Great Impersonator (Deluxe)</v>
+        <v>Toy With Me (Deluxe)</v>
       </c>
       <c r="G23" t="str">
-        <v>3:09</v>
+        <v>2:27</v>
       </c>
       <c r="H23" t="str">
-        <v>Halsey</v>
+        <v>Meghan Trainor</v>
       </c>
       <c r="I23" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J23" t="str">
-        <v>https://music.apple.com/us/artist/halsey/324916925</v>
+        <v>https://music.apple.com/us/artist/meghan-trainor/348580754</v>
       </c>
       <c r="K23" t="str">
-        <v>https://music.apple.com/us/album/carry-the-weight/1895397523</v>
+        <v>https://music.apple.com/us/album/just-wanna-cry/1895303290</v>
       </c>
       <c r="L23" t="str">
-        <v>Carry the Weight - Halsey</v>
+        <v>Just Wanna Cry - Meghan Trainor</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="str">
-        <v>PROSTITUTE</v>
+        <v>Carry the Weight</v>
       </c>
       <c r="B24" t="str">
         <v/>
       </c>
       <c r="C24" t="str">
-        <v>https://music.apple.com/us/song/prostitute/1894092341</v>
+        <v>https://music.apple.com/us/song/carry-the-weight/6763611647</v>
       </c>
       <c r="D24" t="str">
         <v>2026-05-04</v>
@@ -1287,36 +1287,36 @@
         <v/>
       </c>
       <c r="F24" t="str">
-        <v>COSMIC OPERA ACT II</v>
+        <v>The Great Impersonator (Deluxe)</v>
       </c>
       <c r="G24" t="str">
-        <v>2:44</v>
+        <v>3:09</v>
       </c>
       <c r="H24" t="str">
-        <v>Labrinth</v>
+        <v>Halsey</v>
       </c>
       <c r="I24" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J24" t="str">
-        <v>https://music.apple.com/us/artist/labrinth/205732582</v>
+        <v>https://music.apple.com/us/artist/halsey/324916925</v>
       </c>
       <c r="K24" t="str">
-        <v>https://music.apple.com/us/album/prostitute/1894092339</v>
+        <v>https://music.apple.com/us/album/carry-the-weight/1895397523</v>
       </c>
       <c r="L24" t="str">
-        <v>PROSTITUTE - Labrinth</v>
+        <v>Carry the Weight - Halsey</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="str">
-        <v>i'm not joking</v>
+        <v>PROSTITUTE</v>
       </c>
       <c r="B25" t="str">
         <v/>
       </c>
       <c r="C25" t="str">
-        <v>https://music.apple.com/us/song/im-not-joking/1872842623</v>
+        <v>https://music.apple.com/us/song/prostitute/1894092341</v>
       </c>
       <c r="D25" t="str">
         <v>2026-05-04</v>
@@ -1325,36 +1325,36 @@
         <v/>
       </c>
       <c r="F25" t="str">
-        <v>everyone for ten minutes</v>
+        <v>COSMIC OPERA ACT II</v>
       </c>
       <c r="G25" t="str">
-        <v>3:54</v>
+        <v>2:44</v>
       </c>
       <c r="H25" t="str">
-        <v>Bleachers</v>
+        <v>Labrinth</v>
       </c>
       <c r="I25" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J25" t="str">
-        <v>https://music.apple.com/us/artist/bleachers/824434533</v>
+        <v>https://music.apple.com/us/artist/labrinth/205732582</v>
       </c>
       <c r="K25" t="str">
-        <v>https://music.apple.com/us/album/im-not-joking/1872842313</v>
+        <v>https://music.apple.com/us/album/prostitute/1894092339</v>
       </c>
       <c r="L25" t="str">
-        <v>i'm not joking - Bleachers</v>
+        <v>PROSTITUTE - Labrinth</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="str">
-        <v>Ruca</v>
+        <v>i'm not joking</v>
       </c>
       <c r="B26" t="str">
         <v/>
       </c>
       <c r="C26" t="str">
-        <v>https://music.apple.com/us/song/ruca/6763671002</v>
+        <v>https://music.apple.com/us/song/im-not-joking/1872842623</v>
       </c>
       <c r="D26" t="str">
         <v>2026-05-04</v>
@@ -1363,36 +1363,36 @@
         <v/>
       </c>
       <c r="F26" t="str">
-        <v>MUDA</v>
+        <v>everyone for ten minutes</v>
       </c>
       <c r="G26" t="str">
-        <v>3:01</v>
+        <v>3:54</v>
       </c>
       <c r="H26" t="str">
-        <v>Carín León</v>
+        <v>Bleachers</v>
       </c>
       <c r="I26" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J26" t="str">
-        <v>https://music.apple.com/us/artist/car%C3%ADn-le%C3%B3n/1370196486</v>
+        <v>https://music.apple.com/us/artist/bleachers/824434533</v>
       </c>
       <c r="K26" t="str">
-        <v>https://music.apple.com/us/album/ruca/1895429814</v>
+        <v>https://music.apple.com/us/album/im-not-joking/1872842313</v>
       </c>
       <c r="L26" t="str">
-        <v>Ruca - Carín León</v>
+        <v>i'm not joking - Bleachers</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="str">
-        <v>Make You Fight</v>
+        <v>Ruca</v>
       </c>
       <c r="B27" t="str">
         <v/>
       </c>
       <c r="C27" t="str">
-        <v>https://music.apple.com/us/song/make-you-fight/1892332386</v>
+        <v>https://music.apple.com/us/song/ruca/6763671002</v>
       </c>
       <c r="D27" t="str">
         <v>2026-05-04</v>
@@ -1401,36 +1401,36 @@
         <v/>
       </c>
       <c r="F27" t="str">
-        <v>Make You Fight - Single</v>
+        <v>MUDA</v>
       </c>
       <c r="G27" t="str">
-        <v>2:55</v>
+        <v>3:01</v>
       </c>
       <c r="H27" t="str">
-        <v>Chris Lake</v>
+        <v>Carín León</v>
       </c>
       <c r="I27" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J27" t="str">
-        <v>https://music.apple.com/us/artist/chris-lake/135067114</v>
+        <v>https://music.apple.com/us/artist/car%C3%ADn-le%C3%B3n/1370196486</v>
       </c>
       <c r="K27" t="str">
-        <v>https://music.apple.com/us/album/make-you-fight/1892332385</v>
+        <v>https://music.apple.com/us/album/ruca/1895429814</v>
       </c>
       <c r="L27" t="str">
-        <v>Make You Fight - Chris Lake</v>
+        <v>Ruca - Carín León</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="str">
-        <v>#N0rth4evr</v>
+        <v>Make You Fight</v>
       </c>
       <c r="B28" t="str">
         <v/>
       </c>
       <c r="C28" t="str">
-        <v>https://music.apple.com/us/song/n0rth4evr/6763302230</v>
+        <v>https://music.apple.com/us/song/make-you-fight/1892332386</v>
       </c>
       <c r="D28" t="str">
         <v>2026-05-04</v>
@@ -1439,36 +1439,36 @@
         <v/>
       </c>
       <c r="F28" t="str">
-        <v>N0rth4evr - EP</v>
+        <v>Make You Fight - Single</v>
       </c>
       <c r="G28" t="str">
-        <v>1:43</v>
+        <v>2:55</v>
       </c>
       <c r="H28" t="str">
-        <v>North West</v>
+        <v>Chris Lake</v>
       </c>
       <c r="I28" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J28" t="str">
-        <v>https://music.apple.com/us/artist/north-west/1729862520</v>
+        <v>https://music.apple.com/us/artist/chris-lake/135067114</v>
       </c>
       <c r="K28" t="str">
-        <v>https://music.apple.com/us/album/n0rth4evr/1895254115</v>
+        <v>https://music.apple.com/us/album/make-you-fight/1892332385</v>
       </c>
       <c r="L28" t="str">
-        <v>#N0rth4evr - North West</v>
+        <v>Make You Fight - Chris Lake</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="str">
-        <v>BOY IN RED</v>
+        <v>#N0rth4evr</v>
       </c>
       <c r="B29" t="str">
         <v/>
       </c>
       <c r="C29" t="str">
-        <v>https://music.apple.com/us/song/boy-in-red/1892543110</v>
+        <v>https://music.apple.com/us/song/n0rth4evr/6763302230</v>
       </c>
       <c r="D29" t="str">
         <v>2026-05-04</v>
@@ -1477,36 +1477,36 @@
         <v/>
       </c>
       <c r="F29" t="str">
-        <v>IT'S BEEN AWFUL</v>
+        <v>N0rth4evr - EP</v>
       </c>
       <c r="G29" t="str">
-        <v>3:09</v>
+        <v>1:43</v>
       </c>
       <c r="H29" t="str">
-        <v>Isaiah Rashad</v>
+        <v>North West</v>
       </c>
       <c r="I29" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J29" t="str">
-        <v>https://music.apple.com/us/artist/isaiah-rashad/605391263</v>
+        <v>https://music.apple.com/us/artist/north-west/1729862520</v>
       </c>
       <c r="K29" t="str">
-        <v>https://music.apple.com/us/album/boy-in-red/1892543099</v>
+        <v>https://music.apple.com/us/album/n0rth4evr/1895254115</v>
       </c>
       <c r="L29" t="str">
-        <v>BOY IN RED - Isaiah Rashad</v>
+        <v>#N0rth4evr - North West</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="str">
-        <v>EA EA EA</v>
+        <v>BOY IN RED</v>
       </c>
       <c r="B30" t="str">
         <v/>
       </c>
       <c r="C30" t="str">
-        <v>https://music.apple.com/us/song/ea-ea-ea/6763438376</v>
+        <v>https://music.apple.com/us/song/boy-in-red/1892543110</v>
       </c>
       <c r="D30" t="str">
         <v>2026-05-04</v>
@@ -1515,36 +1515,36 @@
         <v/>
       </c>
       <c r="F30" t="str">
-        <v>AFTERAFTER - EP</v>
+        <v>IT'S BEEN AWFUL</v>
       </c>
       <c r="G30" t="str">
-        <v>2:42</v>
+        <v>3:09</v>
       </c>
       <c r="H30" t="str">
-        <v>Clave Especial</v>
+        <v>Isaiah Rashad</v>
       </c>
       <c r="I30" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J30" t="str">
-        <v>https://music.apple.com/us/artist/clave-especial/1569749622</v>
+        <v>https://music.apple.com/us/artist/isaiah-rashad/605391263</v>
       </c>
       <c r="K30" t="str">
-        <v>https://music.apple.com/us/album/ea-ea-ea/1895315118</v>
+        <v>https://music.apple.com/us/album/boy-in-red/1892543099</v>
       </c>
       <c r="L30" t="str">
-        <v>EA EA EA - Clave Especial</v>
+        <v>BOY IN RED - Isaiah Rashad</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="str">
-        <v>Just A Man</v>
+        <v>EA EA EA</v>
       </c>
       <c r="B31" t="str">
         <v/>
       </c>
       <c r="C31" t="str">
-        <v>https://music.apple.com/us/song/just-a-man/6762944365</v>
+        <v>https://music.apple.com/us/song/ea-ea-ea/6763438376</v>
       </c>
       <c r="D31" t="str">
         <v>2026-05-04</v>
@@ -1553,36 +1553,36 @@
         <v/>
       </c>
       <c r="F31" t="str">
-        <v>Just A Man - Single</v>
+        <v>AFTERAFTER - EP</v>
       </c>
       <c r="G31" t="str">
-        <v>2:19</v>
+        <v>2:42</v>
       </c>
       <c r="H31" t="str">
-        <v>Claire Rosinkranz</v>
+        <v>Clave Especial</v>
       </c>
       <c r="I31" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J31" t="str">
-        <v>https://music.apple.com/us/artist/claire-rosinkranz/1483262366</v>
+        <v>https://music.apple.com/us/artist/clave-especial/1569749622</v>
       </c>
       <c r="K31" t="str">
-        <v>https://music.apple.com/us/album/just-a-man/1895089709</v>
+        <v>https://music.apple.com/us/album/ea-ea-ea/1895315118</v>
       </c>
       <c r="L31" t="str">
-        <v>Just A Man - Claire Rosinkranz</v>
+        <v>EA EA EA - Clave Especial</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="str">
-        <v>The Observer</v>
+        <v>Just A Man</v>
       </c>
       <c r="B32" t="str">
         <v/>
       </c>
       <c r="C32" t="str">
-        <v>https://music.apple.com/us/song/the-observer/1891982314</v>
+        <v>https://music.apple.com/us/song/just-a-man/6762944365</v>
       </c>
       <c r="D32" t="str">
         <v>2026-05-04</v>
@@ -1591,36 +1591,36 @@
         <v/>
       </c>
       <c r="F32" t="str">
-        <v>How Did I Get Here? (Extended Edition)</v>
+        <v>Just A Man - Single</v>
       </c>
       <c r="G32" t="str">
-        <v>2:50</v>
+        <v>2:19</v>
       </c>
       <c r="H32" t="str">
-        <v>Louis Tomlinson</v>
+        <v>Claire Rosinkranz</v>
       </c>
       <c r="I32" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J32" t="str">
-        <v>https://music.apple.com/us/artist/louis-tomlinson/471260295</v>
+        <v>https://music.apple.com/us/artist/claire-rosinkranz/1483262366</v>
       </c>
       <c r="K32" t="str">
-        <v>https://music.apple.com/us/album/the-observer/1891982287</v>
+        <v>https://music.apple.com/us/album/just-a-man/1895089709</v>
       </c>
       <c r="L32" t="str">
-        <v>The Observer - Louis Tomlinson</v>
+        <v>Just A Man - Claire Rosinkranz</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="str">
-        <v>Heroine</v>
+        <v>The Observer</v>
       </c>
       <c r="B33" t="str">
         <v/>
       </c>
       <c r="C33" t="str">
-        <v>https://music.apple.com/us/song/heroine/6762693177</v>
+        <v>https://music.apple.com/us/song/the-observer/1891982314</v>
       </c>
       <c r="D33" t="str">
         <v>2026-05-04</v>
@@ -1629,36 +1629,36 @@
         <v/>
       </c>
       <c r="F33" t="str">
-        <v>Heroine - Single</v>
+        <v>How Did I Get Here? (Extended Edition)</v>
       </c>
       <c r="G33" t="str">
-        <v>2:35</v>
+        <v>2:50</v>
       </c>
       <c r="H33" t="str">
-        <v>Maroon 5</v>
+        <v>Louis Tomlinson</v>
       </c>
       <c r="I33" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J33" t="str">
-        <v>https://music.apple.com/us/artist/maroon-5/1798556</v>
+        <v>https://music.apple.com/us/artist/louis-tomlinson/471260295</v>
       </c>
       <c r="K33" t="str">
-        <v>https://music.apple.com/us/album/heroine/1894966605</v>
+        <v>https://music.apple.com/us/album/the-observer/1891982287</v>
       </c>
       <c r="L33" t="str">
-        <v>Heroine - Maroon 5</v>
+        <v>The Observer - Louis Tomlinson</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="str">
-        <v>Do Me Right</v>
+        <v>Heroine</v>
       </c>
       <c r="B34" t="str">
         <v/>
       </c>
       <c r="C34" t="str">
-        <v>https://music.apple.com/us/song/do-me-right/6764667658</v>
+        <v>https://music.apple.com/us/song/heroine/6762693177</v>
       </c>
       <c r="D34" t="str">
         <v>2026-05-04</v>
@@ -1667,36 +1667,36 @@
         <v/>
       </c>
       <c r="F34" t="str">
-        <v>FANTASYLAND</v>
+        <v>Heroine - Single</v>
       </c>
       <c r="G34" t="str">
-        <v>4:10</v>
+        <v>2:35</v>
       </c>
       <c r="H34" t="str">
-        <v>MR. FANTASY</v>
+        <v>Maroon 5</v>
       </c>
       <c r="I34" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J34" t="str">
-        <v>https://music.apple.com/us/artist/mr-fantasy/1834481769</v>
+        <v>https://music.apple.com/us/artist/maroon-5/1798556</v>
       </c>
       <c r="K34" t="str">
-        <v>https://music.apple.com/us/album/do-me-right/1895871261</v>
+        <v>https://music.apple.com/us/album/heroine/1894966605</v>
       </c>
       <c r="L34" t="str">
-        <v>Do Me Right - MR. FANTASY</v>
+        <v>Heroine - Maroon 5</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="str">
-        <v>It's Me</v>
+        <v>Do Me Right</v>
       </c>
       <c r="B35" t="str">
         <v/>
       </c>
       <c r="C35" t="str">
-        <v>https://music.apple.com/us/song/its-me/1887194026</v>
+        <v>https://music.apple.com/us/song/do-me-right/6764667658</v>
       </c>
       <c r="D35" t="str">
         <v>2026-05-04</v>
@@ -1705,36 +1705,36 @@
         <v/>
       </c>
       <c r="F35" t="str">
-        <v>MAMIHLAPINATAPAI - EP</v>
+        <v>FANTASYLAND</v>
       </c>
       <c r="G35" t="str">
-        <v>2:18</v>
+        <v>4:10</v>
       </c>
       <c r="H35" t="str">
-        <v>ILLIT</v>
+        <v>MR. FANTASY</v>
       </c>
       <c r="I35" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J35" t="str">
-        <v>https://music.apple.com/us/artist/illit/1734551937</v>
+        <v>https://music.apple.com/us/artist/mr-fantasy/1834481769</v>
       </c>
       <c r="K35" t="str">
-        <v>https://music.apple.com/us/album/its-me/1887194024</v>
+        <v>https://music.apple.com/us/album/do-me-right/1895871261</v>
       </c>
       <c r="L35" t="str">
-        <v>It's Me - ILLIT</v>
+        <v>Do Me Right - MR. FANTASY</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="str">
-        <v>the precipice</v>
+        <v>It's Me</v>
       </c>
       <c r="B36" t="str">
         <v/>
       </c>
       <c r="C36" t="str">
-        <v>https://music.apple.com/us/song/the-precipice/1891830326</v>
+        <v>https://music.apple.com/us/song/its-me/1887194026</v>
       </c>
       <c r="D36" t="str">
         <v>2026-05-04</v>
@@ -1743,36 +1743,36 @@
         <v/>
       </c>
       <c r="F36" t="str">
-        <v>untitled.jpeg - EP</v>
+        <v>MAMIHLAPINATAPAI - EP</v>
       </c>
       <c r="G36" t="str">
-        <v>3:52</v>
+        <v>2:18</v>
       </c>
       <c r="H36" t="str">
-        <v>Jessie Mazin</v>
+        <v>ILLIT</v>
       </c>
       <c r="I36" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J36" t="str">
-        <v>https://music.apple.com/us/artist/jessie-mazin/1887707056</v>
+        <v>https://music.apple.com/us/artist/illit/1734551937</v>
       </c>
       <c r="K36" t="str">
-        <v>https://music.apple.com/us/album/the-precipice/1891830323</v>
+        <v>https://music.apple.com/us/album/its-me/1887194024</v>
       </c>
       <c r="L36" t="str">
-        <v>the precipice - Jessie Mazin</v>
+        <v>It's Me - ILLIT</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="str">
-        <v>Hello Lonesome</v>
+        <v>the precipice</v>
       </c>
       <c r="B37" t="str">
         <v/>
       </c>
       <c r="C37" t="str">
-        <v>https://music.apple.com/us/song/hello-lonesome/1892466003</v>
+        <v>https://music.apple.com/us/song/the-precipice/1891830326</v>
       </c>
       <c r="D37" t="str">
         <v>2026-05-04</v>
@@ -1781,36 +1781,36 @@
         <v/>
       </c>
       <c r="F37" t="str">
-        <v>Banks Of The Trinity</v>
+        <v>untitled.jpeg - EP</v>
       </c>
       <c r="G37" t="str">
-        <v>2:58</v>
+        <v>3:52</v>
       </c>
       <c r="H37" t="str">
-        <v>Cody Johnson</v>
+        <v>Jessie Mazin</v>
       </c>
       <c r="I37" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J37" t="str">
-        <v>https://music.apple.com/us/artist/cody-johnson/331459657</v>
+        <v>https://music.apple.com/us/artist/jessie-mazin/1887707056</v>
       </c>
       <c r="K37" t="str">
-        <v>https://music.apple.com/us/album/hello-lonesome/1892465981</v>
+        <v>https://music.apple.com/us/album/the-precipice/1891830323</v>
       </c>
       <c r="L37" t="str">
-        <v>Hello Lonesome - Cody Johnson</v>
+        <v>the precipice - Jessie Mazin</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="str">
-        <v>TRIPPIN (Opera Edit)</v>
+        <v>Hello Lonesome</v>
       </c>
       <c r="B38" t="str">
         <v/>
       </c>
       <c r="C38" t="str">
-        <v>https://music.apple.com/us/song/trippin-opera-edit/6764648776</v>
+        <v>https://music.apple.com/us/song/hello-lonesome/1892466003</v>
       </c>
       <c r="D38" t="str">
         <v>2026-05-04</v>
@@ -1819,36 +1819,36 @@
         <v/>
       </c>
       <c r="F38" t="str">
-        <v>TRIPPIN (Opera Edit) - Single</v>
+        <v>Banks Of The Trinity</v>
       </c>
       <c r="G38" t="str">
-        <v>2:21</v>
+        <v>2:58</v>
       </c>
       <c r="H38" t="str">
-        <v>BUNT.</v>
+        <v>Cody Johnson</v>
       </c>
       <c r="I38" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J38" t="str">
-        <v>https://music.apple.com/us/artist/bunt/1436090348</v>
+        <v>https://music.apple.com/us/artist/cody-johnson/331459657</v>
       </c>
       <c r="K38" t="str">
-        <v>https://music.apple.com/us/album/trippin-opera-edit/1895863999</v>
+        <v>https://music.apple.com/us/album/hello-lonesome/1892465981</v>
       </c>
       <c r="L38" t="str">
-        <v>TRIPPIN (Opera Edit) - BUNT.</v>
+        <v>Hello Lonesome - Cody Johnson</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="str">
-        <v>The Mandalorian and Grogu (Boys Noize Remix) [From "Star Wars: The Mandalorian and Grogu"]</v>
+        <v>TRIPPIN (Opera Edit)</v>
       </c>
       <c r="B39" t="str">
         <v/>
       </c>
       <c r="C39" t="str">
-        <v>https://music.apple.com/us/song/the-mandalorian-and-grogu-boys-noize-remix-from-star/6764131630</v>
+        <v>https://music.apple.com/us/song/trippin-opera-edit/6764648776</v>
       </c>
       <c r="D39" t="str">
         <v>2026-05-04</v>
@@ -1857,36 +1857,36 @@
         <v/>
       </c>
       <c r="F39" t="str">
-        <v>The Mandalorian and Grogu (Boys Noize Remix) [From "Star Wars: The Mandalorian and Grogu"] - Single</v>
+        <v>TRIPPIN (Opera Edit) - Single</v>
       </c>
       <c r="G39" t="str">
-        <v>5:54</v>
+        <v>2:21</v>
       </c>
       <c r="H39" t="str">
-        <v>Ludwig Göransson</v>
+        <v>BUNT.</v>
       </c>
       <c r="I39" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J39" t="str">
-        <v>https://music.apple.com/us/artist/ludwig-g%C3%B6ransson/391832320</v>
+        <v>https://music.apple.com/us/artist/bunt/1436090348</v>
       </c>
       <c r="K39" t="str">
-        <v>https://music.apple.com/us/album/the-mandalorian-and-grogu-boys-noize-remix-from-star/1895653302</v>
+        <v>https://music.apple.com/us/album/trippin-opera-edit/1895863999</v>
       </c>
       <c r="L39" t="str">
-        <v>The Mandalorian and Grogu (Boys Noize Remix) [From "Star Wars: The Mandalorian and Grogu"] - Ludwig Göransson</v>
+        <v>TRIPPIN (Opera Edit) - BUNT.</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="str">
-        <v>Blow My Mind (CA7RIEL &amp; Paco Amoroso Version)</v>
+        <v>The Mandalorian and Grogu (Boys Noize Remix) [From "Star Wars: The Mandalorian and Grogu"]</v>
       </c>
       <c r="B40" t="str">
         <v/>
       </c>
       <c r="C40" t="str">
-        <v>https://music.apple.com/us/song/blow-my-mind-ca7riel-paco-amoroso-version/1894344140</v>
+        <v>https://music.apple.com/us/song/the-mandalorian-and-grogu-boys-noize-remix-from-star/6764131630</v>
       </c>
       <c r="D40" t="str">
         <v>2026-05-04</v>
@@ -1895,36 +1895,36 @@
         <v/>
       </c>
       <c r="F40" t="str">
-        <v>Blow My Mind (CA7RIEL &amp; Paco Amoroso Version) - Single</v>
+        <v>The Mandalorian and Grogu (Boys Noize Remix) [From "Star Wars: The Mandalorian and Grogu"] - Single</v>
       </c>
       <c r="G40" t="str">
-        <v>2:49</v>
+        <v>5:54</v>
       </c>
       <c r="H40" t="str">
-        <v>Robyn</v>
+        <v>Ludwig Göransson</v>
       </c>
       <c r="I40" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J40" t="str">
-        <v>https://music.apple.com/us/artist/robyn/535211</v>
+        <v>https://music.apple.com/us/artist/ludwig-g%C3%B6ransson/391832320</v>
       </c>
       <c r="K40" t="str">
-        <v>https://music.apple.com/us/album/blow-my-mind-ca7riel-paco-amoroso-version/1894344139</v>
+        <v>https://music.apple.com/us/album/the-mandalorian-and-grogu-boys-noize-remix-from-star/1895653302</v>
       </c>
       <c r="L40" t="str">
-        <v>Blow My Mind (CA7RIEL &amp; Paco Amoroso Version) - Robyn</v>
+        <v>The Mandalorian and Grogu (Boys Noize Remix) [From "Star Wars: The Mandalorian and Grogu"] - Ludwig Göransson</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="str">
-        <v>Bring That Body</v>
+        <v>Blow My Mind (CA7RIEL &amp; Paco Amoroso Version)</v>
       </c>
       <c r="B41" t="str">
         <v/>
       </c>
       <c r="C41" t="str">
-        <v>https://music.apple.com/us/song/bring-that-body/6764009310</v>
+        <v>https://music.apple.com/us/song/blow-my-mind-ca7riel-paco-amoroso-version/1894344140</v>
       </c>
       <c r="D41" t="str">
         <v>2026-05-04</v>
@@ -1933,36 +1933,36 @@
         <v/>
       </c>
       <c r="F41" t="str">
-        <v>Bring That Body - Single</v>
+        <v>Blow My Mind (CA7RIEL &amp; Paco Amoroso Version) - Single</v>
       </c>
       <c r="G41" t="str">
-        <v>3:34</v>
+        <v>2:49</v>
       </c>
       <c r="H41" t="str">
-        <v>The-Dream</v>
+        <v>Robyn</v>
       </c>
       <c r="I41" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J41" t="str">
-        <v>https://music.apple.com/us/artist/the-dream/259369321</v>
+        <v>https://music.apple.com/us/artist/robyn/535211</v>
       </c>
       <c r="K41" t="str">
-        <v>https://music.apple.com/us/album/bring-that-body/1895596731</v>
+        <v>https://music.apple.com/us/album/blow-my-mind-ca7riel-paco-amoroso-version/1894344139</v>
       </c>
       <c r="L41" t="str">
-        <v>Bring That Body - The-Dream</v>
+        <v>Blow My Mind (CA7RIEL &amp; Paco Amoroso Version) - Robyn</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="str">
-        <v>STAR</v>
+        <v>Bring That Body</v>
       </c>
       <c r="B42" t="str">
         <v/>
       </c>
       <c r="C42" t="str">
-        <v>https://music.apple.com/us/song/star/1891845608</v>
+        <v>https://music.apple.com/us/song/bring-that-body/6764009310</v>
       </c>
       <c r="D42" t="str">
         <v>2026-05-04</v>
@@ -1971,36 +1971,36 @@
         <v/>
       </c>
       <c r="F42" t="str">
-        <v>STAR</v>
+        <v>Bring That Body - Single</v>
       </c>
       <c r="G42" t="str">
-        <v>2:49</v>
+        <v>3:34</v>
       </c>
       <c r="H42" t="str">
-        <v>Tombochio</v>
+        <v>The-Dream</v>
       </c>
       <c r="I42" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J42" t="str">
-        <v>https://music.apple.com/us/artist/tombochio/1570164065</v>
+        <v>https://music.apple.com/us/artist/the-dream/259369321</v>
       </c>
       <c r="K42" t="str">
-        <v>https://music.apple.com/us/album/star/1891845604</v>
+        <v>https://music.apple.com/us/album/bring-that-body/1895596731</v>
       </c>
       <c r="L42" t="str">
-        <v>STAR - Tombochio</v>
+        <v>Bring That Body - The-Dream</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="str">
-        <v>What’s A Little Rain</v>
+        <v>STAR</v>
       </c>
       <c r="B43" t="str">
         <v/>
       </c>
       <c r="C43" t="str">
-        <v>https://music.apple.com/us/song/whats-a-little-rain/1885061171</v>
+        <v>https://music.apple.com/us/song/star/1891845608</v>
       </c>
       <c r="D43" t="str">
         <v>2026-05-04</v>
@@ -2009,36 +2009,36 @@
         <v/>
       </c>
       <c r="F43" t="str">
-        <v>Deep Blue</v>
+        <v>STAR</v>
       </c>
       <c r="G43" t="str">
-        <v>3:37</v>
+        <v>2:49</v>
       </c>
       <c r="H43" t="str">
-        <v>ERNEST</v>
+        <v>Tombochio</v>
       </c>
       <c r="I43" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J43" t="str">
-        <v>https://music.apple.com/us/artist/ernest/1450042443</v>
+        <v>https://music.apple.com/us/artist/tombochio/1570164065</v>
       </c>
       <c r="K43" t="str">
-        <v>https://music.apple.com/us/album/whats-a-little-rain/1885061168</v>
+        <v>https://music.apple.com/us/album/star/1891845604</v>
       </c>
       <c r="L43" t="str">
-        <v>What’s A Little Rain - ERNEST</v>
+        <v>STAR - Tombochio</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="str">
-        <v>Evergreen</v>
+        <v>What’s A Little Rain</v>
       </c>
       <c r="B44" t="str">
         <v/>
       </c>
       <c r="C44" t="str">
-        <v>https://music.apple.com/us/song/evergreen/1866700315</v>
+        <v>https://music.apple.com/us/song/whats-a-little-rain/1885061171</v>
       </c>
       <c r="D44" t="str">
         <v>2026-05-04</v>
@@ -2047,36 +2047,36 @@
         <v/>
       </c>
       <c r="F44" t="str">
-        <v>Victory Garden</v>
+        <v>Deep Blue</v>
       </c>
       <c r="G44" t="str">
-        <v>3:41</v>
+        <v>3:37</v>
       </c>
       <c r="H44" t="str">
-        <v>Young the Giant</v>
+        <v>ERNEST</v>
       </c>
       <c r="I44" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J44" t="str">
-        <v>https://music.apple.com/us/artist/young-the-giant/394582977</v>
+        <v>https://music.apple.com/us/artist/ernest/1450042443</v>
       </c>
       <c r="K44" t="str">
-        <v>https://music.apple.com/us/album/evergreen/1866700309</v>
+        <v>https://music.apple.com/us/album/whats-a-little-rain/1885061168</v>
       </c>
       <c r="L44" t="str">
-        <v>Evergreen - Young the Giant</v>
+        <v>What’s A Little Rain - ERNEST</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="str">
-        <v>She Does It Right</v>
+        <v>Evergreen</v>
       </c>
       <c r="B45" t="str">
         <v/>
       </c>
       <c r="C45" t="str">
-        <v>https://music.apple.com/us/song/she-does-it-right/1873477957</v>
+        <v>https://music.apple.com/us/song/evergreen/1866700315</v>
       </c>
       <c r="D45" t="str">
         <v>2026-05-04</v>
@@ -2085,36 +2085,36 @@
         <v/>
       </c>
       <c r="F45" t="str">
-        <v>Peaches!</v>
+        <v>Victory Garden</v>
       </c>
       <c r="G45" t="str">
-        <v>3:43</v>
+        <v>3:41</v>
       </c>
       <c r="H45" t="str">
-        <v>The Black Keys</v>
+        <v>Young the Giant</v>
       </c>
       <c r="I45" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J45" t="str">
-        <v>https://music.apple.com/us/artist/the-black-keys/5893059</v>
+        <v>https://music.apple.com/us/artist/young-the-giant/394582977</v>
       </c>
       <c r="K45" t="str">
-        <v>https://music.apple.com/us/album/she-does-it-right/1873477948</v>
+        <v>https://music.apple.com/us/album/evergreen/1866700309</v>
       </c>
       <c r="L45" t="str">
-        <v>She Does It Right - The Black Keys</v>
+        <v>Evergreen - Young the Giant</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="str">
-        <v>Punching the Flowers</v>
+        <v>She Does It Right</v>
       </c>
       <c r="B46" t="str">
         <v/>
       </c>
       <c r="C46" t="str">
-        <v>https://music.apple.com/us/song/punching-the-flowers/1878362636</v>
+        <v>https://music.apple.com/us/song/she-does-it-right/1873477957</v>
       </c>
       <c r="D46" t="str">
         <v>2026-05-04</v>
@@ -2123,36 +2123,36 @@
         <v/>
       </c>
       <c r="F46" t="str">
-        <v>I Built You A Tower</v>
+        <v>Peaches!</v>
       </c>
       <c r="G46" t="str">
-        <v>3:11</v>
+        <v>3:43</v>
       </c>
       <c r="H46" t="str">
-        <v>Death Cab for Cutie</v>
+        <v>The Black Keys</v>
       </c>
       <c r="I46" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J46" t="str">
-        <v>https://music.apple.com/us/artist/death-cab-for-cutie/5448636</v>
+        <v>https://music.apple.com/us/artist/the-black-keys/5893059</v>
       </c>
       <c r="K46" t="str">
-        <v>https://music.apple.com/us/album/punching-the-flowers/1878362451</v>
+        <v>https://music.apple.com/us/album/she-does-it-right/1873477948</v>
       </c>
       <c r="L46" t="str">
-        <v>Punching the Flowers - Death Cab for Cutie</v>
+        <v>She Does It Right - The Black Keys</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="str">
-        <v>How Did You Know</v>
+        <v>Punching the Flowers</v>
       </c>
       <c r="B47" t="str">
         <v/>
       </c>
       <c r="C47" t="str">
-        <v>https://music.apple.com/us/song/how-did-you-know/1888553137</v>
+        <v>https://music.apple.com/us/song/punching-the-flowers/1878362636</v>
       </c>
       <c r="D47" t="str">
         <v>2026-05-04</v>
@@ -2161,36 +2161,36 @@
         <v/>
       </c>
       <c r="F47" t="str">
-        <v>California Sunrise (10th Anniversary Edition)</v>
+        <v>I Built You A Tower</v>
       </c>
       <c r="G47" t="str">
-        <v>3:16</v>
+        <v>3:11</v>
       </c>
       <c r="H47" t="str">
-        <v>Jon Pardi</v>
+        <v>Death Cab for Cutie</v>
       </c>
       <c r="I47" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J47" t="str">
-        <v>https://music.apple.com/us/artist/jon-pardi/371085834</v>
+        <v>https://music.apple.com/us/artist/death-cab-for-cutie/5448636</v>
       </c>
       <c r="K47" t="str">
-        <v>https://music.apple.com/us/album/how-did-you-know/1888552935</v>
+        <v>https://music.apple.com/us/album/punching-the-flowers/1878362451</v>
       </c>
       <c r="L47" t="str">
-        <v>How Did You Know - Jon Pardi</v>
+        <v>Punching the Flowers - Death Cab for Cutie</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="str">
-        <v>Summer Breeze</v>
+        <v>How Did You Know</v>
       </c>
       <c r="B48" t="str">
         <v/>
       </c>
       <c r="C48" t="str">
-        <v>https://music.apple.com/us/song/summer-breeze/6763360727</v>
+        <v>https://music.apple.com/us/song/how-did-you-know/1888553137</v>
       </c>
       <c r="D48" t="str">
         <v>2026-05-04</v>
@@ -2199,36 +2199,36 @@
         <v/>
       </c>
       <c r="F48" t="str">
-        <v>flow state</v>
+        <v>California Sunrise (10th Anniversary Edition)</v>
       </c>
       <c r="G48" t="str">
-        <v>4:00</v>
+        <v>3:16</v>
       </c>
       <c r="H48" t="str">
-        <v>Keith Urban</v>
+        <v>Jon Pardi</v>
       </c>
       <c r="I48" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J48" t="str">
-        <v>https://music.apple.com/us/artist/keith-urban/549836</v>
+        <v>https://music.apple.com/us/artist/jon-pardi/371085834</v>
       </c>
       <c r="K48" t="str">
-        <v>https://music.apple.com/us/album/summer-breeze/1895279513</v>
+        <v>https://music.apple.com/us/album/how-did-you-know/1888552935</v>
       </c>
       <c r="L48" t="str">
-        <v>Summer Breeze - Keith Urban</v>
+        <v>How Did You Know - Jon Pardi</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="str">
-        <v>Sound of a Woman</v>
+        <v>Summer Breeze</v>
       </c>
       <c r="B49" t="str">
         <v/>
       </c>
       <c r="C49" t="str">
-        <v>https://music.apple.com/us/song/sound-of-a-woman/1859763367</v>
+        <v>https://music.apple.com/us/song/summer-breeze/6763360727</v>
       </c>
       <c r="D49" t="str">
         <v>2026-05-04</v>
@@ -2237,36 +2237,36 @@
         <v/>
       </c>
       <c r="F49" t="str">
-        <v>Sound of a Woman</v>
+        <v>flow state</v>
       </c>
       <c r="G49" t="str">
-        <v>4:27</v>
+        <v>4:00</v>
       </c>
       <c r="H49" t="str">
-        <v>Rita Wilson</v>
+        <v>Keith Urban</v>
       </c>
       <c r="I49" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J49" t="str">
-        <v>https://music.apple.com/us/artist/rita-wilson/270048575</v>
+        <v>https://music.apple.com/us/artist/keith-urban/549836</v>
       </c>
       <c r="K49" t="str">
-        <v>https://music.apple.com/us/album/sound-of-a-woman/1859763034</v>
+        <v>https://music.apple.com/us/album/summer-breeze/1895279513</v>
       </c>
       <c r="L49" t="str">
-        <v>Sound of a Woman - Rita Wilson</v>
+        <v>Summer Breeze - Keith Urban</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="str">
-        <v>My Life</v>
+        <v>Sound of a Woman</v>
       </c>
       <c r="B50" t="str">
         <v/>
       </c>
       <c r="C50" t="str">
-        <v>https://music.apple.com/us/song/my-life/1893157347</v>
+        <v>https://music.apple.com/us/song/sound-of-a-woman/1859763367</v>
       </c>
       <c r="D50" t="str">
         <v>2026-05-04</v>
@@ -2275,36 +2275,36 @@
         <v/>
       </c>
       <c r="F50" t="str">
-        <v>BERNARR.</v>
+        <v>Sound of a Woman</v>
       </c>
       <c r="G50" t="str">
-        <v>3:31</v>
+        <v>4:27</v>
       </c>
       <c r="H50" t="str">
-        <v>Durand Bernarr</v>
+        <v>Rita Wilson</v>
       </c>
       <c r="I50" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J50" t="str">
-        <v>https://music.apple.com/us/artist/durand-bernarr/584124023</v>
+        <v>https://music.apple.com/us/artist/rita-wilson/270048575</v>
       </c>
       <c r="K50" t="str">
-        <v>https://music.apple.com/us/album/my-life/1893156957</v>
+        <v>https://music.apple.com/us/album/sound-of-a-woman/1859763034</v>
       </c>
       <c r="L50" t="str">
-        <v>My Life - Durand Bernarr</v>
+        <v>Sound of a Woman - Rita Wilson</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="str">
-        <v>Ribcage</v>
+        <v>My Life</v>
       </c>
       <c r="B51" t="str">
         <v/>
       </c>
       <c r="C51" t="str">
-        <v>https://music.apple.com/us/song/ribcage/1893155593</v>
+        <v>https://music.apple.com/us/song/my-life/1893157347</v>
       </c>
       <c r="D51" t="str">
         <v>2026-05-04</v>
@@ -2313,36 +2313,36 @@
         <v/>
       </c>
       <c r="F51" t="str">
-        <v>Ribcage - Single</v>
+        <v>BERNARR.</v>
       </c>
       <c r="G51" t="str">
-        <v>3:00</v>
+        <v>3:31</v>
       </c>
       <c r="H51" t="str">
-        <v>Bella Poarch</v>
+        <v>Durand Bernarr</v>
       </c>
       <c r="I51" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J51" t="str">
-        <v>https://music.apple.com/us/artist/bella-poarch/1567245769</v>
+        <v>https://music.apple.com/us/artist/durand-bernarr/584124023</v>
       </c>
       <c r="K51" t="str">
-        <v>https://music.apple.com/us/album/ribcage/1893155591</v>
+        <v>https://music.apple.com/us/album/my-life/1893156957</v>
       </c>
       <c r="L51" t="str">
-        <v>Ribcage - Bella Poarch</v>
+        <v>My Life - Durand Bernarr</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="str">
-        <v>i loved you then</v>
+        <v>Ribcage</v>
       </c>
       <c r="B52" t="str">
         <v/>
       </c>
       <c r="C52" t="str">
-        <v>https://music.apple.com/us/song/i-loved-you-then/1878232821</v>
+        <v>https://music.apple.com/us/song/ribcage/1893155593</v>
       </c>
       <c r="D52" t="str">
         <v>2026-05-04</v>
@@ -2351,36 +2351,36 @@
         <v/>
       </c>
       <c r="F52" t="str">
-        <v>I HOPE THIS HELPS</v>
+        <v>Ribcage - Single</v>
       </c>
       <c r="G52" t="str">
-        <v>3:42</v>
+        <v>3:00</v>
       </c>
       <c r="H52" t="str">
-        <v>Alana Springsteen</v>
+        <v>Bella Poarch</v>
       </c>
       <c r="I52" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J52" t="str">
-        <v>https://music.apple.com/us/artist/alana-springsteen/1309335606</v>
+        <v>https://music.apple.com/us/artist/bella-poarch/1567245769</v>
       </c>
       <c r="K52" t="str">
-        <v>https://music.apple.com/us/album/i-loved-you-then/1878232194</v>
+        <v>https://music.apple.com/us/album/ribcage/1893155591</v>
       </c>
       <c r="L52" t="str">
-        <v>i loved you then - Alana Springsteen</v>
+        <v>Ribcage - Bella Poarch</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="str">
-        <v>I'll Let You Finish</v>
+        <v>i loved you then</v>
       </c>
       <c r="B53" t="str">
         <v/>
       </c>
       <c r="C53" t="str">
-        <v>https://music.apple.com/us/song/ill-let-you-finish/1891844342</v>
+        <v>https://music.apple.com/us/song/i-loved-you-then/1878232821</v>
       </c>
       <c r="D53" t="str">
         <v>2026-05-04</v>
@@ -2389,36 +2389,36 @@
         <v/>
       </c>
       <c r="F53" t="str">
-        <v>Fire From The Hip</v>
+        <v>I HOPE THIS HELPS</v>
       </c>
       <c r="G53" t="str">
-        <v>3:54</v>
+        <v>3:42</v>
       </c>
       <c r="H53" t="str">
-        <v>Finn Wolfhard</v>
+        <v>Alana Springsteen</v>
       </c>
       <c r="I53" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J53" t="str">
-        <v>https://music.apple.com/us/artist/finn-wolfhard/1275324142</v>
+        <v>https://music.apple.com/us/artist/alana-springsteen/1309335606</v>
       </c>
       <c r="K53" t="str">
-        <v>https://music.apple.com/us/album/ill-let-you-finish/1891844033</v>
+        <v>https://music.apple.com/us/album/i-loved-you-then/1878232194</v>
       </c>
       <c r="L53" t="str">
-        <v>I'll Let You Finish - Finn Wolfhard</v>
+        <v>i loved you then - Alana Springsteen</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="str">
-        <v>It Gets Me Through</v>
+        <v>I'll Let You Finish</v>
       </c>
       <c r="B54" t="str">
         <v/>
       </c>
       <c r="C54" t="str">
-        <v>https://music.apple.com/us/song/it-gets-me-through/1884798927</v>
+        <v>https://music.apple.com/us/song/ill-let-you-finish/1891844342</v>
       </c>
       <c r="D54" t="str">
         <v>2026-05-04</v>
@@ -2427,36 +2427,36 @@
         <v/>
       </c>
       <c r="F54" t="str">
-        <v>Original Sound (Original Motion Picture Soundtrack)</v>
+        <v>Fire From The Hip</v>
       </c>
       <c r="G54" t="str">
-        <v>2:53</v>
+        <v>3:54</v>
       </c>
       <c r="H54" t="str">
-        <v>Laura Marano</v>
+        <v>Finn Wolfhard</v>
       </c>
       <c r="I54" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J54" t="str">
-        <v>https://music.apple.com/us/artist/laura-marano/357181332</v>
+        <v>https://music.apple.com/us/artist/finn-wolfhard/1275324142</v>
       </c>
       <c r="K54" t="str">
-        <v>https://music.apple.com/us/album/it-gets-me-through/1884798598</v>
+        <v>https://music.apple.com/us/album/ill-let-you-finish/1891844033</v>
       </c>
       <c r="L54" t="str">
-        <v>It Gets Me Through - Laura Marano</v>
+        <v>I'll Let You Finish - Finn Wolfhard</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="str">
-        <v>The Author</v>
+        <v>It Gets Me Through</v>
       </c>
       <c r="B55" t="str">
         <v/>
       </c>
       <c r="C55" t="str">
-        <v>https://music.apple.com/us/song/the-author/6763327641</v>
+        <v>https://music.apple.com/us/song/it-gets-me-through/1884798927</v>
       </c>
       <c r="D55" t="str">
         <v>2026-05-04</v>
@@ -2465,36 +2465,36 @@
         <v/>
       </c>
       <c r="F55" t="str">
-        <v>The Author - Single</v>
+        <v>Original Sound (Original Motion Picture Soundtrack)</v>
       </c>
       <c r="G55" t="str">
-        <v>4:36</v>
+        <v>2:53</v>
       </c>
       <c r="H55" t="str">
-        <v>Brandon Lake</v>
+        <v>Laura Marano</v>
       </c>
       <c r="I55" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J55" t="str">
-        <v>https://music.apple.com/us/artist/brandon-lake/1050382282</v>
+        <v>https://music.apple.com/us/artist/laura-marano/357181332</v>
       </c>
       <c r="K55" t="str">
-        <v>https://music.apple.com/us/album/the-author/1895265952</v>
+        <v>https://music.apple.com/us/album/it-gets-me-through/1884798598</v>
       </c>
       <c r="L55" t="str">
-        <v>The Author - Brandon Lake</v>
+        <v>It Gets Me Through - Laura Marano</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="str">
-        <v>Want Me Back (feat. Tors)</v>
+        <v>The Author</v>
       </c>
       <c r="B56" t="str">
         <v/>
       </c>
       <c r="C56" t="str">
-        <v>https://music.apple.com/us/song/want-me-back-feat-tors/1889370756</v>
+        <v>https://music.apple.com/us/song/the-author/6763327641</v>
       </c>
       <c r="D56" t="str">
         <v>2026-05-04</v>
@@ -2503,36 +2503,36 @@
         <v/>
       </c>
       <c r="F56" t="str">
-        <v>Want Me Back (feat. Tors) - Single</v>
+        <v>The Author - Single</v>
       </c>
       <c r="G56" t="str">
-        <v>3:44</v>
+        <v>4:36</v>
       </c>
       <c r="H56" t="str">
-        <v>Trousdale</v>
+        <v>Brandon Lake</v>
       </c>
       <c r="I56" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J56" t="str">
-        <v>https://music.apple.com/us/artist/trousdale/1534241692</v>
+        <v>https://music.apple.com/us/artist/brandon-lake/1050382282</v>
       </c>
       <c r="K56" t="str">
-        <v>https://music.apple.com/us/album/want-me-back-feat-tors/1889370752</v>
+        <v>https://music.apple.com/us/album/the-author/1895265952</v>
       </c>
       <c r="L56" t="str">
-        <v>Want Me Back (feat. Tors) - Trousdale</v>
+        <v>The Author - Brandon Lake</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="str">
-        <v>RUIN</v>
+        <v>Want Me Back (feat. Tors)</v>
       </c>
       <c r="B57" t="str">
         <v/>
       </c>
       <c r="C57" t="str">
-        <v>https://music.apple.com/us/song/ruin/1886537117</v>
+        <v>https://music.apple.com/us/song/want-me-back-feat-tors/1889370756</v>
       </c>
       <c r="D57" t="str">
         <v>2026-05-04</v>
@@ -2541,36 +2541,36 @@
         <v/>
       </c>
       <c r="F57" t="str">
-        <v>ADDENDUM</v>
+        <v>Want Me Back (feat. Tors) - Single</v>
       </c>
       <c r="G57" t="str">
-        <v>3:23</v>
+        <v>3:44</v>
       </c>
       <c r="H57" t="str">
-        <v>HEALTH</v>
+        <v>Trousdale</v>
       </c>
       <c r="I57" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J57" t="str">
-        <v>https://music.apple.com/us/artist/health/317478211</v>
+        <v>https://music.apple.com/us/artist/trousdale/1534241692</v>
       </c>
       <c r="K57" t="str">
-        <v>https://music.apple.com/us/album/ruin/1886536873</v>
+        <v>https://music.apple.com/us/album/want-me-back-feat-tors/1889370752</v>
       </c>
       <c r="L57" t="str">
-        <v>RUIN - HEALTH</v>
+        <v>Want Me Back (feat. Tors) - Trousdale</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="str">
-        <v>I Know I Know</v>
+        <v>RUIN</v>
       </c>
       <c r="B58" t="str">
         <v/>
       </c>
       <c r="C58" t="str">
-        <v>https://music.apple.com/us/song/i-know-i-know/1894354139</v>
+        <v>https://music.apple.com/us/song/ruin/1886537117</v>
       </c>
       <c r="D58" t="str">
         <v>2026-05-04</v>
@@ -2579,36 +2579,36 @@
         <v/>
       </c>
       <c r="F58" t="str">
-        <v>I Know I Know - Single</v>
+        <v>ADDENDUM</v>
       </c>
       <c r="G58" t="str">
-        <v>2:39</v>
+        <v>3:23</v>
       </c>
       <c r="H58" t="str">
-        <v>STELLA LEFTY</v>
+        <v>HEALTH</v>
       </c>
       <c r="I58" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J58" t="str">
-        <v>https://music.apple.com/us/artist/stella-lefty/1641742186</v>
+        <v>https://music.apple.com/us/artist/health/317478211</v>
       </c>
       <c r="K58" t="str">
-        <v>https://music.apple.com/us/album/i-know-i-know/1894354136</v>
+        <v>https://music.apple.com/us/album/ruin/1886536873</v>
       </c>
       <c r="L58" t="str">
-        <v>I Know I Know - STELLA LEFTY</v>
+        <v>RUIN - HEALTH</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="str">
-        <v>Drive All Night</v>
+        <v>I Know I Know</v>
       </c>
       <c r="B59" t="str">
         <v/>
       </c>
       <c r="C59" t="str">
-        <v>https://music.apple.com/us/song/drive-all-night/6763189759</v>
+        <v>https://music.apple.com/us/song/i-know-i-know/1894354139</v>
       </c>
       <c r="D59" t="str">
         <v>2026-05-04</v>
@@ -2617,36 +2617,36 @@
         <v/>
       </c>
       <c r="F59" t="str">
-        <v>Drive All Night - Single</v>
+        <v>I Know I Know - Single</v>
       </c>
       <c r="G59" t="str">
-        <v>2:50</v>
+        <v>2:39</v>
       </c>
       <c r="H59" t="str">
-        <v>Wyatt Flores</v>
+        <v>STELLA LEFTY</v>
       </c>
       <c r="I59" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J59" t="str">
-        <v>https://music.apple.com/us/artist/wyatt-flores/1563146833</v>
+        <v>https://music.apple.com/us/artist/stella-lefty/1641742186</v>
       </c>
       <c r="K59" t="str">
-        <v>https://music.apple.com/us/album/drive-all-night/1895207255</v>
+        <v>https://music.apple.com/us/album/i-know-i-know/1894354136</v>
       </c>
       <c r="L59" t="str">
-        <v>Drive All Night - Wyatt Flores</v>
+        <v>I Know I Know - STELLA LEFTY</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="str">
-        <v>AIN'T U TIRED?</v>
+        <v>Drive All Night</v>
       </c>
       <c r="B60" t="str">
         <v/>
       </c>
       <c r="C60" t="str">
-        <v>https://music.apple.com/us/song/aint-u-tired/6763115235</v>
+        <v>https://music.apple.com/us/song/drive-all-night/6763189759</v>
       </c>
       <c r="D60" t="str">
         <v>2026-05-04</v>
@@ -2655,36 +2655,36 @@
         <v/>
       </c>
       <c r="F60" t="str">
-        <v>AIN'T U TIRED? - Single</v>
+        <v>Drive All Night - Single</v>
       </c>
       <c r="G60" t="str">
-        <v>3:41</v>
+        <v>2:50</v>
       </c>
       <c r="H60" t="str">
-        <v>Jessie Reyez</v>
+        <v>Wyatt Flores</v>
       </c>
       <c r="I60" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J60" t="str">
-        <v>https://music.apple.com/us/artist/jessie-reyez/1043591612</v>
+        <v>https://music.apple.com/us/artist/wyatt-flores/1563146833</v>
       </c>
       <c r="K60" t="str">
-        <v>https://music.apple.com/us/album/aint-u-tired/1895167276</v>
+        <v>https://music.apple.com/us/album/drive-all-night/1895207255</v>
       </c>
       <c r="L60" t="str">
-        <v>AIN'T U TIRED? - Jessie Reyez</v>
+        <v>Drive All Night - Wyatt Flores</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="str">
-        <v>Boys In Blue</v>
+        <v>AIN'T U TIRED?</v>
       </c>
       <c r="B61" t="str">
         <v/>
       </c>
       <c r="C61" t="str">
-        <v>https://music.apple.com/us/song/boys-in-blue/1892436920</v>
+        <v>https://music.apple.com/us/song/aint-u-tired/6763115235</v>
       </c>
       <c r="D61" t="str">
         <v>2026-05-04</v>
@@ -2693,36 +2693,36 @@
         <v/>
       </c>
       <c r="F61" t="str">
-        <v>Emotional Junglist</v>
+        <v>AIN'T U TIRED? - Single</v>
       </c>
       <c r="G61" t="str">
-        <v>2:33</v>
+        <v>3:41</v>
       </c>
       <c r="H61" t="str">
-        <v>Nia Archives</v>
+        <v>Jessie Reyez</v>
       </c>
       <c r="I61" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J61" t="str">
-        <v>https://music.apple.com/us/artist/nia-archives/1515978311</v>
+        <v>https://music.apple.com/us/artist/jessie-reyez/1043591612</v>
       </c>
       <c r="K61" t="str">
-        <v>https://music.apple.com/us/album/boys-in-blue/1892436329</v>
+        <v>https://music.apple.com/us/album/aint-u-tired/1895167276</v>
       </c>
       <c r="L61" t="str">
-        <v>Boys In Blue - Nia Archives</v>
+        <v>AIN'T U TIRED? - Jessie Reyez</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="str">
-        <v>Salma Hayek</v>
+        <v>Boys In Blue</v>
       </c>
       <c r="B62" t="str">
         <v/>
       </c>
       <c r="C62" t="str">
-        <v>https://music.apple.com/us/song/salma-hayek/1891815286</v>
+        <v>https://music.apple.com/us/song/boys-in-blue/1892436920</v>
       </c>
       <c r="D62" t="str">
         <v>2026-05-04</v>
@@ -2731,36 +2731,36 @@
         <v/>
       </c>
       <c r="F62" t="str">
-        <v>Salma Hayek - Single</v>
+        <v>Emotional Junglist</v>
       </c>
       <c r="G62" t="str">
-        <v>3:43</v>
+        <v>2:33</v>
       </c>
       <c r="H62" t="str">
-        <v>Luis R Conriquez</v>
+        <v>Nia Archives</v>
       </c>
       <c r="I62" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J62" t="str">
-        <v>https://music.apple.com/us/artist/luis-r-conriquez/1252271456</v>
+        <v>https://music.apple.com/us/artist/nia-archives/1515978311</v>
       </c>
       <c r="K62" t="str">
-        <v>https://music.apple.com/us/album/salma-hayek/1891815277</v>
+        <v>https://music.apple.com/us/album/boys-in-blue/1892436329</v>
       </c>
       <c r="L62" t="str">
-        <v>Salma Hayek - Luis R Conriquez</v>
+        <v>Boys In Blue - Nia Archives</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="str">
-        <v>Stubborn Mouth</v>
+        <v>Salma Hayek</v>
       </c>
       <c r="B63" t="str">
         <v/>
       </c>
       <c r="C63" t="str">
-        <v>https://music.apple.com/us/song/stubborn-mouth/1893194800</v>
+        <v>https://music.apple.com/us/song/salma-hayek/1891815286</v>
       </c>
       <c r="D63" t="str">
         <v>2026-05-04</v>
@@ -2769,36 +2769,36 @@
         <v/>
       </c>
       <c r="F63" t="str">
-        <v>Stubborn Mouth - Single</v>
+        <v>Salma Hayek - Single</v>
       </c>
       <c r="G63" t="str">
-        <v>3:02</v>
+        <v>3:43</v>
       </c>
       <c r="H63" t="str">
-        <v>Girl Tones</v>
+        <v>Luis R Conriquez</v>
       </c>
       <c r="I63" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J63" t="str">
-        <v>https://music.apple.com/us/artist/girl-tones/1761267584</v>
+        <v>https://music.apple.com/us/artist/luis-r-conriquez/1252271456</v>
       </c>
       <c r="K63" t="str">
-        <v>https://music.apple.com/us/album/stubborn-mouth/1893194649</v>
+        <v>https://music.apple.com/us/album/salma-hayek/1891815277</v>
       </c>
       <c r="L63" t="str">
-        <v>Stubborn Mouth - Girl Tones</v>
+        <v>Salma Hayek - Luis R Conriquez</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="str">
-        <v>Hallucination</v>
+        <v>Stubborn Mouth</v>
       </c>
       <c r="B64" t="str">
         <v/>
       </c>
       <c r="C64" t="str">
-        <v>https://music.apple.com/us/song/hallucination/6764110976</v>
+        <v>https://music.apple.com/us/song/stubborn-mouth/1893194800</v>
       </c>
       <c r="D64" t="str">
         <v>2026-05-04</v>
@@ -2807,36 +2807,36 @@
         <v/>
       </c>
       <c r="F64" t="str">
-        <v>Promising Young Woman - EP</v>
+        <v>Stubborn Mouth - Single</v>
       </c>
       <c r="G64" t="str">
-        <v>3:22</v>
+        <v>3:02</v>
       </c>
       <c r="H64" t="str">
-        <v>Isabel LaRosa</v>
+        <v>Girl Tones</v>
       </c>
       <c r="I64" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J64" t="str">
-        <v>https://music.apple.com/us/artist/isabel-larosa/1578296103</v>
+        <v>https://music.apple.com/us/artist/girl-tones/1761267584</v>
       </c>
       <c r="K64" t="str">
-        <v>https://music.apple.com/us/album/hallucination/1895644574</v>
+        <v>https://music.apple.com/us/album/stubborn-mouth/1893194649</v>
       </c>
       <c r="L64" t="str">
-        <v>Hallucination - Isabel LaRosa</v>
+        <v>Stubborn Mouth - Girl Tones</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="str">
-        <v>In Da Jungle</v>
+        <v>Hallucination</v>
       </c>
       <c r="B65" t="str">
         <v/>
       </c>
       <c r="C65" t="str">
-        <v>https://music.apple.com/us/song/in-da-jungle/1891136400</v>
+        <v>https://music.apple.com/us/song/hallucination/6764110976</v>
       </c>
       <c r="D65" t="str">
         <v>2026-05-04</v>
@@ -2845,36 +2845,36 @@
         <v/>
       </c>
       <c r="F65" t="str">
-        <v>In Da Jungle - Single</v>
+        <v>Promising Young Woman - EP</v>
       </c>
       <c r="G65" t="str">
-        <v>2:44</v>
+        <v>3:22</v>
       </c>
       <c r="H65" t="str">
-        <v>BLOND:ISH</v>
+        <v>Isabel LaRosa</v>
       </c>
       <c r="I65" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J65" t="str">
-        <v>https://music.apple.com/us/artist/blond-ish/394776491</v>
+        <v>https://music.apple.com/us/artist/isabel-larosa/1578296103</v>
       </c>
       <c r="K65" t="str">
-        <v>https://music.apple.com/us/album/in-da-jungle/1891136398</v>
+        <v>https://music.apple.com/us/album/hallucination/1895644574</v>
       </c>
       <c r="L65" t="str">
-        <v>In Da Jungle - BLOND:ISH</v>
+        <v>Hallucination - Isabel LaRosa</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="str">
-        <v>Fall Short</v>
+        <v>In Da Jungle</v>
       </c>
       <c r="B66" t="str">
         <v/>
       </c>
       <c r="C66" t="str">
-        <v>https://music.apple.com/us/song/fall-short/1894662749</v>
+        <v>https://music.apple.com/us/song/in-da-jungle/1891136400</v>
       </c>
       <c r="D66" t="str">
         <v>2026-05-04</v>
@@ -2883,36 +2883,36 @@
         <v/>
       </c>
       <c r="F66" t="str">
-        <v>Fall Short - Single</v>
+        <v>In Da Jungle - Single</v>
       </c>
       <c r="G66" t="str">
         <v>2:44</v>
       </c>
       <c r="H66" t="str">
-        <v>nyan</v>
+        <v>BLOND:ISH</v>
       </c>
       <c r="I66" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J66" t="str">
-        <v>https://music.apple.com/us/artist/nyan/1478138732</v>
+        <v>https://music.apple.com/us/artist/blond-ish/394776491</v>
       </c>
       <c r="K66" t="str">
-        <v>https://music.apple.com/us/album/fall-short/1894662748</v>
+        <v>https://music.apple.com/us/album/in-da-jungle/1891136398</v>
       </c>
       <c r="L66" t="str">
-        <v>Fall Short - nyan</v>
+        <v>In Da Jungle - BLOND:ISH</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="str">
-        <v>Irish Goodbye (feat. Kae Tempest)</v>
+        <v>Fall Short</v>
       </c>
       <c r="B67" t="str">
         <v/>
       </c>
       <c r="C67" t="str">
-        <v>https://music.apple.com/us/song/irish-goodbye-feat-kae-tempest/1862224205</v>
+        <v>https://music.apple.com/us/song/fall-short/1894662749</v>
       </c>
       <c r="D67" t="str">
         <v>2026-05-04</v>
@@ -2921,36 +2921,36 @@
         <v/>
       </c>
       <c r="F67" t="str">
-        <v>FENIAN</v>
+        <v>Fall Short - Single</v>
       </c>
       <c r="G67" t="str">
-        <v>3:34</v>
+        <v>2:44</v>
       </c>
       <c r="H67" t="str">
-        <v>Kneecap</v>
+        <v>nyan</v>
       </c>
       <c r="I67" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J67" t="str">
-        <v>https://music.apple.com/us/artist/kneecap/1330315811</v>
+        <v>https://music.apple.com/us/artist/nyan/1478138732</v>
       </c>
       <c r="K67" t="str">
-        <v>https://music.apple.com/us/album/irish-goodbye-feat-kae-tempest/1862223497</v>
+        <v>https://music.apple.com/us/album/fall-short/1894662748</v>
       </c>
       <c r="L67" t="str">
-        <v>Irish Goodbye (feat. Kae Tempest) - Kneecap</v>
+        <v>Fall Short - nyan</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="str">
-        <v>1989</v>
+        <v>Irish Goodbye (feat. Kae Tempest)</v>
       </c>
       <c r="B68" t="str">
         <v/>
       </c>
       <c r="C68" t="str">
-        <v>https://music.apple.com/us/song/1989/1893089382</v>
+        <v>https://music.apple.com/us/song/irish-goodbye-feat-kae-tempest/1862224205</v>
       </c>
       <c r="D68" t="str">
         <v>2026-05-04</v>
@@ -2959,36 +2959,36 @@
         <v/>
       </c>
       <c r="F68" t="str">
-        <v>1989 - Single</v>
+        <v>FENIAN</v>
       </c>
       <c r="G68" t="str">
-        <v>3:05</v>
+        <v>3:34</v>
       </c>
       <c r="H68" t="str">
-        <v>Nightly</v>
+        <v>Kneecap</v>
       </c>
       <c r="I68" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J68" t="str">
-        <v>https://music.apple.com/us/artist/nightly/352310972</v>
+        <v>https://music.apple.com/us/artist/kneecap/1330315811</v>
       </c>
       <c r="K68" t="str">
-        <v>https://music.apple.com/us/album/1989/1893089381</v>
+        <v>https://music.apple.com/us/album/irish-goodbye-feat-kae-tempest/1862223497</v>
       </c>
       <c r="L68" t="str">
-        <v>1989 - Nightly</v>
+        <v>Irish Goodbye (feat. Kae Tempest) - Kneecap</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="str">
-        <v>no more regrets</v>
+        <v>1989</v>
       </c>
       <c r="B69" t="str">
         <v/>
       </c>
       <c r="C69" t="str">
-        <v>https://music.apple.com/us/song/no-more-regrets/1893191803</v>
+        <v>https://music.apple.com/us/song/1989/1893089382</v>
       </c>
       <c r="D69" t="str">
         <v>2026-05-04</v>
@@ -2997,36 +2997,36 @@
         <v/>
       </c>
       <c r="F69" t="str">
-        <v>no more regrets - Single</v>
+        <v>1989 - Single</v>
       </c>
       <c r="G69" t="str">
-        <v>2:58</v>
+        <v>3:05</v>
       </c>
       <c r="H69" t="str">
-        <v>almost monday</v>
+        <v>Nightly</v>
       </c>
       <c r="I69" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J69" t="str">
-        <v>https://music.apple.com/us/artist/almost-monday/1300723925</v>
+        <v>https://music.apple.com/us/artist/nightly/352310972</v>
       </c>
       <c r="K69" t="str">
-        <v>https://music.apple.com/us/album/no-more-regrets/1893191802</v>
+        <v>https://music.apple.com/us/album/1989/1893089381</v>
       </c>
       <c r="L69" t="str">
-        <v>no more regrets - almost monday</v>
+        <v>1989 - Nightly</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="str">
-        <v>Drum Machine</v>
+        <v>no more regrets</v>
       </c>
       <c r="B70" t="str">
         <v/>
       </c>
       <c r="C70" t="str">
-        <v>https://music.apple.com/us/song/drum-machine/1840517102</v>
+        <v>https://music.apple.com/us/song/no-more-regrets/1893191803</v>
       </c>
       <c r="D70" t="str">
         <v>2026-05-04</v>
@@ -3035,36 +3035,36 @@
         <v/>
       </c>
       <c r="F70" t="str">
-        <v>Sweat</v>
+        <v>no more regrets - Single</v>
       </c>
       <c r="G70" t="str">
-        <v>3:16</v>
+        <v>2:58</v>
       </c>
       <c r="H70" t="str">
-        <v>Melanie C</v>
+        <v>almost monday</v>
       </c>
       <c r="I70" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J70" t="str">
-        <v>https://music.apple.com/us/artist/melanie-c/653819</v>
+        <v>https://music.apple.com/us/artist/almost-monday/1300723925</v>
       </c>
       <c r="K70" t="str">
-        <v>https://music.apple.com/us/album/drum-machine/1840516706</v>
+        <v>https://music.apple.com/us/album/no-more-regrets/1893191802</v>
       </c>
       <c r="L70" t="str">
-        <v>Drum Machine - Melanie C</v>
+        <v>no more regrets - almost monday</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="str">
-        <v>I'm Perfect</v>
+        <v>Drum Machine</v>
       </c>
       <c r="B71" t="str">
         <v/>
       </c>
       <c r="C71" t="str">
-        <v>https://music.apple.com/us/song/im-perfect/1893181359</v>
+        <v>https://music.apple.com/us/song/drum-machine/1840517102</v>
       </c>
       <c r="D71" t="str">
         <v>2026-05-04</v>
@@ -3073,36 +3073,36 @@
         <v/>
       </c>
       <c r="F71" t="str">
-        <v>I'm Perfect - Single</v>
+        <v>Sweat</v>
       </c>
       <c r="G71" t="str">
-        <v>2:36</v>
+        <v>3:16</v>
       </c>
       <c r="H71" t="str">
-        <v>Olivia O'Brien</v>
+        <v>Melanie C</v>
       </c>
       <c r="I71" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J71" t="str">
-        <v>https://music.apple.com/us/artist/olivia-obrien/1023538468</v>
+        <v>https://music.apple.com/us/artist/melanie-c/653819</v>
       </c>
       <c r="K71" t="str">
-        <v>https://music.apple.com/us/album/im-perfect/1893181351</v>
+        <v>https://music.apple.com/us/album/drum-machine/1840516706</v>
       </c>
       <c r="L71" t="str">
-        <v>I'm Perfect - Olivia O'Brien</v>
+        <v>Drum Machine - Melanie C</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="str">
-        <v>Theme for a Train Journey</v>
+        <v>I'm Perfect</v>
       </c>
       <c r="B72" t="str">
         <v/>
       </c>
       <c r="C72" t="str">
-        <v>https://music.apple.com/us/song/theme-for-a-train-journey/1880699785</v>
+        <v>https://music.apple.com/us/song/im-perfect/1893181359</v>
       </c>
       <c r="D72" t="str">
         <v>2026-05-04</v>
@@ -3111,36 +3111,36 @@
         <v/>
       </c>
       <c r="F72" t="str">
-        <v>AK Cuts: Vol 3 - EP</v>
+        <v>I'm Perfect - Single</v>
       </c>
       <c r="G72" t="str">
-        <v>5:05</v>
+        <v>2:36</v>
       </c>
       <c r="H72" t="str">
-        <v>Anish Kumar</v>
+        <v>Olivia O'Brien</v>
       </c>
       <c r="I72" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J72" t="str">
-        <v>https://music.apple.com/us/artist/anish-kumar/1510744726</v>
+        <v>https://music.apple.com/us/artist/olivia-obrien/1023538468</v>
       </c>
       <c r="K72" t="str">
-        <v>https://music.apple.com/us/album/theme-for-a-train-journey/1880699566</v>
+        <v>https://music.apple.com/us/album/im-perfect/1893181351</v>
       </c>
       <c r="L72" t="str">
-        <v>Theme for a Train Journey - Anish Kumar</v>
+        <v>I'm Perfect - Olivia O'Brien</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="str">
-        <v>Bitch You Weird</v>
+        <v>Theme for a Train Journey</v>
       </c>
       <c r="B73" t="str">
         <v/>
       </c>
       <c r="C73" t="str">
-        <v>https://music.apple.com/us/song/bitch-you-weird/6763395875</v>
+        <v>https://music.apple.com/us/song/theme-for-a-train-journey/1880699785</v>
       </c>
       <c r="D73" t="str">
         <v>2026-05-04</v>
@@ -3149,36 +3149,36 @@
         <v/>
       </c>
       <c r="F73" t="str">
-        <v>Bitch You Weird - Single</v>
+        <v>AK Cuts: Vol 3 - EP</v>
       </c>
       <c r="G73" t="str">
-        <v>2:27</v>
+        <v>5:05</v>
       </c>
       <c r="H73" t="str">
-        <v>Real Boston Richey</v>
+        <v>Anish Kumar</v>
       </c>
       <c r="I73" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J73" t="str">
-        <v>https://music.apple.com/us/artist/real-boston-richey/1595496755</v>
+        <v>https://music.apple.com/us/artist/anish-kumar/1510744726</v>
       </c>
       <c r="K73" t="str">
-        <v>https://music.apple.com/us/album/bitch-you-weird/1895294715</v>
+        <v>https://music.apple.com/us/album/theme-for-a-train-journey/1880699566</v>
       </c>
       <c r="L73" t="str">
-        <v>Bitch You Weird - Real Boston Richey</v>
+        <v>Theme for a Train Journey - Anish Kumar</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="str">
-        <v>Blackbird Rising</v>
+        <v>Bitch You Weird</v>
       </c>
       <c r="B74" t="str">
         <v/>
       </c>
       <c r="C74" t="str">
-        <v>https://music.apple.com/us/song/blackbird-rising/1887166611</v>
+        <v>https://music.apple.com/us/song/bitch-you-weird/6763395875</v>
       </c>
       <c r="D74" t="str">
         <v>2026-05-04</v>
@@ -3187,36 +3187,36 @@
         <v/>
       </c>
       <c r="F74" t="str">
-        <v>24</v>
+        <v>Bitch You Weird - Single</v>
       </c>
       <c r="G74" t="str">
-        <v>2:24</v>
+        <v>2:27</v>
       </c>
       <c r="H74" t="str">
-        <v>Alexis Ffrench</v>
+        <v>Real Boston Richey</v>
       </c>
       <c r="I74" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J74" t="str">
-        <v>https://music.apple.com/us/artist/alexis-ffrench/342515428</v>
+        <v>https://music.apple.com/us/artist/real-boston-richey/1595496755</v>
       </c>
       <c r="K74" t="str">
-        <v>https://music.apple.com/us/album/blackbird-rising/1887166427</v>
+        <v>https://music.apple.com/us/album/bitch-you-weird/1895294715</v>
       </c>
       <c r="L74" t="str">
-        <v>Blackbird Rising - Alexis Ffrench</v>
+        <v>Bitch You Weird - Real Boston Richey</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="str">
-        <v>usher in the spirit</v>
+        <v>Blackbird Rising</v>
       </c>
       <c r="B75" t="str">
         <v/>
       </c>
       <c r="C75" t="str">
-        <v>https://music.apple.com/us/song/usher-in-the-spirit/6763373678</v>
+        <v>https://music.apple.com/us/song/blackbird-rising/1887166611</v>
       </c>
       <c r="D75" t="str">
         <v>2026-05-04</v>
@@ -3225,36 +3225,36 @@
         <v/>
       </c>
       <c r="F75" t="str">
-        <v>usher in the spirit - Single</v>
+        <v>24</v>
       </c>
       <c r="G75" t="str">
-        <v>3:00</v>
+        <v>2:24</v>
       </c>
       <c r="H75" t="str">
-        <v>Aaron Cole</v>
+        <v>Alexis Ffrench</v>
       </c>
       <c r="I75" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J75" t="str">
-        <v>https://music.apple.com/us/artist/aaron-cole/507522696</v>
+        <v>https://music.apple.com/us/artist/alexis-ffrench/342515428</v>
       </c>
       <c r="K75" t="str">
-        <v>https://music.apple.com/us/album/usher-in-the-spirit/1895286256</v>
+        <v>https://music.apple.com/us/album/blackbird-rising/1887166427</v>
       </c>
       <c r="L75" t="str">
-        <v>usher in the spirit - Aaron Cole</v>
+        <v>Blackbird Rising - Alexis Ffrench</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="str">
-        <v>Moonlight</v>
+        <v>usher in the spirit</v>
       </c>
       <c r="B76" t="str">
         <v/>
       </c>
       <c r="C76" t="str">
-        <v>https://music.apple.com/us/song/moonlight/1892950791</v>
+        <v>https://music.apple.com/us/song/usher-in-the-spirit/6763373678</v>
       </c>
       <c r="D76" t="str">
         <v>2026-05-04</v>
@@ -3263,36 +3263,36 @@
         <v/>
       </c>
       <c r="F76" t="str">
-        <v>Moonlight - Single</v>
+        <v>usher in the spirit - Single</v>
       </c>
       <c r="G76" t="str">
-        <v>3:23</v>
+        <v>3:00</v>
       </c>
       <c r="H76" t="str">
-        <v>Chelsea Plank</v>
+        <v>Aaron Cole</v>
       </c>
       <c r="I76" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J76" t="str">
-        <v>https://music.apple.com/us/artist/chelsea-plank/1246169844</v>
+        <v>https://music.apple.com/us/artist/aaron-cole/507522696</v>
       </c>
       <c r="K76" t="str">
-        <v>https://music.apple.com/us/album/moonlight/1892950782</v>
+        <v>https://music.apple.com/us/album/usher-in-the-spirit/1895286256</v>
       </c>
       <c r="L76" t="str">
-        <v>Moonlight - Chelsea Plank</v>
+        <v>usher in the spirit - Aaron Cole</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="str">
-        <v>&gt;&gt;&gt;hands on me&lt;&lt;&lt;</v>
+        <v>Moonlight</v>
       </c>
       <c r="B77" t="str">
         <v/>
       </c>
       <c r="C77" t="str">
-        <v>https://music.apple.com/us/song/hands-on-me/1893960365</v>
+        <v>https://music.apple.com/us/song/moonlight/1892950791</v>
       </c>
       <c r="D77" t="str">
         <v>2026-05-04</v>
@@ -3301,36 +3301,36 @@
         <v/>
       </c>
       <c r="F77" t="str">
-        <v>&gt;&gt;&gt;hands on me&lt;&lt;&lt; - Single</v>
+        <v>Moonlight - Single</v>
       </c>
       <c r="G77" t="str">
-        <v>2:17</v>
+        <v>3:23</v>
       </c>
       <c r="H77" t="str">
-        <v>Becky Hill</v>
+        <v>Chelsea Plank</v>
       </c>
       <c r="I77" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J77" t="str">
-        <v>https://music.apple.com/us/artist/becky-hill/533839517</v>
+        <v>https://music.apple.com/us/artist/chelsea-plank/1246169844</v>
       </c>
       <c r="K77" t="str">
-        <v>https://music.apple.com/us/album/hands-on-me/1893960148</v>
+        <v>https://music.apple.com/us/album/moonlight/1892950782</v>
       </c>
       <c r="L77" t="str">
-        <v>&gt;&gt;&gt;hands on me&lt;&lt;&lt; - Becky Hill</v>
+        <v>Moonlight - Chelsea Plank</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="str">
-        <v>Closure</v>
+        <v>&gt;&gt;&gt;hands on me&lt;&lt;&lt;</v>
       </c>
       <c r="B78" t="str">
         <v/>
       </c>
       <c r="C78" t="str">
-        <v>https://music.apple.com/us/song/closure/1892418294</v>
+        <v>https://music.apple.com/us/song/hands-on-me/1893960365</v>
       </c>
       <c r="D78" t="str">
         <v>2026-05-04</v>
@@ -3339,36 +3339,36 @@
         <v/>
       </c>
       <c r="F78" t="str">
-        <v>Closure - Single</v>
+        <v>&gt;&gt;&gt;hands on me&lt;&lt;&lt; - Single</v>
       </c>
       <c r="G78" t="str">
-        <v>2:27</v>
+        <v>2:17</v>
       </c>
       <c r="H78" t="str">
-        <v>D.O.D</v>
+        <v>Becky Hill</v>
       </c>
       <c r="I78" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J78" t="str">
-        <v>https://music.apple.com/us/artist/d-o-d/444171843</v>
+        <v>https://music.apple.com/us/artist/becky-hill/533839517</v>
       </c>
       <c r="K78" t="str">
-        <v>https://music.apple.com/us/album/closure/1892418283</v>
+        <v>https://music.apple.com/us/album/hands-on-me/1893960148</v>
       </c>
       <c r="L78" t="str">
-        <v>Closure - D.O.D</v>
+        <v>&gt;&gt;&gt;hands on me&lt;&lt;&lt; - Becky Hill</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="str">
-        <v>HOTS 4 U</v>
+        <v>Closure</v>
       </c>
       <c r="B79" t="str">
         <v/>
       </c>
       <c r="C79" t="str">
-        <v>https://music.apple.com/us/song/hots-4-u/1891478541</v>
+        <v>https://music.apple.com/us/song/closure/1892418294</v>
       </c>
       <c r="D79" t="str">
         <v>2026-05-04</v>
@@ -3377,36 +3377,36 @@
         <v/>
       </c>
       <c r="F79" t="str">
-        <v>HOTS 4 U - Single</v>
+        <v>Closure - Single</v>
       </c>
       <c r="G79" t="str">
-        <v>3:34</v>
+        <v>2:27</v>
       </c>
       <c r="H79" t="str">
-        <v>Chris Lorenzo</v>
+        <v>D.O.D</v>
       </c>
       <c r="I79" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J79" t="str">
-        <v>https://music.apple.com/us/artist/chris-lorenzo/621431022</v>
+        <v>https://music.apple.com/us/artist/d-o-d/444171843</v>
       </c>
       <c r="K79" t="str">
-        <v>https://music.apple.com/us/album/hots-4-u/1891478539</v>
+        <v>https://music.apple.com/us/album/closure/1892418283</v>
       </c>
       <c r="L79" t="str">
-        <v>HOTS 4 U - Chris Lorenzo</v>
+        <v>Closure - D.O.D</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="str">
-        <v>CULE POCO (sirena_besarico_costeña)</v>
+        <v>HOTS 4 U</v>
       </c>
       <c r="B80" t="str">
         <v/>
       </c>
       <c r="C80" t="str">
-        <v>https://music.apple.com/us/song/cule-poco-sirena-besarico-coste%C3%B1a/1893480200</v>
+        <v>https://music.apple.com/us/song/hots-4-u/1891478541</v>
       </c>
       <c r="D80" t="str">
         <v>2026-05-04</v>
@@ -3415,36 +3415,36 @@
         <v/>
       </c>
       <c r="F80" t="str">
-        <v>CULE POCO (sirena_besarico_costeña) - Single</v>
+        <v>HOTS 4 U - Single</v>
       </c>
       <c r="G80" t="str">
-        <v>2:20</v>
+        <v>3:34</v>
       </c>
       <c r="H80" t="str">
-        <v>ARIA VEGA</v>
+        <v>Chris Lorenzo</v>
       </c>
       <c r="I80" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J80" t="str">
-        <v>https://music.apple.com/us/artist/aria-vega/1449328559</v>
+        <v>https://music.apple.com/us/artist/chris-lorenzo/621431022</v>
       </c>
       <c r="K80" t="str">
-        <v>https://music.apple.com/us/album/cule-poco-sirena-besarico-coste%C3%B1a/1893480124</v>
+        <v>https://music.apple.com/us/album/hots-4-u/1891478539</v>
       </c>
       <c r="L80" t="str">
-        <v>CULE POCO (sirena_besarico_costeña) - ARIA VEGA</v>
+        <v>HOTS 4 U - Chris Lorenzo</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="str">
-        <v>The Coin Toss</v>
+        <v>CULE POCO (sirena_besarico_costeña)</v>
       </c>
       <c r="B81" t="str">
         <v/>
       </c>
       <c r="C81" t="str">
-        <v>https://music.apple.com/us/song/the-coin-toss/1894872115</v>
+        <v>https://music.apple.com/us/song/cule-poco-sirena-besarico-coste%C3%B1a/1893480200</v>
       </c>
       <c r="D81" t="str">
         <v>2026-05-04</v>
@@ -3453,36 +3453,36 @@
         <v/>
       </c>
       <c r="F81" t="str">
-        <v>Roofless Records For Drop Tops: Disc 2</v>
+        <v>CULE POCO (sirena_besarico_costeña) - Single</v>
       </c>
       <c r="G81" t="str">
-        <v>2:46</v>
+        <v>2:20</v>
       </c>
       <c r="H81" t="str">
-        <v>Curren$y</v>
+        <v>ARIA VEGA</v>
       </c>
       <c r="I81" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J81" t="str">
-        <v>https://music.apple.com/us/artist/curren%24y/5914039</v>
+        <v>https://music.apple.com/us/artist/aria-vega/1449328559</v>
       </c>
       <c r="K81" t="str">
-        <v>https://music.apple.com/us/album/the-coin-toss/1894872108</v>
+        <v>https://music.apple.com/us/album/cule-poco-sirena-besarico-coste%C3%B1a/1893480124</v>
       </c>
       <c r="L81" t="str">
-        <v>The Coin Toss - Curren$y</v>
+        <v>CULE POCO (sirena_besarico_costeña) - ARIA VEGA</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="str">
-        <v>Bottles &amp; Lights</v>
+        <v>The Coin Toss</v>
       </c>
       <c r="B82" t="str">
         <v/>
       </c>
       <c r="C82" t="str">
-        <v>https://music.apple.com/us/song/bottles-lights/6763041153</v>
+        <v>https://music.apple.com/us/song/the-coin-toss/1894872115</v>
       </c>
       <c r="D82" t="str">
         <v>2026-05-04</v>
@@ -3491,36 +3491,36 @@
         <v/>
       </c>
       <c r="F82" t="str">
-        <v>Bottles &amp; Lights - Single</v>
+        <v>Roofless Records For Drop Tops: Disc 2</v>
       </c>
       <c r="G82" t="str">
-        <v>3:25</v>
+        <v>2:46</v>
       </c>
       <c r="H82" t="str">
-        <v>Chxrry</v>
+        <v>Curren$y</v>
       </c>
       <c r="I82" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J82" t="str">
-        <v>https://music.apple.com/us/artist/chxrry/1520135642</v>
+        <v>https://music.apple.com/us/artist/curren%24y/5914039</v>
       </c>
       <c r="K82" t="str">
-        <v>https://music.apple.com/us/album/bottles-lights/1895133498</v>
+        <v>https://music.apple.com/us/album/the-coin-toss/1894872108</v>
       </c>
       <c r="L82" t="str">
-        <v>Bottles &amp; Lights - Chxrry</v>
+        <v>The Coin Toss - Curren$y</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="str">
-        <v>Perfect For Me</v>
+        <v>Bottles &amp; Lights</v>
       </c>
       <c r="B83" t="str">
         <v/>
       </c>
       <c r="C83" t="str">
-        <v>https://music.apple.com/us/song/perfect-for-me/6762879981</v>
+        <v>https://music.apple.com/us/song/bottles-lights/6763041153</v>
       </c>
       <c r="D83" t="str">
         <v>2026-05-04</v>
@@ -3529,36 +3529,36 @@
         <v/>
       </c>
       <c r="F83" t="str">
-        <v>Perfect For Me - Single</v>
+        <v>Bottles &amp; Lights - Single</v>
       </c>
       <c r="G83" t="str">
-        <v>3:02</v>
+        <v>3:25</v>
       </c>
       <c r="H83" t="str">
-        <v>Jamal Roberts</v>
+        <v>Chxrry</v>
       </c>
       <c r="I83" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J83" t="str">
-        <v>https://music.apple.com/us/artist/jamal-roberts/920647552</v>
+        <v>https://music.apple.com/us/artist/chxrry/1520135642</v>
       </c>
       <c r="K83" t="str">
-        <v>https://music.apple.com/us/album/perfect-for-me/1895056299</v>
+        <v>https://music.apple.com/us/album/bottles-lights/1895133498</v>
       </c>
       <c r="L83" t="str">
-        <v>Perfect For Me - Jamal Roberts</v>
+        <v>Bottles &amp; Lights - Chxrry</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="str">
-        <v>So…</v>
+        <v>Perfect For Me</v>
       </c>
       <c r="B84" t="str">
         <v/>
       </c>
       <c r="C84" t="str">
-        <v>https://music.apple.com/us/song/so/1893162424</v>
+        <v>https://music.apple.com/us/song/perfect-for-me/6762879981</v>
       </c>
       <c r="D84" t="str">
         <v>2026-05-04</v>
@@ -3567,36 +3567,36 @@
         <v/>
       </c>
       <c r="F84" t="str">
-        <v>So… - Single</v>
+        <v>Perfect For Me - Single</v>
       </c>
       <c r="G84" t="str">
-        <v>3:16</v>
+        <v>3:02</v>
       </c>
       <c r="H84" t="str">
-        <v>Ama</v>
+        <v>Jamal Roberts</v>
       </c>
       <c r="I84" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J84" t="str">
-        <v>https://music.apple.com/us/artist/ama/1801560081</v>
+        <v>https://music.apple.com/us/artist/jamal-roberts/920647552</v>
       </c>
       <c r="K84" t="str">
-        <v>https://music.apple.com/us/album/so/1893162419</v>
+        <v>https://music.apple.com/us/album/perfect-for-me/1895056299</v>
       </c>
       <c r="L84" t="str">
-        <v>So… - Ama</v>
+        <v>Perfect For Me - Jamal Roberts</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="str">
-        <v>PASE Y PASE</v>
+        <v>So…</v>
       </c>
       <c r="B85" t="str">
         <v/>
       </c>
       <c r="C85" t="str">
-        <v>https://music.apple.com/us/song/pase-y-pase/1894076490</v>
+        <v>https://music.apple.com/us/song/so/1893162424</v>
       </c>
       <c r="D85" t="str">
         <v>2026-05-04</v>
@@ -3605,36 +3605,36 @@
         <v/>
       </c>
       <c r="F85" t="str">
-        <v>PASE Y PASE - Single</v>
+        <v>So… - Single</v>
       </c>
       <c r="G85" t="str">
-        <v>3:01</v>
+        <v>3:16</v>
       </c>
       <c r="H85" t="str">
-        <v>Tito Double P</v>
+        <v>Ama</v>
       </c>
       <c r="I85" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J85" t="str">
-        <v>https://music.apple.com/us/artist/tito-double-p/1690905306</v>
+        <v>https://music.apple.com/us/artist/ama/1801560081</v>
       </c>
       <c r="K85" t="str">
-        <v>https://music.apple.com/us/album/pase-y-pase/1894076487</v>
+        <v>https://music.apple.com/us/album/so/1893162419</v>
       </c>
       <c r="L85" t="str">
-        <v>PASE Y PASE - Tito Double P</v>
+        <v>So… - Ama</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="str">
-        <v>Agoué-Dambala (Yanvalou) 1</v>
+        <v>PASE Y PASE</v>
       </c>
       <c r="B86" t="str">
         <v/>
       </c>
       <c r="C86" t="str">
-        <v>https://music.apple.com/us/song/agou%C3%A9-dambala-yanvalou-1/1888242486</v>
+        <v>https://music.apple.com/us/song/pase-y-pase/1894076490</v>
       </c>
       <c r="D86" t="str">
         <v>2026-05-04</v>
@@ -3643,36 +3643,36 @@
         <v/>
       </c>
       <c r="F86" t="str">
-        <v>Soul Jazz Records Presents HAITIAN VODOU</v>
+        <v>PASE Y PASE - Single</v>
       </c>
       <c r="G86" t="str">
-        <v>4:13</v>
+        <v>3:01</v>
       </c>
       <c r="H86" t="str">
-        <v>Societe Absolument Guinin</v>
+        <v>Tito Double P</v>
       </c>
       <c r="I86" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J86" t="str">
-        <v>https://music.apple.com/us/artist/societe-absolument-guinin/1083463027</v>
+        <v>https://music.apple.com/us/artist/tito-double-p/1690905306</v>
       </c>
       <c r="K86" t="str">
-        <v>https://music.apple.com/us/album/agou%C3%A9-dambala-yanvalou-1/1888242483</v>
+        <v>https://music.apple.com/us/album/pase-y-pase/1894076487</v>
       </c>
       <c r="L86" t="str">
-        <v>Agoué-Dambala (Yanvalou) 1 - Societe Absolument Guinin</v>
+        <v>PASE Y PASE - Tito Double P</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="str">
-        <v>Aljahalat</v>
+        <v>Agoué-Dambala (Yanvalou) 1</v>
       </c>
       <c r="B87" t="str">
         <v/>
       </c>
       <c r="C87" t="str">
-        <v>https://music.apple.com/us/song/aljahalat/1889267983</v>
+        <v>https://music.apple.com/us/song/agou%C3%A9-dambala-yanvalou-1/1888242486</v>
       </c>
       <c r="D87" t="str">
         <v>2026-05-04</v>
@@ -3681,36 +3681,36 @@
         <v/>
       </c>
       <c r="F87" t="str">
-        <v>Aljahalat - Single</v>
+        <v>Soul Jazz Records Presents HAITIAN VODOU</v>
       </c>
       <c r="G87" t="str">
-        <v>6:12</v>
+        <v>4:13</v>
       </c>
       <c r="H87" t="str">
-        <v>Ahmed Ag Kaedy</v>
+        <v>Societe Absolument Guinin</v>
       </c>
       <c r="I87" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J87" t="str">
-        <v>https://music.apple.com/us/artist/ahmed-ag-kaedy/1445296267</v>
+        <v>https://music.apple.com/us/artist/societe-absolument-guinin/1083463027</v>
       </c>
       <c r="K87" t="str">
-        <v>https://music.apple.com/us/album/aljahalat/1889267980</v>
+        <v>https://music.apple.com/us/album/agou%C3%A9-dambala-yanvalou-1/1888242483</v>
       </c>
       <c r="L87" t="str">
-        <v>Aljahalat - Ahmed Ag Kaedy</v>
+        <v>Agoué-Dambala (Yanvalou) 1 - Societe Absolument Guinin</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="str">
-        <v>Puleza</v>
+        <v>Aljahalat</v>
       </c>
       <c r="B88" t="str">
         <v/>
       </c>
       <c r="C88" t="str">
-        <v>https://music.apple.com/us/song/puleza/1893765840</v>
+        <v>https://music.apple.com/us/song/aljahalat/1889267983</v>
       </c>
       <c r="D88" t="str">
         <v>2026-05-04</v>
@@ -3719,36 +3719,36 @@
         <v/>
       </c>
       <c r="F88" t="str">
-        <v>People of the Moon</v>
+        <v>Aljahalat - Single</v>
       </c>
       <c r="G88" t="str">
-        <v>3:47</v>
+        <v>6:12</v>
       </c>
       <c r="H88" t="str">
-        <v>Nu Genea</v>
+        <v>Ahmed Ag Kaedy</v>
       </c>
       <c r="I88" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J88" t="str">
-        <v>https://music.apple.com/us/artist/nu-genea/997053217</v>
+        <v>https://music.apple.com/us/artist/ahmed-ag-kaedy/1445296267</v>
       </c>
       <c r="K88" t="str">
-        <v>https://music.apple.com/us/album/puleza/1893765826</v>
+        <v>https://music.apple.com/us/album/aljahalat/1889267980</v>
       </c>
       <c r="L88" t="str">
-        <v>Puleza - Nu Genea</v>
+        <v>Aljahalat - Ahmed Ag Kaedy</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="str">
-        <v>Bastards</v>
+        <v>Puleza</v>
       </c>
       <c r="B89" t="str">
         <v/>
       </c>
       <c r="C89" t="str">
-        <v>https://music.apple.com/us/song/bastards/6762403102</v>
+        <v>https://music.apple.com/us/song/puleza/1893765840</v>
       </c>
       <c r="D89" t="str">
         <v>2026-05-04</v>
@@ -3757,36 +3757,36 @@
         <v/>
       </c>
       <c r="F89" t="str">
-        <v>Bunny - EP</v>
+        <v>People of the Moon</v>
       </c>
       <c r="G89" t="str">
-        <v>2:56</v>
+        <v>3:47</v>
       </c>
       <c r="H89" t="str">
-        <v>People I’ve Met</v>
+        <v>Nu Genea</v>
       </c>
       <c r="I89" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J89" t="str">
-        <v>https://music.apple.com/us/artist/people-ive-met/1853169947</v>
+        <v>https://music.apple.com/us/artist/nu-genea/997053217</v>
       </c>
       <c r="K89" t="str">
-        <v>https://music.apple.com/us/album/bastards/1894044276</v>
+        <v>https://music.apple.com/us/album/puleza/1893765826</v>
       </c>
       <c r="L89" t="str">
-        <v>Bastards - People I’ve Met</v>
+        <v>Puleza - Nu Genea</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="str">
-        <v>Crutch</v>
+        <v>Bastards</v>
       </c>
       <c r="B90" t="str">
         <v/>
       </c>
       <c r="C90" t="str">
-        <v>https://music.apple.com/us/song/crutch/6763345020</v>
+        <v>https://music.apple.com/us/song/bastards/6762403102</v>
       </c>
       <c r="D90" t="str">
         <v>2026-05-04</v>
@@ -3795,36 +3795,36 @@
         <v/>
       </c>
       <c r="F90" t="str">
-        <v>Crutch - Single</v>
+        <v>Bunny - EP</v>
       </c>
       <c r="G90" t="str">
-        <v>3:31</v>
+        <v>2:56</v>
       </c>
       <c r="H90" t="str">
-        <v>Love Spells</v>
+        <v>People I’ve Met</v>
       </c>
       <c r="I90" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J90" t="str">
-        <v>https://music.apple.com/us/artist/love-spells/1597025563</v>
+        <v>https://music.apple.com/us/artist/people-ive-met/1853169947</v>
       </c>
       <c r="K90" t="str">
-        <v>https://music.apple.com/us/album/crutch/1895274406</v>
+        <v>https://music.apple.com/us/album/bastards/1894044276</v>
       </c>
       <c r="L90" t="str">
-        <v>Crutch - Love Spells</v>
+        <v>Bastards - People I’ve Met</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="str">
-        <v>Just A Man</v>
+        <v>Crutch</v>
       </c>
       <c r="B91" t="str">
         <v/>
       </c>
       <c r="C91" t="str">
-        <v>https://music.apple.com/us/song/just-a-man/1893736206</v>
+        <v>https://music.apple.com/us/song/crutch/6763345020</v>
       </c>
       <c r="D91" t="str">
         <v>2026-05-04</v>
@@ -3833,36 +3833,36 @@
         <v/>
       </c>
       <c r="F91" t="str">
-        <v>Just A Man - Single</v>
+        <v>Crutch - Single</v>
       </c>
       <c r="G91" t="str">
-        <v>2:38</v>
+        <v>3:31</v>
       </c>
       <c r="H91" t="str">
-        <v>MOIO</v>
+        <v>Love Spells</v>
       </c>
       <c r="I91" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J91" t="str">
-        <v>https://music.apple.com/us/artist/moio/1664183608</v>
+        <v>https://music.apple.com/us/artist/love-spells/1597025563</v>
       </c>
       <c r="K91" t="str">
-        <v>https://music.apple.com/us/album/just-a-man/1893736201</v>
+        <v>https://music.apple.com/us/album/crutch/1895274406</v>
       </c>
       <c r="L91" t="str">
-        <v>Just A Man - MOIO</v>
+        <v>Crutch - Love Spells</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="str">
-        <v>Take Care Of You</v>
+        <v>Just A Man</v>
       </c>
       <c r="B92" t="str">
         <v/>
       </c>
       <c r="C92" t="str">
-        <v>https://music.apple.com/us/song/take-care-of-you/6762283983</v>
+        <v>https://music.apple.com/us/song/just-a-man/1893736206</v>
       </c>
       <c r="D92" t="str">
         <v>2026-05-04</v>
@@ -3871,36 +3871,36 @@
         <v/>
       </c>
       <c r="F92" t="str">
-        <v>Take Care Of You - Single</v>
+        <v>Just A Man - Single</v>
       </c>
       <c r="G92" t="str">
-        <v>3:51</v>
+        <v>2:38</v>
       </c>
       <c r="H92" t="str">
-        <v>Alina Baraz</v>
+        <v>MOIO</v>
       </c>
       <c r="I92" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J92" t="str">
-        <v>https://music.apple.com/us/artist/alina-baraz/757852571</v>
+        <v>https://music.apple.com/us/artist/moio/1664183608</v>
       </c>
       <c r="K92" t="str">
-        <v>https://music.apple.com/us/album/take-care-of-you/1893646113</v>
+        <v>https://music.apple.com/us/album/just-a-man/1893736201</v>
       </c>
       <c r="L92" t="str">
-        <v>Take Care Of You - Alina Baraz</v>
+        <v>Just A Man - MOIO</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="str">
-        <v>Love You More</v>
+        <v>Take Care Of You</v>
       </c>
       <c r="B93" t="str">
         <v/>
       </c>
       <c r="C93" t="str">
-        <v>https://music.apple.com/us/song/love-you-more/1889686330</v>
+        <v>https://music.apple.com/us/song/take-care-of-you/6762283983</v>
       </c>
       <c r="D93" t="str">
         <v>2026-05-04</v>
@@ -3909,36 +3909,36 @@
         <v/>
       </c>
       <c r="F93" t="str">
-        <v>Love You More - Single</v>
+        <v>Take Care Of You - Single</v>
       </c>
       <c r="G93" t="str">
-        <v>2:48</v>
+        <v>3:51</v>
       </c>
       <c r="H93" t="str">
-        <v>Rudimental</v>
+        <v>Alina Baraz</v>
       </c>
       <c r="I93" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J93" t="str">
-        <v>https://music.apple.com/us/artist/rudimental/474022504</v>
+        <v>https://music.apple.com/us/artist/alina-baraz/757852571</v>
       </c>
       <c r="K93" t="str">
-        <v>https://music.apple.com/us/album/love-you-more/1889686315</v>
+        <v>https://music.apple.com/us/album/take-care-of-you/1893646113</v>
       </c>
       <c r="L93" t="str">
-        <v>Love You More - Rudimental</v>
+        <v>Take Care Of You - Alina Baraz</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="str">
-        <v>Construct</v>
+        <v>Love You More</v>
       </c>
       <c r="B94" t="str">
         <v/>
       </c>
       <c r="C94" t="str">
-        <v>https://music.apple.com/us/song/construct/1869323374</v>
+        <v>https://music.apple.com/us/song/love-you-more/1889686330</v>
       </c>
       <c r="D94" t="str">
         <v>2026-05-04</v>
@@ -3947,36 +3947,36 @@
         <v/>
       </c>
       <c r="F94" t="str">
-        <v>ONE</v>
+        <v>Love You More - Single</v>
       </c>
       <c r="G94" t="str">
-        <v>3:57</v>
+        <v>2:48</v>
       </c>
       <c r="H94" t="str">
-        <v>Sevendust</v>
+        <v>Rudimental</v>
       </c>
       <c r="I94" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J94" t="str">
-        <v>https://music.apple.com/us/artist/sevendust/13125174</v>
+        <v>https://music.apple.com/us/artist/rudimental/474022504</v>
       </c>
       <c r="K94" t="str">
-        <v>https://music.apple.com/us/album/construct/1869323199</v>
+        <v>https://music.apple.com/us/album/love-you-more/1889686315</v>
       </c>
       <c r="L94" t="str">
-        <v>Construct - Sevendust</v>
+        <v>Love You More - Rudimental</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="str">
-        <v>As Above So Below</v>
+        <v>Construct</v>
       </c>
       <c r="B95" t="str">
         <v/>
       </c>
       <c r="C95" t="str">
-        <v>https://music.apple.com/us/song/as-above-so-below/1872651422</v>
+        <v>https://music.apple.com/us/song/construct/1869323374</v>
       </c>
       <c r="D95" t="str">
         <v>2026-05-04</v>
@@ -3985,36 +3985,36 @@
         <v/>
       </c>
       <c r="F95" t="str">
-        <v>Into Oblivion</v>
+        <v>ONE</v>
       </c>
       <c r="G95" t="str">
-        <v>4:54</v>
+        <v>3:57</v>
       </c>
       <c r="H95" t="str">
-        <v>Venom</v>
+        <v>Sevendust</v>
       </c>
       <c r="I95" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J95" t="str">
-        <v>https://music.apple.com/us/artist/venom/3222127</v>
+        <v>https://music.apple.com/us/artist/sevendust/13125174</v>
       </c>
       <c r="K95" t="str">
-        <v>https://music.apple.com/us/album/as-above-so-below/1872651243</v>
+        <v>https://music.apple.com/us/album/construct/1869323199</v>
       </c>
       <c r="L95" t="str">
-        <v>As Above So Below - Venom</v>
+        <v>Construct - Sevendust</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="str">
-        <v>Revenant</v>
+        <v>As Above So Below</v>
       </c>
       <c r="B96" t="str">
         <v/>
       </c>
       <c r="C96" t="str">
-        <v>https://music.apple.com/us/song/revenant/6763148056</v>
+        <v>https://music.apple.com/us/song/as-above-so-below/1872651422</v>
       </c>
       <c r="D96" t="str">
         <v>2026-05-04</v>
@@ -4023,36 +4023,36 @@
         <v/>
       </c>
       <c r="F96" t="str">
-        <v>A Stranger To You</v>
+        <v>Into Oblivion</v>
       </c>
       <c r="G96" t="str">
-        <v>3:31</v>
+        <v>4:54</v>
       </c>
       <c r="H96" t="str">
-        <v>Loathe</v>
+        <v>Venom</v>
       </c>
       <c r="I96" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J96" t="str">
-        <v>https://music.apple.com/us/artist/loathe/377883434</v>
+        <v>https://music.apple.com/us/artist/venom/3222127</v>
       </c>
       <c r="K96" t="str">
-        <v>https://music.apple.com/us/album/revenant/1895184628</v>
+        <v>https://music.apple.com/us/album/as-above-so-below/1872651243</v>
       </c>
       <c r="L96" t="str">
-        <v>Revenant - Loathe</v>
+        <v>As Above So Below - Venom</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="str">
-        <v>Black Box (feat. Joe Duplantier &amp; The Mystery Of The Bulgarian Voices)</v>
+        <v>Revenant</v>
       </c>
       <c r="B97" t="str">
         <v/>
       </c>
       <c r="C97" t="str">
-        <v>https://music.apple.com/us/song/black-box-feat-joe-duplantier-the-mystery-of/6762312582</v>
+        <v>https://music.apple.com/us/song/revenant/6763148056</v>
       </c>
       <c r="D97" t="str">
         <v>2026-05-04</v>
@@ -4061,36 +4061,36 @@
         <v/>
       </c>
       <c r="F97" t="str">
-        <v>Black Box (feat. Joe Duplantier &amp; The Mystery Of The Bulgarian Voices) - Single</v>
+        <v>A Stranger To You</v>
       </c>
       <c r="G97" t="str">
-        <v>4:56</v>
+        <v>3:31</v>
       </c>
       <c r="H97" t="str">
-        <v>Bear McCreary</v>
+        <v>Loathe</v>
       </c>
       <c r="I97" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J97" t="str">
-        <v>https://music.apple.com/us/artist/bear-mccreary/204012062</v>
+        <v>https://music.apple.com/us/artist/loathe/377883434</v>
       </c>
       <c r="K97" t="str">
-        <v>https://music.apple.com/us/album/black-box-feat-joe-duplantier-the-mystery-of/1893773367</v>
+        <v>https://music.apple.com/us/album/revenant/1895184628</v>
       </c>
       <c r="L97" t="str">
-        <v>Black Box (feat. Joe Duplantier &amp; The Mystery Of The Bulgarian Voices) - Bear McCreary</v>
+        <v>Revenant - Loathe</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="str">
-        <v>Power 4</v>
+        <v>Black Box (feat. Joe Duplantier &amp; The Mystery Of The Bulgarian Voices)</v>
       </c>
       <c r="B98" t="str">
         <v/>
       </c>
       <c r="C98" t="str">
-        <v>https://music.apple.com/us/song/power-4/6763647813</v>
+        <v>https://music.apple.com/us/song/black-box-feat-joe-duplantier-the-mystery-of/6762312582</v>
       </c>
       <c r="D98" t="str">
         <v>2026-05-04</v>
@@ -4099,36 +4099,36 @@
         <v/>
       </c>
       <c r="F98" t="str">
-        <v>Power 4 - Single</v>
+        <v>Black Box (feat. Joe Duplantier &amp; The Mystery Of The Bulgarian Voices) - Single</v>
       </c>
       <c r="G98" t="str">
-        <v>1:40</v>
+        <v>4:56</v>
       </c>
       <c r="H98" t="str">
-        <v>slayr</v>
+        <v>Bear McCreary</v>
       </c>
       <c r="I98" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J98" t="str">
-        <v>https://music.apple.com/us/artist/slayr/1676805496</v>
+        <v>https://music.apple.com/us/artist/bear-mccreary/204012062</v>
       </c>
       <c r="K98" t="str">
-        <v>https://music.apple.com/us/album/power-4/1895416494</v>
+        <v>https://music.apple.com/us/album/black-box-feat-joe-duplantier-the-mystery-of/1893773367</v>
       </c>
       <c r="L98" t="str">
-        <v>Power 4 - slayr</v>
+        <v>Black Box (feat. Joe Duplantier &amp; The Mystery Of The Bulgarian Voices) - Bear McCreary</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="str">
-        <v>Too Easy</v>
+        <v>Power 4</v>
       </c>
       <c r="B99" t="str">
         <v/>
       </c>
       <c r="C99" t="str">
-        <v>https://music.apple.com/us/song/too-easy/1893814702</v>
+        <v>https://music.apple.com/us/song/power-4/6763647813</v>
       </c>
       <c r="D99" t="str">
         <v>2026-05-04</v>
@@ -4137,36 +4137,36 @@
         <v/>
       </c>
       <c r="F99" t="str">
-        <v>Too Easy - Single</v>
+        <v>Power 4 - Single</v>
       </c>
       <c r="G99" t="str">
-        <v>4:14</v>
+        <v>1:40</v>
       </c>
       <c r="H99" t="str">
-        <v>tig3r lewis</v>
+        <v>slayr</v>
       </c>
       <c r="I99" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J99" t="str">
-        <v>https://music.apple.com/us/artist/tig3r-lewis/1850089834</v>
+        <v>https://music.apple.com/us/artist/slayr/1676805496</v>
       </c>
       <c r="K99" t="str">
-        <v>https://music.apple.com/us/album/too-easy/1893814697</v>
+        <v>https://music.apple.com/us/album/power-4/1895416494</v>
       </c>
       <c r="L99" t="str">
-        <v>Too Easy - tig3r lewis</v>
+        <v>Power 4 - slayr</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="str">
-        <v>If You Want It</v>
+        <v>Too Easy</v>
       </c>
       <c r="B100" t="str">
         <v/>
       </c>
       <c r="C100" t="str">
-        <v>https://music.apple.com/us/song/if-you-want-it/1892503347</v>
+        <v>https://music.apple.com/us/song/too-easy/1893814702</v>
       </c>
       <c r="D100" t="str">
         <v>2026-05-04</v>
@@ -4175,36 +4175,36 @@
         <v/>
       </c>
       <c r="F100" t="str">
-        <v>If You Want It - Single</v>
+        <v>Too Easy - Single</v>
       </c>
       <c r="G100" t="str">
-        <v>3:56</v>
+        <v>4:14</v>
       </c>
       <c r="H100" t="str">
-        <v>ALAC</v>
+        <v>tig3r lewis</v>
       </c>
       <c r="I100" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J100" t="str">
-        <v>https://music.apple.com/us/artist/alac/1885586915</v>
+        <v>https://music.apple.com/us/artist/tig3r-lewis/1850089834</v>
       </c>
       <c r="K100" t="str">
-        <v>https://music.apple.com/us/album/if-you-want-it/1892503333</v>
+        <v>https://music.apple.com/us/album/too-easy/1893814697</v>
       </c>
       <c r="L100" t="str">
-        <v>If You Want It - ALAC</v>
+        <v>Too Easy - tig3r lewis</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="str">
-        <v>Shoplifting</v>
+        <v>If You Want It</v>
       </c>
       <c r="B101" t="str">
         <v/>
       </c>
       <c r="C101" t="str">
-        <v>https://music.apple.com/us/song/shoplifting/1852812659</v>
+        <v>https://music.apple.com/us/song/if-you-want-it/1892503347</v>
       </c>
       <c r="D101" t="str">
         <v>2026-05-04</v>
@@ -4213,68 +4213,106 @@
         <v/>
       </c>
       <c r="F101" t="str">
-        <v>Theft World</v>
+        <v>If You Want It - Single</v>
       </c>
       <c r="G101" t="str">
-        <v>3:02</v>
+        <v>3:56</v>
       </c>
       <c r="H101" t="str">
-        <v>Lip Critic</v>
+        <v>ALAC</v>
       </c>
       <c r="I101" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J101" t="str">
-        <v>https://music.apple.com/us/artist/lip-critic/1458046064</v>
+        <v>https://music.apple.com/us/artist/alac/1885586915</v>
       </c>
       <c r="K101" t="str">
-        <v>https://music.apple.com/us/album/shoplifting/1852812554</v>
+        <v>https://music.apple.com/us/album/if-you-want-it/1892503333</v>
       </c>
       <c r="L101" t="str">
-        <v>Shoplifting - Lip Critic</v>
+        <v>If You Want It - ALAC</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="str">
+        <v>Shoplifting</v>
+      </c>
+      <c r="B102" t="str">
+        <v/>
+      </c>
+      <c r="C102" t="str">
+        <v>https://music.apple.com/us/song/shoplifting/1852812659</v>
+      </c>
+      <c r="D102" t="str">
+        <v>2026-05-04</v>
+      </c>
+      <c r="E102" t="str">
+        <v/>
+      </c>
+      <c r="F102" t="str">
+        <v>Theft World</v>
+      </c>
+      <c r="G102" t="str">
+        <v>3:02</v>
+      </c>
+      <c r="H102" t="str">
+        <v>Lip Critic</v>
+      </c>
+      <c r="I102" t="str">
+        <v>מוזיקה לועזית חדשה</v>
+      </c>
+      <c r="J102" t="str">
+        <v>https://music.apple.com/us/artist/lip-critic/1458046064</v>
+      </c>
+      <c r="K102" t="str">
+        <v>https://music.apple.com/us/album/shoplifting/1852812554</v>
+      </c>
+      <c r="L102" t="str">
+        <v>Shoplifting - Lip Critic</v>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="str">
         <v>Endlessly (feat. BEA1991)</v>
       </c>
-      <c r="B102" t="str">
-        <v/>
-      </c>
-      <c r="C102" t="str">
+      <c r="B103" t="str">
+        <v/>
+      </c>
+      <c r="C103" t="str">
         <v>https://music.apple.com/us/song/endlessly-feat-bea1991/1876022833</v>
       </c>
-      <c r="D102" t="str">
-        <v>2026-05-04</v>
-      </c>
-      <c r="E102" t="str">
-        <v/>
-      </c>
-      <c r="F102" t="str">
+      <c r="D103" t="str">
+        <v>2026-05-04</v>
+      </c>
+      <c r="E103" t="str">
+        <v/>
+      </c>
+      <c r="F103" t="str">
         <v>Fold</v>
       </c>
-      <c r="G102" t="str">
+      <c r="G103" t="str">
         <v>5:57</v>
       </c>
-      <c r="H102" t="str">
+      <c r="H103" t="str">
         <v>Jump Source</v>
       </c>
-      <c r="I102" t="str">
-        <v>מוזיקה לועזית חדשה</v>
-      </c>
-      <c r="J102" t="str">
+      <c r="I103" t="str">
+        <v>מוזיקה לועזית חדשה</v>
+      </c>
+      <c r="J103" t="str">
         <v>https://music.apple.com/us/artist/jump-source/1169060818</v>
       </c>
-      <c r="K102" t="str">
+      <c r="K103" t="str">
         <v>https://music.apple.com/us/album/endlessly-feat-bea1991/1876022817</v>
       </c>
-      <c r="L102" t="str">
+      <c r="L103" t="str">
         <v>Endlessly (feat. BEA1991) - Jump Source</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:L102"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:L103"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/data/tags/מוזיקה לועזית חדשה/sites/apple-music-playlist/2026-05-week01/titles.xlsx
+++ b/data/tags/מוזיקה לועזית חדשה/sites/apple-music-playlist/2026-05-week01/titles.xlsx
@@ -2579,7 +2579,7 @@
         <v/>
       </c>
       <c r="F58" t="str">
-        <v>ADDENDUM</v>
+        <v>ADDENDUM - EP</v>
       </c>
       <c r="G58" t="str">
         <v>3:23</v>

--- a/data/tags/מוזיקה לועזית חדשה/sites/apple-music-playlist/2026-05-week01/titles.xlsx
+++ b/data/tags/מוזיקה לועזית חדשה/sites/apple-music-playlist/2026-05-week01/titles.xlsx
@@ -445,7 +445,7 @@
         <v>https://music.apple.com/us/song/robotic-love/6763638857</v>
       </c>
       <c r="D2" t="str">
-        <v>2026-05-04</v>
+        <v>2026-05-05</v>
       </c>
       <c r="E2" t="str">
         <v/>
@@ -483,7 +483,7 @@
         <v>https://music.apple.com/us/song/eurosummer-girls-trip/1894058279</v>
       </c>
       <c r="D3" t="str">
-        <v>2026-05-04</v>
+        <v>2026-05-05</v>
       </c>
       <c r="E3" t="str">
         <v/>
@@ -521,7 +521,7 @@
         <v>https://music.apple.com/us/song/shape-of-a-woman/6764429252</v>
       </c>
       <c r="D4" t="str">
-        <v>2026-05-04</v>
+        <v>2026-05-05</v>
       </c>
       <c r="E4" t="str">
         <v/>
@@ -559,7 +559,7 @@
         <v>https://music.apple.com/us/song/bring-your-love/1892545227</v>
       </c>
       <c r="D5" t="str">
-        <v>2026-05-04</v>
+        <v>2026-05-05</v>
       </c>
       <c r="E5" t="str">
         <v/>
@@ -597,7 +597,7 @@
         <v>https://music.apple.com/us/song/horses-and-divorces/1883177267</v>
       </c>
       <c r="D6" t="str">
-        <v>2026-05-04</v>
+        <v>2026-05-05</v>
       </c>
       <c r="E6" t="str">
         <v/>
@@ -635,7 +635,7 @@
         <v>https://music.apple.com/us/song/staying-still/6762758806</v>
       </c>
       <c r="D7" t="str">
-        <v>2026-05-04</v>
+        <v>2026-05-05</v>
       </c>
       <c r="E7" t="str">
         <v/>
@@ -673,7 +673,7 @@
         <v>https://music.apple.com/us/song/fine-place-to-die/6764686279</v>
       </c>
       <c r="D8" t="str">
-        <v>2026-05-04</v>
+        <v>2026-05-05</v>
       </c>
       <c r="E8" t="str">
         <v/>
@@ -711,7 +711,7 @@
         <v>https://music.apple.com/us/song/mutt/6763145178</v>
       </c>
       <c r="D9" t="str">
-        <v>2026-05-04</v>
+        <v>2026-05-05</v>
       </c>
       <c r="E9" t="str">
         <v/>
@@ -749,7 +749,7 @@
         <v>https://music.apple.com/us/song/fire-away-feat-slayyyter/1892422570</v>
       </c>
       <c r="D10" t="str">
-        <v>2026-05-04</v>
+        <v>2026-05-05</v>
       </c>
       <c r="E10" t="str">
         <v/>
@@ -787,7 +787,7 @@
         <v>https://music.apple.com/us/song/lioness/1878649397</v>
       </c>
       <c r="D11" t="str">
-        <v>2026-05-04</v>
+        <v>2026-05-05</v>
       </c>
       <c r="E11" t="str">
         <v/>
@@ -825,7 +825,7 @@
         <v>https://music.apple.com/us/song/its-ok/6763134121</v>
       </c>
       <c r="D12" t="str">
-        <v>2026-05-04</v>
+        <v>2026-05-05</v>
       </c>
       <c r="E12" t="str">
         <v/>
@@ -863,7 +863,7 @@
         <v>https://music.apple.com/us/song/promise/6763162287</v>
       </c>
       <c r="D13" t="str">
-        <v>2026-05-04</v>
+        <v>2026-05-05</v>
       </c>
       <c r="E13" t="str">
         <v/>
@@ -901,7 +901,7 @@
         <v>https://music.apple.com/us/song/cool-buzz/1880470657</v>
       </c>
       <c r="D14" t="str">
-        <v>2026-05-04</v>
+        <v>2026-05-05</v>
       </c>
       <c r="E14" t="str">
         <v/>
@@ -939,7 +939,7 @@
         <v>https://music.apple.com/us/song/material-lover/6764429256</v>
       </c>
       <c r="D15" t="str">
-        <v>2026-05-04</v>
+        <v>2026-05-05</v>
       </c>
       <c r="E15" t="str">
         <v/>
@@ -977,7 +977,7 @@
         <v>https://music.apple.com/us/song/fallin-feat-leon-thomas/6764419265</v>
       </c>
       <c r="D16" t="str">
-        <v>2026-05-04</v>
+        <v>2026-05-05</v>
       </c>
       <c r="E16" t="str">
         <v/>
@@ -1015,7 +1015,7 @@
         <v>https://music.apple.com/us/song/echo/6763379683</v>
       </c>
       <c r="D17" t="str">
-        <v>2026-05-04</v>
+        <v>2026-05-05</v>
       </c>
       <c r="E17" t="str">
         <v/>
@@ -1053,7 +1053,7 @@
         <v>https://music.apple.com/us/song/blackberry-marmalade/1887627837</v>
       </c>
       <c r="D18" t="str">
-        <v>2026-05-04</v>
+        <v>2026-05-05</v>
       </c>
       <c r="E18" t="str">
         <v/>
@@ -1091,7 +1091,7 @@
         <v>https://music.apple.com/us/song/ricky-bobby/6764406571</v>
       </c>
       <c r="D19" t="str">
-        <v>2026-05-04</v>
+        <v>2026-05-05</v>
       </c>
       <c r="E19" t="str">
         <v/>
@@ -1129,7 +1129,7 @@
         <v>https://music.apple.com/us/song/te-entiendo-remix/6763665638</v>
       </c>
       <c r="D20" t="str">
-        <v>2026-05-04</v>
+        <v>2026-05-05</v>
       </c>
       <c r="E20" t="str">
         <v/>
@@ -1167,7 +1167,7 @@
         <v>https://music.apple.com/us/song/dont-worry-baby/1894294411</v>
       </c>
       <c r="D21" t="str">
-        <v>2026-05-04</v>
+        <v>2026-05-05</v>
       </c>
       <c r="E21" t="str">
         <v/>
@@ -1205,7 +1205,7 @@
         <v>https://music.apple.com/us/song/bitch/6763622110</v>
       </c>
       <c r="D22" t="str">
-        <v>2026-05-04</v>
+        <v>2026-05-05</v>
       </c>
       <c r="E22" t="str">
         <v/>
@@ -1243,7 +1243,7 @@
         <v>https://music.apple.com/us/song/just-wanna-cry/6763414703</v>
       </c>
       <c r="D23" t="str">
-        <v>2026-05-04</v>
+        <v>2026-05-05</v>
       </c>
       <c r="E23" t="str">
         <v/>
@@ -1281,7 +1281,7 @@
         <v>https://music.apple.com/us/song/carry-the-weight/6763611647</v>
       </c>
       <c r="D24" t="str">
-        <v>2026-05-04</v>
+        <v>2026-05-05</v>
       </c>
       <c r="E24" t="str">
         <v/>
@@ -1319,7 +1319,7 @@
         <v>https://music.apple.com/us/song/prostitute/1894092341</v>
       </c>
       <c r="D25" t="str">
-        <v>2026-05-04</v>
+        <v>2026-05-05</v>
       </c>
       <c r="E25" t="str">
         <v/>
@@ -1357,7 +1357,7 @@
         <v>https://music.apple.com/us/song/im-not-joking/1872842623</v>
       </c>
       <c r="D26" t="str">
-        <v>2026-05-04</v>
+        <v>2026-05-05</v>
       </c>
       <c r="E26" t="str">
         <v/>
@@ -1395,7 +1395,7 @@
         <v>https://music.apple.com/us/song/ruca/6763671002</v>
       </c>
       <c r="D27" t="str">
-        <v>2026-05-04</v>
+        <v>2026-05-05</v>
       </c>
       <c r="E27" t="str">
         <v/>
@@ -1433,7 +1433,7 @@
         <v>https://music.apple.com/us/song/make-you-fight/1892332386</v>
       </c>
       <c r="D28" t="str">
-        <v>2026-05-04</v>
+        <v>2026-05-05</v>
       </c>
       <c r="E28" t="str">
         <v/>
@@ -1471,7 +1471,7 @@
         <v>https://music.apple.com/us/song/n0rth4evr/6763302230</v>
       </c>
       <c r="D29" t="str">
-        <v>2026-05-04</v>
+        <v>2026-05-05</v>
       </c>
       <c r="E29" t="str">
         <v/>
@@ -1509,7 +1509,7 @@
         <v>https://music.apple.com/us/song/boy-in-red/1892543110</v>
       </c>
       <c r="D30" t="str">
-        <v>2026-05-04</v>
+        <v>2026-05-05</v>
       </c>
       <c r="E30" t="str">
         <v/>
@@ -1547,7 +1547,7 @@
         <v>https://music.apple.com/us/song/ea-ea-ea/6763438376</v>
       </c>
       <c r="D31" t="str">
-        <v>2026-05-04</v>
+        <v>2026-05-05</v>
       </c>
       <c r="E31" t="str">
         <v/>
@@ -1585,7 +1585,7 @@
         <v>https://music.apple.com/us/song/just-a-man/6762944365</v>
       </c>
       <c r="D32" t="str">
-        <v>2026-05-04</v>
+        <v>2026-05-05</v>
       </c>
       <c r="E32" t="str">
         <v/>
@@ -1623,7 +1623,7 @@
         <v>https://music.apple.com/us/song/the-observer/1891982314</v>
       </c>
       <c r="D33" t="str">
-        <v>2026-05-04</v>
+        <v>2026-05-05</v>
       </c>
       <c r="E33" t="str">
         <v/>
@@ -1661,7 +1661,7 @@
         <v>https://music.apple.com/us/song/heroine/6762693177</v>
       </c>
       <c r="D34" t="str">
-        <v>2026-05-04</v>
+        <v>2026-05-05</v>
       </c>
       <c r="E34" t="str">
         <v/>
@@ -1699,7 +1699,7 @@
         <v>https://music.apple.com/us/song/do-me-right/6764667658</v>
       </c>
       <c r="D35" t="str">
-        <v>2026-05-04</v>
+        <v>2026-05-05</v>
       </c>
       <c r="E35" t="str">
         <v/>
@@ -1737,7 +1737,7 @@
         <v>https://music.apple.com/us/song/its-me/1887194026</v>
       </c>
       <c r="D36" t="str">
-        <v>2026-05-04</v>
+        <v>2026-05-05</v>
       </c>
       <c r="E36" t="str">
         <v/>
@@ -1775,7 +1775,7 @@
         <v>https://music.apple.com/us/song/the-precipice/1891830326</v>
       </c>
       <c r="D37" t="str">
-        <v>2026-05-04</v>
+        <v>2026-05-05</v>
       </c>
       <c r="E37" t="str">
         <v/>
@@ -1813,7 +1813,7 @@
         <v>https://music.apple.com/us/song/hello-lonesome/1892466003</v>
       </c>
       <c r="D38" t="str">
-        <v>2026-05-04</v>
+        <v>2026-05-05</v>
       </c>
       <c r="E38" t="str">
         <v/>
@@ -1851,7 +1851,7 @@
         <v>https://music.apple.com/us/song/trippin-opera-edit/6764648776</v>
       </c>
       <c r="D39" t="str">
-        <v>2026-05-04</v>
+        <v>2026-05-05</v>
       </c>
       <c r="E39" t="str">
         <v/>
@@ -1889,7 +1889,7 @@
         <v>https://music.apple.com/us/song/the-mandalorian-and-grogu-boys-noize-remix-from-star/6764131630</v>
       </c>
       <c r="D40" t="str">
-        <v>2026-05-04</v>
+        <v>2026-05-05</v>
       </c>
       <c r="E40" t="str">
         <v/>
@@ -1927,7 +1927,7 @@
         <v>https://music.apple.com/us/song/blow-my-mind-ca7riel-paco-amoroso-version/1894344140</v>
       </c>
       <c r="D41" t="str">
-        <v>2026-05-04</v>
+        <v>2026-05-05</v>
       </c>
       <c r="E41" t="str">
         <v/>
@@ -1965,7 +1965,7 @@
         <v>https://music.apple.com/us/song/bring-that-body/6764009310</v>
       </c>
       <c r="D42" t="str">
-        <v>2026-05-04</v>
+        <v>2026-05-05</v>
       </c>
       <c r="E42" t="str">
         <v/>
@@ -2003,7 +2003,7 @@
         <v>https://music.apple.com/us/song/star/1891845608</v>
       </c>
       <c r="D43" t="str">
-        <v>2026-05-04</v>
+        <v>2026-05-05</v>
       </c>
       <c r="E43" t="str">
         <v/>
@@ -2041,7 +2041,7 @@
         <v>https://music.apple.com/us/song/whats-a-little-rain/1885061171</v>
       </c>
       <c r="D44" t="str">
-        <v>2026-05-04</v>
+        <v>2026-05-05</v>
       </c>
       <c r="E44" t="str">
         <v/>
@@ -2079,7 +2079,7 @@
         <v>https://music.apple.com/us/song/evergreen/1866700315</v>
       </c>
       <c r="D45" t="str">
-        <v>2026-05-04</v>
+        <v>2026-05-05</v>
       </c>
       <c r="E45" t="str">
         <v/>
@@ -2117,7 +2117,7 @@
         <v>https://music.apple.com/us/song/she-does-it-right/1873477957</v>
       </c>
       <c r="D46" t="str">
-        <v>2026-05-04</v>
+        <v>2026-05-05</v>
       </c>
       <c r="E46" t="str">
         <v/>
@@ -2155,7 +2155,7 @@
         <v>https://music.apple.com/us/song/punching-the-flowers/1878362636</v>
       </c>
       <c r="D47" t="str">
-        <v>2026-05-04</v>
+        <v>2026-05-05</v>
       </c>
       <c r="E47" t="str">
         <v/>
@@ -2193,7 +2193,7 @@
         <v>https://music.apple.com/us/song/how-did-you-know/1888553137</v>
       </c>
       <c r="D48" t="str">
-        <v>2026-05-04</v>
+        <v>2026-05-05</v>
       </c>
       <c r="E48" t="str">
         <v/>
@@ -2231,7 +2231,7 @@
         <v>https://music.apple.com/us/song/summer-breeze/6763360727</v>
       </c>
       <c r="D49" t="str">
-        <v>2026-05-04</v>
+        <v>2026-05-05</v>
       </c>
       <c r="E49" t="str">
         <v/>
@@ -2269,7 +2269,7 @@
         <v>https://music.apple.com/us/song/sound-of-a-woman/1859763367</v>
       </c>
       <c r="D50" t="str">
-        <v>2026-05-04</v>
+        <v>2026-05-05</v>
       </c>
       <c r="E50" t="str">
         <v/>
@@ -2307,7 +2307,7 @@
         <v>https://music.apple.com/us/song/my-life/1893157347</v>
       </c>
       <c r="D51" t="str">
-        <v>2026-05-04</v>
+        <v>2026-05-05</v>
       </c>
       <c r="E51" t="str">
         <v/>
@@ -2345,7 +2345,7 @@
         <v>https://music.apple.com/us/song/ribcage/1893155593</v>
       </c>
       <c r="D52" t="str">
-        <v>2026-05-04</v>
+        <v>2026-05-05</v>
       </c>
       <c r="E52" t="str">
         <v/>
@@ -2383,7 +2383,7 @@
         <v>https://music.apple.com/us/song/i-loved-you-then/1878232821</v>
       </c>
       <c r="D53" t="str">
-        <v>2026-05-04</v>
+        <v>2026-05-05</v>
       </c>
       <c r="E53" t="str">
         <v/>
@@ -2421,7 +2421,7 @@
         <v>https://music.apple.com/us/song/ill-let-you-finish/1891844342</v>
       </c>
       <c r="D54" t="str">
-        <v>2026-05-04</v>
+        <v>2026-05-05</v>
       </c>
       <c r="E54" t="str">
         <v/>
@@ -2459,7 +2459,7 @@
         <v>https://music.apple.com/us/song/it-gets-me-through/1884798927</v>
       </c>
       <c r="D55" t="str">
-        <v>2026-05-04</v>
+        <v>2026-05-05</v>
       </c>
       <c r="E55" t="str">
         <v/>
@@ -2497,7 +2497,7 @@
         <v>https://music.apple.com/us/song/the-author/6763327641</v>
       </c>
       <c r="D56" t="str">
-        <v>2026-05-04</v>
+        <v>2026-05-05</v>
       </c>
       <c r="E56" t="str">
         <v/>
@@ -2535,7 +2535,7 @@
         <v>https://music.apple.com/us/song/want-me-back-feat-tors/1889370756</v>
       </c>
       <c r="D57" t="str">
-        <v>2026-05-04</v>
+        <v>2026-05-05</v>
       </c>
       <c r="E57" t="str">
         <v/>
@@ -2573,7 +2573,7 @@
         <v>https://music.apple.com/us/song/ruin/1886537117</v>
       </c>
       <c r="D58" t="str">
-        <v>2026-05-04</v>
+        <v>2026-05-05</v>
       </c>
       <c r="E58" t="str">
         <v/>
@@ -2611,7 +2611,7 @@
         <v>https://music.apple.com/us/song/i-know-i-know/1894354139</v>
       </c>
       <c r="D59" t="str">
-        <v>2026-05-04</v>
+        <v>2026-05-05</v>
       </c>
       <c r="E59" t="str">
         <v/>
@@ -2649,7 +2649,7 @@
         <v>https://music.apple.com/us/song/drive-all-night/6763189759</v>
       </c>
       <c r="D60" t="str">
-        <v>2026-05-04</v>
+        <v>2026-05-05</v>
       </c>
       <c r="E60" t="str">
         <v/>
@@ -2687,7 +2687,7 @@
         <v>https://music.apple.com/us/song/aint-u-tired/6763115235</v>
       </c>
       <c r="D61" t="str">
-        <v>2026-05-04</v>
+        <v>2026-05-05</v>
       </c>
       <c r="E61" t="str">
         <v/>
@@ -2725,7 +2725,7 @@
         <v>https://music.apple.com/us/song/boys-in-blue/1892436920</v>
       </c>
       <c r="D62" t="str">
-        <v>2026-05-04</v>
+        <v>2026-05-05</v>
       </c>
       <c r="E62" t="str">
         <v/>
@@ -2763,7 +2763,7 @@
         <v>https://music.apple.com/us/song/salma-hayek/1891815286</v>
       </c>
       <c r="D63" t="str">
-        <v>2026-05-04</v>
+        <v>2026-05-05</v>
       </c>
       <c r="E63" t="str">
         <v/>
@@ -2801,7 +2801,7 @@
         <v>https://music.apple.com/us/song/stubborn-mouth/1893194800</v>
       </c>
       <c r="D64" t="str">
-        <v>2026-05-04</v>
+        <v>2026-05-05</v>
       </c>
       <c r="E64" t="str">
         <v/>
@@ -2839,7 +2839,7 @@
         <v>https://music.apple.com/us/song/hallucination/6764110976</v>
       </c>
       <c r="D65" t="str">
-        <v>2026-05-04</v>
+        <v>2026-05-05</v>
       </c>
       <c r="E65" t="str">
         <v/>
@@ -2877,7 +2877,7 @@
         <v>https://music.apple.com/us/song/in-da-jungle/1891136400</v>
       </c>
       <c r="D66" t="str">
-        <v>2026-05-04</v>
+        <v>2026-05-05</v>
       </c>
       <c r="E66" t="str">
         <v/>
@@ -2915,7 +2915,7 @@
         <v>https://music.apple.com/us/song/fall-short/1894662749</v>
       </c>
       <c r="D67" t="str">
-        <v>2026-05-04</v>
+        <v>2026-05-05</v>
       </c>
       <c r="E67" t="str">
         <v/>
@@ -2953,7 +2953,7 @@
         <v>https://music.apple.com/us/song/irish-goodbye-feat-kae-tempest/1862224205</v>
       </c>
       <c r="D68" t="str">
-        <v>2026-05-04</v>
+        <v>2026-05-05</v>
       </c>
       <c r="E68" t="str">
         <v/>
@@ -2991,7 +2991,7 @@
         <v>https://music.apple.com/us/song/1989/1893089382</v>
       </c>
       <c r="D69" t="str">
-        <v>2026-05-04</v>
+        <v>2026-05-05</v>
       </c>
       <c r="E69" t="str">
         <v/>
@@ -3029,7 +3029,7 @@
         <v>https://music.apple.com/us/song/no-more-regrets/1893191803</v>
       </c>
       <c r="D70" t="str">
-        <v>2026-05-04</v>
+        <v>2026-05-05</v>
       </c>
       <c r="E70" t="str">
         <v/>
@@ -3067,7 +3067,7 @@
         <v>https://music.apple.com/us/song/drum-machine/1840517102</v>
       </c>
       <c r="D71" t="str">
-        <v>2026-05-04</v>
+        <v>2026-05-05</v>
       </c>
       <c r="E71" t="str">
         <v/>
@@ -3105,7 +3105,7 @@
         <v>https://music.apple.com/us/song/im-perfect/1893181359</v>
       </c>
       <c r="D72" t="str">
-        <v>2026-05-04</v>
+        <v>2026-05-05</v>
       </c>
       <c r="E72" t="str">
         <v/>
@@ -3143,7 +3143,7 @@
         <v>https://music.apple.com/us/song/theme-for-a-train-journey/1880699785</v>
       </c>
       <c r="D73" t="str">
-        <v>2026-05-04</v>
+        <v>2026-05-05</v>
       </c>
       <c r="E73" t="str">
         <v/>
@@ -3181,7 +3181,7 @@
         <v>https://music.apple.com/us/song/bitch-you-weird/6763395875</v>
       </c>
       <c r="D74" t="str">
-        <v>2026-05-04</v>
+        <v>2026-05-05</v>
       </c>
       <c r="E74" t="str">
         <v/>
@@ -3219,7 +3219,7 @@
         <v>https://music.apple.com/us/song/blackbird-rising/1887166611</v>
       </c>
       <c r="D75" t="str">
-        <v>2026-05-04</v>
+        <v>2026-05-05</v>
       </c>
       <c r="E75" t="str">
         <v/>
@@ -3257,7 +3257,7 @@
         <v>https://music.apple.com/us/song/usher-in-the-spirit/6763373678</v>
       </c>
       <c r="D76" t="str">
-        <v>2026-05-04</v>
+        <v>2026-05-05</v>
       </c>
       <c r="E76" t="str">
         <v/>
@@ -3295,7 +3295,7 @@
         <v>https://music.apple.com/us/song/moonlight/1892950791</v>
       </c>
       <c r="D77" t="str">
-        <v>2026-05-04</v>
+        <v>2026-05-05</v>
       </c>
       <c r="E77" t="str">
         <v/>
@@ -3333,7 +3333,7 @@
         <v>https://music.apple.com/us/song/hands-on-me/1893960365</v>
       </c>
       <c r="D78" t="str">
-        <v>2026-05-04</v>
+        <v>2026-05-05</v>
       </c>
       <c r="E78" t="str">
         <v/>
@@ -3371,7 +3371,7 @@
         <v>https://music.apple.com/us/song/closure/1892418294</v>
       </c>
       <c r="D79" t="str">
-        <v>2026-05-04</v>
+        <v>2026-05-05</v>
       </c>
       <c r="E79" t="str">
         <v/>
@@ -3409,7 +3409,7 @@
         <v>https://music.apple.com/us/song/hots-4-u/1891478541</v>
       </c>
       <c r="D80" t="str">
-        <v>2026-05-04</v>
+        <v>2026-05-05</v>
       </c>
       <c r="E80" t="str">
         <v/>
@@ -3447,7 +3447,7 @@
         <v>https://music.apple.com/us/song/cule-poco-sirena-besarico-coste%C3%B1a/1893480200</v>
       </c>
       <c r="D81" t="str">
-        <v>2026-05-04</v>
+        <v>2026-05-05</v>
       </c>
       <c r="E81" t="str">
         <v/>
@@ -3485,7 +3485,7 @@
         <v>https://music.apple.com/us/song/the-coin-toss/1894872115</v>
       </c>
       <c r="D82" t="str">
-        <v>2026-05-04</v>
+        <v>2026-05-05</v>
       </c>
       <c r="E82" t="str">
         <v/>
@@ -3523,7 +3523,7 @@
         <v>https://music.apple.com/us/song/bottles-lights/6763041153</v>
       </c>
       <c r="D83" t="str">
-        <v>2026-05-04</v>
+        <v>2026-05-05</v>
       </c>
       <c r="E83" t="str">
         <v/>
@@ -3561,7 +3561,7 @@
         <v>https://music.apple.com/us/song/perfect-for-me/6762879981</v>
       </c>
       <c r="D84" t="str">
-        <v>2026-05-04</v>
+        <v>2026-05-05</v>
       </c>
       <c r="E84" t="str">
         <v/>
@@ -3599,7 +3599,7 @@
         <v>https://music.apple.com/us/song/so/1893162424</v>
       </c>
       <c r="D85" t="str">
-        <v>2026-05-04</v>
+        <v>2026-05-05</v>
       </c>
       <c r="E85" t="str">
         <v/>
@@ -3637,7 +3637,7 @@
         <v>https://music.apple.com/us/song/pase-y-pase/1894076490</v>
       </c>
       <c r="D86" t="str">
-        <v>2026-05-04</v>
+        <v>2026-05-05</v>
       </c>
       <c r="E86" t="str">
         <v/>
@@ -3675,7 +3675,7 @@
         <v>https://music.apple.com/us/song/agou%C3%A9-dambala-yanvalou-1/1888242486</v>
       </c>
       <c r="D87" t="str">
-        <v>2026-05-04</v>
+        <v>2026-05-05</v>
       </c>
       <c r="E87" t="str">
         <v/>
@@ -3713,7 +3713,7 @@
         <v>https://music.apple.com/us/song/aljahalat/1889267983</v>
       </c>
       <c r="D88" t="str">
-        <v>2026-05-04</v>
+        <v>2026-05-05</v>
       </c>
       <c r="E88" t="str">
         <v/>
@@ -3751,7 +3751,7 @@
         <v>https://music.apple.com/us/song/puleza/1893765840</v>
       </c>
       <c r="D89" t="str">
-        <v>2026-05-04</v>
+        <v>2026-05-05</v>
       </c>
       <c r="E89" t="str">
         <v/>
@@ -3789,7 +3789,7 @@
         <v>https://music.apple.com/us/song/bastards/6762403102</v>
       </c>
       <c r="D90" t="str">
-        <v>2026-05-04</v>
+        <v>2026-05-05</v>
       </c>
       <c r="E90" t="str">
         <v/>
@@ -3827,7 +3827,7 @@
         <v>https://music.apple.com/us/song/crutch/6763345020</v>
       </c>
       <c r="D91" t="str">
-        <v>2026-05-04</v>
+        <v>2026-05-05</v>
       </c>
       <c r="E91" t="str">
         <v/>
@@ -3865,7 +3865,7 @@
         <v>https://music.apple.com/us/song/just-a-man/1893736206</v>
       </c>
       <c r="D92" t="str">
-        <v>2026-05-04</v>
+        <v>2026-05-05</v>
       </c>
       <c r="E92" t="str">
         <v/>
@@ -3903,7 +3903,7 @@
         <v>https://music.apple.com/us/song/take-care-of-you/6762283983</v>
       </c>
       <c r="D93" t="str">
-        <v>2026-05-04</v>
+        <v>2026-05-05</v>
       </c>
       <c r="E93" t="str">
         <v/>
@@ -3941,7 +3941,7 @@
         <v>https://music.apple.com/us/song/love-you-more/1889686330</v>
       </c>
       <c r="D94" t="str">
-        <v>2026-05-04</v>
+        <v>2026-05-05</v>
       </c>
       <c r="E94" t="str">
         <v/>
@@ -3979,7 +3979,7 @@
         <v>https://music.apple.com/us/song/construct/1869323374</v>
       </c>
       <c r="D95" t="str">
-        <v>2026-05-04</v>
+        <v>2026-05-05</v>
       </c>
       <c r="E95" t="str">
         <v/>
@@ -4017,7 +4017,7 @@
         <v>https://music.apple.com/us/song/as-above-so-below/1872651422</v>
       </c>
       <c r="D96" t="str">
-        <v>2026-05-04</v>
+        <v>2026-05-05</v>
       </c>
       <c r="E96" t="str">
         <v/>
@@ -4055,7 +4055,7 @@
         <v>https://music.apple.com/us/song/revenant/6763148056</v>
       </c>
       <c r="D97" t="str">
-        <v>2026-05-04</v>
+        <v>2026-05-05</v>
       </c>
       <c r="E97" t="str">
         <v/>
@@ -4093,7 +4093,7 @@
         <v>https://music.apple.com/us/song/black-box-feat-joe-duplantier-the-mystery-of/6762312582</v>
       </c>
       <c r="D98" t="str">
-        <v>2026-05-04</v>
+        <v>2026-05-05</v>
       </c>
       <c r="E98" t="str">
         <v/>
@@ -4131,7 +4131,7 @@
         <v>https://music.apple.com/us/song/power-4/6763647813</v>
       </c>
       <c r="D99" t="str">
-        <v>2026-05-04</v>
+        <v>2026-05-05</v>
       </c>
       <c r="E99" t="str">
         <v/>
@@ -4169,7 +4169,7 @@
         <v>https://music.apple.com/us/song/too-easy/1893814702</v>
       </c>
       <c r="D100" t="str">
-        <v>2026-05-04</v>
+        <v>2026-05-05</v>
       </c>
       <c r="E100" t="str">
         <v/>
@@ -4207,7 +4207,7 @@
         <v>https://music.apple.com/us/song/if-you-want-it/1892503347</v>
       </c>
       <c r="D101" t="str">
-        <v>2026-05-04</v>
+        <v>2026-05-05</v>
       </c>
       <c r="E101" t="str">
         <v/>
@@ -4245,7 +4245,7 @@
         <v>https://music.apple.com/us/song/shoplifting/1852812659</v>
       </c>
       <c r="D102" t="str">
-        <v>2026-05-04</v>
+        <v>2026-05-05</v>
       </c>
       <c r="E102" t="str">
         <v/>
@@ -4283,7 +4283,7 @@
         <v>https://music.apple.com/us/song/endlessly-feat-bea1991/1876022833</v>
       </c>
       <c r="D103" t="str">
-        <v>2026-05-04</v>
+        <v>2026-05-05</v>
       </c>
       <c r="E103" t="str">
         <v/>

--- a/data/tags/מוזיקה לועזית חדשה/sites/apple-music-playlist/2026-05-week01/titles.xlsx
+++ b/data/tags/מוזיקה לועזית חדשה/sites/apple-music-playlist/2026-05-week01/titles.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L103"/>
+  <dimension ref="A1:L104"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -436,13 +436,13 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>Robotic Love</v>
+        <v>linknb</v>
       </c>
       <c r="B2" t="str">
         <v/>
       </c>
       <c r="C2" t="str">
-        <v>https://music.apple.com/us/song/robotic-love/6763638857</v>
+        <v>https://music.apple.com/us/song/linknb/1888561848</v>
       </c>
       <c r="D2" t="str">
         <v>2026-05-05</v>
@@ -451,25 +451,25 @@
         <v/>
       </c>
       <c r="F2" t="str">
-        <v>Robotic Love - Single</v>
+        <v>new avatar</v>
       </c>
       <c r="G2" t="str">
-        <v>3:25</v>
+        <v>1:55</v>
       </c>
       <c r="H2" t="str">
-        <v>elkan</v>
+        <v>Kelela</v>
       </c>
       <c r="I2" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J2" t="str">
-        <v>https://music.apple.com/us/artist/elkan/1805013361</v>
+        <v>https://music.apple.com/us/artist/kelela/549186342</v>
       </c>
       <c r="K2" t="str">
-        <v>https://music.apple.com/us/album/robotic-love/1895412608</v>
+        <v>https://music.apple.com/us/album/linknb/1888561538</v>
       </c>
       <c r="L2" t="str">
-        <v>Robotic Love - elkan</v>
+        <v>linknb - Kelela</v>
       </c>
     </row>
     <row r="3">
@@ -778,13 +778,13 @@
     </row>
     <row r="11">
       <c r="A11" t="str">
-        <v>Lioness</v>
+        <v>Robotic Love</v>
       </c>
       <c r="B11" t="str">
         <v/>
       </c>
       <c r="C11" t="str">
-        <v>https://music.apple.com/us/song/lioness/1878649397</v>
+        <v>https://music.apple.com/us/song/robotic-love/6763638857</v>
       </c>
       <c r="D11" t="str">
         <v>2026-05-05</v>
@@ -793,36 +793,36 @@
         <v/>
       </c>
       <c r="F11" t="str">
-        <v>MAITREYA CORSO</v>
+        <v>Robotic Love - Single</v>
       </c>
       <c r="G11" t="str">
-        <v>3:32</v>
+        <v>3:25</v>
       </c>
       <c r="H11" t="str">
-        <v>Maya Hawke</v>
+        <v>elkan</v>
       </c>
       <c r="I11" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J11" t="str">
-        <v>https://music.apple.com/us/artist/maya-hawke/1473393677</v>
+        <v>https://music.apple.com/us/artist/elkan/1805013361</v>
       </c>
       <c r="K11" t="str">
-        <v>https://music.apple.com/us/album/lioness/1878649394</v>
+        <v>https://music.apple.com/us/album/robotic-love/1895412608</v>
       </c>
       <c r="L11" t="str">
-        <v>Lioness - Maya Hawke</v>
+        <v>Robotic Love - elkan</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="str">
-        <v>IT'S OK</v>
+        <v>Lioness</v>
       </c>
       <c r="B12" t="str">
         <v/>
       </c>
       <c r="C12" t="str">
-        <v>https://music.apple.com/us/song/its-ok/6763134121</v>
+        <v>https://music.apple.com/us/song/lioness/1878649397</v>
       </c>
       <c r="D12" t="str">
         <v>2026-05-05</v>
@@ -831,36 +831,36 @@
         <v/>
       </c>
       <c r="F12" t="str">
-        <v>IT'S OK - Single</v>
+        <v>MAITREYA CORSO</v>
       </c>
       <c r="G12" t="str">
-        <v>2:19</v>
+        <v>3:32</v>
       </c>
       <c r="H12" t="str">
-        <v>Bryson Tiller</v>
+        <v>Maya Hawke</v>
       </c>
       <c r="I12" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J12" t="str">
-        <v>https://music.apple.com/us/artist/bryson-tiller/642591128</v>
+        <v>https://music.apple.com/us/artist/maya-hawke/1473393677</v>
       </c>
       <c r="K12" t="str">
-        <v>https://music.apple.com/us/album/its-ok/1895176998</v>
+        <v>https://music.apple.com/us/album/lioness/1878649394</v>
       </c>
       <c r="L12" t="str">
-        <v>IT'S OK - Bryson Tiller</v>
+        <v>Lioness - Maya Hawke</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="str">
-        <v>Promise?</v>
+        <v>IT'S OK</v>
       </c>
       <c r="B13" t="str">
         <v/>
       </c>
       <c r="C13" t="str">
-        <v>https://music.apple.com/us/song/promise/6763162287</v>
+        <v>https://music.apple.com/us/song/its-ok/6763134121</v>
       </c>
       <c r="D13" t="str">
         <v>2026-05-05</v>
@@ -869,36 +869,36 @@
         <v/>
       </c>
       <c r="F13" t="str">
-        <v>Promise? - Single</v>
+        <v>IT'S OK - Single</v>
       </c>
       <c r="G13" t="str">
-        <v>3:12</v>
+        <v>2:19</v>
       </c>
       <c r="H13" t="str">
-        <v>Bella Kay</v>
+        <v>Bryson Tiller</v>
       </c>
       <c r="I13" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J13" t="str">
-        <v>https://music.apple.com/us/artist/bella-kay/1706434165</v>
+        <v>https://music.apple.com/us/artist/bryson-tiller/642591128</v>
       </c>
       <c r="K13" t="str">
-        <v>https://music.apple.com/us/album/promise/1895191463</v>
+        <v>https://music.apple.com/us/album/its-ok/1895176998</v>
       </c>
       <c r="L13" t="str">
-        <v>Promise? - Bella Kay</v>
+        <v>IT'S OK - Bryson Tiller</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="str">
-        <v>Cool Buzz</v>
+        <v>Promise?</v>
       </c>
       <c r="B14" t="str">
         <v/>
       </c>
       <c r="C14" t="str">
-        <v>https://music.apple.com/us/song/cool-buzz/1880470657</v>
+        <v>https://music.apple.com/us/song/promise/6763162287</v>
       </c>
       <c r="D14" t="str">
         <v>2026-05-05</v>
@@ -907,36 +907,36 @@
         <v/>
       </c>
       <c r="F14" t="str">
-        <v>Be Sweet To Me</v>
+        <v>Promise? - Single</v>
       </c>
       <c r="G14" t="str">
-        <v>2:32</v>
+        <v>3:12</v>
       </c>
       <c r="H14" t="str">
-        <v>Violet Grohl</v>
+        <v>Bella Kay</v>
       </c>
       <c r="I14" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J14" t="str">
-        <v>https://music.apple.com/us/artist/violet-grohl/1538671509</v>
+        <v>https://music.apple.com/us/artist/bella-kay/1706434165</v>
       </c>
       <c r="K14" t="str">
-        <v>https://music.apple.com/us/album/cool-buzz/1880470537</v>
+        <v>https://music.apple.com/us/album/promise/1895191463</v>
       </c>
       <c r="L14" t="str">
-        <v>Cool Buzz - Violet Grohl</v>
+        <v>Promise? - Bella Kay</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="str">
-        <v>Material Lover</v>
+        <v>Cool Buzz</v>
       </c>
       <c r="B15" t="str">
         <v/>
       </c>
       <c r="C15" t="str">
-        <v>https://music.apple.com/us/song/material-lover/6764429256</v>
+        <v>https://music.apple.com/us/song/cool-buzz/1880470657</v>
       </c>
       <c r="D15" t="str">
         <v>2026-05-05</v>
@@ -945,36 +945,36 @@
         <v/>
       </c>
       <c r="F15" t="str">
-        <v>The Devil Wears Prada 2 (Music From The Motion Picture)</v>
+        <v>Be Sweet To Me</v>
       </c>
       <c r="G15" t="str">
-        <v>2:58</v>
+        <v>2:32</v>
       </c>
       <c r="H15" t="str">
-        <v>SIENNA SPIRO</v>
+        <v>Violet Grohl</v>
       </c>
       <c r="I15" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J15" t="str">
-        <v>https://music.apple.com/us/artist/sienna-spiro/1745678083</v>
+        <v>https://music.apple.com/us/artist/violet-grohl/1538671509</v>
       </c>
       <c r="K15" t="str">
-        <v>https://music.apple.com/us/album/material-lover/1895776688</v>
+        <v>https://music.apple.com/us/album/cool-buzz/1880470537</v>
       </c>
       <c r="L15" t="str">
-        <v>Material Lover - SIENNA SPIRO</v>
+        <v>Cool Buzz - Violet Grohl</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="str">
-        <v>Fallin' (feat. Leon Thomas)</v>
+        <v>Material Lover</v>
       </c>
       <c r="B16" t="str">
         <v/>
       </c>
       <c r="C16" t="str">
-        <v>https://music.apple.com/us/song/fallin-feat-leon-thomas/6764419265</v>
+        <v>https://music.apple.com/us/song/material-lover/6764429256</v>
       </c>
       <c r="D16" t="str">
         <v>2026-05-05</v>
@@ -983,36 +983,36 @@
         <v/>
       </c>
       <c r="F16" t="str">
-        <v>BROWN</v>
+        <v>The Devil Wears Prada 2 (Music From The Motion Picture)</v>
       </c>
       <c r="G16" t="str">
-        <v>4:26</v>
+        <v>2:58</v>
       </c>
       <c r="H16" t="str">
-        <v>Chris Brown</v>
+        <v>SIENNA SPIRO</v>
       </c>
       <c r="I16" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J16" t="str">
-        <v>https://music.apple.com/us/artist/chris-brown/95705522</v>
+        <v>https://music.apple.com/us/artist/sienna-spiro/1745678083</v>
       </c>
       <c r="K16" t="str">
-        <v>https://music.apple.com/us/album/fallin-feat-leon-thomas/1895772091</v>
+        <v>https://music.apple.com/us/album/material-lover/1895776688</v>
       </c>
       <c r="L16" t="str">
-        <v>Fallin' (feat. Leon Thomas) - Chris Brown</v>
+        <v>Material Lover - SIENNA SPIRO</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="str">
-        <v>Echo</v>
+        <v>Fallin' (feat. Leon Thomas)</v>
       </c>
       <c r="B17" t="str">
         <v/>
       </c>
       <c r="C17" t="str">
-        <v>https://music.apple.com/us/song/echo/6763379683</v>
+        <v>https://music.apple.com/us/song/fallin-feat-leon-thomas/6764419265</v>
       </c>
       <c r="D17" t="str">
         <v>2026-05-05</v>
@@ -1021,36 +1021,36 @@
         <v/>
       </c>
       <c r="F17" t="str">
-        <v>Echo (FIFA World Cup 2026™) - Single</v>
+        <v>BROWN</v>
       </c>
       <c r="G17" t="str">
-        <v>2:15</v>
+        <v>4:26</v>
       </c>
       <c r="H17" t="str">
-        <v>Daddy Yankee</v>
+        <v>Chris Brown</v>
       </c>
       <c r="I17" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J17" t="str">
-        <v>https://music.apple.com/us/artist/daddy-yankee/25514958</v>
+        <v>https://music.apple.com/us/artist/chris-brown/95705522</v>
       </c>
       <c r="K17" t="str">
-        <v>https://music.apple.com/us/album/echo/1895288918</v>
+        <v>https://music.apple.com/us/album/fallin-feat-leon-thomas/1895772091</v>
       </c>
       <c r="L17" t="str">
-        <v>Echo - Daddy Yankee</v>
+        <v>Fallin' (feat. Leon Thomas) - Chris Brown</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="str">
-        <v>Blackberry Marmalade</v>
+        <v>Echo</v>
       </c>
       <c r="B18" t="str">
         <v/>
       </c>
       <c r="C18" t="str">
-        <v>https://music.apple.com/us/song/blackberry-marmalade/1887627837</v>
+        <v>https://music.apple.com/us/song/echo/6763379683</v>
       </c>
       <c r="D18" t="str">
         <v>2026-05-05</v>
@@ -1059,36 +1059,36 @@
         <v/>
       </c>
       <c r="F18" t="str">
-        <v>Cry Baby</v>
+        <v>Echo (FIFA World Cup 2026™) - Single</v>
       </c>
       <c r="G18" t="str">
-        <v>3:52</v>
+        <v>2:15</v>
       </c>
       <c r="H18" t="str">
-        <v>Vince Staples</v>
+        <v>Daddy Yankee</v>
       </c>
       <c r="I18" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J18" t="str">
-        <v>https://music.apple.com/us/artist/vince-staples/566639154</v>
+        <v>https://music.apple.com/us/artist/daddy-yankee/25514958</v>
       </c>
       <c r="K18" t="str">
-        <v>https://music.apple.com/us/album/blackberry-marmalade/1887627836</v>
+        <v>https://music.apple.com/us/album/echo/1895288918</v>
       </c>
       <c r="L18" t="str">
-        <v>Blackberry Marmalade - Vince Staples</v>
+        <v>Echo - Daddy Yankee</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="str">
-        <v>Ricky Bobby</v>
+        <v>Blackberry Marmalade</v>
       </c>
       <c r="B19" t="str">
         <v/>
       </c>
       <c r="C19" t="str">
-        <v>https://music.apple.com/us/song/ricky-bobby/6764406571</v>
+        <v>https://music.apple.com/us/song/blackberry-marmalade/1887627837</v>
       </c>
       <c r="D19" t="str">
         <v>2026-05-05</v>
@@ -1097,36 +1097,36 @@
         <v/>
       </c>
       <c r="F19" t="str">
-        <v>CORSA</v>
+        <v>Cry Baby</v>
       </c>
       <c r="G19" t="str">
-        <v>2:55</v>
+        <v>3:52</v>
       </c>
       <c r="H19" t="str">
-        <v>Eladio Carrión</v>
+        <v>Vince Staples</v>
       </c>
       <c r="I19" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J19" t="str">
-        <v>https://music.apple.com/us/artist/eladio-carri%C3%B3n/1024801206</v>
+        <v>https://music.apple.com/us/artist/vince-staples/566639154</v>
       </c>
       <c r="K19" t="str">
-        <v>https://music.apple.com/us/album/ricky-bobby/1895766650</v>
+        <v>https://music.apple.com/us/album/blackberry-marmalade/1887627836</v>
       </c>
       <c r="L19" t="str">
-        <v>Ricky Bobby - Eladio Carrión</v>
+        <v>Blackberry Marmalade - Vince Staples</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="str">
-        <v>Te Entiendo (Remix)</v>
+        <v>Ricky Bobby</v>
       </c>
       <c r="B20" t="str">
         <v/>
       </c>
       <c r="C20" t="str">
-        <v>https://music.apple.com/us/song/te-entiendo-remix/6763665638</v>
+        <v>https://music.apple.com/us/song/ricky-bobby/6764406571</v>
       </c>
       <c r="D20" t="str">
         <v>2026-05-05</v>
@@ -1135,36 +1135,36 @@
         <v/>
       </c>
       <c r="F20" t="str">
-        <v>Te Entiendo (Remix) - Single</v>
+        <v>CORSA</v>
       </c>
       <c r="G20" t="str">
-        <v>5:35</v>
+        <v>2:55</v>
       </c>
       <c r="H20" t="str">
-        <v>Maisak</v>
+        <v>Eladio Carrión</v>
       </c>
       <c r="I20" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J20" t="str">
-        <v>https://music.apple.com/us/artist/maisak/1610652984</v>
+        <v>https://music.apple.com/us/artist/eladio-carri%C3%B3n/1024801206</v>
       </c>
       <c r="K20" t="str">
-        <v>https://music.apple.com/us/album/te-entiendo-remix/1895426152</v>
+        <v>https://music.apple.com/us/album/ricky-bobby/1895766650</v>
       </c>
       <c r="L20" t="str">
-        <v>Te Entiendo (Remix) - Maisak</v>
+        <v>Ricky Bobby - Eladio Carrión</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="str">
-        <v>Don't Worry Baby</v>
+        <v>Te Entiendo (Remix)</v>
       </c>
       <c r="B21" t="str">
         <v/>
       </c>
       <c r="C21" t="str">
-        <v>https://music.apple.com/us/song/dont-worry-baby/1894294411</v>
+        <v>https://music.apple.com/us/song/te-entiendo-remix/6763665638</v>
       </c>
       <c r="D21" t="str">
         <v>2026-05-05</v>
@@ -1173,36 +1173,36 @@
         <v/>
       </c>
       <c r="F21" t="str">
-        <v>Don't Worry Baby - Single</v>
+        <v>Te Entiendo (Remix) - Single</v>
       </c>
       <c r="G21" t="str">
-        <v>3:27</v>
+        <v>5:35</v>
       </c>
       <c r="H21" t="str">
-        <v>Dom Dolla</v>
+        <v>Maisak</v>
       </c>
       <c r="I21" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J21" t="str">
-        <v>https://music.apple.com/us/artist/dom-dolla/555348065</v>
+        <v>https://music.apple.com/us/artist/maisak/1610652984</v>
       </c>
       <c r="K21" t="str">
-        <v>https://music.apple.com/us/album/dont-worry-baby/1894294408</v>
+        <v>https://music.apple.com/us/album/te-entiendo-remix/1895426152</v>
       </c>
       <c r="L21" t="str">
-        <v>Don't Worry Baby - Dom Dolla</v>
+        <v>Te Entiendo (Remix) - Maisak</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="str">
-        <v>BITCH</v>
+        <v>Don't Worry Baby</v>
       </c>
       <c r="B22" t="str">
         <v/>
       </c>
       <c r="C22" t="str">
-        <v>https://music.apple.com/us/song/bitch/6763622110</v>
+        <v>https://music.apple.com/us/song/dont-worry-baby/1894294411</v>
       </c>
       <c r="D22" t="str">
         <v>2026-05-05</v>
@@ -1211,36 +1211,36 @@
         <v/>
       </c>
       <c r="F22" t="str">
-        <v>BITCH</v>
+        <v>Don't Worry Baby - Single</v>
       </c>
       <c r="G22" t="str">
-        <v>2:42</v>
+        <v>3:27</v>
       </c>
       <c r="H22" t="str">
-        <v>Lizzo</v>
+        <v>Dom Dolla</v>
       </c>
       <c r="I22" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J22" t="str">
-        <v>https://music.apple.com/us/artist/lizzo/472949623</v>
+        <v>https://music.apple.com/us/artist/dom-dolla/555348065</v>
       </c>
       <c r="K22" t="str">
-        <v>https://music.apple.com/us/album/bitch/1895402771</v>
+        <v>https://music.apple.com/us/album/dont-worry-baby/1894294408</v>
       </c>
       <c r="L22" t="str">
-        <v>BITCH - Lizzo</v>
+        <v>Don't Worry Baby - Dom Dolla</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="str">
-        <v>Just Wanna Cry</v>
+        <v>BITCH</v>
       </c>
       <c r="B23" t="str">
         <v/>
       </c>
       <c r="C23" t="str">
-        <v>https://music.apple.com/us/song/just-wanna-cry/6763414703</v>
+        <v>https://music.apple.com/us/song/bitch/6763622110</v>
       </c>
       <c r="D23" t="str">
         <v>2026-05-05</v>
@@ -1249,36 +1249,36 @@
         <v/>
       </c>
       <c r="F23" t="str">
-        <v>Toy With Me (Deluxe)</v>
+        <v>BITCH</v>
       </c>
       <c r="G23" t="str">
-        <v>2:27</v>
+        <v>2:42</v>
       </c>
       <c r="H23" t="str">
-        <v>Meghan Trainor</v>
+        <v>Lizzo</v>
       </c>
       <c r="I23" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J23" t="str">
-        <v>https://music.apple.com/us/artist/meghan-trainor/348580754</v>
+        <v>https://music.apple.com/us/artist/lizzo/472949623</v>
       </c>
       <c r="K23" t="str">
-        <v>https://music.apple.com/us/album/just-wanna-cry/1895303290</v>
+        <v>https://music.apple.com/us/album/bitch/1895402771</v>
       </c>
       <c r="L23" t="str">
-        <v>Just Wanna Cry - Meghan Trainor</v>
+        <v>BITCH - Lizzo</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="str">
-        <v>Carry the Weight</v>
+        <v>Just Wanna Cry</v>
       </c>
       <c r="B24" t="str">
         <v/>
       </c>
       <c r="C24" t="str">
-        <v>https://music.apple.com/us/song/carry-the-weight/6763611647</v>
+        <v>https://music.apple.com/us/song/just-wanna-cry/6763414703</v>
       </c>
       <c r="D24" t="str">
         <v>2026-05-05</v>
@@ -1287,36 +1287,36 @@
         <v/>
       </c>
       <c r="F24" t="str">
-        <v>The Great Impersonator (Deluxe)</v>
+        <v>Toy With Me (Deluxe)</v>
       </c>
       <c r="G24" t="str">
-        <v>3:09</v>
+        <v>2:27</v>
       </c>
       <c r="H24" t="str">
-        <v>Halsey</v>
+        <v>Meghan Trainor</v>
       </c>
       <c r="I24" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J24" t="str">
-        <v>https://music.apple.com/us/artist/halsey/324916925</v>
+        <v>https://music.apple.com/us/artist/meghan-trainor/348580754</v>
       </c>
       <c r="K24" t="str">
-        <v>https://music.apple.com/us/album/carry-the-weight/1895397523</v>
+        <v>https://music.apple.com/us/album/just-wanna-cry/1895303290</v>
       </c>
       <c r="L24" t="str">
-        <v>Carry the Weight - Halsey</v>
+        <v>Just Wanna Cry - Meghan Trainor</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="str">
-        <v>PROSTITUTE</v>
+        <v>Carry the Weight</v>
       </c>
       <c r="B25" t="str">
         <v/>
       </c>
       <c r="C25" t="str">
-        <v>https://music.apple.com/us/song/prostitute/1894092341</v>
+        <v>https://music.apple.com/us/song/carry-the-weight/6763611647</v>
       </c>
       <c r="D25" t="str">
         <v>2026-05-05</v>
@@ -1325,36 +1325,36 @@
         <v/>
       </c>
       <c r="F25" t="str">
-        <v>COSMIC OPERA ACT II</v>
+        <v>The Great Impersonator (Deluxe)</v>
       </c>
       <c r="G25" t="str">
-        <v>2:44</v>
+        <v>3:09</v>
       </c>
       <c r="H25" t="str">
-        <v>Labrinth</v>
+        <v>Halsey</v>
       </c>
       <c r="I25" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J25" t="str">
-        <v>https://music.apple.com/us/artist/labrinth/205732582</v>
+        <v>https://music.apple.com/us/artist/halsey/324916925</v>
       </c>
       <c r="K25" t="str">
-        <v>https://music.apple.com/us/album/prostitute/1894092339</v>
+        <v>https://music.apple.com/us/album/carry-the-weight/1895397523</v>
       </c>
       <c r="L25" t="str">
-        <v>PROSTITUTE - Labrinth</v>
+        <v>Carry the Weight - Halsey</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="str">
-        <v>i'm not joking</v>
+        <v>PROSTITUTE</v>
       </c>
       <c r="B26" t="str">
         <v/>
       </c>
       <c r="C26" t="str">
-        <v>https://music.apple.com/us/song/im-not-joking/1872842623</v>
+        <v>https://music.apple.com/us/song/prostitute/1894092341</v>
       </c>
       <c r="D26" t="str">
         <v>2026-05-05</v>
@@ -1363,36 +1363,36 @@
         <v/>
       </c>
       <c r="F26" t="str">
-        <v>everyone for ten minutes</v>
+        <v>COSMIC OPERA ACT II</v>
       </c>
       <c r="G26" t="str">
-        <v>3:54</v>
+        <v>2:44</v>
       </c>
       <c r="H26" t="str">
-        <v>Bleachers</v>
+        <v>Labrinth</v>
       </c>
       <c r="I26" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J26" t="str">
-        <v>https://music.apple.com/us/artist/bleachers/824434533</v>
+        <v>https://music.apple.com/us/artist/labrinth/205732582</v>
       </c>
       <c r="K26" t="str">
-        <v>https://music.apple.com/us/album/im-not-joking/1872842313</v>
+        <v>https://music.apple.com/us/album/prostitute/1894092339</v>
       </c>
       <c r="L26" t="str">
-        <v>i'm not joking - Bleachers</v>
+        <v>PROSTITUTE - Labrinth</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="str">
-        <v>Ruca</v>
+        <v>i'm not joking</v>
       </c>
       <c r="B27" t="str">
         <v/>
       </c>
       <c r="C27" t="str">
-        <v>https://music.apple.com/us/song/ruca/6763671002</v>
+        <v>https://music.apple.com/us/song/im-not-joking/1872842623</v>
       </c>
       <c r="D27" t="str">
         <v>2026-05-05</v>
@@ -1401,36 +1401,36 @@
         <v/>
       </c>
       <c r="F27" t="str">
-        <v>MUDA</v>
+        <v>everyone for ten minutes</v>
       </c>
       <c r="G27" t="str">
-        <v>3:01</v>
+        <v>3:54</v>
       </c>
       <c r="H27" t="str">
-        <v>Carín León</v>
+        <v>Bleachers</v>
       </c>
       <c r="I27" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J27" t="str">
-        <v>https://music.apple.com/us/artist/car%C3%ADn-le%C3%B3n/1370196486</v>
+        <v>https://music.apple.com/us/artist/bleachers/824434533</v>
       </c>
       <c r="K27" t="str">
-        <v>https://music.apple.com/us/album/ruca/1895429814</v>
+        <v>https://music.apple.com/us/album/im-not-joking/1872842313</v>
       </c>
       <c r="L27" t="str">
-        <v>Ruca - Carín León</v>
+        <v>i'm not joking - Bleachers</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="str">
-        <v>Make You Fight</v>
+        <v>Ruca</v>
       </c>
       <c r="B28" t="str">
         <v/>
       </c>
       <c r="C28" t="str">
-        <v>https://music.apple.com/us/song/make-you-fight/1892332386</v>
+        <v>https://music.apple.com/us/song/ruca/6763671002</v>
       </c>
       <c r="D28" t="str">
         <v>2026-05-05</v>
@@ -1439,36 +1439,36 @@
         <v/>
       </c>
       <c r="F28" t="str">
-        <v>Make You Fight - Single</v>
+        <v>MUDA</v>
       </c>
       <c r="G28" t="str">
-        <v>2:55</v>
+        <v>3:01</v>
       </c>
       <c r="H28" t="str">
-        <v>Chris Lake</v>
+        <v>Carín León</v>
       </c>
       <c r="I28" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J28" t="str">
-        <v>https://music.apple.com/us/artist/chris-lake/135067114</v>
+        <v>https://music.apple.com/us/artist/car%C3%ADn-le%C3%B3n/1370196486</v>
       </c>
       <c r="K28" t="str">
-        <v>https://music.apple.com/us/album/make-you-fight/1892332385</v>
+        <v>https://music.apple.com/us/album/ruca/1895429814</v>
       </c>
       <c r="L28" t="str">
-        <v>Make You Fight - Chris Lake</v>
+        <v>Ruca - Carín León</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="str">
-        <v>#N0rth4evr</v>
+        <v>Make You Fight</v>
       </c>
       <c r="B29" t="str">
         <v/>
       </c>
       <c r="C29" t="str">
-        <v>https://music.apple.com/us/song/n0rth4evr/6763302230</v>
+        <v>https://music.apple.com/us/song/make-you-fight/1892332386</v>
       </c>
       <c r="D29" t="str">
         <v>2026-05-05</v>
@@ -1477,36 +1477,36 @@
         <v/>
       </c>
       <c r="F29" t="str">
-        <v>N0rth4evr - EP</v>
+        <v>Make You Fight - Single</v>
       </c>
       <c r="G29" t="str">
-        <v>1:43</v>
+        <v>2:55</v>
       </c>
       <c r="H29" t="str">
-        <v>North West</v>
+        <v>Chris Lake</v>
       </c>
       <c r="I29" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J29" t="str">
-        <v>https://music.apple.com/us/artist/north-west/1729862520</v>
+        <v>https://music.apple.com/us/artist/chris-lake/135067114</v>
       </c>
       <c r="K29" t="str">
-        <v>https://music.apple.com/us/album/n0rth4evr/1895254115</v>
+        <v>https://music.apple.com/us/album/make-you-fight/1892332385</v>
       </c>
       <c r="L29" t="str">
-        <v>#N0rth4evr - North West</v>
+        <v>Make You Fight - Chris Lake</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="str">
-        <v>BOY IN RED</v>
+        <v>#N0rth4evr</v>
       </c>
       <c r="B30" t="str">
         <v/>
       </c>
       <c r="C30" t="str">
-        <v>https://music.apple.com/us/song/boy-in-red/1892543110</v>
+        <v>https://music.apple.com/us/song/n0rth4evr/6763302230</v>
       </c>
       <c r="D30" t="str">
         <v>2026-05-05</v>
@@ -1515,36 +1515,36 @@
         <v/>
       </c>
       <c r="F30" t="str">
-        <v>IT'S BEEN AWFUL</v>
+        <v>N0rth4evr - EP</v>
       </c>
       <c r="G30" t="str">
-        <v>3:09</v>
+        <v>1:43</v>
       </c>
       <c r="H30" t="str">
-        <v>Isaiah Rashad</v>
+        <v>North West</v>
       </c>
       <c r="I30" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J30" t="str">
-        <v>https://music.apple.com/us/artist/isaiah-rashad/605391263</v>
+        <v>https://music.apple.com/us/artist/north-west/1729862520</v>
       </c>
       <c r="K30" t="str">
-        <v>https://music.apple.com/us/album/boy-in-red/1892543099</v>
+        <v>https://music.apple.com/us/album/n0rth4evr/1895254115</v>
       </c>
       <c r="L30" t="str">
-        <v>BOY IN RED - Isaiah Rashad</v>
+        <v>#N0rth4evr - North West</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="str">
-        <v>EA EA EA</v>
+        <v>BOY IN RED</v>
       </c>
       <c r="B31" t="str">
         <v/>
       </c>
       <c r="C31" t="str">
-        <v>https://music.apple.com/us/song/ea-ea-ea/6763438376</v>
+        <v>https://music.apple.com/us/song/boy-in-red/1892543110</v>
       </c>
       <c r="D31" t="str">
         <v>2026-05-05</v>
@@ -1553,36 +1553,36 @@
         <v/>
       </c>
       <c r="F31" t="str">
-        <v>AFTERAFTER - EP</v>
+        <v>IT'S BEEN AWFUL</v>
       </c>
       <c r="G31" t="str">
-        <v>2:42</v>
+        <v>3:09</v>
       </c>
       <c r="H31" t="str">
-        <v>Clave Especial</v>
+        <v>Isaiah Rashad</v>
       </c>
       <c r="I31" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J31" t="str">
-        <v>https://music.apple.com/us/artist/clave-especial/1569749622</v>
+        <v>https://music.apple.com/us/artist/isaiah-rashad/605391263</v>
       </c>
       <c r="K31" t="str">
-        <v>https://music.apple.com/us/album/ea-ea-ea/1895315118</v>
+        <v>https://music.apple.com/us/album/boy-in-red/1892543099</v>
       </c>
       <c r="L31" t="str">
-        <v>EA EA EA - Clave Especial</v>
+        <v>BOY IN RED - Isaiah Rashad</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="str">
-        <v>Just A Man</v>
+        <v>EA EA EA</v>
       </c>
       <c r="B32" t="str">
         <v/>
       </c>
       <c r="C32" t="str">
-        <v>https://music.apple.com/us/song/just-a-man/6762944365</v>
+        <v>https://music.apple.com/us/song/ea-ea-ea/6763438376</v>
       </c>
       <c r="D32" t="str">
         <v>2026-05-05</v>
@@ -1591,36 +1591,36 @@
         <v/>
       </c>
       <c r="F32" t="str">
-        <v>Just A Man - Single</v>
+        <v>AFTERAFTER - EP</v>
       </c>
       <c r="G32" t="str">
-        <v>2:19</v>
+        <v>2:42</v>
       </c>
       <c r="H32" t="str">
-        <v>Claire Rosinkranz</v>
+        <v>Clave Especial</v>
       </c>
       <c r="I32" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J32" t="str">
-        <v>https://music.apple.com/us/artist/claire-rosinkranz/1483262366</v>
+        <v>https://music.apple.com/us/artist/clave-especial/1569749622</v>
       </c>
       <c r="K32" t="str">
-        <v>https://music.apple.com/us/album/just-a-man/1895089709</v>
+        <v>https://music.apple.com/us/album/ea-ea-ea/1895315118</v>
       </c>
       <c r="L32" t="str">
-        <v>Just A Man - Claire Rosinkranz</v>
+        <v>EA EA EA - Clave Especial</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="str">
-        <v>The Observer</v>
+        <v>Just A Man</v>
       </c>
       <c r="B33" t="str">
         <v/>
       </c>
       <c r="C33" t="str">
-        <v>https://music.apple.com/us/song/the-observer/1891982314</v>
+        <v>https://music.apple.com/us/song/just-a-man/6762944365</v>
       </c>
       <c r="D33" t="str">
         <v>2026-05-05</v>
@@ -1629,36 +1629,36 @@
         <v/>
       </c>
       <c r="F33" t="str">
-        <v>How Did I Get Here? (Extended Edition)</v>
+        <v>Just A Man - Single</v>
       </c>
       <c r="G33" t="str">
-        <v>2:50</v>
+        <v>2:19</v>
       </c>
       <c r="H33" t="str">
-        <v>Louis Tomlinson</v>
+        <v>Claire Rosinkranz</v>
       </c>
       <c r="I33" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J33" t="str">
-        <v>https://music.apple.com/us/artist/louis-tomlinson/471260295</v>
+        <v>https://music.apple.com/us/artist/claire-rosinkranz/1483262366</v>
       </c>
       <c r="K33" t="str">
-        <v>https://music.apple.com/us/album/the-observer/1891982287</v>
+        <v>https://music.apple.com/us/album/just-a-man/1895089709</v>
       </c>
       <c r="L33" t="str">
-        <v>The Observer - Louis Tomlinson</v>
+        <v>Just A Man - Claire Rosinkranz</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="str">
-        <v>Heroine</v>
+        <v>The Observer</v>
       </c>
       <c r="B34" t="str">
         <v/>
       </c>
       <c r="C34" t="str">
-        <v>https://music.apple.com/us/song/heroine/6762693177</v>
+        <v>https://music.apple.com/us/song/the-observer/1891982314</v>
       </c>
       <c r="D34" t="str">
         <v>2026-05-05</v>
@@ -1667,36 +1667,36 @@
         <v/>
       </c>
       <c r="F34" t="str">
-        <v>Heroine - Single</v>
+        <v>How Did I Get Here? (Extended Edition)</v>
       </c>
       <c r="G34" t="str">
-        <v>2:35</v>
+        <v>2:50</v>
       </c>
       <c r="H34" t="str">
-        <v>Maroon 5</v>
+        <v>Louis Tomlinson</v>
       </c>
       <c r="I34" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J34" t="str">
-        <v>https://music.apple.com/us/artist/maroon-5/1798556</v>
+        <v>https://music.apple.com/us/artist/louis-tomlinson/471260295</v>
       </c>
       <c r="K34" t="str">
-        <v>https://music.apple.com/us/album/heroine/1894966605</v>
+        <v>https://music.apple.com/us/album/the-observer/1891982287</v>
       </c>
       <c r="L34" t="str">
-        <v>Heroine - Maroon 5</v>
+        <v>The Observer - Louis Tomlinson</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="str">
-        <v>Do Me Right</v>
+        <v>Heroine</v>
       </c>
       <c r="B35" t="str">
         <v/>
       </c>
       <c r="C35" t="str">
-        <v>https://music.apple.com/us/song/do-me-right/6764667658</v>
+        <v>https://music.apple.com/us/song/heroine/6762693177</v>
       </c>
       <c r="D35" t="str">
         <v>2026-05-05</v>
@@ -1705,36 +1705,36 @@
         <v/>
       </c>
       <c r="F35" t="str">
-        <v>FANTASYLAND</v>
+        <v>Heroine - Single</v>
       </c>
       <c r="G35" t="str">
-        <v>4:10</v>
+        <v>2:35</v>
       </c>
       <c r="H35" t="str">
-        <v>MR. FANTASY</v>
+        <v>Maroon 5</v>
       </c>
       <c r="I35" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J35" t="str">
-        <v>https://music.apple.com/us/artist/mr-fantasy/1834481769</v>
+        <v>https://music.apple.com/us/artist/maroon-5/1798556</v>
       </c>
       <c r="K35" t="str">
-        <v>https://music.apple.com/us/album/do-me-right/1895871261</v>
+        <v>https://music.apple.com/us/album/heroine/1894966605</v>
       </c>
       <c r="L35" t="str">
-        <v>Do Me Right - MR. FANTASY</v>
+        <v>Heroine - Maroon 5</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="str">
-        <v>It's Me</v>
+        <v>Do Me Right</v>
       </c>
       <c r="B36" t="str">
         <v/>
       </c>
       <c r="C36" t="str">
-        <v>https://music.apple.com/us/song/its-me/1887194026</v>
+        <v>https://music.apple.com/us/song/do-me-right/6764667658</v>
       </c>
       <c r="D36" t="str">
         <v>2026-05-05</v>
@@ -1743,36 +1743,36 @@
         <v/>
       </c>
       <c r="F36" t="str">
-        <v>MAMIHLAPINATAPAI - EP</v>
+        <v>FANTASYLAND</v>
       </c>
       <c r="G36" t="str">
-        <v>2:18</v>
+        <v>4:10</v>
       </c>
       <c r="H36" t="str">
-        <v>ILLIT</v>
+        <v>MR. FANTASY</v>
       </c>
       <c r="I36" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J36" t="str">
-        <v>https://music.apple.com/us/artist/illit/1734551937</v>
+        <v>https://music.apple.com/us/artist/mr-fantasy/1834481769</v>
       </c>
       <c r="K36" t="str">
-        <v>https://music.apple.com/us/album/its-me/1887194024</v>
+        <v>https://music.apple.com/us/album/do-me-right/1895871261</v>
       </c>
       <c r="L36" t="str">
-        <v>It's Me - ILLIT</v>
+        <v>Do Me Right - MR. FANTASY</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="str">
-        <v>the precipice</v>
+        <v>It's Me</v>
       </c>
       <c r="B37" t="str">
         <v/>
       </c>
       <c r="C37" t="str">
-        <v>https://music.apple.com/us/song/the-precipice/1891830326</v>
+        <v>https://music.apple.com/us/song/its-me/1887194026</v>
       </c>
       <c r="D37" t="str">
         <v>2026-05-05</v>
@@ -1781,36 +1781,36 @@
         <v/>
       </c>
       <c r="F37" t="str">
-        <v>untitled.jpeg - EP</v>
+        <v>MAMIHLAPINATAPAI - EP</v>
       </c>
       <c r="G37" t="str">
-        <v>3:52</v>
+        <v>2:18</v>
       </c>
       <c r="H37" t="str">
-        <v>Jessie Mazin</v>
+        <v>ILLIT</v>
       </c>
       <c r="I37" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J37" t="str">
-        <v>https://music.apple.com/us/artist/jessie-mazin/1887707056</v>
+        <v>https://music.apple.com/us/artist/illit/1734551937</v>
       </c>
       <c r="K37" t="str">
-        <v>https://music.apple.com/us/album/the-precipice/1891830323</v>
+        <v>https://music.apple.com/us/album/its-me/1887194024</v>
       </c>
       <c r="L37" t="str">
-        <v>the precipice - Jessie Mazin</v>
+        <v>It's Me - ILLIT</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="str">
-        <v>Hello Lonesome</v>
+        <v>the precipice</v>
       </c>
       <c r="B38" t="str">
         <v/>
       </c>
       <c r="C38" t="str">
-        <v>https://music.apple.com/us/song/hello-lonesome/1892466003</v>
+        <v>https://music.apple.com/us/song/the-precipice/1891830326</v>
       </c>
       <c r="D38" t="str">
         <v>2026-05-05</v>
@@ -1819,36 +1819,36 @@
         <v/>
       </c>
       <c r="F38" t="str">
-        <v>Banks Of The Trinity</v>
+        <v>untitled.jpeg - EP</v>
       </c>
       <c r="G38" t="str">
-        <v>2:58</v>
+        <v>3:52</v>
       </c>
       <c r="H38" t="str">
-        <v>Cody Johnson</v>
+        <v>Jessie Mazin</v>
       </c>
       <c r="I38" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J38" t="str">
-        <v>https://music.apple.com/us/artist/cody-johnson/331459657</v>
+        <v>https://music.apple.com/us/artist/jessie-mazin/1887707056</v>
       </c>
       <c r="K38" t="str">
-        <v>https://music.apple.com/us/album/hello-lonesome/1892465981</v>
+        <v>https://music.apple.com/us/album/the-precipice/1891830323</v>
       </c>
       <c r="L38" t="str">
-        <v>Hello Lonesome - Cody Johnson</v>
+        <v>the precipice - Jessie Mazin</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="str">
-        <v>TRIPPIN (Opera Edit)</v>
+        <v>Hello Lonesome</v>
       </c>
       <c r="B39" t="str">
         <v/>
       </c>
       <c r="C39" t="str">
-        <v>https://music.apple.com/us/song/trippin-opera-edit/6764648776</v>
+        <v>https://music.apple.com/us/song/hello-lonesome/1892466003</v>
       </c>
       <c r="D39" t="str">
         <v>2026-05-05</v>
@@ -1857,36 +1857,36 @@
         <v/>
       </c>
       <c r="F39" t="str">
-        <v>TRIPPIN (Opera Edit) - Single</v>
+        <v>Banks Of The Trinity</v>
       </c>
       <c r="G39" t="str">
-        <v>2:21</v>
+        <v>2:58</v>
       </c>
       <c r="H39" t="str">
-        <v>BUNT.</v>
+        <v>Cody Johnson</v>
       </c>
       <c r="I39" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J39" t="str">
-        <v>https://music.apple.com/us/artist/bunt/1436090348</v>
+        <v>https://music.apple.com/us/artist/cody-johnson/331459657</v>
       </c>
       <c r="K39" t="str">
-        <v>https://music.apple.com/us/album/trippin-opera-edit/1895863999</v>
+        <v>https://music.apple.com/us/album/hello-lonesome/1892465981</v>
       </c>
       <c r="L39" t="str">
-        <v>TRIPPIN (Opera Edit) - BUNT.</v>
+        <v>Hello Lonesome - Cody Johnson</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="str">
-        <v>The Mandalorian and Grogu (Boys Noize Remix) [From "Star Wars: The Mandalorian and Grogu"]</v>
+        <v>TRIPPIN (Opera Edit)</v>
       </c>
       <c r="B40" t="str">
         <v/>
       </c>
       <c r="C40" t="str">
-        <v>https://music.apple.com/us/song/the-mandalorian-and-grogu-boys-noize-remix-from-star/6764131630</v>
+        <v>https://music.apple.com/us/song/trippin-opera-edit/6764648776</v>
       </c>
       <c r="D40" t="str">
         <v>2026-05-05</v>
@@ -1895,36 +1895,36 @@
         <v/>
       </c>
       <c r="F40" t="str">
-        <v>The Mandalorian and Grogu (Boys Noize Remix) [From "Star Wars: The Mandalorian and Grogu"] - Single</v>
+        <v>TRIPPIN (Opera Edit) - Single</v>
       </c>
       <c r="G40" t="str">
-        <v>5:54</v>
+        <v>2:21</v>
       </c>
       <c r="H40" t="str">
-        <v>Ludwig Göransson</v>
+        <v>BUNT.</v>
       </c>
       <c r="I40" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J40" t="str">
-        <v>https://music.apple.com/us/artist/ludwig-g%C3%B6ransson/391832320</v>
+        <v>https://music.apple.com/us/artist/bunt/1436090348</v>
       </c>
       <c r="K40" t="str">
-        <v>https://music.apple.com/us/album/the-mandalorian-and-grogu-boys-noize-remix-from-star/1895653302</v>
+        <v>https://music.apple.com/us/album/trippin-opera-edit/1895863999</v>
       </c>
       <c r="L40" t="str">
-        <v>The Mandalorian and Grogu (Boys Noize Remix) [From "Star Wars: The Mandalorian and Grogu"] - Ludwig Göransson</v>
+        <v>TRIPPIN (Opera Edit) - BUNT.</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="str">
-        <v>Blow My Mind (CA7RIEL &amp; Paco Amoroso Version)</v>
+        <v>The Mandalorian and Grogu (Boys Noize Remix) [From "Star Wars: The Mandalorian and Grogu"]</v>
       </c>
       <c r="B41" t="str">
         <v/>
       </c>
       <c r="C41" t="str">
-        <v>https://music.apple.com/us/song/blow-my-mind-ca7riel-paco-amoroso-version/1894344140</v>
+        <v>https://music.apple.com/us/song/the-mandalorian-and-grogu-boys-noize-remix-from-star/6764131630</v>
       </c>
       <c r="D41" t="str">
         <v>2026-05-05</v>
@@ -1933,36 +1933,36 @@
         <v/>
       </c>
       <c r="F41" t="str">
-        <v>Blow My Mind (CA7RIEL &amp; Paco Amoroso Version) - Single</v>
+        <v>The Mandalorian and Grogu (Boys Noize Remix) [From "Star Wars: The Mandalorian and Grogu"] - Single</v>
       </c>
       <c r="G41" t="str">
-        <v>2:49</v>
+        <v>5:54</v>
       </c>
       <c r="H41" t="str">
-        <v>Robyn</v>
+        <v>Ludwig Göransson</v>
       </c>
       <c r="I41" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J41" t="str">
-        <v>https://music.apple.com/us/artist/robyn/535211</v>
+        <v>https://music.apple.com/us/artist/ludwig-g%C3%B6ransson/391832320</v>
       </c>
       <c r="K41" t="str">
-        <v>https://music.apple.com/us/album/blow-my-mind-ca7riel-paco-amoroso-version/1894344139</v>
+        <v>https://music.apple.com/us/album/the-mandalorian-and-grogu-boys-noize-remix-from-star/1895653302</v>
       </c>
       <c r="L41" t="str">
-        <v>Blow My Mind (CA7RIEL &amp; Paco Amoroso Version) - Robyn</v>
+        <v>The Mandalorian and Grogu (Boys Noize Remix) [From "Star Wars: The Mandalorian and Grogu"] - Ludwig Göransson</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="str">
-        <v>Bring That Body</v>
+        <v>Blow My Mind (CA7RIEL &amp; Paco Amoroso Version)</v>
       </c>
       <c r="B42" t="str">
         <v/>
       </c>
       <c r="C42" t="str">
-        <v>https://music.apple.com/us/song/bring-that-body/6764009310</v>
+        <v>https://music.apple.com/us/song/blow-my-mind-ca7riel-paco-amoroso-version/1894344140</v>
       </c>
       <c r="D42" t="str">
         <v>2026-05-05</v>
@@ -1971,36 +1971,36 @@
         <v/>
       </c>
       <c r="F42" t="str">
-        <v>Bring That Body - Single</v>
+        <v>Blow My Mind (CA7RIEL &amp; Paco Amoroso Version) - Single</v>
       </c>
       <c r="G42" t="str">
-        <v>3:34</v>
+        <v>2:49</v>
       </c>
       <c r="H42" t="str">
-        <v>The-Dream</v>
+        <v>Robyn</v>
       </c>
       <c r="I42" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J42" t="str">
-        <v>https://music.apple.com/us/artist/the-dream/259369321</v>
+        <v>https://music.apple.com/us/artist/robyn/535211</v>
       </c>
       <c r="K42" t="str">
-        <v>https://music.apple.com/us/album/bring-that-body/1895596731</v>
+        <v>https://music.apple.com/us/album/blow-my-mind-ca7riel-paco-amoroso-version/1894344139</v>
       </c>
       <c r="L42" t="str">
-        <v>Bring That Body - The-Dream</v>
+        <v>Blow My Mind (CA7RIEL &amp; Paco Amoroso Version) - Robyn</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="str">
-        <v>STAR</v>
+        <v>Bring That Body</v>
       </c>
       <c r="B43" t="str">
         <v/>
       </c>
       <c r="C43" t="str">
-        <v>https://music.apple.com/us/song/star/1891845608</v>
+        <v>https://music.apple.com/us/song/bring-that-body/6764009310</v>
       </c>
       <c r="D43" t="str">
         <v>2026-05-05</v>
@@ -2009,36 +2009,36 @@
         <v/>
       </c>
       <c r="F43" t="str">
-        <v>STAR</v>
+        <v>Bring That Body - Single</v>
       </c>
       <c r="G43" t="str">
-        <v>2:49</v>
+        <v>3:34</v>
       </c>
       <c r="H43" t="str">
-        <v>Tombochio</v>
+        <v>The-Dream</v>
       </c>
       <c r="I43" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J43" t="str">
-        <v>https://music.apple.com/us/artist/tombochio/1570164065</v>
+        <v>https://music.apple.com/us/artist/the-dream/259369321</v>
       </c>
       <c r="K43" t="str">
-        <v>https://music.apple.com/us/album/star/1891845604</v>
+        <v>https://music.apple.com/us/album/bring-that-body/1895596731</v>
       </c>
       <c r="L43" t="str">
-        <v>STAR - Tombochio</v>
+        <v>Bring That Body - The-Dream</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="str">
-        <v>What’s A Little Rain</v>
+        <v>STAR</v>
       </c>
       <c r="B44" t="str">
         <v/>
       </c>
       <c r="C44" t="str">
-        <v>https://music.apple.com/us/song/whats-a-little-rain/1885061171</v>
+        <v>https://music.apple.com/us/song/star/1891845608</v>
       </c>
       <c r="D44" t="str">
         <v>2026-05-05</v>
@@ -2047,36 +2047,36 @@
         <v/>
       </c>
       <c r="F44" t="str">
-        <v>Deep Blue</v>
+        <v>STAR</v>
       </c>
       <c r="G44" t="str">
-        <v>3:37</v>
+        <v>2:49</v>
       </c>
       <c r="H44" t="str">
-        <v>ERNEST</v>
+        <v>Tombochio</v>
       </c>
       <c r="I44" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J44" t="str">
-        <v>https://music.apple.com/us/artist/ernest/1450042443</v>
+        <v>https://music.apple.com/us/artist/tombochio/1570164065</v>
       </c>
       <c r="K44" t="str">
-        <v>https://music.apple.com/us/album/whats-a-little-rain/1885061168</v>
+        <v>https://music.apple.com/us/album/star/1891845604</v>
       </c>
       <c r="L44" t="str">
-        <v>What’s A Little Rain - ERNEST</v>
+        <v>STAR - Tombochio</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="str">
-        <v>Evergreen</v>
+        <v>What’s A Little Rain</v>
       </c>
       <c r="B45" t="str">
         <v/>
       </c>
       <c r="C45" t="str">
-        <v>https://music.apple.com/us/song/evergreen/1866700315</v>
+        <v>https://music.apple.com/us/song/whats-a-little-rain/1885061171</v>
       </c>
       <c r="D45" t="str">
         <v>2026-05-05</v>
@@ -2085,36 +2085,36 @@
         <v/>
       </c>
       <c r="F45" t="str">
-        <v>Victory Garden</v>
+        <v>Deep Blue</v>
       </c>
       <c r="G45" t="str">
-        <v>3:41</v>
+        <v>3:37</v>
       </c>
       <c r="H45" t="str">
-        <v>Young the Giant</v>
+        <v>ERNEST</v>
       </c>
       <c r="I45" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J45" t="str">
-        <v>https://music.apple.com/us/artist/young-the-giant/394582977</v>
+        <v>https://music.apple.com/us/artist/ernest/1450042443</v>
       </c>
       <c r="K45" t="str">
-        <v>https://music.apple.com/us/album/evergreen/1866700309</v>
+        <v>https://music.apple.com/us/album/whats-a-little-rain/1885061168</v>
       </c>
       <c r="L45" t="str">
-        <v>Evergreen - Young the Giant</v>
+        <v>What’s A Little Rain - ERNEST</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="str">
-        <v>She Does It Right</v>
+        <v>Evergreen</v>
       </c>
       <c r="B46" t="str">
         <v/>
       </c>
       <c r="C46" t="str">
-        <v>https://music.apple.com/us/song/she-does-it-right/1873477957</v>
+        <v>https://music.apple.com/us/song/evergreen/1866700315</v>
       </c>
       <c r="D46" t="str">
         <v>2026-05-05</v>
@@ -2123,36 +2123,36 @@
         <v/>
       </c>
       <c r="F46" t="str">
-        <v>Peaches!</v>
+        <v>Victory Garden</v>
       </c>
       <c r="G46" t="str">
-        <v>3:43</v>
+        <v>3:41</v>
       </c>
       <c r="H46" t="str">
-        <v>The Black Keys</v>
+        <v>Young the Giant</v>
       </c>
       <c r="I46" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J46" t="str">
-        <v>https://music.apple.com/us/artist/the-black-keys/5893059</v>
+        <v>https://music.apple.com/us/artist/young-the-giant/394582977</v>
       </c>
       <c r="K46" t="str">
-        <v>https://music.apple.com/us/album/she-does-it-right/1873477948</v>
+        <v>https://music.apple.com/us/album/evergreen/1866700309</v>
       </c>
       <c r="L46" t="str">
-        <v>She Does It Right - The Black Keys</v>
+        <v>Evergreen - Young the Giant</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="str">
-        <v>Punching the Flowers</v>
+        <v>She Does It Right</v>
       </c>
       <c r="B47" t="str">
         <v/>
       </c>
       <c r="C47" t="str">
-        <v>https://music.apple.com/us/song/punching-the-flowers/1878362636</v>
+        <v>https://music.apple.com/us/song/she-does-it-right/1873477957</v>
       </c>
       <c r="D47" t="str">
         <v>2026-05-05</v>
@@ -2161,36 +2161,36 @@
         <v/>
       </c>
       <c r="F47" t="str">
-        <v>I Built You A Tower</v>
+        <v>Peaches!</v>
       </c>
       <c r="G47" t="str">
-        <v>3:11</v>
+        <v>3:43</v>
       </c>
       <c r="H47" t="str">
-        <v>Death Cab for Cutie</v>
+        <v>The Black Keys</v>
       </c>
       <c r="I47" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J47" t="str">
-        <v>https://music.apple.com/us/artist/death-cab-for-cutie/5448636</v>
+        <v>https://music.apple.com/us/artist/the-black-keys/5893059</v>
       </c>
       <c r="K47" t="str">
-        <v>https://music.apple.com/us/album/punching-the-flowers/1878362451</v>
+        <v>https://music.apple.com/us/album/she-does-it-right/1873477948</v>
       </c>
       <c r="L47" t="str">
-        <v>Punching the Flowers - Death Cab for Cutie</v>
+        <v>She Does It Right - The Black Keys</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="str">
-        <v>How Did You Know</v>
+        <v>Punching the Flowers</v>
       </c>
       <c r="B48" t="str">
         <v/>
       </c>
       <c r="C48" t="str">
-        <v>https://music.apple.com/us/song/how-did-you-know/1888553137</v>
+        <v>https://music.apple.com/us/song/punching-the-flowers/1878362636</v>
       </c>
       <c r="D48" t="str">
         <v>2026-05-05</v>
@@ -2199,36 +2199,36 @@
         <v/>
       </c>
       <c r="F48" t="str">
-        <v>California Sunrise (10th Anniversary Edition)</v>
+        <v>I Built You A Tower</v>
       </c>
       <c r="G48" t="str">
-        <v>3:16</v>
+        <v>3:11</v>
       </c>
       <c r="H48" t="str">
-        <v>Jon Pardi</v>
+        <v>Death Cab for Cutie</v>
       </c>
       <c r="I48" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J48" t="str">
-        <v>https://music.apple.com/us/artist/jon-pardi/371085834</v>
+        <v>https://music.apple.com/us/artist/death-cab-for-cutie/5448636</v>
       </c>
       <c r="K48" t="str">
-        <v>https://music.apple.com/us/album/how-did-you-know/1888552935</v>
+        <v>https://music.apple.com/us/album/punching-the-flowers/1878362451</v>
       </c>
       <c r="L48" t="str">
-        <v>How Did You Know - Jon Pardi</v>
+        <v>Punching the Flowers - Death Cab for Cutie</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="str">
-        <v>Summer Breeze</v>
+        <v>How Did You Know</v>
       </c>
       <c r="B49" t="str">
         <v/>
       </c>
       <c r="C49" t="str">
-        <v>https://music.apple.com/us/song/summer-breeze/6763360727</v>
+        <v>https://music.apple.com/us/song/how-did-you-know/1888553137</v>
       </c>
       <c r="D49" t="str">
         <v>2026-05-05</v>
@@ -2237,36 +2237,36 @@
         <v/>
       </c>
       <c r="F49" t="str">
-        <v>flow state</v>
+        <v>California Sunrise (10th Anniversary Edition)</v>
       </c>
       <c r="G49" t="str">
-        <v>4:00</v>
+        <v>3:16</v>
       </c>
       <c r="H49" t="str">
-        <v>Keith Urban</v>
+        <v>Jon Pardi</v>
       </c>
       <c r="I49" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J49" t="str">
-        <v>https://music.apple.com/us/artist/keith-urban/549836</v>
+        <v>https://music.apple.com/us/artist/jon-pardi/371085834</v>
       </c>
       <c r="K49" t="str">
-        <v>https://music.apple.com/us/album/summer-breeze/1895279513</v>
+        <v>https://music.apple.com/us/album/how-did-you-know/1888552935</v>
       </c>
       <c r="L49" t="str">
-        <v>Summer Breeze - Keith Urban</v>
+        <v>How Did You Know - Jon Pardi</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="str">
-        <v>Sound of a Woman</v>
+        <v>Summer Breeze</v>
       </c>
       <c r="B50" t="str">
         <v/>
       </c>
       <c r="C50" t="str">
-        <v>https://music.apple.com/us/song/sound-of-a-woman/1859763367</v>
+        <v>https://music.apple.com/us/song/summer-breeze/6763360727</v>
       </c>
       <c r="D50" t="str">
         <v>2026-05-05</v>
@@ -2275,36 +2275,36 @@
         <v/>
       </c>
       <c r="F50" t="str">
-        <v>Sound of a Woman</v>
+        <v>flow state</v>
       </c>
       <c r="G50" t="str">
-        <v>4:27</v>
+        <v>4:00</v>
       </c>
       <c r="H50" t="str">
-        <v>Rita Wilson</v>
+        <v>Keith Urban</v>
       </c>
       <c r="I50" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J50" t="str">
-        <v>https://music.apple.com/us/artist/rita-wilson/270048575</v>
+        <v>https://music.apple.com/us/artist/keith-urban/549836</v>
       </c>
       <c r="K50" t="str">
-        <v>https://music.apple.com/us/album/sound-of-a-woman/1859763034</v>
+        <v>https://music.apple.com/us/album/summer-breeze/1895279513</v>
       </c>
       <c r="L50" t="str">
-        <v>Sound of a Woman - Rita Wilson</v>
+        <v>Summer Breeze - Keith Urban</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="str">
-        <v>My Life</v>
+        <v>Sound of a Woman</v>
       </c>
       <c r="B51" t="str">
         <v/>
       </c>
       <c r="C51" t="str">
-        <v>https://music.apple.com/us/song/my-life/1893157347</v>
+        <v>https://music.apple.com/us/song/sound-of-a-woman/1859763367</v>
       </c>
       <c r="D51" t="str">
         <v>2026-05-05</v>
@@ -2313,36 +2313,36 @@
         <v/>
       </c>
       <c r="F51" t="str">
-        <v>BERNARR.</v>
+        <v>Sound of a Woman</v>
       </c>
       <c r="G51" t="str">
-        <v>3:31</v>
+        <v>4:27</v>
       </c>
       <c r="H51" t="str">
-        <v>Durand Bernarr</v>
+        <v>Rita Wilson</v>
       </c>
       <c r="I51" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J51" t="str">
-        <v>https://music.apple.com/us/artist/durand-bernarr/584124023</v>
+        <v>https://music.apple.com/us/artist/rita-wilson/270048575</v>
       </c>
       <c r="K51" t="str">
-        <v>https://music.apple.com/us/album/my-life/1893156957</v>
+        <v>https://music.apple.com/us/album/sound-of-a-woman/1859763034</v>
       </c>
       <c r="L51" t="str">
-        <v>My Life - Durand Bernarr</v>
+        <v>Sound of a Woman - Rita Wilson</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="str">
-        <v>Ribcage</v>
+        <v>My Life</v>
       </c>
       <c r="B52" t="str">
         <v/>
       </c>
       <c r="C52" t="str">
-        <v>https://music.apple.com/us/song/ribcage/1893155593</v>
+        <v>https://music.apple.com/us/song/my-life/1893157347</v>
       </c>
       <c r="D52" t="str">
         <v>2026-05-05</v>
@@ -2351,36 +2351,36 @@
         <v/>
       </c>
       <c r="F52" t="str">
-        <v>Ribcage - Single</v>
+        <v>BERNARR.</v>
       </c>
       <c r="G52" t="str">
-        <v>3:00</v>
+        <v>3:31</v>
       </c>
       <c r="H52" t="str">
-        <v>Bella Poarch</v>
+        <v>Durand Bernarr</v>
       </c>
       <c r="I52" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J52" t="str">
-        <v>https://music.apple.com/us/artist/bella-poarch/1567245769</v>
+        <v>https://music.apple.com/us/artist/durand-bernarr/584124023</v>
       </c>
       <c r="K52" t="str">
-        <v>https://music.apple.com/us/album/ribcage/1893155591</v>
+        <v>https://music.apple.com/us/album/my-life/1893156957</v>
       </c>
       <c r="L52" t="str">
-        <v>Ribcage - Bella Poarch</v>
+        <v>My Life - Durand Bernarr</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="str">
-        <v>i loved you then</v>
+        <v>Ribcage</v>
       </c>
       <c r="B53" t="str">
         <v/>
       </c>
       <c r="C53" t="str">
-        <v>https://music.apple.com/us/song/i-loved-you-then/1878232821</v>
+        <v>https://music.apple.com/us/song/ribcage/1893155593</v>
       </c>
       <c r="D53" t="str">
         <v>2026-05-05</v>
@@ -2389,36 +2389,36 @@
         <v/>
       </c>
       <c r="F53" t="str">
-        <v>I HOPE THIS HELPS</v>
+        <v>Ribcage - Single</v>
       </c>
       <c r="G53" t="str">
-        <v>3:42</v>
+        <v>3:00</v>
       </c>
       <c r="H53" t="str">
-        <v>Alana Springsteen</v>
+        <v>Bella Poarch</v>
       </c>
       <c r="I53" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J53" t="str">
-        <v>https://music.apple.com/us/artist/alana-springsteen/1309335606</v>
+        <v>https://music.apple.com/us/artist/bella-poarch/1567245769</v>
       </c>
       <c r="K53" t="str">
-        <v>https://music.apple.com/us/album/i-loved-you-then/1878232194</v>
+        <v>https://music.apple.com/us/album/ribcage/1893155591</v>
       </c>
       <c r="L53" t="str">
-        <v>i loved you then - Alana Springsteen</v>
+        <v>Ribcage - Bella Poarch</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="str">
-        <v>I'll Let You Finish</v>
+        <v>i loved you then</v>
       </c>
       <c r="B54" t="str">
         <v/>
       </c>
       <c r="C54" t="str">
-        <v>https://music.apple.com/us/song/ill-let-you-finish/1891844342</v>
+        <v>https://music.apple.com/us/song/i-loved-you-then/1878232821</v>
       </c>
       <c r="D54" t="str">
         <v>2026-05-05</v>
@@ -2427,36 +2427,36 @@
         <v/>
       </c>
       <c r="F54" t="str">
-        <v>Fire From The Hip</v>
+        <v>I HOPE THIS HELPS</v>
       </c>
       <c r="G54" t="str">
-        <v>3:54</v>
+        <v>3:42</v>
       </c>
       <c r="H54" t="str">
-        <v>Finn Wolfhard</v>
+        <v>Alana Springsteen</v>
       </c>
       <c r="I54" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J54" t="str">
-        <v>https://music.apple.com/us/artist/finn-wolfhard/1275324142</v>
+        <v>https://music.apple.com/us/artist/alana-springsteen/1309335606</v>
       </c>
       <c r="K54" t="str">
-        <v>https://music.apple.com/us/album/ill-let-you-finish/1891844033</v>
+        <v>https://music.apple.com/us/album/i-loved-you-then/1878232194</v>
       </c>
       <c r="L54" t="str">
-        <v>I'll Let You Finish - Finn Wolfhard</v>
+        <v>i loved you then - Alana Springsteen</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="str">
-        <v>It Gets Me Through</v>
+        <v>I'll Let You Finish</v>
       </c>
       <c r="B55" t="str">
         <v/>
       </c>
       <c r="C55" t="str">
-        <v>https://music.apple.com/us/song/it-gets-me-through/1884798927</v>
+        <v>https://music.apple.com/us/song/ill-let-you-finish/1891844342</v>
       </c>
       <c r="D55" t="str">
         <v>2026-05-05</v>
@@ -2465,36 +2465,36 @@
         <v/>
       </c>
       <c r="F55" t="str">
-        <v>Original Sound (Original Motion Picture Soundtrack)</v>
+        <v>Fire From The Hip</v>
       </c>
       <c r="G55" t="str">
-        <v>2:53</v>
+        <v>3:54</v>
       </c>
       <c r="H55" t="str">
-        <v>Laura Marano</v>
+        <v>Finn Wolfhard</v>
       </c>
       <c r="I55" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J55" t="str">
-        <v>https://music.apple.com/us/artist/laura-marano/357181332</v>
+        <v>https://music.apple.com/us/artist/finn-wolfhard/1275324142</v>
       </c>
       <c r="K55" t="str">
-        <v>https://music.apple.com/us/album/it-gets-me-through/1884798598</v>
+        <v>https://music.apple.com/us/album/ill-let-you-finish/1891844033</v>
       </c>
       <c r="L55" t="str">
-        <v>It Gets Me Through - Laura Marano</v>
+        <v>I'll Let You Finish - Finn Wolfhard</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="str">
-        <v>The Author</v>
+        <v>It Gets Me Through</v>
       </c>
       <c r="B56" t="str">
         <v/>
       </c>
       <c r="C56" t="str">
-        <v>https://music.apple.com/us/song/the-author/6763327641</v>
+        <v>https://music.apple.com/us/song/it-gets-me-through/1884798927</v>
       </c>
       <c r="D56" t="str">
         <v>2026-05-05</v>
@@ -2503,36 +2503,36 @@
         <v/>
       </c>
       <c r="F56" t="str">
-        <v>The Author - Single</v>
+        <v>Original Sound (Original Motion Picture Soundtrack)</v>
       </c>
       <c r="G56" t="str">
-        <v>4:36</v>
+        <v>2:53</v>
       </c>
       <c r="H56" t="str">
-        <v>Brandon Lake</v>
+        <v>Laura Marano</v>
       </c>
       <c r="I56" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J56" t="str">
-        <v>https://music.apple.com/us/artist/brandon-lake/1050382282</v>
+        <v>https://music.apple.com/us/artist/laura-marano/357181332</v>
       </c>
       <c r="K56" t="str">
-        <v>https://music.apple.com/us/album/the-author/1895265952</v>
+        <v>https://music.apple.com/us/album/it-gets-me-through/1884798598</v>
       </c>
       <c r="L56" t="str">
-        <v>The Author - Brandon Lake</v>
+        <v>It Gets Me Through - Laura Marano</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="str">
-        <v>Want Me Back (feat. Tors)</v>
+        <v>The Author</v>
       </c>
       <c r="B57" t="str">
         <v/>
       </c>
       <c r="C57" t="str">
-        <v>https://music.apple.com/us/song/want-me-back-feat-tors/1889370756</v>
+        <v>https://music.apple.com/us/song/the-author/6763327641</v>
       </c>
       <c r="D57" t="str">
         <v>2026-05-05</v>
@@ -2541,36 +2541,36 @@
         <v/>
       </c>
       <c r="F57" t="str">
-        <v>Want Me Back (feat. Tors) - Single</v>
+        <v>The Author - Single</v>
       </c>
       <c r="G57" t="str">
-        <v>3:44</v>
+        <v>4:36</v>
       </c>
       <c r="H57" t="str">
-        <v>Trousdale</v>
+        <v>Brandon Lake</v>
       </c>
       <c r="I57" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J57" t="str">
-        <v>https://music.apple.com/us/artist/trousdale/1534241692</v>
+        <v>https://music.apple.com/us/artist/brandon-lake/1050382282</v>
       </c>
       <c r="K57" t="str">
-        <v>https://music.apple.com/us/album/want-me-back-feat-tors/1889370752</v>
+        <v>https://music.apple.com/us/album/the-author/1895265952</v>
       </c>
       <c r="L57" t="str">
-        <v>Want Me Back (feat. Tors) - Trousdale</v>
+        <v>The Author - Brandon Lake</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="str">
-        <v>RUIN</v>
+        <v>Want Me Back (feat. Tors)</v>
       </c>
       <c r="B58" t="str">
         <v/>
       </c>
       <c r="C58" t="str">
-        <v>https://music.apple.com/us/song/ruin/1886537117</v>
+        <v>https://music.apple.com/us/song/want-me-back-feat-tors/1889370756</v>
       </c>
       <c r="D58" t="str">
         <v>2026-05-05</v>
@@ -2579,36 +2579,36 @@
         <v/>
       </c>
       <c r="F58" t="str">
-        <v>ADDENDUM - EP</v>
+        <v>Want Me Back (feat. Tors) - Single</v>
       </c>
       <c r="G58" t="str">
-        <v>3:23</v>
+        <v>3:44</v>
       </c>
       <c r="H58" t="str">
-        <v>HEALTH</v>
+        <v>Trousdale</v>
       </c>
       <c r="I58" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J58" t="str">
-        <v>https://music.apple.com/us/artist/health/317478211</v>
+        <v>https://music.apple.com/us/artist/trousdale/1534241692</v>
       </c>
       <c r="K58" t="str">
-        <v>https://music.apple.com/us/album/ruin/1886536873</v>
+        <v>https://music.apple.com/us/album/want-me-back-feat-tors/1889370752</v>
       </c>
       <c r="L58" t="str">
-        <v>RUIN - HEALTH</v>
+        <v>Want Me Back (feat. Tors) - Trousdale</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="str">
-        <v>I Know I Know</v>
+        <v>RUIN</v>
       </c>
       <c r="B59" t="str">
         <v/>
       </c>
       <c r="C59" t="str">
-        <v>https://music.apple.com/us/song/i-know-i-know/1894354139</v>
+        <v>https://music.apple.com/us/song/ruin/1886537117</v>
       </c>
       <c r="D59" t="str">
         <v>2026-05-05</v>
@@ -2617,36 +2617,36 @@
         <v/>
       </c>
       <c r="F59" t="str">
-        <v>I Know I Know - Single</v>
+        <v>ADDENDUM - EP</v>
       </c>
       <c r="G59" t="str">
-        <v>2:39</v>
+        <v>3:23</v>
       </c>
       <c r="H59" t="str">
-        <v>STELLA LEFTY</v>
+        <v>HEALTH</v>
       </c>
       <c r="I59" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J59" t="str">
-        <v>https://music.apple.com/us/artist/stella-lefty/1641742186</v>
+        <v>https://music.apple.com/us/artist/health/317478211</v>
       </c>
       <c r="K59" t="str">
-        <v>https://music.apple.com/us/album/i-know-i-know/1894354136</v>
+        <v>https://music.apple.com/us/album/ruin/1886536873</v>
       </c>
       <c r="L59" t="str">
-        <v>I Know I Know - STELLA LEFTY</v>
+        <v>RUIN - HEALTH</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="str">
-        <v>Drive All Night</v>
+        <v>I Know I Know</v>
       </c>
       <c r="B60" t="str">
         <v/>
       </c>
       <c r="C60" t="str">
-        <v>https://music.apple.com/us/song/drive-all-night/6763189759</v>
+        <v>https://music.apple.com/us/song/i-know-i-know/1894354139</v>
       </c>
       <c r="D60" t="str">
         <v>2026-05-05</v>
@@ -2655,36 +2655,36 @@
         <v/>
       </c>
       <c r="F60" t="str">
-        <v>Drive All Night - Single</v>
+        <v>I Know I Know - Single</v>
       </c>
       <c r="G60" t="str">
-        <v>2:50</v>
+        <v>2:39</v>
       </c>
       <c r="H60" t="str">
-        <v>Wyatt Flores</v>
+        <v>STELLA LEFTY</v>
       </c>
       <c r="I60" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J60" t="str">
-        <v>https://music.apple.com/us/artist/wyatt-flores/1563146833</v>
+        <v>https://music.apple.com/us/artist/stella-lefty/1641742186</v>
       </c>
       <c r="K60" t="str">
-        <v>https://music.apple.com/us/album/drive-all-night/1895207255</v>
+        <v>https://music.apple.com/us/album/i-know-i-know/1894354136</v>
       </c>
       <c r="L60" t="str">
-        <v>Drive All Night - Wyatt Flores</v>
+        <v>I Know I Know - STELLA LEFTY</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="str">
-        <v>AIN'T U TIRED?</v>
+        <v>Drive All Night</v>
       </c>
       <c r="B61" t="str">
         <v/>
       </c>
       <c r="C61" t="str">
-        <v>https://music.apple.com/us/song/aint-u-tired/6763115235</v>
+        <v>https://music.apple.com/us/song/drive-all-night/6763189759</v>
       </c>
       <c r="D61" t="str">
         <v>2026-05-05</v>
@@ -2693,36 +2693,36 @@
         <v/>
       </c>
       <c r="F61" t="str">
-        <v>AIN'T U TIRED? - Single</v>
+        <v>Drive All Night - Single</v>
       </c>
       <c r="G61" t="str">
-        <v>3:41</v>
+        <v>2:50</v>
       </c>
       <c r="H61" t="str">
-        <v>Jessie Reyez</v>
+        <v>Wyatt Flores</v>
       </c>
       <c r="I61" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J61" t="str">
-        <v>https://music.apple.com/us/artist/jessie-reyez/1043591612</v>
+        <v>https://music.apple.com/us/artist/wyatt-flores/1563146833</v>
       </c>
       <c r="K61" t="str">
-        <v>https://music.apple.com/us/album/aint-u-tired/1895167276</v>
+        <v>https://music.apple.com/us/album/drive-all-night/1895207255</v>
       </c>
       <c r="L61" t="str">
-        <v>AIN'T U TIRED? - Jessie Reyez</v>
+        <v>Drive All Night - Wyatt Flores</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="str">
-        <v>Boys In Blue</v>
+        <v>AIN'T U TIRED?</v>
       </c>
       <c r="B62" t="str">
         <v/>
       </c>
       <c r="C62" t="str">
-        <v>https://music.apple.com/us/song/boys-in-blue/1892436920</v>
+        <v>https://music.apple.com/us/song/aint-u-tired/6763115235</v>
       </c>
       <c r="D62" t="str">
         <v>2026-05-05</v>
@@ -2731,36 +2731,36 @@
         <v/>
       </c>
       <c r="F62" t="str">
-        <v>Emotional Junglist</v>
+        <v>AIN'T U TIRED? - Single</v>
       </c>
       <c r="G62" t="str">
-        <v>2:33</v>
+        <v>3:41</v>
       </c>
       <c r="H62" t="str">
-        <v>Nia Archives</v>
+        <v>Jessie Reyez</v>
       </c>
       <c r="I62" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J62" t="str">
-        <v>https://music.apple.com/us/artist/nia-archives/1515978311</v>
+        <v>https://music.apple.com/us/artist/jessie-reyez/1043591612</v>
       </c>
       <c r="K62" t="str">
-        <v>https://music.apple.com/us/album/boys-in-blue/1892436329</v>
+        <v>https://music.apple.com/us/album/aint-u-tired/1895167276</v>
       </c>
       <c r="L62" t="str">
-        <v>Boys In Blue - Nia Archives</v>
+        <v>AIN'T U TIRED? - Jessie Reyez</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="str">
-        <v>Salma Hayek</v>
+        <v>Boys In Blue</v>
       </c>
       <c r="B63" t="str">
         <v/>
       </c>
       <c r="C63" t="str">
-        <v>https://music.apple.com/us/song/salma-hayek/1891815286</v>
+        <v>https://music.apple.com/us/song/boys-in-blue/1892436920</v>
       </c>
       <c r="D63" t="str">
         <v>2026-05-05</v>
@@ -2769,36 +2769,36 @@
         <v/>
       </c>
       <c r="F63" t="str">
-        <v>Salma Hayek - Single</v>
+        <v>Emotional Junglist</v>
       </c>
       <c r="G63" t="str">
-        <v>3:43</v>
+        <v>2:33</v>
       </c>
       <c r="H63" t="str">
-        <v>Luis R Conriquez</v>
+        <v>Nia Archives</v>
       </c>
       <c r="I63" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J63" t="str">
-        <v>https://music.apple.com/us/artist/luis-r-conriquez/1252271456</v>
+        <v>https://music.apple.com/us/artist/nia-archives/1515978311</v>
       </c>
       <c r="K63" t="str">
-        <v>https://music.apple.com/us/album/salma-hayek/1891815277</v>
+        <v>https://music.apple.com/us/album/boys-in-blue/1892436329</v>
       </c>
       <c r="L63" t="str">
-        <v>Salma Hayek - Luis R Conriquez</v>
+        <v>Boys In Blue - Nia Archives</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="str">
-        <v>Stubborn Mouth</v>
+        <v>Salma Hayek</v>
       </c>
       <c r="B64" t="str">
         <v/>
       </c>
       <c r="C64" t="str">
-        <v>https://music.apple.com/us/song/stubborn-mouth/1893194800</v>
+        <v>https://music.apple.com/us/song/salma-hayek/1891815286</v>
       </c>
       <c r="D64" t="str">
         <v>2026-05-05</v>
@@ -2807,36 +2807,36 @@
         <v/>
       </c>
       <c r="F64" t="str">
-        <v>Stubborn Mouth - Single</v>
+        <v>Salma Hayek - Single</v>
       </c>
       <c r="G64" t="str">
-        <v>3:02</v>
+        <v>3:43</v>
       </c>
       <c r="H64" t="str">
-        <v>Girl Tones</v>
+        <v>Luis R Conriquez</v>
       </c>
       <c r="I64" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J64" t="str">
-        <v>https://music.apple.com/us/artist/girl-tones/1761267584</v>
+        <v>https://music.apple.com/us/artist/luis-r-conriquez/1252271456</v>
       </c>
       <c r="K64" t="str">
-        <v>https://music.apple.com/us/album/stubborn-mouth/1893194649</v>
+        <v>https://music.apple.com/us/album/salma-hayek/1891815277</v>
       </c>
       <c r="L64" t="str">
-        <v>Stubborn Mouth - Girl Tones</v>
+        <v>Salma Hayek - Luis R Conriquez</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="str">
-        <v>Hallucination</v>
+        <v>Stubborn Mouth</v>
       </c>
       <c r="B65" t="str">
         <v/>
       </c>
       <c r="C65" t="str">
-        <v>https://music.apple.com/us/song/hallucination/6764110976</v>
+        <v>https://music.apple.com/us/song/stubborn-mouth/1893194800</v>
       </c>
       <c r="D65" t="str">
         <v>2026-05-05</v>
@@ -2845,36 +2845,36 @@
         <v/>
       </c>
       <c r="F65" t="str">
-        <v>Promising Young Woman - EP</v>
+        <v>Stubborn Mouth - Single</v>
       </c>
       <c r="G65" t="str">
-        <v>3:22</v>
+        <v>3:02</v>
       </c>
       <c r="H65" t="str">
-        <v>Isabel LaRosa</v>
+        <v>Girl Tones</v>
       </c>
       <c r="I65" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J65" t="str">
-        <v>https://music.apple.com/us/artist/isabel-larosa/1578296103</v>
+        <v>https://music.apple.com/us/artist/girl-tones/1761267584</v>
       </c>
       <c r="K65" t="str">
-        <v>https://music.apple.com/us/album/hallucination/1895644574</v>
+        <v>https://music.apple.com/us/album/stubborn-mouth/1893194649</v>
       </c>
       <c r="L65" t="str">
-        <v>Hallucination - Isabel LaRosa</v>
+        <v>Stubborn Mouth - Girl Tones</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="str">
-        <v>In Da Jungle</v>
+        <v>Hallucination</v>
       </c>
       <c r="B66" t="str">
         <v/>
       </c>
       <c r="C66" t="str">
-        <v>https://music.apple.com/us/song/in-da-jungle/1891136400</v>
+        <v>https://music.apple.com/us/song/hallucination/6764110976</v>
       </c>
       <c r="D66" t="str">
         <v>2026-05-05</v>
@@ -2883,36 +2883,36 @@
         <v/>
       </c>
       <c r="F66" t="str">
-        <v>In Da Jungle - Single</v>
+        <v>Promising Young Woman - EP</v>
       </c>
       <c r="G66" t="str">
-        <v>2:44</v>
+        <v>3:22</v>
       </c>
       <c r="H66" t="str">
-        <v>BLOND:ISH</v>
+        <v>Isabel LaRosa</v>
       </c>
       <c r="I66" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J66" t="str">
-        <v>https://music.apple.com/us/artist/blond-ish/394776491</v>
+        <v>https://music.apple.com/us/artist/isabel-larosa/1578296103</v>
       </c>
       <c r="K66" t="str">
-        <v>https://music.apple.com/us/album/in-da-jungle/1891136398</v>
+        <v>https://music.apple.com/us/album/hallucination/1895644574</v>
       </c>
       <c r="L66" t="str">
-        <v>In Da Jungle - BLOND:ISH</v>
+        <v>Hallucination - Isabel LaRosa</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="str">
-        <v>Fall Short</v>
+        <v>In Da Jungle</v>
       </c>
       <c r="B67" t="str">
         <v/>
       </c>
       <c r="C67" t="str">
-        <v>https://music.apple.com/us/song/fall-short/1894662749</v>
+        <v>https://music.apple.com/us/song/in-da-jungle/1891136400</v>
       </c>
       <c r="D67" t="str">
         <v>2026-05-05</v>
@@ -2921,36 +2921,36 @@
         <v/>
       </c>
       <c r="F67" t="str">
-        <v>Fall Short - Single</v>
+        <v>In Da Jungle - Single</v>
       </c>
       <c r="G67" t="str">
         <v>2:44</v>
       </c>
       <c r="H67" t="str">
-        <v>nyan</v>
+        <v>BLOND:ISH</v>
       </c>
       <c r="I67" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J67" t="str">
-        <v>https://music.apple.com/us/artist/nyan/1478138732</v>
+        <v>https://music.apple.com/us/artist/blond-ish/394776491</v>
       </c>
       <c r="K67" t="str">
-        <v>https://music.apple.com/us/album/fall-short/1894662748</v>
+        <v>https://music.apple.com/us/album/in-da-jungle/1891136398</v>
       </c>
       <c r="L67" t="str">
-        <v>Fall Short - nyan</v>
+        <v>In Da Jungle - BLOND:ISH</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="str">
-        <v>Irish Goodbye (feat. Kae Tempest)</v>
+        <v>Fall Short</v>
       </c>
       <c r="B68" t="str">
         <v/>
       </c>
       <c r="C68" t="str">
-        <v>https://music.apple.com/us/song/irish-goodbye-feat-kae-tempest/1862224205</v>
+        <v>https://music.apple.com/us/song/fall-short/1894662749</v>
       </c>
       <c r="D68" t="str">
         <v>2026-05-05</v>
@@ -2959,36 +2959,36 @@
         <v/>
       </c>
       <c r="F68" t="str">
-        <v>FENIAN</v>
+        <v>Fall Short - Single</v>
       </c>
       <c r="G68" t="str">
-        <v>3:34</v>
+        <v>2:44</v>
       </c>
       <c r="H68" t="str">
-        <v>Kneecap</v>
+        <v>nyan</v>
       </c>
       <c r="I68" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J68" t="str">
-        <v>https://music.apple.com/us/artist/kneecap/1330315811</v>
+        <v>https://music.apple.com/us/artist/nyan/1478138732</v>
       </c>
       <c r="K68" t="str">
-        <v>https://music.apple.com/us/album/irish-goodbye-feat-kae-tempest/1862223497</v>
+        <v>https://music.apple.com/us/album/fall-short/1894662748</v>
       </c>
       <c r="L68" t="str">
-        <v>Irish Goodbye (feat. Kae Tempest) - Kneecap</v>
+        <v>Fall Short - nyan</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="str">
-        <v>1989</v>
+        <v>Irish Goodbye (feat. Kae Tempest)</v>
       </c>
       <c r="B69" t="str">
         <v/>
       </c>
       <c r="C69" t="str">
-        <v>https://music.apple.com/us/song/1989/1893089382</v>
+        <v>https://music.apple.com/us/song/irish-goodbye-feat-kae-tempest/1862224205</v>
       </c>
       <c r="D69" t="str">
         <v>2026-05-05</v>
@@ -2997,36 +2997,36 @@
         <v/>
       </c>
       <c r="F69" t="str">
-        <v>1989 - Single</v>
+        <v>FENIAN</v>
       </c>
       <c r="G69" t="str">
-        <v>3:05</v>
+        <v>3:34</v>
       </c>
       <c r="H69" t="str">
-        <v>Nightly</v>
+        <v>Kneecap</v>
       </c>
       <c r="I69" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J69" t="str">
-        <v>https://music.apple.com/us/artist/nightly/352310972</v>
+        <v>https://music.apple.com/us/artist/kneecap/1330315811</v>
       </c>
       <c r="K69" t="str">
-        <v>https://music.apple.com/us/album/1989/1893089381</v>
+        <v>https://music.apple.com/us/album/irish-goodbye-feat-kae-tempest/1862223497</v>
       </c>
       <c r="L69" t="str">
-        <v>1989 - Nightly</v>
+        <v>Irish Goodbye (feat. Kae Tempest) - Kneecap</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="str">
-        <v>no more regrets</v>
+        <v>1989</v>
       </c>
       <c r="B70" t="str">
         <v/>
       </c>
       <c r="C70" t="str">
-        <v>https://music.apple.com/us/song/no-more-regrets/1893191803</v>
+        <v>https://music.apple.com/us/song/1989/1893089382</v>
       </c>
       <c r="D70" t="str">
         <v>2026-05-05</v>
@@ -3035,36 +3035,36 @@
         <v/>
       </c>
       <c r="F70" t="str">
-        <v>no more regrets - Single</v>
+        <v>1989 - Single</v>
       </c>
       <c r="G70" t="str">
-        <v>2:58</v>
+        <v>3:05</v>
       </c>
       <c r="H70" t="str">
-        <v>almost monday</v>
+        <v>Nightly</v>
       </c>
       <c r="I70" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J70" t="str">
-        <v>https://music.apple.com/us/artist/almost-monday/1300723925</v>
+        <v>https://music.apple.com/us/artist/nightly/352310972</v>
       </c>
       <c r="K70" t="str">
-        <v>https://music.apple.com/us/album/no-more-regrets/1893191802</v>
+        <v>https://music.apple.com/us/album/1989/1893089381</v>
       </c>
       <c r="L70" t="str">
-        <v>no more regrets - almost monday</v>
+        <v>1989 - Nightly</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="str">
-        <v>Drum Machine</v>
+        <v>no more regrets</v>
       </c>
       <c r="B71" t="str">
         <v/>
       </c>
       <c r="C71" t="str">
-        <v>https://music.apple.com/us/song/drum-machine/1840517102</v>
+        <v>https://music.apple.com/us/song/no-more-regrets/1893191803</v>
       </c>
       <c r="D71" t="str">
         <v>2026-05-05</v>
@@ -3073,36 +3073,36 @@
         <v/>
       </c>
       <c r="F71" t="str">
-        <v>Sweat</v>
+        <v>no more regrets - Single</v>
       </c>
       <c r="G71" t="str">
-        <v>3:16</v>
+        <v>2:58</v>
       </c>
       <c r="H71" t="str">
-        <v>Melanie C</v>
+        <v>almost monday</v>
       </c>
       <c r="I71" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J71" t="str">
-        <v>https://music.apple.com/us/artist/melanie-c/653819</v>
+        <v>https://music.apple.com/us/artist/almost-monday/1300723925</v>
       </c>
       <c r="K71" t="str">
-        <v>https://music.apple.com/us/album/drum-machine/1840516706</v>
+        <v>https://music.apple.com/us/album/no-more-regrets/1893191802</v>
       </c>
       <c r="L71" t="str">
-        <v>Drum Machine - Melanie C</v>
+        <v>no more regrets - almost monday</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="str">
-        <v>I'm Perfect</v>
+        <v>Drum Machine</v>
       </c>
       <c r="B72" t="str">
         <v/>
       </c>
       <c r="C72" t="str">
-        <v>https://music.apple.com/us/song/im-perfect/1893181359</v>
+        <v>https://music.apple.com/us/song/drum-machine/1840517102</v>
       </c>
       <c r="D72" t="str">
         <v>2026-05-05</v>
@@ -3111,36 +3111,36 @@
         <v/>
       </c>
       <c r="F72" t="str">
-        <v>I'm Perfect - Single</v>
+        <v>Sweat</v>
       </c>
       <c r="G72" t="str">
-        <v>2:36</v>
+        <v>3:16</v>
       </c>
       <c r="H72" t="str">
-        <v>Olivia O'Brien</v>
+        <v>Melanie C</v>
       </c>
       <c r="I72" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J72" t="str">
-        <v>https://music.apple.com/us/artist/olivia-obrien/1023538468</v>
+        <v>https://music.apple.com/us/artist/melanie-c/653819</v>
       </c>
       <c r="K72" t="str">
-        <v>https://music.apple.com/us/album/im-perfect/1893181351</v>
+        <v>https://music.apple.com/us/album/drum-machine/1840516706</v>
       </c>
       <c r="L72" t="str">
-        <v>I'm Perfect - Olivia O'Brien</v>
+        <v>Drum Machine - Melanie C</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="str">
-        <v>Theme for a Train Journey</v>
+        <v>I'm Perfect</v>
       </c>
       <c r="B73" t="str">
         <v/>
       </c>
       <c r="C73" t="str">
-        <v>https://music.apple.com/us/song/theme-for-a-train-journey/1880699785</v>
+        <v>https://music.apple.com/us/song/im-perfect/1893181359</v>
       </c>
       <c r="D73" t="str">
         <v>2026-05-05</v>
@@ -3149,36 +3149,36 @@
         <v/>
       </c>
       <c r="F73" t="str">
-        <v>AK Cuts: Vol 3 - EP</v>
+        <v>I'm Perfect - Single</v>
       </c>
       <c r="G73" t="str">
-        <v>5:05</v>
+        <v>2:36</v>
       </c>
       <c r="H73" t="str">
-        <v>Anish Kumar</v>
+        <v>Olivia O'Brien</v>
       </c>
       <c r="I73" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J73" t="str">
-        <v>https://music.apple.com/us/artist/anish-kumar/1510744726</v>
+        <v>https://music.apple.com/us/artist/olivia-obrien/1023538468</v>
       </c>
       <c r="K73" t="str">
-        <v>https://music.apple.com/us/album/theme-for-a-train-journey/1880699566</v>
+        <v>https://music.apple.com/us/album/im-perfect/1893181351</v>
       </c>
       <c r="L73" t="str">
-        <v>Theme for a Train Journey - Anish Kumar</v>
+        <v>I'm Perfect - Olivia O'Brien</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="str">
-        <v>Bitch You Weird</v>
+        <v>Theme for a Train Journey</v>
       </c>
       <c r="B74" t="str">
         <v/>
       </c>
       <c r="C74" t="str">
-        <v>https://music.apple.com/us/song/bitch-you-weird/6763395875</v>
+        <v>https://music.apple.com/us/song/theme-for-a-train-journey/1880699785</v>
       </c>
       <c r="D74" t="str">
         <v>2026-05-05</v>
@@ -3187,36 +3187,36 @@
         <v/>
       </c>
       <c r="F74" t="str">
-        <v>Bitch You Weird - Single</v>
+        <v>AK Cuts: Vol 3 - EP</v>
       </c>
       <c r="G74" t="str">
-        <v>2:27</v>
+        <v>5:05</v>
       </c>
       <c r="H74" t="str">
-        <v>Real Boston Richey</v>
+        <v>Anish Kumar</v>
       </c>
       <c r="I74" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J74" t="str">
-        <v>https://music.apple.com/us/artist/real-boston-richey/1595496755</v>
+        <v>https://music.apple.com/us/artist/anish-kumar/1510744726</v>
       </c>
       <c r="K74" t="str">
-        <v>https://music.apple.com/us/album/bitch-you-weird/1895294715</v>
+        <v>https://music.apple.com/us/album/theme-for-a-train-journey/1880699566</v>
       </c>
       <c r="L74" t="str">
-        <v>Bitch You Weird - Real Boston Richey</v>
+        <v>Theme for a Train Journey - Anish Kumar</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="str">
-        <v>Blackbird Rising</v>
+        <v>Bitch You Weird</v>
       </c>
       <c r="B75" t="str">
         <v/>
       </c>
       <c r="C75" t="str">
-        <v>https://music.apple.com/us/song/blackbird-rising/1887166611</v>
+        <v>https://music.apple.com/us/song/bitch-you-weird/6763395875</v>
       </c>
       <c r="D75" t="str">
         <v>2026-05-05</v>
@@ -3225,36 +3225,36 @@
         <v/>
       </c>
       <c r="F75" t="str">
-        <v>24</v>
+        <v>Bitch You Weird - Single</v>
       </c>
       <c r="G75" t="str">
-        <v>2:24</v>
+        <v>2:27</v>
       </c>
       <c r="H75" t="str">
-        <v>Alexis Ffrench</v>
+        <v>Real Boston Richey</v>
       </c>
       <c r="I75" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J75" t="str">
-        <v>https://music.apple.com/us/artist/alexis-ffrench/342515428</v>
+        <v>https://music.apple.com/us/artist/real-boston-richey/1595496755</v>
       </c>
       <c r="K75" t="str">
-        <v>https://music.apple.com/us/album/blackbird-rising/1887166427</v>
+        <v>https://music.apple.com/us/album/bitch-you-weird/1895294715</v>
       </c>
       <c r="L75" t="str">
-        <v>Blackbird Rising - Alexis Ffrench</v>
+        <v>Bitch You Weird - Real Boston Richey</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="str">
-        <v>usher in the spirit</v>
+        <v>Blackbird Rising</v>
       </c>
       <c r="B76" t="str">
         <v/>
       </c>
       <c r="C76" t="str">
-        <v>https://music.apple.com/us/song/usher-in-the-spirit/6763373678</v>
+        <v>https://music.apple.com/us/song/blackbird-rising/1887166611</v>
       </c>
       <c r="D76" t="str">
         <v>2026-05-05</v>
@@ -3263,36 +3263,36 @@
         <v/>
       </c>
       <c r="F76" t="str">
-        <v>usher in the spirit - Single</v>
+        <v>24</v>
       </c>
       <c r="G76" t="str">
-        <v>3:00</v>
+        <v>2:24</v>
       </c>
       <c r="H76" t="str">
-        <v>Aaron Cole</v>
+        <v>Alexis Ffrench</v>
       </c>
       <c r="I76" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J76" t="str">
-        <v>https://music.apple.com/us/artist/aaron-cole/507522696</v>
+        <v>https://music.apple.com/us/artist/alexis-ffrench/342515428</v>
       </c>
       <c r="K76" t="str">
-        <v>https://music.apple.com/us/album/usher-in-the-spirit/1895286256</v>
+        <v>https://music.apple.com/us/album/blackbird-rising/1887166427</v>
       </c>
       <c r="L76" t="str">
-        <v>usher in the spirit - Aaron Cole</v>
+        <v>Blackbird Rising - Alexis Ffrench</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="str">
-        <v>Moonlight</v>
+        <v>usher in the spirit</v>
       </c>
       <c r="B77" t="str">
         <v/>
       </c>
       <c r="C77" t="str">
-        <v>https://music.apple.com/us/song/moonlight/1892950791</v>
+        <v>https://music.apple.com/us/song/usher-in-the-spirit/6763373678</v>
       </c>
       <c r="D77" t="str">
         <v>2026-05-05</v>
@@ -3301,36 +3301,36 @@
         <v/>
       </c>
       <c r="F77" t="str">
-        <v>Moonlight - Single</v>
+        <v>usher in the spirit - Single</v>
       </c>
       <c r="G77" t="str">
-        <v>3:23</v>
+        <v>3:00</v>
       </c>
       <c r="H77" t="str">
-        <v>Chelsea Plank</v>
+        <v>Aaron Cole</v>
       </c>
       <c r="I77" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J77" t="str">
-        <v>https://music.apple.com/us/artist/chelsea-plank/1246169844</v>
+        <v>https://music.apple.com/us/artist/aaron-cole/507522696</v>
       </c>
       <c r="K77" t="str">
-        <v>https://music.apple.com/us/album/moonlight/1892950782</v>
+        <v>https://music.apple.com/us/album/usher-in-the-spirit/1895286256</v>
       </c>
       <c r="L77" t="str">
-        <v>Moonlight - Chelsea Plank</v>
+        <v>usher in the spirit - Aaron Cole</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="str">
-        <v>&gt;&gt;&gt;hands on me&lt;&lt;&lt;</v>
+        <v>Moonlight</v>
       </c>
       <c r="B78" t="str">
         <v/>
       </c>
       <c r="C78" t="str">
-        <v>https://music.apple.com/us/song/hands-on-me/1893960365</v>
+        <v>https://music.apple.com/us/song/moonlight/1892950791</v>
       </c>
       <c r="D78" t="str">
         <v>2026-05-05</v>
@@ -3339,36 +3339,36 @@
         <v/>
       </c>
       <c r="F78" t="str">
-        <v>&gt;&gt;&gt;hands on me&lt;&lt;&lt; - Single</v>
+        <v>Moonlight - Single</v>
       </c>
       <c r="G78" t="str">
-        <v>2:17</v>
+        <v>3:23</v>
       </c>
       <c r="H78" t="str">
-        <v>Becky Hill</v>
+        <v>Chelsea Plank</v>
       </c>
       <c r="I78" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J78" t="str">
-        <v>https://music.apple.com/us/artist/becky-hill/533839517</v>
+        <v>https://music.apple.com/us/artist/chelsea-plank/1246169844</v>
       </c>
       <c r="K78" t="str">
-        <v>https://music.apple.com/us/album/hands-on-me/1893960148</v>
+        <v>https://music.apple.com/us/album/moonlight/1892950782</v>
       </c>
       <c r="L78" t="str">
-        <v>&gt;&gt;&gt;hands on me&lt;&lt;&lt; - Becky Hill</v>
+        <v>Moonlight - Chelsea Plank</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="str">
-        <v>Closure</v>
+        <v>&gt;&gt;&gt;hands on me&lt;&lt;&lt;</v>
       </c>
       <c r="B79" t="str">
         <v/>
       </c>
       <c r="C79" t="str">
-        <v>https://music.apple.com/us/song/closure/1892418294</v>
+        <v>https://music.apple.com/us/song/hands-on-me/1893960365</v>
       </c>
       <c r="D79" t="str">
         <v>2026-05-05</v>
@@ -3377,36 +3377,36 @@
         <v/>
       </c>
       <c r="F79" t="str">
-        <v>Closure - Single</v>
+        <v>&gt;&gt;&gt;hands on me&lt;&lt;&lt; - Single</v>
       </c>
       <c r="G79" t="str">
-        <v>2:27</v>
+        <v>2:17</v>
       </c>
       <c r="H79" t="str">
-        <v>D.O.D</v>
+        <v>Becky Hill</v>
       </c>
       <c r="I79" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J79" t="str">
-        <v>https://music.apple.com/us/artist/d-o-d/444171843</v>
+        <v>https://music.apple.com/us/artist/becky-hill/533839517</v>
       </c>
       <c r="K79" t="str">
-        <v>https://music.apple.com/us/album/closure/1892418283</v>
+        <v>https://music.apple.com/us/album/hands-on-me/1893960148</v>
       </c>
       <c r="L79" t="str">
-        <v>Closure - D.O.D</v>
+        <v>&gt;&gt;&gt;hands on me&lt;&lt;&lt; - Becky Hill</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="str">
-        <v>HOTS 4 U</v>
+        <v>Closure</v>
       </c>
       <c r="B80" t="str">
         <v/>
       </c>
       <c r="C80" t="str">
-        <v>https://music.apple.com/us/song/hots-4-u/1891478541</v>
+        <v>https://music.apple.com/us/song/closure/1892418294</v>
       </c>
       <c r="D80" t="str">
         <v>2026-05-05</v>
@@ -3415,36 +3415,36 @@
         <v/>
       </c>
       <c r="F80" t="str">
-        <v>HOTS 4 U - Single</v>
+        <v>Closure - Single</v>
       </c>
       <c r="G80" t="str">
-        <v>3:34</v>
+        <v>2:27</v>
       </c>
       <c r="H80" t="str">
-        <v>Chris Lorenzo</v>
+        <v>D.O.D</v>
       </c>
       <c r="I80" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J80" t="str">
-        <v>https://music.apple.com/us/artist/chris-lorenzo/621431022</v>
+        <v>https://music.apple.com/us/artist/d-o-d/444171843</v>
       </c>
       <c r="K80" t="str">
-        <v>https://music.apple.com/us/album/hots-4-u/1891478539</v>
+        <v>https://music.apple.com/us/album/closure/1892418283</v>
       </c>
       <c r="L80" t="str">
-        <v>HOTS 4 U - Chris Lorenzo</v>
+        <v>Closure - D.O.D</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="str">
-        <v>CULE POCO (sirena_besarico_costeña)</v>
+        <v>HOTS 4 U</v>
       </c>
       <c r="B81" t="str">
         <v/>
       </c>
       <c r="C81" t="str">
-        <v>https://music.apple.com/us/song/cule-poco-sirena-besarico-coste%C3%B1a/1893480200</v>
+        <v>https://music.apple.com/us/song/hots-4-u/1891478541</v>
       </c>
       <c r="D81" t="str">
         <v>2026-05-05</v>
@@ -3453,36 +3453,36 @@
         <v/>
       </c>
       <c r="F81" t="str">
-        <v>CULE POCO (sirena_besarico_costeña) - Single</v>
+        <v>HOTS 4 U - Single</v>
       </c>
       <c r="G81" t="str">
-        <v>2:20</v>
+        <v>3:34</v>
       </c>
       <c r="H81" t="str">
-        <v>ARIA VEGA</v>
+        <v>Chris Lorenzo</v>
       </c>
       <c r="I81" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J81" t="str">
-        <v>https://music.apple.com/us/artist/aria-vega/1449328559</v>
+        <v>https://music.apple.com/us/artist/chris-lorenzo/621431022</v>
       </c>
       <c r="K81" t="str">
-        <v>https://music.apple.com/us/album/cule-poco-sirena-besarico-coste%C3%B1a/1893480124</v>
+        <v>https://music.apple.com/us/album/hots-4-u/1891478539</v>
       </c>
       <c r="L81" t="str">
-        <v>CULE POCO (sirena_besarico_costeña) - ARIA VEGA</v>
+        <v>HOTS 4 U - Chris Lorenzo</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="str">
-        <v>The Coin Toss</v>
+        <v>CULE POCO (sirena_besarico_costeña)</v>
       </c>
       <c r="B82" t="str">
         <v/>
       </c>
       <c r="C82" t="str">
-        <v>https://music.apple.com/us/song/the-coin-toss/1894872115</v>
+        <v>https://music.apple.com/us/song/cule-poco-sirena-besarico-coste%C3%B1a/1893480200</v>
       </c>
       <c r="D82" t="str">
         <v>2026-05-05</v>
@@ -3491,36 +3491,36 @@
         <v/>
       </c>
       <c r="F82" t="str">
-        <v>Roofless Records For Drop Tops: Disc 2</v>
+        <v>CULE POCO (sirena_besarico_costeña) - Single</v>
       </c>
       <c r="G82" t="str">
-        <v>2:46</v>
+        <v>2:20</v>
       </c>
       <c r="H82" t="str">
-        <v>Curren$y</v>
+        <v>ARIA VEGA</v>
       </c>
       <c r="I82" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J82" t="str">
-        <v>https://music.apple.com/us/artist/curren%24y/5914039</v>
+        <v>https://music.apple.com/us/artist/aria-vega/1449328559</v>
       </c>
       <c r="K82" t="str">
-        <v>https://music.apple.com/us/album/the-coin-toss/1894872108</v>
+        <v>https://music.apple.com/us/album/cule-poco-sirena-besarico-coste%C3%B1a/1893480124</v>
       </c>
       <c r="L82" t="str">
-        <v>The Coin Toss - Curren$y</v>
+        <v>CULE POCO (sirena_besarico_costeña) - ARIA VEGA</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="str">
-        <v>Bottles &amp; Lights</v>
+        <v>The Coin Toss</v>
       </c>
       <c r="B83" t="str">
         <v/>
       </c>
       <c r="C83" t="str">
-        <v>https://music.apple.com/us/song/bottles-lights/6763041153</v>
+        <v>https://music.apple.com/us/song/the-coin-toss/1894872115</v>
       </c>
       <c r="D83" t="str">
         <v>2026-05-05</v>
@@ -3529,36 +3529,36 @@
         <v/>
       </c>
       <c r="F83" t="str">
-        <v>Bottles &amp; Lights - Single</v>
+        <v>Roofless Records For Drop Tops: Disc 2</v>
       </c>
       <c r="G83" t="str">
-        <v>3:25</v>
+        <v>2:46</v>
       </c>
       <c r="H83" t="str">
-        <v>Chxrry</v>
+        <v>Curren$y</v>
       </c>
       <c r="I83" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J83" t="str">
-        <v>https://music.apple.com/us/artist/chxrry/1520135642</v>
+        <v>https://music.apple.com/us/artist/curren%24y/5914039</v>
       </c>
       <c r="K83" t="str">
-        <v>https://music.apple.com/us/album/bottles-lights/1895133498</v>
+        <v>https://music.apple.com/us/album/the-coin-toss/1894872108</v>
       </c>
       <c r="L83" t="str">
-        <v>Bottles &amp; Lights - Chxrry</v>
+        <v>The Coin Toss - Curren$y</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="str">
-        <v>Perfect For Me</v>
+        <v>Bottles &amp; Lights</v>
       </c>
       <c r="B84" t="str">
         <v/>
       </c>
       <c r="C84" t="str">
-        <v>https://music.apple.com/us/song/perfect-for-me/6762879981</v>
+        <v>https://music.apple.com/us/song/bottles-lights/6763041153</v>
       </c>
       <c r="D84" t="str">
         <v>2026-05-05</v>
@@ -3567,36 +3567,36 @@
         <v/>
       </c>
       <c r="F84" t="str">
-        <v>Perfect For Me - Single</v>
+        <v>Bottles &amp; Lights - Single</v>
       </c>
       <c r="G84" t="str">
-        <v>3:02</v>
+        <v>3:25</v>
       </c>
       <c r="H84" t="str">
-        <v>Jamal Roberts</v>
+        <v>Chxrry</v>
       </c>
       <c r="I84" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J84" t="str">
-        <v>https://music.apple.com/us/artist/jamal-roberts/920647552</v>
+        <v>https://music.apple.com/us/artist/chxrry/1520135642</v>
       </c>
       <c r="K84" t="str">
-        <v>https://music.apple.com/us/album/perfect-for-me/1895056299</v>
+        <v>https://music.apple.com/us/album/bottles-lights/1895133498</v>
       </c>
       <c r="L84" t="str">
-        <v>Perfect For Me - Jamal Roberts</v>
+        <v>Bottles &amp; Lights - Chxrry</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="str">
-        <v>So…</v>
+        <v>Perfect For Me</v>
       </c>
       <c r="B85" t="str">
         <v/>
       </c>
       <c r="C85" t="str">
-        <v>https://music.apple.com/us/song/so/1893162424</v>
+        <v>https://music.apple.com/us/song/perfect-for-me/6762879981</v>
       </c>
       <c r="D85" t="str">
         <v>2026-05-05</v>
@@ -3605,36 +3605,36 @@
         <v/>
       </c>
       <c r="F85" t="str">
-        <v>So… - Single</v>
+        <v>Perfect For Me - Single</v>
       </c>
       <c r="G85" t="str">
-        <v>3:16</v>
+        <v>3:02</v>
       </c>
       <c r="H85" t="str">
-        <v>Ama</v>
+        <v>Jamal Roberts</v>
       </c>
       <c r="I85" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J85" t="str">
-        <v>https://music.apple.com/us/artist/ama/1801560081</v>
+        <v>https://music.apple.com/us/artist/jamal-roberts/920647552</v>
       </c>
       <c r="K85" t="str">
-        <v>https://music.apple.com/us/album/so/1893162419</v>
+        <v>https://music.apple.com/us/album/perfect-for-me/1895056299</v>
       </c>
       <c r="L85" t="str">
-        <v>So… - Ama</v>
+        <v>Perfect For Me - Jamal Roberts</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="str">
-        <v>PASE Y PASE</v>
+        <v>So…</v>
       </c>
       <c r="B86" t="str">
         <v/>
       </c>
       <c r="C86" t="str">
-        <v>https://music.apple.com/us/song/pase-y-pase/1894076490</v>
+        <v>https://music.apple.com/us/song/so/1893162424</v>
       </c>
       <c r="D86" t="str">
         <v>2026-05-05</v>
@@ -3643,36 +3643,36 @@
         <v/>
       </c>
       <c r="F86" t="str">
-        <v>PASE Y PASE - Single</v>
+        <v>So… - Single</v>
       </c>
       <c r="G86" t="str">
-        <v>3:01</v>
+        <v>3:16</v>
       </c>
       <c r="H86" t="str">
-        <v>Tito Double P</v>
+        <v>Ama</v>
       </c>
       <c r="I86" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J86" t="str">
-        <v>https://music.apple.com/us/artist/tito-double-p/1690905306</v>
+        <v>https://music.apple.com/us/artist/ama/1801560081</v>
       </c>
       <c r="K86" t="str">
-        <v>https://music.apple.com/us/album/pase-y-pase/1894076487</v>
+        <v>https://music.apple.com/us/album/so/1893162419</v>
       </c>
       <c r="L86" t="str">
-        <v>PASE Y PASE - Tito Double P</v>
+        <v>So… - Ama</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="str">
-        <v>Agoué-Dambala (Yanvalou) 1</v>
+        <v>PASE Y PASE</v>
       </c>
       <c r="B87" t="str">
         <v/>
       </c>
       <c r="C87" t="str">
-        <v>https://music.apple.com/us/song/agou%C3%A9-dambala-yanvalou-1/1888242486</v>
+        <v>https://music.apple.com/us/song/pase-y-pase/1894076490</v>
       </c>
       <c r="D87" t="str">
         <v>2026-05-05</v>
@@ -3681,36 +3681,36 @@
         <v/>
       </c>
       <c r="F87" t="str">
-        <v>Soul Jazz Records Presents HAITIAN VODOU</v>
+        <v>PASE Y PASE - Single</v>
       </c>
       <c r="G87" t="str">
-        <v>4:13</v>
+        <v>3:01</v>
       </c>
       <c r="H87" t="str">
-        <v>Societe Absolument Guinin</v>
+        <v>Tito Double P</v>
       </c>
       <c r="I87" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J87" t="str">
-        <v>https://music.apple.com/us/artist/societe-absolument-guinin/1083463027</v>
+        <v>https://music.apple.com/us/artist/tito-double-p/1690905306</v>
       </c>
       <c r="K87" t="str">
-        <v>https://music.apple.com/us/album/agou%C3%A9-dambala-yanvalou-1/1888242483</v>
+        <v>https://music.apple.com/us/album/pase-y-pase/1894076487</v>
       </c>
       <c r="L87" t="str">
-        <v>Agoué-Dambala (Yanvalou) 1 - Societe Absolument Guinin</v>
+        <v>PASE Y PASE - Tito Double P</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="str">
-        <v>Aljahalat</v>
+        <v>Agoué-Dambala (Yanvalou) 1</v>
       </c>
       <c r="B88" t="str">
         <v/>
       </c>
       <c r="C88" t="str">
-        <v>https://music.apple.com/us/song/aljahalat/1889267983</v>
+        <v>https://music.apple.com/us/song/agou%C3%A9-dambala-yanvalou-1/1888242486</v>
       </c>
       <c r="D88" t="str">
         <v>2026-05-05</v>
@@ -3719,36 +3719,36 @@
         <v/>
       </c>
       <c r="F88" t="str">
-        <v>Aljahalat - Single</v>
+        <v>Soul Jazz Records Presents HAITIAN VODOU</v>
       </c>
       <c r="G88" t="str">
-        <v>6:12</v>
+        <v>4:13</v>
       </c>
       <c r="H88" t="str">
-        <v>Ahmed Ag Kaedy</v>
+        <v>Societe Absolument Guinin</v>
       </c>
       <c r="I88" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J88" t="str">
-        <v>https://music.apple.com/us/artist/ahmed-ag-kaedy/1445296267</v>
+        <v>https://music.apple.com/us/artist/societe-absolument-guinin/1083463027</v>
       </c>
       <c r="K88" t="str">
-        <v>https://music.apple.com/us/album/aljahalat/1889267980</v>
+        <v>https://music.apple.com/us/album/agou%C3%A9-dambala-yanvalou-1/1888242483</v>
       </c>
       <c r="L88" t="str">
-        <v>Aljahalat - Ahmed Ag Kaedy</v>
+        <v>Agoué-Dambala (Yanvalou) 1 - Societe Absolument Guinin</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="str">
-        <v>Puleza</v>
+        <v>Aljahalat</v>
       </c>
       <c r="B89" t="str">
         <v/>
       </c>
       <c r="C89" t="str">
-        <v>https://music.apple.com/us/song/puleza/1893765840</v>
+        <v>https://music.apple.com/us/song/aljahalat/1889267983</v>
       </c>
       <c r="D89" t="str">
         <v>2026-05-05</v>
@@ -3757,36 +3757,36 @@
         <v/>
       </c>
       <c r="F89" t="str">
-        <v>People of the Moon</v>
+        <v>Aljahalat - Single</v>
       </c>
       <c r="G89" t="str">
-        <v>3:47</v>
+        <v>6:12</v>
       </c>
       <c r="H89" t="str">
-        <v>Nu Genea</v>
+        <v>Ahmed Ag Kaedy</v>
       </c>
       <c r="I89" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J89" t="str">
-        <v>https://music.apple.com/us/artist/nu-genea/997053217</v>
+        <v>https://music.apple.com/us/artist/ahmed-ag-kaedy/1445296267</v>
       </c>
       <c r="K89" t="str">
-        <v>https://music.apple.com/us/album/puleza/1893765826</v>
+        <v>https://music.apple.com/us/album/aljahalat/1889267980</v>
       </c>
       <c r="L89" t="str">
-        <v>Puleza - Nu Genea</v>
+        <v>Aljahalat - Ahmed Ag Kaedy</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="str">
-        <v>Bastards</v>
+        <v>Puleza</v>
       </c>
       <c r="B90" t="str">
         <v/>
       </c>
       <c r="C90" t="str">
-        <v>https://music.apple.com/us/song/bastards/6762403102</v>
+        <v>https://music.apple.com/us/song/puleza/1893765840</v>
       </c>
       <c r="D90" t="str">
         <v>2026-05-05</v>
@@ -3795,36 +3795,36 @@
         <v/>
       </c>
       <c r="F90" t="str">
-        <v>Bunny - EP</v>
+        <v>People of the Moon</v>
       </c>
       <c r="G90" t="str">
-        <v>2:56</v>
+        <v>3:47</v>
       </c>
       <c r="H90" t="str">
-        <v>People I’ve Met</v>
+        <v>Nu Genea</v>
       </c>
       <c r="I90" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J90" t="str">
-        <v>https://music.apple.com/us/artist/people-ive-met/1853169947</v>
+        <v>https://music.apple.com/us/artist/nu-genea/997053217</v>
       </c>
       <c r="K90" t="str">
-        <v>https://music.apple.com/us/album/bastards/1894044276</v>
+        <v>https://music.apple.com/us/album/puleza/1893765826</v>
       </c>
       <c r="L90" t="str">
-        <v>Bastards - People I’ve Met</v>
+        <v>Puleza - Nu Genea</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="str">
-        <v>Crutch</v>
+        <v>Bastards</v>
       </c>
       <c r="B91" t="str">
         <v/>
       </c>
       <c r="C91" t="str">
-        <v>https://music.apple.com/us/song/crutch/6763345020</v>
+        <v>https://music.apple.com/us/song/bastards/6762403102</v>
       </c>
       <c r="D91" t="str">
         <v>2026-05-05</v>
@@ -3833,36 +3833,36 @@
         <v/>
       </c>
       <c r="F91" t="str">
-        <v>Crutch - Single</v>
+        <v>Bunny - EP</v>
       </c>
       <c r="G91" t="str">
-        <v>3:31</v>
+        <v>2:56</v>
       </c>
       <c r="H91" t="str">
-        <v>Love Spells</v>
+        <v>People I’ve Met</v>
       </c>
       <c r="I91" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J91" t="str">
-        <v>https://music.apple.com/us/artist/love-spells/1597025563</v>
+        <v>https://music.apple.com/us/artist/people-ive-met/1853169947</v>
       </c>
       <c r="K91" t="str">
-        <v>https://music.apple.com/us/album/crutch/1895274406</v>
+        <v>https://music.apple.com/us/album/bastards/1894044276</v>
       </c>
       <c r="L91" t="str">
-        <v>Crutch - Love Spells</v>
+        <v>Bastards - People I’ve Met</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="str">
-        <v>Just A Man</v>
+        <v>Crutch</v>
       </c>
       <c r="B92" t="str">
         <v/>
       </c>
       <c r="C92" t="str">
-        <v>https://music.apple.com/us/song/just-a-man/1893736206</v>
+        <v>https://music.apple.com/us/song/crutch/6763345020</v>
       </c>
       <c r="D92" t="str">
         <v>2026-05-05</v>
@@ -3871,36 +3871,36 @@
         <v/>
       </c>
       <c r="F92" t="str">
-        <v>Just A Man - Single</v>
+        <v>Crutch - Single</v>
       </c>
       <c r="G92" t="str">
-        <v>2:38</v>
+        <v>3:31</v>
       </c>
       <c r="H92" t="str">
-        <v>MOIO</v>
+        <v>Love Spells</v>
       </c>
       <c r="I92" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J92" t="str">
-        <v>https://music.apple.com/us/artist/moio/1664183608</v>
+        <v>https://music.apple.com/us/artist/love-spells/1597025563</v>
       </c>
       <c r="K92" t="str">
-        <v>https://music.apple.com/us/album/just-a-man/1893736201</v>
+        <v>https://music.apple.com/us/album/crutch/1895274406</v>
       </c>
       <c r="L92" t="str">
-        <v>Just A Man - MOIO</v>
+        <v>Crutch - Love Spells</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="str">
-        <v>Take Care Of You</v>
+        <v>Just A Man</v>
       </c>
       <c r="B93" t="str">
         <v/>
       </c>
       <c r="C93" t="str">
-        <v>https://music.apple.com/us/song/take-care-of-you/6762283983</v>
+        <v>https://music.apple.com/us/song/just-a-man/1893736206</v>
       </c>
       <c r="D93" t="str">
         <v>2026-05-05</v>
@@ -3909,36 +3909,36 @@
         <v/>
       </c>
       <c r="F93" t="str">
-        <v>Take Care Of You - Single</v>
+        <v>Just A Man - Single</v>
       </c>
       <c r="G93" t="str">
-        <v>3:51</v>
+        <v>2:38</v>
       </c>
       <c r="H93" t="str">
-        <v>Alina Baraz</v>
+        <v>MOIO</v>
       </c>
       <c r="I93" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J93" t="str">
-        <v>https://music.apple.com/us/artist/alina-baraz/757852571</v>
+        <v>https://music.apple.com/us/artist/moio/1664183608</v>
       </c>
       <c r="K93" t="str">
-        <v>https://music.apple.com/us/album/take-care-of-you/1893646113</v>
+        <v>https://music.apple.com/us/album/just-a-man/1893736201</v>
       </c>
       <c r="L93" t="str">
-        <v>Take Care Of You - Alina Baraz</v>
+        <v>Just A Man - MOIO</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="str">
-        <v>Love You More</v>
+        <v>Take Care Of You</v>
       </c>
       <c r="B94" t="str">
         <v/>
       </c>
       <c r="C94" t="str">
-        <v>https://music.apple.com/us/song/love-you-more/1889686330</v>
+        <v>https://music.apple.com/us/song/take-care-of-you/6762283983</v>
       </c>
       <c r="D94" t="str">
         <v>2026-05-05</v>
@@ -3947,36 +3947,36 @@
         <v/>
       </c>
       <c r="F94" t="str">
-        <v>Love You More - Single</v>
+        <v>Take Care Of You - Single</v>
       </c>
       <c r="G94" t="str">
-        <v>2:48</v>
+        <v>3:51</v>
       </c>
       <c r="H94" t="str">
-        <v>Rudimental</v>
+        <v>Alina Baraz</v>
       </c>
       <c r="I94" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J94" t="str">
-        <v>https://music.apple.com/us/artist/rudimental/474022504</v>
+        <v>https://music.apple.com/us/artist/alina-baraz/757852571</v>
       </c>
       <c r="K94" t="str">
-        <v>https://music.apple.com/us/album/love-you-more/1889686315</v>
+        <v>https://music.apple.com/us/album/take-care-of-you/1893646113</v>
       </c>
       <c r="L94" t="str">
-        <v>Love You More - Rudimental</v>
+        <v>Take Care Of You - Alina Baraz</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="str">
-        <v>Construct</v>
+        <v>Love You More</v>
       </c>
       <c r="B95" t="str">
         <v/>
       </c>
       <c r="C95" t="str">
-        <v>https://music.apple.com/us/song/construct/1869323374</v>
+        <v>https://music.apple.com/us/song/love-you-more/1889686330</v>
       </c>
       <c r="D95" t="str">
         <v>2026-05-05</v>
@@ -3985,36 +3985,36 @@
         <v/>
       </c>
       <c r="F95" t="str">
-        <v>ONE</v>
+        <v>Love You More - Single</v>
       </c>
       <c r="G95" t="str">
-        <v>3:57</v>
+        <v>2:48</v>
       </c>
       <c r="H95" t="str">
-        <v>Sevendust</v>
+        <v>Rudimental</v>
       </c>
       <c r="I95" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J95" t="str">
-        <v>https://music.apple.com/us/artist/sevendust/13125174</v>
+        <v>https://music.apple.com/us/artist/rudimental/474022504</v>
       </c>
       <c r="K95" t="str">
-        <v>https://music.apple.com/us/album/construct/1869323199</v>
+        <v>https://music.apple.com/us/album/love-you-more/1889686315</v>
       </c>
       <c r="L95" t="str">
-        <v>Construct - Sevendust</v>
+        <v>Love You More - Rudimental</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="str">
-        <v>As Above So Below</v>
+        <v>Construct</v>
       </c>
       <c r="B96" t="str">
         <v/>
       </c>
       <c r="C96" t="str">
-        <v>https://music.apple.com/us/song/as-above-so-below/1872651422</v>
+        <v>https://music.apple.com/us/song/construct/1869323374</v>
       </c>
       <c r="D96" t="str">
         <v>2026-05-05</v>
@@ -4023,36 +4023,36 @@
         <v/>
       </c>
       <c r="F96" t="str">
-        <v>Into Oblivion</v>
+        <v>ONE</v>
       </c>
       <c r="G96" t="str">
-        <v>4:54</v>
+        <v>3:57</v>
       </c>
       <c r="H96" t="str">
-        <v>Venom</v>
+        <v>Sevendust</v>
       </c>
       <c r="I96" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J96" t="str">
-        <v>https://music.apple.com/us/artist/venom/3222127</v>
+        <v>https://music.apple.com/us/artist/sevendust/13125174</v>
       </c>
       <c r="K96" t="str">
-        <v>https://music.apple.com/us/album/as-above-so-below/1872651243</v>
+        <v>https://music.apple.com/us/album/construct/1869323199</v>
       </c>
       <c r="L96" t="str">
-        <v>As Above So Below - Venom</v>
+        <v>Construct - Sevendust</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="str">
-        <v>Revenant</v>
+        <v>As Above So Below</v>
       </c>
       <c r="B97" t="str">
         <v/>
       </c>
       <c r="C97" t="str">
-        <v>https://music.apple.com/us/song/revenant/6763148056</v>
+        <v>https://music.apple.com/us/song/as-above-so-below/1872651422</v>
       </c>
       <c r="D97" t="str">
         <v>2026-05-05</v>
@@ -4061,36 +4061,36 @@
         <v/>
       </c>
       <c r="F97" t="str">
-        <v>A Stranger To You</v>
+        <v>Into Oblivion</v>
       </c>
       <c r="G97" t="str">
-        <v>3:31</v>
+        <v>4:54</v>
       </c>
       <c r="H97" t="str">
-        <v>Loathe</v>
+        <v>Venom</v>
       </c>
       <c r="I97" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J97" t="str">
-        <v>https://music.apple.com/us/artist/loathe/377883434</v>
+        <v>https://music.apple.com/us/artist/venom/3222127</v>
       </c>
       <c r="K97" t="str">
-        <v>https://music.apple.com/us/album/revenant/1895184628</v>
+        <v>https://music.apple.com/us/album/as-above-so-below/1872651243</v>
       </c>
       <c r="L97" t="str">
-        <v>Revenant - Loathe</v>
+        <v>As Above So Below - Venom</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="str">
-        <v>Black Box (feat. Joe Duplantier &amp; The Mystery Of The Bulgarian Voices)</v>
+        <v>Revenant</v>
       </c>
       <c r="B98" t="str">
         <v/>
       </c>
       <c r="C98" t="str">
-        <v>https://music.apple.com/us/song/black-box-feat-joe-duplantier-the-mystery-of/6762312582</v>
+        <v>https://music.apple.com/us/song/revenant/6763148056</v>
       </c>
       <c r="D98" t="str">
         <v>2026-05-05</v>
@@ -4099,36 +4099,36 @@
         <v/>
       </c>
       <c r="F98" t="str">
-        <v>Black Box (feat. Joe Duplantier &amp; The Mystery Of The Bulgarian Voices) - Single</v>
+        <v>A Stranger To You</v>
       </c>
       <c r="G98" t="str">
-        <v>4:56</v>
+        <v>3:31</v>
       </c>
       <c r="H98" t="str">
-        <v>Bear McCreary</v>
+        <v>Loathe</v>
       </c>
       <c r="I98" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J98" t="str">
-        <v>https://music.apple.com/us/artist/bear-mccreary/204012062</v>
+        <v>https://music.apple.com/us/artist/loathe/377883434</v>
       </c>
       <c r="K98" t="str">
-        <v>https://music.apple.com/us/album/black-box-feat-joe-duplantier-the-mystery-of/1893773367</v>
+        <v>https://music.apple.com/us/album/revenant/1895184628</v>
       </c>
       <c r="L98" t="str">
-        <v>Black Box (feat. Joe Duplantier &amp; The Mystery Of The Bulgarian Voices) - Bear McCreary</v>
+        <v>Revenant - Loathe</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="str">
-        <v>Power 4</v>
+        <v>Black Box (feat. Joe Duplantier &amp; The Mystery Of The Bulgarian Voices)</v>
       </c>
       <c r="B99" t="str">
         <v/>
       </c>
       <c r="C99" t="str">
-        <v>https://music.apple.com/us/song/power-4/6763647813</v>
+        <v>https://music.apple.com/us/song/black-box-feat-joe-duplantier-the-mystery-of/6762312582</v>
       </c>
       <c r="D99" t="str">
         <v>2026-05-05</v>
@@ -4137,36 +4137,36 @@
         <v/>
       </c>
       <c r="F99" t="str">
-        <v>Power 4 - Single</v>
+        <v>Black Box (feat. Joe Duplantier &amp; The Mystery Of The Bulgarian Voices) - Single</v>
       </c>
       <c r="G99" t="str">
-        <v>1:40</v>
+        <v>4:56</v>
       </c>
       <c r="H99" t="str">
-        <v>slayr</v>
+        <v>Bear McCreary</v>
       </c>
       <c r="I99" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J99" t="str">
-        <v>https://music.apple.com/us/artist/slayr/1676805496</v>
+        <v>https://music.apple.com/us/artist/bear-mccreary/204012062</v>
       </c>
       <c r="K99" t="str">
-        <v>https://music.apple.com/us/album/power-4/1895416494</v>
+        <v>https://music.apple.com/us/album/black-box-feat-joe-duplantier-the-mystery-of/1893773367</v>
       </c>
       <c r="L99" t="str">
-        <v>Power 4 - slayr</v>
+        <v>Black Box (feat. Joe Duplantier &amp; The Mystery Of The Bulgarian Voices) - Bear McCreary</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="str">
-        <v>Too Easy</v>
+        <v>Power 4</v>
       </c>
       <c r="B100" t="str">
         <v/>
       </c>
       <c r="C100" t="str">
-        <v>https://music.apple.com/us/song/too-easy/1893814702</v>
+        <v>https://music.apple.com/us/song/power-4/6763647813</v>
       </c>
       <c r="D100" t="str">
         <v>2026-05-05</v>
@@ -4175,36 +4175,36 @@
         <v/>
       </c>
       <c r="F100" t="str">
-        <v>Too Easy - Single</v>
+        <v>Power 4 - Single</v>
       </c>
       <c r="G100" t="str">
-        <v>4:14</v>
+        <v>1:40</v>
       </c>
       <c r="H100" t="str">
-        <v>tig3r lewis</v>
+        <v>slayr</v>
       </c>
       <c r="I100" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J100" t="str">
-        <v>https://music.apple.com/us/artist/tig3r-lewis/1850089834</v>
+        <v>https://music.apple.com/us/artist/slayr/1676805496</v>
       </c>
       <c r="K100" t="str">
-        <v>https://music.apple.com/us/album/too-easy/1893814697</v>
+        <v>https://music.apple.com/us/album/power-4/1895416494</v>
       </c>
       <c r="L100" t="str">
-        <v>Too Easy - tig3r lewis</v>
+        <v>Power 4 - slayr</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="str">
-        <v>If You Want It</v>
+        <v>Too Easy</v>
       </c>
       <c r="B101" t="str">
         <v/>
       </c>
       <c r="C101" t="str">
-        <v>https://music.apple.com/us/song/if-you-want-it/1892503347</v>
+        <v>https://music.apple.com/us/song/too-easy/1893814702</v>
       </c>
       <c r="D101" t="str">
         <v>2026-05-05</v>
@@ -4213,36 +4213,36 @@
         <v/>
       </c>
       <c r="F101" t="str">
-        <v>If You Want It - Single</v>
+        <v>Too Easy - Single</v>
       </c>
       <c r="G101" t="str">
-        <v>3:56</v>
+        <v>4:14</v>
       </c>
       <c r="H101" t="str">
-        <v>ALAC</v>
+        <v>tig3r lewis</v>
       </c>
       <c r="I101" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J101" t="str">
-        <v>https://music.apple.com/us/artist/alac/1885586915</v>
+        <v>https://music.apple.com/us/artist/tig3r-lewis/1850089834</v>
       </c>
       <c r="K101" t="str">
-        <v>https://music.apple.com/us/album/if-you-want-it/1892503333</v>
+        <v>https://music.apple.com/us/album/too-easy/1893814697</v>
       </c>
       <c r="L101" t="str">
-        <v>If You Want It - ALAC</v>
+        <v>Too Easy - tig3r lewis</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="str">
-        <v>Shoplifting</v>
+        <v>If You Want It</v>
       </c>
       <c r="B102" t="str">
         <v/>
       </c>
       <c r="C102" t="str">
-        <v>https://music.apple.com/us/song/shoplifting/1852812659</v>
+        <v>https://music.apple.com/us/song/if-you-want-it/1892503347</v>
       </c>
       <c r="D102" t="str">
         <v>2026-05-05</v>
@@ -4251,68 +4251,106 @@
         <v/>
       </c>
       <c r="F102" t="str">
-        <v>Theft World</v>
+        <v>If You Want It - Single</v>
       </c>
       <c r="G102" t="str">
-        <v>3:02</v>
+        <v>3:56</v>
       </c>
       <c r="H102" t="str">
-        <v>Lip Critic</v>
+        <v>ALAC</v>
       </c>
       <c r="I102" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J102" t="str">
-        <v>https://music.apple.com/us/artist/lip-critic/1458046064</v>
+        <v>https://music.apple.com/us/artist/alac/1885586915</v>
       </c>
       <c r="K102" t="str">
-        <v>https://music.apple.com/us/album/shoplifting/1852812554</v>
+        <v>https://music.apple.com/us/album/if-you-want-it/1892503333</v>
       </c>
       <c r="L102" t="str">
-        <v>Shoplifting - Lip Critic</v>
+        <v>If You Want It - ALAC</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="str">
+        <v>Shoplifting</v>
+      </c>
+      <c r="B103" t="str">
+        <v/>
+      </c>
+      <c r="C103" t="str">
+        <v>https://music.apple.com/us/song/shoplifting/1852812659</v>
+      </c>
+      <c r="D103" t="str">
+        <v>2026-05-05</v>
+      </c>
+      <c r="E103" t="str">
+        <v/>
+      </c>
+      <c r="F103" t="str">
+        <v>Theft World</v>
+      </c>
+      <c r="G103" t="str">
+        <v>3:02</v>
+      </c>
+      <c r="H103" t="str">
+        <v>Lip Critic</v>
+      </c>
+      <c r="I103" t="str">
+        <v>מוזיקה לועזית חדשה</v>
+      </c>
+      <c r="J103" t="str">
+        <v>https://music.apple.com/us/artist/lip-critic/1458046064</v>
+      </c>
+      <c r="K103" t="str">
+        <v>https://music.apple.com/us/album/shoplifting/1852812554</v>
+      </c>
+      <c r="L103" t="str">
+        <v>Shoplifting - Lip Critic</v>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="str">
         <v>Endlessly (feat. BEA1991)</v>
       </c>
-      <c r="B103" t="str">
-        <v/>
-      </c>
-      <c r="C103" t="str">
+      <c r="B104" t="str">
+        <v/>
+      </c>
+      <c r="C104" t="str">
         <v>https://music.apple.com/us/song/endlessly-feat-bea1991/1876022833</v>
       </c>
-      <c r="D103" t="str">
-        <v>2026-05-05</v>
-      </c>
-      <c r="E103" t="str">
-        <v/>
-      </c>
-      <c r="F103" t="str">
+      <c r="D104" t="str">
+        <v>2026-05-05</v>
+      </c>
+      <c r="E104" t="str">
+        <v/>
+      </c>
+      <c r="F104" t="str">
         <v>Fold</v>
       </c>
-      <c r="G103" t="str">
+      <c r="G104" t="str">
         <v>5:57</v>
       </c>
-      <c r="H103" t="str">
+      <c r="H104" t="str">
         <v>Jump Source</v>
       </c>
-      <c r="I103" t="str">
-        <v>מוזיקה לועזית חדשה</v>
-      </c>
-      <c r="J103" t="str">
+      <c r="I104" t="str">
+        <v>מוזיקה לועזית חדשה</v>
+      </c>
+      <c r="J104" t="str">
         <v>https://music.apple.com/us/artist/jump-source/1169060818</v>
       </c>
-      <c r="K103" t="str">
+      <c r="K104" t="str">
         <v>https://music.apple.com/us/album/endlessly-feat-bea1991/1876022817</v>
       </c>
-      <c r="L103" t="str">
+      <c r="L104" t="str">
         <v>Endlessly (feat. BEA1991) - Jump Source</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:L103"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:L104"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/data/tags/מוזיקה לועזית חדשה/sites/apple-music-playlist/2026-05-week01/titles.xlsx
+++ b/data/tags/מוזיקה לועזית חדשה/sites/apple-music-playlist/2026-05-week01/titles.xlsx
@@ -445,7 +445,7 @@
         <v>https://music.apple.com/us/song/linknb/1888561848</v>
       </c>
       <c r="D2" t="str">
-        <v>2026-05-05</v>
+        <v>2026-05-06</v>
       </c>
       <c r="E2" t="str">
         <v/>
@@ -483,7 +483,7 @@
         <v>https://music.apple.com/us/song/eurosummer-girls-trip/1894058279</v>
       </c>
       <c r="D3" t="str">
-        <v>2026-05-05</v>
+        <v>2026-05-06</v>
       </c>
       <c r="E3" t="str">
         <v/>
@@ -521,7 +521,7 @@
         <v>https://music.apple.com/us/song/shape-of-a-woman/6764429252</v>
       </c>
       <c r="D4" t="str">
-        <v>2026-05-05</v>
+        <v>2026-05-06</v>
       </c>
       <c r="E4" t="str">
         <v/>
@@ -559,7 +559,7 @@
         <v>https://music.apple.com/us/song/bring-your-love/1892545227</v>
       </c>
       <c r="D5" t="str">
-        <v>2026-05-05</v>
+        <v>2026-05-06</v>
       </c>
       <c r="E5" t="str">
         <v/>
@@ -597,7 +597,7 @@
         <v>https://music.apple.com/us/song/horses-and-divorces/1883177267</v>
       </c>
       <c r="D6" t="str">
-        <v>2026-05-05</v>
+        <v>2026-05-06</v>
       </c>
       <c r="E6" t="str">
         <v/>
@@ -635,7 +635,7 @@
         <v>https://music.apple.com/us/song/staying-still/6762758806</v>
       </c>
       <c r="D7" t="str">
-        <v>2026-05-05</v>
+        <v>2026-05-06</v>
       </c>
       <c r="E7" t="str">
         <v/>
@@ -673,7 +673,7 @@
         <v>https://music.apple.com/us/song/fine-place-to-die/6764686279</v>
       </c>
       <c r="D8" t="str">
-        <v>2026-05-05</v>
+        <v>2026-05-06</v>
       </c>
       <c r="E8" t="str">
         <v/>
@@ -711,7 +711,7 @@
         <v>https://music.apple.com/us/song/mutt/6763145178</v>
       </c>
       <c r="D9" t="str">
-        <v>2026-05-05</v>
+        <v>2026-05-06</v>
       </c>
       <c r="E9" t="str">
         <v/>
@@ -749,7 +749,7 @@
         <v>https://music.apple.com/us/song/fire-away-feat-slayyyter/1892422570</v>
       </c>
       <c r="D10" t="str">
-        <v>2026-05-05</v>
+        <v>2026-05-06</v>
       </c>
       <c r="E10" t="str">
         <v/>
@@ -787,7 +787,7 @@
         <v>https://music.apple.com/us/song/robotic-love/6763638857</v>
       </c>
       <c r="D11" t="str">
-        <v>2026-05-05</v>
+        <v>2026-05-06</v>
       </c>
       <c r="E11" t="str">
         <v/>
@@ -825,7 +825,7 @@
         <v>https://music.apple.com/us/song/lioness/1878649397</v>
       </c>
       <c r="D12" t="str">
-        <v>2026-05-05</v>
+        <v>2026-05-06</v>
       </c>
       <c r="E12" t="str">
         <v/>
@@ -863,7 +863,7 @@
         <v>https://music.apple.com/us/song/its-ok/6763134121</v>
       </c>
       <c r="D13" t="str">
-        <v>2026-05-05</v>
+        <v>2026-05-06</v>
       </c>
       <c r="E13" t="str">
         <v/>
@@ -901,7 +901,7 @@
         <v>https://music.apple.com/us/song/promise/6763162287</v>
       </c>
       <c r="D14" t="str">
-        <v>2026-05-05</v>
+        <v>2026-05-06</v>
       </c>
       <c r="E14" t="str">
         <v/>
@@ -939,7 +939,7 @@
         <v>https://music.apple.com/us/song/cool-buzz/1880470657</v>
       </c>
       <c r="D15" t="str">
-        <v>2026-05-05</v>
+        <v>2026-05-06</v>
       </c>
       <c r="E15" t="str">
         <v/>
@@ -977,7 +977,7 @@
         <v>https://music.apple.com/us/song/material-lover/6764429256</v>
       </c>
       <c r="D16" t="str">
-        <v>2026-05-05</v>
+        <v>2026-05-06</v>
       </c>
       <c r="E16" t="str">
         <v/>
@@ -1015,7 +1015,7 @@
         <v>https://music.apple.com/us/song/fallin-feat-leon-thomas/6764419265</v>
       </c>
       <c r="D17" t="str">
-        <v>2026-05-05</v>
+        <v>2026-05-06</v>
       </c>
       <c r="E17" t="str">
         <v/>
@@ -1053,7 +1053,7 @@
         <v>https://music.apple.com/us/song/echo/6763379683</v>
       </c>
       <c r="D18" t="str">
-        <v>2026-05-05</v>
+        <v>2026-05-06</v>
       </c>
       <c r="E18" t="str">
         <v/>
@@ -1091,7 +1091,7 @@
         <v>https://music.apple.com/us/song/blackberry-marmalade/1887627837</v>
       </c>
       <c r="D19" t="str">
-        <v>2026-05-05</v>
+        <v>2026-05-06</v>
       </c>
       <c r="E19" t="str">
         <v/>
@@ -1129,7 +1129,7 @@
         <v>https://music.apple.com/us/song/ricky-bobby/6764406571</v>
       </c>
       <c r="D20" t="str">
-        <v>2026-05-05</v>
+        <v>2026-05-06</v>
       </c>
       <c r="E20" t="str">
         <v/>
@@ -1167,7 +1167,7 @@
         <v>https://music.apple.com/us/song/te-entiendo-remix/6763665638</v>
       </c>
       <c r="D21" t="str">
-        <v>2026-05-05</v>
+        <v>2026-05-06</v>
       </c>
       <c r="E21" t="str">
         <v/>
@@ -1205,7 +1205,7 @@
         <v>https://music.apple.com/us/song/dont-worry-baby/1894294411</v>
       </c>
       <c r="D22" t="str">
-        <v>2026-05-05</v>
+        <v>2026-05-06</v>
       </c>
       <c r="E22" t="str">
         <v/>
@@ -1243,7 +1243,7 @@
         <v>https://music.apple.com/us/song/bitch/6763622110</v>
       </c>
       <c r="D23" t="str">
-        <v>2026-05-05</v>
+        <v>2026-05-06</v>
       </c>
       <c r="E23" t="str">
         <v/>
@@ -1281,7 +1281,7 @@
         <v>https://music.apple.com/us/song/just-wanna-cry/6763414703</v>
       </c>
       <c r="D24" t="str">
-        <v>2026-05-05</v>
+        <v>2026-05-06</v>
       </c>
       <c r="E24" t="str">
         <v/>
@@ -1319,7 +1319,7 @@
         <v>https://music.apple.com/us/song/carry-the-weight/6763611647</v>
       </c>
       <c r="D25" t="str">
-        <v>2026-05-05</v>
+        <v>2026-05-06</v>
       </c>
       <c r="E25" t="str">
         <v/>
@@ -1357,7 +1357,7 @@
         <v>https://music.apple.com/us/song/prostitute/1894092341</v>
       </c>
       <c r="D26" t="str">
-        <v>2026-05-05</v>
+        <v>2026-05-06</v>
       </c>
       <c r="E26" t="str">
         <v/>
@@ -1395,7 +1395,7 @@
         <v>https://music.apple.com/us/song/im-not-joking/1872842623</v>
       </c>
       <c r="D27" t="str">
-        <v>2026-05-05</v>
+        <v>2026-05-06</v>
       </c>
       <c r="E27" t="str">
         <v/>
@@ -1433,7 +1433,7 @@
         <v>https://music.apple.com/us/song/ruca/6763671002</v>
       </c>
       <c r="D28" t="str">
-        <v>2026-05-05</v>
+        <v>2026-05-06</v>
       </c>
       <c r="E28" t="str">
         <v/>
@@ -1471,7 +1471,7 @@
         <v>https://music.apple.com/us/song/make-you-fight/1892332386</v>
       </c>
       <c r="D29" t="str">
-        <v>2026-05-05</v>
+        <v>2026-05-06</v>
       </c>
       <c r="E29" t="str">
         <v/>
@@ -1509,7 +1509,7 @@
         <v>https://music.apple.com/us/song/n0rth4evr/6763302230</v>
       </c>
       <c r="D30" t="str">
-        <v>2026-05-05</v>
+        <v>2026-05-06</v>
       </c>
       <c r="E30" t="str">
         <v/>
@@ -1547,7 +1547,7 @@
         <v>https://music.apple.com/us/song/boy-in-red/1892543110</v>
       </c>
       <c r="D31" t="str">
-        <v>2026-05-05</v>
+        <v>2026-05-06</v>
       </c>
       <c r="E31" t="str">
         <v/>
@@ -1585,7 +1585,7 @@
         <v>https://music.apple.com/us/song/ea-ea-ea/6763438376</v>
       </c>
       <c r="D32" t="str">
-        <v>2026-05-05</v>
+        <v>2026-05-06</v>
       </c>
       <c r="E32" t="str">
         <v/>
@@ -1623,7 +1623,7 @@
         <v>https://music.apple.com/us/song/just-a-man/6762944365</v>
       </c>
       <c r="D33" t="str">
-        <v>2026-05-05</v>
+        <v>2026-05-06</v>
       </c>
       <c r="E33" t="str">
         <v/>
@@ -1661,7 +1661,7 @@
         <v>https://music.apple.com/us/song/the-observer/1891982314</v>
       </c>
       <c r="D34" t="str">
-        <v>2026-05-05</v>
+        <v>2026-05-06</v>
       </c>
       <c r="E34" t="str">
         <v/>
@@ -1699,7 +1699,7 @@
         <v>https://music.apple.com/us/song/heroine/6762693177</v>
       </c>
       <c r="D35" t="str">
-        <v>2026-05-05</v>
+        <v>2026-05-06</v>
       </c>
       <c r="E35" t="str">
         <v/>
@@ -1737,7 +1737,7 @@
         <v>https://music.apple.com/us/song/do-me-right/6764667658</v>
       </c>
       <c r="D36" t="str">
-        <v>2026-05-05</v>
+        <v>2026-05-06</v>
       </c>
       <c r="E36" t="str">
         <v/>
@@ -1775,7 +1775,7 @@
         <v>https://music.apple.com/us/song/its-me/1887194026</v>
       </c>
       <c r="D37" t="str">
-        <v>2026-05-05</v>
+        <v>2026-05-06</v>
       </c>
       <c r="E37" t="str">
         <v/>
@@ -1813,7 +1813,7 @@
         <v>https://music.apple.com/us/song/the-precipice/1891830326</v>
       </c>
       <c r="D38" t="str">
-        <v>2026-05-05</v>
+        <v>2026-05-06</v>
       </c>
       <c r="E38" t="str">
         <v/>
@@ -1851,7 +1851,7 @@
         <v>https://music.apple.com/us/song/hello-lonesome/1892466003</v>
       </c>
       <c r="D39" t="str">
-        <v>2026-05-05</v>
+        <v>2026-05-06</v>
       </c>
       <c r="E39" t="str">
         <v/>
@@ -1889,7 +1889,7 @@
         <v>https://music.apple.com/us/song/trippin-opera-edit/6764648776</v>
       </c>
       <c r="D40" t="str">
-        <v>2026-05-05</v>
+        <v>2026-05-06</v>
       </c>
       <c r="E40" t="str">
         <v/>
@@ -1927,7 +1927,7 @@
         <v>https://music.apple.com/us/song/the-mandalorian-and-grogu-boys-noize-remix-from-star/6764131630</v>
       </c>
       <c r="D41" t="str">
-        <v>2026-05-05</v>
+        <v>2026-05-06</v>
       </c>
       <c r="E41" t="str">
         <v/>
@@ -1965,7 +1965,7 @@
         <v>https://music.apple.com/us/song/blow-my-mind-ca7riel-paco-amoroso-version/1894344140</v>
       </c>
       <c r="D42" t="str">
-        <v>2026-05-05</v>
+        <v>2026-05-06</v>
       </c>
       <c r="E42" t="str">
         <v/>
@@ -2003,7 +2003,7 @@
         <v>https://music.apple.com/us/song/bring-that-body/6764009310</v>
       </c>
       <c r="D43" t="str">
-        <v>2026-05-05</v>
+        <v>2026-05-06</v>
       </c>
       <c r="E43" t="str">
         <v/>
@@ -2041,7 +2041,7 @@
         <v>https://music.apple.com/us/song/star/1891845608</v>
       </c>
       <c r="D44" t="str">
-        <v>2026-05-05</v>
+        <v>2026-05-06</v>
       </c>
       <c r="E44" t="str">
         <v/>
@@ -2079,7 +2079,7 @@
         <v>https://music.apple.com/us/song/whats-a-little-rain/1885061171</v>
       </c>
       <c r="D45" t="str">
-        <v>2026-05-05</v>
+        <v>2026-05-06</v>
       </c>
       <c r="E45" t="str">
         <v/>
@@ -2117,7 +2117,7 @@
         <v>https://music.apple.com/us/song/evergreen/1866700315</v>
       </c>
       <c r="D46" t="str">
-        <v>2026-05-05</v>
+        <v>2026-05-06</v>
       </c>
       <c r="E46" t="str">
         <v/>
@@ -2155,7 +2155,7 @@
         <v>https://music.apple.com/us/song/she-does-it-right/1873477957</v>
       </c>
       <c r="D47" t="str">
-        <v>2026-05-05</v>
+        <v>2026-05-06</v>
       </c>
       <c r="E47" t="str">
         <v/>
@@ -2193,7 +2193,7 @@
         <v>https://music.apple.com/us/song/punching-the-flowers/1878362636</v>
       </c>
       <c r="D48" t="str">
-        <v>2026-05-05</v>
+        <v>2026-05-06</v>
       </c>
       <c r="E48" t="str">
         <v/>
@@ -2231,7 +2231,7 @@
         <v>https://music.apple.com/us/song/how-did-you-know/1888553137</v>
       </c>
       <c r="D49" t="str">
-        <v>2026-05-05</v>
+        <v>2026-05-06</v>
       </c>
       <c r="E49" t="str">
         <v/>
@@ -2269,7 +2269,7 @@
         <v>https://music.apple.com/us/song/summer-breeze/6763360727</v>
       </c>
       <c r="D50" t="str">
-        <v>2026-05-05</v>
+        <v>2026-05-06</v>
       </c>
       <c r="E50" t="str">
         <v/>
@@ -2307,7 +2307,7 @@
         <v>https://music.apple.com/us/song/sound-of-a-woman/1859763367</v>
       </c>
       <c r="D51" t="str">
-        <v>2026-05-05</v>
+        <v>2026-05-06</v>
       </c>
       <c r="E51" t="str">
         <v/>
@@ -2345,7 +2345,7 @@
         <v>https://music.apple.com/us/song/my-life/1893157347</v>
       </c>
       <c r="D52" t="str">
-        <v>2026-05-05</v>
+        <v>2026-05-06</v>
       </c>
       <c r="E52" t="str">
         <v/>
@@ -2383,7 +2383,7 @@
         <v>https://music.apple.com/us/song/ribcage/1893155593</v>
       </c>
       <c r="D53" t="str">
-        <v>2026-05-05</v>
+        <v>2026-05-06</v>
       </c>
       <c r="E53" t="str">
         <v/>
@@ -2421,7 +2421,7 @@
         <v>https://music.apple.com/us/song/i-loved-you-then/1878232821</v>
       </c>
       <c r="D54" t="str">
-        <v>2026-05-05</v>
+        <v>2026-05-06</v>
       </c>
       <c r="E54" t="str">
         <v/>
@@ -2459,7 +2459,7 @@
         <v>https://music.apple.com/us/song/ill-let-you-finish/1891844342</v>
       </c>
       <c r="D55" t="str">
-        <v>2026-05-05</v>
+        <v>2026-05-06</v>
       </c>
       <c r="E55" t="str">
         <v/>
@@ -2497,7 +2497,7 @@
         <v>https://music.apple.com/us/song/it-gets-me-through/1884798927</v>
       </c>
       <c r="D56" t="str">
-        <v>2026-05-05</v>
+        <v>2026-05-06</v>
       </c>
       <c r="E56" t="str">
         <v/>
@@ -2535,7 +2535,7 @@
         <v>https://music.apple.com/us/song/the-author/6763327641</v>
       </c>
       <c r="D57" t="str">
-        <v>2026-05-05</v>
+        <v>2026-05-06</v>
       </c>
       <c r="E57" t="str">
         <v/>
@@ -2573,7 +2573,7 @@
         <v>https://music.apple.com/us/song/want-me-back-feat-tors/1889370756</v>
       </c>
       <c r="D58" t="str">
-        <v>2026-05-05</v>
+        <v>2026-05-06</v>
       </c>
       <c r="E58" t="str">
         <v/>
@@ -2611,7 +2611,7 @@
         <v>https://music.apple.com/us/song/ruin/1886537117</v>
       </c>
       <c r="D59" t="str">
-        <v>2026-05-05</v>
+        <v>2026-05-06</v>
       </c>
       <c r="E59" t="str">
         <v/>
@@ -2649,7 +2649,7 @@
         <v>https://music.apple.com/us/song/i-know-i-know/1894354139</v>
       </c>
       <c r="D60" t="str">
-        <v>2026-05-05</v>
+        <v>2026-05-06</v>
       </c>
       <c r="E60" t="str">
         <v/>
@@ -2687,7 +2687,7 @@
         <v>https://music.apple.com/us/song/drive-all-night/6763189759</v>
       </c>
       <c r="D61" t="str">
-        <v>2026-05-05</v>
+        <v>2026-05-06</v>
       </c>
       <c r="E61" t="str">
         <v/>
@@ -2725,7 +2725,7 @@
         <v>https://music.apple.com/us/song/aint-u-tired/6763115235</v>
       </c>
       <c r="D62" t="str">
-        <v>2026-05-05</v>
+        <v>2026-05-06</v>
       </c>
       <c r="E62" t="str">
         <v/>
@@ -2763,7 +2763,7 @@
         <v>https://music.apple.com/us/song/boys-in-blue/1892436920</v>
       </c>
       <c r="D63" t="str">
-        <v>2026-05-05</v>
+        <v>2026-05-06</v>
       </c>
       <c r="E63" t="str">
         <v/>
@@ -2801,7 +2801,7 @@
         <v>https://music.apple.com/us/song/salma-hayek/1891815286</v>
       </c>
       <c r="D64" t="str">
-        <v>2026-05-05</v>
+        <v>2026-05-06</v>
       </c>
       <c r="E64" t="str">
         <v/>
@@ -2839,7 +2839,7 @@
         <v>https://music.apple.com/us/song/stubborn-mouth/1893194800</v>
       </c>
       <c r="D65" t="str">
-        <v>2026-05-05</v>
+        <v>2026-05-06</v>
       </c>
       <c r="E65" t="str">
         <v/>
@@ -2877,7 +2877,7 @@
         <v>https://music.apple.com/us/song/hallucination/6764110976</v>
       </c>
       <c r="D66" t="str">
-        <v>2026-05-05</v>
+        <v>2026-05-06</v>
       </c>
       <c r="E66" t="str">
         <v/>
@@ -2915,7 +2915,7 @@
         <v>https://music.apple.com/us/song/in-da-jungle/1891136400</v>
       </c>
       <c r="D67" t="str">
-        <v>2026-05-05</v>
+        <v>2026-05-06</v>
       </c>
       <c r="E67" t="str">
         <v/>
@@ -2953,7 +2953,7 @@
         <v>https://music.apple.com/us/song/fall-short/1894662749</v>
       </c>
       <c r="D68" t="str">
-        <v>2026-05-05</v>
+        <v>2026-05-06</v>
       </c>
       <c r="E68" t="str">
         <v/>
@@ -2991,7 +2991,7 @@
         <v>https://music.apple.com/us/song/irish-goodbye-feat-kae-tempest/1862224205</v>
       </c>
       <c r="D69" t="str">
-        <v>2026-05-05</v>
+        <v>2026-05-06</v>
       </c>
       <c r="E69" t="str">
         <v/>
@@ -3029,7 +3029,7 @@
         <v>https://music.apple.com/us/song/1989/1893089382</v>
       </c>
       <c r="D70" t="str">
-        <v>2026-05-05</v>
+        <v>2026-05-06</v>
       </c>
       <c r="E70" t="str">
         <v/>
@@ -3067,7 +3067,7 @@
         <v>https://music.apple.com/us/song/no-more-regrets/1893191803</v>
       </c>
       <c r="D71" t="str">
-        <v>2026-05-05</v>
+        <v>2026-05-06</v>
       </c>
       <c r="E71" t="str">
         <v/>
@@ -3105,7 +3105,7 @@
         <v>https://music.apple.com/us/song/drum-machine/1840517102</v>
       </c>
       <c r="D72" t="str">
-        <v>2026-05-05</v>
+        <v>2026-05-06</v>
       </c>
       <c r="E72" t="str">
         <v/>
@@ -3143,7 +3143,7 @@
         <v>https://music.apple.com/us/song/im-perfect/1893181359</v>
       </c>
       <c r="D73" t="str">
-        <v>2026-05-05</v>
+        <v>2026-05-06</v>
       </c>
       <c r="E73" t="str">
         <v/>
@@ -3181,7 +3181,7 @@
         <v>https://music.apple.com/us/song/theme-for-a-train-journey/1880699785</v>
       </c>
       <c r="D74" t="str">
-        <v>2026-05-05</v>
+        <v>2026-05-06</v>
       </c>
       <c r="E74" t="str">
         <v/>
@@ -3219,7 +3219,7 @@
         <v>https://music.apple.com/us/song/bitch-you-weird/6763395875</v>
       </c>
       <c r="D75" t="str">
-        <v>2026-05-05</v>
+        <v>2026-05-06</v>
       </c>
       <c r="E75" t="str">
         <v/>
@@ -3257,7 +3257,7 @@
         <v>https://music.apple.com/us/song/blackbird-rising/1887166611</v>
       </c>
       <c r="D76" t="str">
-        <v>2026-05-05</v>
+        <v>2026-05-06</v>
       </c>
       <c r="E76" t="str">
         <v/>
@@ -3295,7 +3295,7 @@
         <v>https://music.apple.com/us/song/usher-in-the-spirit/6763373678</v>
       </c>
       <c r="D77" t="str">
-        <v>2026-05-05</v>
+        <v>2026-05-06</v>
       </c>
       <c r="E77" t="str">
         <v/>
@@ -3333,7 +3333,7 @@
         <v>https://music.apple.com/us/song/moonlight/1892950791</v>
       </c>
       <c r="D78" t="str">
-        <v>2026-05-05</v>
+        <v>2026-05-06</v>
       </c>
       <c r="E78" t="str">
         <v/>
@@ -3371,7 +3371,7 @@
         <v>https://music.apple.com/us/song/hands-on-me/1893960365</v>
       </c>
       <c r="D79" t="str">
-        <v>2026-05-05</v>
+        <v>2026-05-06</v>
       </c>
       <c r="E79" t="str">
         <v/>
@@ -3409,7 +3409,7 @@
         <v>https://music.apple.com/us/song/closure/1892418294</v>
       </c>
       <c r="D80" t="str">
-        <v>2026-05-05</v>
+        <v>2026-05-06</v>
       </c>
       <c r="E80" t="str">
         <v/>
@@ -3447,7 +3447,7 @@
         <v>https://music.apple.com/us/song/hots-4-u/1891478541</v>
       </c>
       <c r="D81" t="str">
-        <v>2026-05-05</v>
+        <v>2026-05-06</v>
       </c>
       <c r="E81" t="str">
         <v/>
@@ -3485,7 +3485,7 @@
         <v>https://music.apple.com/us/song/cule-poco-sirena-besarico-coste%C3%B1a/1893480200</v>
       </c>
       <c r="D82" t="str">
-        <v>2026-05-05</v>
+        <v>2026-05-06</v>
       </c>
       <c r="E82" t="str">
         <v/>
@@ -3523,7 +3523,7 @@
         <v>https://music.apple.com/us/song/the-coin-toss/1894872115</v>
       </c>
       <c r="D83" t="str">
-        <v>2026-05-05</v>
+        <v>2026-05-06</v>
       </c>
       <c r="E83" t="str">
         <v/>
@@ -3561,7 +3561,7 @@
         <v>https://music.apple.com/us/song/bottles-lights/6763041153</v>
       </c>
       <c r="D84" t="str">
-        <v>2026-05-05</v>
+        <v>2026-05-06</v>
       </c>
       <c r="E84" t="str">
         <v/>
@@ -3599,7 +3599,7 @@
         <v>https://music.apple.com/us/song/perfect-for-me/6762879981</v>
       </c>
       <c r="D85" t="str">
-        <v>2026-05-05</v>
+        <v>2026-05-06</v>
       </c>
       <c r="E85" t="str">
         <v/>
@@ -3637,7 +3637,7 @@
         <v>https://music.apple.com/us/song/so/1893162424</v>
       </c>
       <c r="D86" t="str">
-        <v>2026-05-05</v>
+        <v>2026-05-06</v>
       </c>
       <c r="E86" t="str">
         <v/>
@@ -3675,7 +3675,7 @@
         <v>https://music.apple.com/us/song/pase-y-pase/1894076490</v>
       </c>
       <c r="D87" t="str">
-        <v>2026-05-05</v>
+        <v>2026-05-06</v>
       </c>
       <c r="E87" t="str">
         <v/>
@@ -3713,7 +3713,7 @@
         <v>https://music.apple.com/us/song/agou%C3%A9-dambala-yanvalou-1/1888242486</v>
       </c>
       <c r="D88" t="str">
-        <v>2026-05-05</v>
+        <v>2026-05-06</v>
       </c>
       <c r="E88" t="str">
         <v/>
@@ -3751,7 +3751,7 @@
         <v>https://music.apple.com/us/song/aljahalat/1889267983</v>
       </c>
       <c r="D89" t="str">
-        <v>2026-05-05</v>
+        <v>2026-05-06</v>
       </c>
       <c r="E89" t="str">
         <v/>
@@ -3789,7 +3789,7 @@
         <v>https://music.apple.com/us/song/puleza/1893765840</v>
       </c>
       <c r="D90" t="str">
-        <v>2026-05-05</v>
+        <v>2026-05-06</v>
       </c>
       <c r="E90" t="str">
         <v/>
@@ -3827,7 +3827,7 @@
         <v>https://music.apple.com/us/song/bastards/6762403102</v>
       </c>
       <c r="D91" t="str">
-        <v>2026-05-05</v>
+        <v>2026-05-06</v>
       </c>
       <c r="E91" t="str">
         <v/>
@@ -3865,7 +3865,7 @@
         <v>https://music.apple.com/us/song/crutch/6763345020</v>
       </c>
       <c r="D92" t="str">
-        <v>2026-05-05</v>
+        <v>2026-05-06</v>
       </c>
       <c r="E92" t="str">
         <v/>
@@ -3903,7 +3903,7 @@
         <v>https://music.apple.com/us/song/just-a-man/1893736206</v>
       </c>
       <c r="D93" t="str">
-        <v>2026-05-05</v>
+        <v>2026-05-06</v>
       </c>
       <c r="E93" t="str">
         <v/>
@@ -3941,7 +3941,7 @@
         <v>https://music.apple.com/us/song/take-care-of-you/6762283983</v>
       </c>
       <c r="D94" t="str">
-        <v>2026-05-05</v>
+        <v>2026-05-06</v>
       </c>
       <c r="E94" t="str">
         <v/>
@@ -3979,7 +3979,7 @@
         <v>https://music.apple.com/us/song/love-you-more/1889686330</v>
       </c>
       <c r="D95" t="str">
-        <v>2026-05-05</v>
+        <v>2026-05-06</v>
       </c>
       <c r="E95" t="str">
         <v/>
@@ -4017,7 +4017,7 @@
         <v>https://music.apple.com/us/song/construct/1869323374</v>
       </c>
       <c r="D96" t="str">
-        <v>2026-05-05</v>
+        <v>2026-05-06</v>
       </c>
       <c r="E96" t="str">
         <v/>
@@ -4055,7 +4055,7 @@
         <v>https://music.apple.com/us/song/as-above-so-below/1872651422</v>
       </c>
       <c r="D97" t="str">
-        <v>2026-05-05</v>
+        <v>2026-05-06</v>
       </c>
       <c r="E97" t="str">
         <v/>
@@ -4093,7 +4093,7 @@
         <v>https://music.apple.com/us/song/revenant/6763148056</v>
       </c>
       <c r="D98" t="str">
-        <v>2026-05-05</v>
+        <v>2026-05-06</v>
       </c>
       <c r="E98" t="str">
         <v/>
@@ -4131,7 +4131,7 @@
         <v>https://music.apple.com/us/song/black-box-feat-joe-duplantier-the-mystery-of/6762312582</v>
       </c>
       <c r="D99" t="str">
-        <v>2026-05-05</v>
+        <v>2026-05-06</v>
       </c>
       <c r="E99" t="str">
         <v/>
@@ -4169,7 +4169,7 @@
         <v>https://music.apple.com/us/song/power-4/6763647813</v>
       </c>
       <c r="D100" t="str">
-        <v>2026-05-05</v>
+        <v>2026-05-06</v>
       </c>
       <c r="E100" t="str">
         <v/>
@@ -4207,7 +4207,7 @@
         <v>https://music.apple.com/us/song/too-easy/1893814702</v>
       </c>
       <c r="D101" t="str">
-        <v>2026-05-05</v>
+        <v>2026-05-06</v>
       </c>
       <c r="E101" t="str">
         <v/>
@@ -4245,7 +4245,7 @@
         <v>https://music.apple.com/us/song/if-you-want-it/1892503347</v>
       </c>
       <c r="D102" t="str">
-        <v>2026-05-05</v>
+        <v>2026-05-06</v>
       </c>
       <c r="E102" t="str">
         <v/>
@@ -4283,7 +4283,7 @@
         <v>https://music.apple.com/us/song/shoplifting/1852812659</v>
       </c>
       <c r="D103" t="str">
-        <v>2026-05-05</v>
+        <v>2026-05-06</v>
       </c>
       <c r="E103" t="str">
         <v/>
@@ -4321,7 +4321,7 @@
         <v>https://music.apple.com/us/song/endlessly-feat-bea1991/1876022833</v>
       </c>
       <c r="D104" t="str">
-        <v>2026-05-05</v>
+        <v>2026-05-06</v>
       </c>
       <c r="E104" t="str">
         <v/>

--- a/data/tags/מוזיקה לועזית חדשה/sites/apple-music-playlist/2026-05-week01/titles.xlsx
+++ b/data/tags/מוזיקה לועזית חדשה/sites/apple-music-playlist/2026-05-week01/titles.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L104"/>
+  <dimension ref="A1:L105"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -436,13 +436,13 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>linknb</v>
+        <v>Therapy at the Club</v>
       </c>
       <c r="B2" t="str">
         <v/>
       </c>
       <c r="C2" t="str">
-        <v>https://music.apple.com/us/song/linknb/1888561848</v>
+        <v>https://music.apple.com/us/song/therapy-at-the-club/6764050150</v>
       </c>
       <c r="D2" t="str">
         <v>2026-05-06</v>
@@ -451,25 +451,25 @@
         <v/>
       </c>
       <c r="F2" t="str">
-        <v>new avatar</v>
+        <v>THERAPY AT THE CLUB</v>
       </c>
       <c r="G2" t="str">
-        <v>1:55</v>
+        <v>2:47</v>
       </c>
       <c r="H2" t="str">
-        <v>Kelela</v>
+        <v>FLO</v>
       </c>
       <c r="I2" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J2" t="str">
-        <v>https://music.apple.com/us/artist/kelela/549186342</v>
+        <v>https://music.apple.com/us/artist/flo/1615611716</v>
       </c>
       <c r="K2" t="str">
-        <v>https://music.apple.com/us/album/linknb/1888561538</v>
+        <v>https://music.apple.com/us/album/therapy-at-the-club/1895613904</v>
       </c>
       <c r="L2" t="str">
-        <v>linknb - Kelela</v>
+        <v>Therapy at the Club - FLO</v>
       </c>
     </row>
     <row r="3">
@@ -778,13 +778,13 @@
     </row>
     <row r="11">
       <c r="A11" t="str">
-        <v>Robotic Love</v>
+        <v>linknb</v>
       </c>
       <c r="B11" t="str">
         <v/>
       </c>
       <c r="C11" t="str">
-        <v>https://music.apple.com/us/song/robotic-love/6763638857</v>
+        <v>https://music.apple.com/us/song/linknb/1888561848</v>
       </c>
       <c r="D11" t="str">
         <v>2026-05-06</v>
@@ -793,25 +793,25 @@
         <v/>
       </c>
       <c r="F11" t="str">
-        <v>Robotic Love - Single</v>
+        <v>new avatar</v>
       </c>
       <c r="G11" t="str">
-        <v>3:25</v>
+        <v>1:55</v>
       </c>
       <c r="H11" t="str">
-        <v>elkan</v>
+        <v>Kelela</v>
       </c>
       <c r="I11" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J11" t="str">
-        <v>https://music.apple.com/us/artist/elkan/1805013361</v>
+        <v>https://music.apple.com/us/artist/kelela/549186342</v>
       </c>
       <c r="K11" t="str">
-        <v>https://music.apple.com/us/album/robotic-love/1895412608</v>
+        <v>https://music.apple.com/us/album/linknb/1888561538</v>
       </c>
       <c r="L11" t="str">
-        <v>Robotic Love - elkan</v>
+        <v>linknb - Kelela</v>
       </c>
     </row>
     <row r="12">
@@ -854,13 +854,13 @@
     </row>
     <row r="13">
       <c r="A13" t="str">
-        <v>IT'S OK</v>
+        <v>Robotic Love</v>
       </c>
       <c r="B13" t="str">
         <v/>
       </c>
       <c r="C13" t="str">
-        <v>https://music.apple.com/us/song/its-ok/6763134121</v>
+        <v>https://music.apple.com/us/song/robotic-love/6763638857</v>
       </c>
       <c r="D13" t="str">
         <v>2026-05-06</v>
@@ -869,36 +869,36 @@
         <v/>
       </c>
       <c r="F13" t="str">
-        <v>IT'S OK - Single</v>
+        <v>Robotic Love - Single</v>
       </c>
       <c r="G13" t="str">
-        <v>2:19</v>
+        <v>3:25</v>
       </c>
       <c r="H13" t="str">
-        <v>Bryson Tiller</v>
+        <v>elkan</v>
       </c>
       <c r="I13" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J13" t="str">
-        <v>https://music.apple.com/us/artist/bryson-tiller/642591128</v>
+        <v>https://music.apple.com/us/artist/elkan/1805013361</v>
       </c>
       <c r="K13" t="str">
-        <v>https://music.apple.com/us/album/its-ok/1895176998</v>
+        <v>https://music.apple.com/us/album/robotic-love/1895412608</v>
       </c>
       <c r="L13" t="str">
-        <v>IT'S OK - Bryson Tiller</v>
+        <v>Robotic Love - elkan</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="str">
-        <v>Promise?</v>
+        <v>IT'S OK</v>
       </c>
       <c r="B14" t="str">
         <v/>
       </c>
       <c r="C14" t="str">
-        <v>https://music.apple.com/us/song/promise/6763162287</v>
+        <v>https://music.apple.com/us/song/its-ok/6763134121</v>
       </c>
       <c r="D14" t="str">
         <v>2026-05-06</v>
@@ -907,36 +907,36 @@
         <v/>
       </c>
       <c r="F14" t="str">
-        <v>Promise? - Single</v>
+        <v>IT'S OK - Single</v>
       </c>
       <c r="G14" t="str">
-        <v>3:12</v>
+        <v>2:19</v>
       </c>
       <c r="H14" t="str">
-        <v>Bella Kay</v>
+        <v>Bryson Tiller</v>
       </c>
       <c r="I14" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J14" t="str">
-        <v>https://music.apple.com/us/artist/bella-kay/1706434165</v>
+        <v>https://music.apple.com/us/artist/bryson-tiller/642591128</v>
       </c>
       <c r="K14" t="str">
-        <v>https://music.apple.com/us/album/promise/1895191463</v>
+        <v>https://music.apple.com/us/album/its-ok/1895176998</v>
       </c>
       <c r="L14" t="str">
-        <v>Promise? - Bella Kay</v>
+        <v>IT'S OK - Bryson Tiller</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="str">
-        <v>Cool Buzz</v>
+        <v>Promise?</v>
       </c>
       <c r="B15" t="str">
         <v/>
       </c>
       <c r="C15" t="str">
-        <v>https://music.apple.com/us/song/cool-buzz/1880470657</v>
+        <v>https://music.apple.com/us/song/promise/6763162287</v>
       </c>
       <c r="D15" t="str">
         <v>2026-05-06</v>
@@ -945,36 +945,36 @@
         <v/>
       </c>
       <c r="F15" t="str">
-        <v>Be Sweet To Me</v>
+        <v>Promise? - Single</v>
       </c>
       <c r="G15" t="str">
-        <v>2:32</v>
+        <v>3:12</v>
       </c>
       <c r="H15" t="str">
-        <v>Violet Grohl</v>
+        <v>Bella Kay</v>
       </c>
       <c r="I15" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J15" t="str">
-        <v>https://music.apple.com/us/artist/violet-grohl/1538671509</v>
+        <v>https://music.apple.com/us/artist/bella-kay/1706434165</v>
       </c>
       <c r="K15" t="str">
-        <v>https://music.apple.com/us/album/cool-buzz/1880470537</v>
+        <v>https://music.apple.com/us/album/promise/1895191463</v>
       </c>
       <c r="L15" t="str">
-        <v>Cool Buzz - Violet Grohl</v>
+        <v>Promise? - Bella Kay</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="str">
-        <v>Material Lover</v>
+        <v>Cool Buzz</v>
       </c>
       <c r="B16" t="str">
         <v/>
       </c>
       <c r="C16" t="str">
-        <v>https://music.apple.com/us/song/material-lover/6764429256</v>
+        <v>https://music.apple.com/us/song/cool-buzz/1880470657</v>
       </c>
       <c r="D16" t="str">
         <v>2026-05-06</v>
@@ -983,36 +983,36 @@
         <v/>
       </c>
       <c r="F16" t="str">
-        <v>The Devil Wears Prada 2 (Music From The Motion Picture)</v>
+        <v>Be Sweet To Me</v>
       </c>
       <c r="G16" t="str">
-        <v>2:58</v>
+        <v>2:32</v>
       </c>
       <c r="H16" t="str">
-        <v>SIENNA SPIRO</v>
+        <v>Violet Grohl</v>
       </c>
       <c r="I16" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J16" t="str">
-        <v>https://music.apple.com/us/artist/sienna-spiro/1745678083</v>
+        <v>https://music.apple.com/us/artist/violet-grohl/1538671509</v>
       </c>
       <c r="K16" t="str">
-        <v>https://music.apple.com/us/album/material-lover/1895776688</v>
+        <v>https://music.apple.com/us/album/cool-buzz/1880470537</v>
       </c>
       <c r="L16" t="str">
-        <v>Material Lover - SIENNA SPIRO</v>
+        <v>Cool Buzz - Violet Grohl</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="str">
-        <v>Fallin' (feat. Leon Thomas)</v>
+        <v>Material Lover</v>
       </c>
       <c r="B17" t="str">
         <v/>
       </c>
       <c r="C17" t="str">
-        <v>https://music.apple.com/us/song/fallin-feat-leon-thomas/6764419265</v>
+        <v>https://music.apple.com/us/song/material-lover/6764429256</v>
       </c>
       <c r="D17" t="str">
         <v>2026-05-06</v>
@@ -1021,36 +1021,36 @@
         <v/>
       </c>
       <c r="F17" t="str">
-        <v>BROWN</v>
+        <v>The Devil Wears Prada 2 (Music From The Motion Picture)</v>
       </c>
       <c r="G17" t="str">
-        <v>4:26</v>
+        <v>2:58</v>
       </c>
       <c r="H17" t="str">
-        <v>Chris Brown</v>
+        <v>SIENNA SPIRO</v>
       </c>
       <c r="I17" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J17" t="str">
-        <v>https://music.apple.com/us/artist/chris-brown/95705522</v>
+        <v>https://music.apple.com/us/artist/sienna-spiro/1745678083</v>
       </c>
       <c r="K17" t="str">
-        <v>https://music.apple.com/us/album/fallin-feat-leon-thomas/1895772091</v>
+        <v>https://music.apple.com/us/album/material-lover/1895776688</v>
       </c>
       <c r="L17" t="str">
-        <v>Fallin' (feat. Leon Thomas) - Chris Brown</v>
+        <v>Material Lover - SIENNA SPIRO</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="str">
-        <v>Echo</v>
+        <v>Fallin' (feat. Leon Thomas)</v>
       </c>
       <c r="B18" t="str">
         <v/>
       </c>
       <c r="C18" t="str">
-        <v>https://music.apple.com/us/song/echo/6763379683</v>
+        <v>https://music.apple.com/us/song/fallin-feat-leon-thomas/6764419265</v>
       </c>
       <c r="D18" t="str">
         <v>2026-05-06</v>
@@ -1059,36 +1059,36 @@
         <v/>
       </c>
       <c r="F18" t="str">
-        <v>Echo (FIFA World Cup 2026™) - Single</v>
+        <v>BROWN</v>
       </c>
       <c r="G18" t="str">
-        <v>2:15</v>
+        <v>4:26</v>
       </c>
       <c r="H18" t="str">
-        <v>Daddy Yankee</v>
+        <v>Chris Brown</v>
       </c>
       <c r="I18" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J18" t="str">
-        <v>https://music.apple.com/us/artist/daddy-yankee/25514958</v>
+        <v>https://music.apple.com/us/artist/chris-brown/95705522</v>
       </c>
       <c r="K18" t="str">
-        <v>https://music.apple.com/us/album/echo/1895288918</v>
+        <v>https://music.apple.com/us/album/fallin-feat-leon-thomas/1895772091</v>
       </c>
       <c r="L18" t="str">
-        <v>Echo - Daddy Yankee</v>
+        <v>Fallin' (feat. Leon Thomas) - Chris Brown</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="str">
-        <v>Blackberry Marmalade</v>
+        <v>Echo</v>
       </c>
       <c r="B19" t="str">
         <v/>
       </c>
       <c r="C19" t="str">
-        <v>https://music.apple.com/us/song/blackberry-marmalade/1887627837</v>
+        <v>https://music.apple.com/us/song/echo/6763379683</v>
       </c>
       <c r="D19" t="str">
         <v>2026-05-06</v>
@@ -1097,36 +1097,36 @@
         <v/>
       </c>
       <c r="F19" t="str">
-        <v>Cry Baby</v>
+        <v>Echo (FIFA World Cup 2026™) - Single</v>
       </c>
       <c r="G19" t="str">
-        <v>3:52</v>
+        <v>2:15</v>
       </c>
       <c r="H19" t="str">
-        <v>Vince Staples</v>
+        <v>Daddy Yankee</v>
       </c>
       <c r="I19" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J19" t="str">
-        <v>https://music.apple.com/us/artist/vince-staples/566639154</v>
+        <v>https://music.apple.com/us/artist/daddy-yankee/25514958</v>
       </c>
       <c r="K19" t="str">
-        <v>https://music.apple.com/us/album/blackberry-marmalade/1887627836</v>
+        <v>https://music.apple.com/us/album/echo/1895288918</v>
       </c>
       <c r="L19" t="str">
-        <v>Blackberry Marmalade - Vince Staples</v>
+        <v>Echo - Daddy Yankee</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="str">
-        <v>Ricky Bobby</v>
+        <v>Blackberry Marmalade</v>
       </c>
       <c r="B20" t="str">
         <v/>
       </c>
       <c r="C20" t="str">
-        <v>https://music.apple.com/us/song/ricky-bobby/6764406571</v>
+        <v>https://music.apple.com/us/song/blackberry-marmalade/1887627837</v>
       </c>
       <c r="D20" t="str">
         <v>2026-05-06</v>
@@ -1135,36 +1135,36 @@
         <v/>
       </c>
       <c r="F20" t="str">
-        <v>CORSA</v>
+        <v>Cry Baby</v>
       </c>
       <c r="G20" t="str">
-        <v>2:55</v>
+        <v>3:52</v>
       </c>
       <c r="H20" t="str">
-        <v>Eladio Carrión</v>
+        <v>Vince Staples</v>
       </c>
       <c r="I20" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J20" t="str">
-        <v>https://music.apple.com/us/artist/eladio-carri%C3%B3n/1024801206</v>
+        <v>https://music.apple.com/us/artist/vince-staples/566639154</v>
       </c>
       <c r="K20" t="str">
-        <v>https://music.apple.com/us/album/ricky-bobby/1895766650</v>
+        <v>https://music.apple.com/us/album/blackberry-marmalade/1887627836</v>
       </c>
       <c r="L20" t="str">
-        <v>Ricky Bobby - Eladio Carrión</v>
+        <v>Blackberry Marmalade - Vince Staples</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="str">
-        <v>Te Entiendo (Remix)</v>
+        <v>Ricky Bobby</v>
       </c>
       <c r="B21" t="str">
         <v/>
       </c>
       <c r="C21" t="str">
-        <v>https://music.apple.com/us/song/te-entiendo-remix/6763665638</v>
+        <v>https://music.apple.com/us/song/ricky-bobby/6764406571</v>
       </c>
       <c r="D21" t="str">
         <v>2026-05-06</v>
@@ -1173,36 +1173,36 @@
         <v/>
       </c>
       <c r="F21" t="str">
-        <v>Te Entiendo (Remix) - Single</v>
+        <v>CORSA</v>
       </c>
       <c r="G21" t="str">
-        <v>5:35</v>
+        <v>2:55</v>
       </c>
       <c r="H21" t="str">
-        <v>Maisak</v>
+        <v>Eladio Carrión</v>
       </c>
       <c r="I21" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J21" t="str">
-        <v>https://music.apple.com/us/artist/maisak/1610652984</v>
+        <v>https://music.apple.com/us/artist/eladio-carri%C3%B3n/1024801206</v>
       </c>
       <c r="K21" t="str">
-        <v>https://music.apple.com/us/album/te-entiendo-remix/1895426152</v>
+        <v>https://music.apple.com/us/album/ricky-bobby/1895766650</v>
       </c>
       <c r="L21" t="str">
-        <v>Te Entiendo (Remix) - Maisak</v>
+        <v>Ricky Bobby - Eladio Carrión</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="str">
-        <v>Don't Worry Baby</v>
+        <v>Te Entiendo (Remix)</v>
       </c>
       <c r="B22" t="str">
         <v/>
       </c>
       <c r="C22" t="str">
-        <v>https://music.apple.com/us/song/dont-worry-baby/1894294411</v>
+        <v>https://music.apple.com/us/song/te-entiendo-remix/6763665638</v>
       </c>
       <c r="D22" t="str">
         <v>2026-05-06</v>
@@ -1211,36 +1211,36 @@
         <v/>
       </c>
       <c r="F22" t="str">
-        <v>Don't Worry Baby - Single</v>
+        <v>Te Entiendo (Remix) - Single</v>
       </c>
       <c r="G22" t="str">
-        <v>3:27</v>
+        <v>5:35</v>
       </c>
       <c r="H22" t="str">
-        <v>Dom Dolla</v>
+        <v>Maisak</v>
       </c>
       <c r="I22" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J22" t="str">
-        <v>https://music.apple.com/us/artist/dom-dolla/555348065</v>
+        <v>https://music.apple.com/us/artist/maisak/1610652984</v>
       </c>
       <c r="K22" t="str">
-        <v>https://music.apple.com/us/album/dont-worry-baby/1894294408</v>
+        <v>https://music.apple.com/us/album/te-entiendo-remix/1895426152</v>
       </c>
       <c r="L22" t="str">
-        <v>Don't Worry Baby - Dom Dolla</v>
+        <v>Te Entiendo (Remix) - Maisak</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="str">
-        <v>BITCH</v>
+        <v>Don't Worry Baby</v>
       </c>
       <c r="B23" t="str">
         <v/>
       </c>
       <c r="C23" t="str">
-        <v>https://music.apple.com/us/song/bitch/6763622110</v>
+        <v>https://music.apple.com/us/song/dont-worry-baby/1894294411</v>
       </c>
       <c r="D23" t="str">
         <v>2026-05-06</v>
@@ -1249,36 +1249,36 @@
         <v/>
       </c>
       <c r="F23" t="str">
-        <v>BITCH</v>
+        <v>Don't Worry Baby - Single</v>
       </c>
       <c r="G23" t="str">
-        <v>2:42</v>
+        <v>3:27</v>
       </c>
       <c r="H23" t="str">
-        <v>Lizzo</v>
+        <v>Dom Dolla</v>
       </c>
       <c r="I23" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J23" t="str">
-        <v>https://music.apple.com/us/artist/lizzo/472949623</v>
+        <v>https://music.apple.com/us/artist/dom-dolla/555348065</v>
       </c>
       <c r="K23" t="str">
-        <v>https://music.apple.com/us/album/bitch/1895402771</v>
+        <v>https://music.apple.com/us/album/dont-worry-baby/1894294408</v>
       </c>
       <c r="L23" t="str">
-        <v>BITCH - Lizzo</v>
+        <v>Don't Worry Baby - Dom Dolla</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="str">
-        <v>Just Wanna Cry</v>
+        <v>BITCH</v>
       </c>
       <c r="B24" t="str">
         <v/>
       </c>
       <c r="C24" t="str">
-        <v>https://music.apple.com/us/song/just-wanna-cry/6763414703</v>
+        <v>https://music.apple.com/us/song/bitch/6763622110</v>
       </c>
       <c r="D24" t="str">
         <v>2026-05-06</v>
@@ -1287,36 +1287,36 @@
         <v/>
       </c>
       <c r="F24" t="str">
-        <v>Toy With Me (Deluxe)</v>
+        <v>BITCH</v>
       </c>
       <c r="G24" t="str">
-        <v>2:27</v>
+        <v>2:42</v>
       </c>
       <c r="H24" t="str">
-        <v>Meghan Trainor</v>
+        <v>Lizzo</v>
       </c>
       <c r="I24" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J24" t="str">
-        <v>https://music.apple.com/us/artist/meghan-trainor/348580754</v>
+        <v>https://music.apple.com/us/artist/lizzo/472949623</v>
       </c>
       <c r="K24" t="str">
-        <v>https://music.apple.com/us/album/just-wanna-cry/1895303290</v>
+        <v>https://music.apple.com/us/album/bitch/1895402771</v>
       </c>
       <c r="L24" t="str">
-        <v>Just Wanna Cry - Meghan Trainor</v>
+        <v>BITCH - Lizzo</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="str">
-        <v>Carry the Weight</v>
+        <v>Just Wanna Cry</v>
       </c>
       <c r="B25" t="str">
         <v/>
       </c>
       <c r="C25" t="str">
-        <v>https://music.apple.com/us/song/carry-the-weight/6763611647</v>
+        <v>https://music.apple.com/us/song/just-wanna-cry/6763414703</v>
       </c>
       <c r="D25" t="str">
         <v>2026-05-06</v>
@@ -1325,36 +1325,36 @@
         <v/>
       </c>
       <c r="F25" t="str">
-        <v>The Great Impersonator (Deluxe)</v>
+        <v>Toy With Me (Deluxe)</v>
       </c>
       <c r="G25" t="str">
-        <v>3:09</v>
+        <v>2:27</v>
       </c>
       <c r="H25" t="str">
-        <v>Halsey</v>
+        <v>Meghan Trainor</v>
       </c>
       <c r="I25" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J25" t="str">
-        <v>https://music.apple.com/us/artist/halsey/324916925</v>
+        <v>https://music.apple.com/us/artist/meghan-trainor/348580754</v>
       </c>
       <c r="K25" t="str">
-        <v>https://music.apple.com/us/album/carry-the-weight/1895397523</v>
+        <v>https://music.apple.com/us/album/just-wanna-cry/1895303290</v>
       </c>
       <c r="L25" t="str">
-        <v>Carry the Weight - Halsey</v>
+        <v>Just Wanna Cry - Meghan Trainor</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="str">
-        <v>PROSTITUTE</v>
+        <v>Carry the Weight</v>
       </c>
       <c r="B26" t="str">
         <v/>
       </c>
       <c r="C26" t="str">
-        <v>https://music.apple.com/us/song/prostitute/1894092341</v>
+        <v>https://music.apple.com/us/song/carry-the-weight/6763611647</v>
       </c>
       <c r="D26" t="str">
         <v>2026-05-06</v>
@@ -1363,36 +1363,36 @@
         <v/>
       </c>
       <c r="F26" t="str">
-        <v>COSMIC OPERA ACT II</v>
+        <v>The Great Impersonator (Deluxe)</v>
       </c>
       <c r="G26" t="str">
-        <v>2:44</v>
+        <v>3:09</v>
       </c>
       <c r="H26" t="str">
-        <v>Labrinth</v>
+        <v>Halsey</v>
       </c>
       <c r="I26" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J26" t="str">
-        <v>https://music.apple.com/us/artist/labrinth/205732582</v>
+        <v>https://music.apple.com/us/artist/halsey/324916925</v>
       </c>
       <c r="K26" t="str">
-        <v>https://music.apple.com/us/album/prostitute/1894092339</v>
+        <v>https://music.apple.com/us/album/carry-the-weight/1895397523</v>
       </c>
       <c r="L26" t="str">
-        <v>PROSTITUTE - Labrinth</v>
+        <v>Carry the Weight - Halsey</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="str">
-        <v>i'm not joking</v>
+        <v>PROSTITUTE</v>
       </c>
       <c r="B27" t="str">
         <v/>
       </c>
       <c r="C27" t="str">
-        <v>https://music.apple.com/us/song/im-not-joking/1872842623</v>
+        <v>https://music.apple.com/us/song/prostitute/1894092341</v>
       </c>
       <c r="D27" t="str">
         <v>2026-05-06</v>
@@ -1401,36 +1401,36 @@
         <v/>
       </c>
       <c r="F27" t="str">
-        <v>everyone for ten minutes</v>
+        <v>COSMIC OPERA ACT II</v>
       </c>
       <c r="G27" t="str">
-        <v>3:54</v>
+        <v>2:44</v>
       </c>
       <c r="H27" t="str">
-        <v>Bleachers</v>
+        <v>Labrinth</v>
       </c>
       <c r="I27" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J27" t="str">
-        <v>https://music.apple.com/us/artist/bleachers/824434533</v>
+        <v>https://music.apple.com/us/artist/labrinth/205732582</v>
       </c>
       <c r="K27" t="str">
-        <v>https://music.apple.com/us/album/im-not-joking/1872842313</v>
+        <v>https://music.apple.com/us/album/prostitute/1894092339</v>
       </c>
       <c r="L27" t="str">
-        <v>i'm not joking - Bleachers</v>
+        <v>PROSTITUTE - Labrinth</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="str">
-        <v>Ruca</v>
+        <v>i'm not joking</v>
       </c>
       <c r="B28" t="str">
         <v/>
       </c>
       <c r="C28" t="str">
-        <v>https://music.apple.com/us/song/ruca/6763671002</v>
+        <v>https://music.apple.com/us/song/im-not-joking/1872842623</v>
       </c>
       <c r="D28" t="str">
         <v>2026-05-06</v>
@@ -1439,36 +1439,36 @@
         <v/>
       </c>
       <c r="F28" t="str">
-        <v>MUDA</v>
+        <v>everyone for ten minutes</v>
       </c>
       <c r="G28" t="str">
-        <v>3:01</v>
+        <v>3:54</v>
       </c>
       <c r="H28" t="str">
-        <v>Carín León</v>
+        <v>Bleachers</v>
       </c>
       <c r="I28" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J28" t="str">
-        <v>https://music.apple.com/us/artist/car%C3%ADn-le%C3%B3n/1370196486</v>
+        <v>https://music.apple.com/us/artist/bleachers/824434533</v>
       </c>
       <c r="K28" t="str">
-        <v>https://music.apple.com/us/album/ruca/1895429814</v>
+        <v>https://music.apple.com/us/album/im-not-joking/1872842313</v>
       </c>
       <c r="L28" t="str">
-        <v>Ruca - Carín León</v>
+        <v>i'm not joking - Bleachers</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="str">
-        <v>Make You Fight</v>
+        <v>Ruca</v>
       </c>
       <c r="B29" t="str">
         <v/>
       </c>
       <c r="C29" t="str">
-        <v>https://music.apple.com/us/song/make-you-fight/1892332386</v>
+        <v>https://music.apple.com/us/song/ruca/6763671002</v>
       </c>
       <c r="D29" t="str">
         <v>2026-05-06</v>
@@ -1477,36 +1477,36 @@
         <v/>
       </c>
       <c r="F29" t="str">
-        <v>Make You Fight - Single</v>
+        <v>MUDA</v>
       </c>
       <c r="G29" t="str">
-        <v>2:55</v>
+        <v>3:01</v>
       </c>
       <c r="H29" t="str">
-        <v>Chris Lake</v>
+        <v>Carín León</v>
       </c>
       <c r="I29" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J29" t="str">
-        <v>https://music.apple.com/us/artist/chris-lake/135067114</v>
+        <v>https://music.apple.com/us/artist/car%C3%ADn-le%C3%B3n/1370196486</v>
       </c>
       <c r="K29" t="str">
-        <v>https://music.apple.com/us/album/make-you-fight/1892332385</v>
+        <v>https://music.apple.com/us/album/ruca/1895429814</v>
       </c>
       <c r="L29" t="str">
-        <v>Make You Fight - Chris Lake</v>
+        <v>Ruca - Carín León</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="str">
-        <v>#N0rth4evr</v>
+        <v>Make You Fight</v>
       </c>
       <c r="B30" t="str">
         <v/>
       </c>
       <c r="C30" t="str">
-        <v>https://music.apple.com/us/song/n0rth4evr/6763302230</v>
+        <v>https://music.apple.com/us/song/make-you-fight/1892332386</v>
       </c>
       <c r="D30" t="str">
         <v>2026-05-06</v>
@@ -1515,36 +1515,36 @@
         <v/>
       </c>
       <c r="F30" t="str">
-        <v>N0rth4evr - EP</v>
+        <v>Make You Fight - Single</v>
       </c>
       <c r="G30" t="str">
-        <v>1:43</v>
+        <v>2:55</v>
       </c>
       <c r="H30" t="str">
-        <v>North West</v>
+        <v>Chris Lake</v>
       </c>
       <c r="I30" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J30" t="str">
-        <v>https://music.apple.com/us/artist/north-west/1729862520</v>
+        <v>https://music.apple.com/us/artist/chris-lake/135067114</v>
       </c>
       <c r="K30" t="str">
-        <v>https://music.apple.com/us/album/n0rth4evr/1895254115</v>
+        <v>https://music.apple.com/us/album/make-you-fight/1892332385</v>
       </c>
       <c r="L30" t="str">
-        <v>#N0rth4evr - North West</v>
+        <v>Make You Fight - Chris Lake</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="str">
-        <v>BOY IN RED</v>
+        <v>#N0rth4evr</v>
       </c>
       <c r="B31" t="str">
         <v/>
       </c>
       <c r="C31" t="str">
-        <v>https://music.apple.com/us/song/boy-in-red/1892543110</v>
+        <v>https://music.apple.com/us/song/n0rth4evr/6763302230</v>
       </c>
       <c r="D31" t="str">
         <v>2026-05-06</v>
@@ -1553,36 +1553,36 @@
         <v/>
       </c>
       <c r="F31" t="str">
-        <v>IT'S BEEN AWFUL</v>
+        <v>N0rth4evr - EP</v>
       </c>
       <c r="G31" t="str">
-        <v>3:09</v>
+        <v>1:43</v>
       </c>
       <c r="H31" t="str">
-        <v>Isaiah Rashad</v>
+        <v>North West</v>
       </c>
       <c r="I31" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J31" t="str">
-        <v>https://music.apple.com/us/artist/isaiah-rashad/605391263</v>
+        <v>https://music.apple.com/us/artist/north-west/1729862520</v>
       </c>
       <c r="K31" t="str">
-        <v>https://music.apple.com/us/album/boy-in-red/1892543099</v>
+        <v>https://music.apple.com/us/album/n0rth4evr/1895254115</v>
       </c>
       <c r="L31" t="str">
-        <v>BOY IN RED - Isaiah Rashad</v>
+        <v>#N0rth4evr - North West</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="str">
-        <v>EA EA EA</v>
+        <v>BOY IN RED</v>
       </c>
       <c r="B32" t="str">
         <v/>
       </c>
       <c r="C32" t="str">
-        <v>https://music.apple.com/us/song/ea-ea-ea/6763438376</v>
+        <v>https://music.apple.com/us/song/boy-in-red/1892543110</v>
       </c>
       <c r="D32" t="str">
         <v>2026-05-06</v>
@@ -1591,36 +1591,36 @@
         <v/>
       </c>
       <c r="F32" t="str">
-        <v>AFTERAFTER - EP</v>
+        <v>IT'S BEEN AWFUL</v>
       </c>
       <c r="G32" t="str">
-        <v>2:42</v>
+        <v>3:09</v>
       </c>
       <c r="H32" t="str">
-        <v>Clave Especial</v>
+        <v>Isaiah Rashad</v>
       </c>
       <c r="I32" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J32" t="str">
-        <v>https://music.apple.com/us/artist/clave-especial/1569749622</v>
+        <v>https://music.apple.com/us/artist/isaiah-rashad/605391263</v>
       </c>
       <c r="K32" t="str">
-        <v>https://music.apple.com/us/album/ea-ea-ea/1895315118</v>
+        <v>https://music.apple.com/us/album/boy-in-red/1892543099</v>
       </c>
       <c r="L32" t="str">
-        <v>EA EA EA - Clave Especial</v>
+        <v>BOY IN RED - Isaiah Rashad</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="str">
-        <v>Just A Man</v>
+        <v>EA EA EA</v>
       </c>
       <c r="B33" t="str">
         <v/>
       </c>
       <c r="C33" t="str">
-        <v>https://music.apple.com/us/song/just-a-man/6762944365</v>
+        <v>https://music.apple.com/us/song/ea-ea-ea/6763438376</v>
       </c>
       <c r="D33" t="str">
         <v>2026-05-06</v>
@@ -1629,36 +1629,36 @@
         <v/>
       </c>
       <c r="F33" t="str">
-        <v>Just A Man - Single</v>
+        <v>AFTERAFTER - EP</v>
       </c>
       <c r="G33" t="str">
-        <v>2:19</v>
+        <v>2:42</v>
       </c>
       <c r="H33" t="str">
-        <v>Claire Rosinkranz</v>
+        <v>Clave Especial</v>
       </c>
       <c r="I33" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J33" t="str">
-        <v>https://music.apple.com/us/artist/claire-rosinkranz/1483262366</v>
+        <v>https://music.apple.com/us/artist/clave-especial/1569749622</v>
       </c>
       <c r="K33" t="str">
-        <v>https://music.apple.com/us/album/just-a-man/1895089709</v>
+        <v>https://music.apple.com/us/album/ea-ea-ea/1895315118</v>
       </c>
       <c r="L33" t="str">
-        <v>Just A Man - Claire Rosinkranz</v>
+        <v>EA EA EA - Clave Especial</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="str">
-        <v>The Observer</v>
+        <v>Just A Man</v>
       </c>
       <c r="B34" t="str">
         <v/>
       </c>
       <c r="C34" t="str">
-        <v>https://music.apple.com/us/song/the-observer/1891982314</v>
+        <v>https://music.apple.com/us/song/just-a-man/6762944365</v>
       </c>
       <c r="D34" t="str">
         <v>2026-05-06</v>
@@ -1667,36 +1667,36 @@
         <v/>
       </c>
       <c r="F34" t="str">
-        <v>How Did I Get Here? (Extended Edition)</v>
+        <v>Just A Man - Single</v>
       </c>
       <c r="G34" t="str">
-        <v>2:50</v>
+        <v>2:19</v>
       </c>
       <c r="H34" t="str">
-        <v>Louis Tomlinson</v>
+        <v>Claire Rosinkranz</v>
       </c>
       <c r="I34" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J34" t="str">
-        <v>https://music.apple.com/us/artist/louis-tomlinson/471260295</v>
+        <v>https://music.apple.com/us/artist/claire-rosinkranz/1483262366</v>
       </c>
       <c r="K34" t="str">
-        <v>https://music.apple.com/us/album/the-observer/1891982287</v>
+        <v>https://music.apple.com/us/album/just-a-man/1895089709</v>
       </c>
       <c r="L34" t="str">
-        <v>The Observer - Louis Tomlinson</v>
+        <v>Just A Man - Claire Rosinkranz</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="str">
-        <v>Heroine</v>
+        <v>The Observer</v>
       </c>
       <c r="B35" t="str">
         <v/>
       </c>
       <c r="C35" t="str">
-        <v>https://music.apple.com/us/song/heroine/6762693177</v>
+        <v>https://music.apple.com/us/song/the-observer/1891982314</v>
       </c>
       <c r="D35" t="str">
         <v>2026-05-06</v>
@@ -1705,36 +1705,36 @@
         <v/>
       </c>
       <c r="F35" t="str">
-        <v>Heroine - Single</v>
+        <v>How Did I Get Here? (Extended Edition)</v>
       </c>
       <c r="G35" t="str">
-        <v>2:35</v>
+        <v>2:50</v>
       </c>
       <c r="H35" t="str">
-        <v>Maroon 5</v>
+        <v>Louis Tomlinson</v>
       </c>
       <c r="I35" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J35" t="str">
-        <v>https://music.apple.com/us/artist/maroon-5/1798556</v>
+        <v>https://music.apple.com/us/artist/louis-tomlinson/471260295</v>
       </c>
       <c r="K35" t="str">
-        <v>https://music.apple.com/us/album/heroine/1894966605</v>
+        <v>https://music.apple.com/us/album/the-observer/1891982287</v>
       </c>
       <c r="L35" t="str">
-        <v>Heroine - Maroon 5</v>
+        <v>The Observer - Louis Tomlinson</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="str">
-        <v>Do Me Right</v>
+        <v>Heroine</v>
       </c>
       <c r="B36" t="str">
         <v/>
       </c>
       <c r="C36" t="str">
-        <v>https://music.apple.com/us/song/do-me-right/6764667658</v>
+        <v>https://music.apple.com/us/song/heroine/6762693177</v>
       </c>
       <c r="D36" t="str">
         <v>2026-05-06</v>
@@ -1743,36 +1743,36 @@
         <v/>
       </c>
       <c r="F36" t="str">
-        <v>FANTASYLAND</v>
+        <v>Heroine - Single</v>
       </c>
       <c r="G36" t="str">
-        <v>4:10</v>
+        <v>2:35</v>
       </c>
       <c r="H36" t="str">
-        <v>MR. FANTASY</v>
+        <v>Maroon 5</v>
       </c>
       <c r="I36" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J36" t="str">
-        <v>https://music.apple.com/us/artist/mr-fantasy/1834481769</v>
+        <v>https://music.apple.com/us/artist/maroon-5/1798556</v>
       </c>
       <c r="K36" t="str">
-        <v>https://music.apple.com/us/album/do-me-right/1895871261</v>
+        <v>https://music.apple.com/us/album/heroine/1894966605</v>
       </c>
       <c r="L36" t="str">
-        <v>Do Me Right - MR. FANTASY</v>
+        <v>Heroine - Maroon 5</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="str">
-        <v>It's Me</v>
+        <v>Do Me Right</v>
       </c>
       <c r="B37" t="str">
         <v/>
       </c>
       <c r="C37" t="str">
-        <v>https://music.apple.com/us/song/its-me/1887194026</v>
+        <v>https://music.apple.com/us/song/do-me-right/6764667658</v>
       </c>
       <c r="D37" t="str">
         <v>2026-05-06</v>
@@ -1781,36 +1781,36 @@
         <v/>
       </c>
       <c r="F37" t="str">
-        <v>MAMIHLAPINATAPAI - EP</v>
+        <v>FANTASYLAND</v>
       </c>
       <c r="G37" t="str">
-        <v>2:18</v>
+        <v>4:10</v>
       </c>
       <c r="H37" t="str">
-        <v>ILLIT</v>
+        <v>MR. FANTASY</v>
       </c>
       <c r="I37" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J37" t="str">
-        <v>https://music.apple.com/us/artist/illit/1734551937</v>
+        <v>https://music.apple.com/us/artist/mr-fantasy/1834481769</v>
       </c>
       <c r="K37" t="str">
-        <v>https://music.apple.com/us/album/its-me/1887194024</v>
+        <v>https://music.apple.com/us/album/do-me-right/1895871261</v>
       </c>
       <c r="L37" t="str">
-        <v>It's Me - ILLIT</v>
+        <v>Do Me Right - MR. FANTASY</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="str">
-        <v>the precipice</v>
+        <v>It's Me</v>
       </c>
       <c r="B38" t="str">
         <v/>
       </c>
       <c r="C38" t="str">
-        <v>https://music.apple.com/us/song/the-precipice/1891830326</v>
+        <v>https://music.apple.com/us/song/its-me/1887194026</v>
       </c>
       <c r="D38" t="str">
         <v>2026-05-06</v>
@@ -1819,36 +1819,36 @@
         <v/>
       </c>
       <c r="F38" t="str">
-        <v>untitled.jpeg - EP</v>
+        <v>MAMIHLAPINATAPAI - EP</v>
       </c>
       <c r="G38" t="str">
-        <v>3:52</v>
+        <v>2:18</v>
       </c>
       <c r="H38" t="str">
-        <v>Jessie Mazin</v>
+        <v>ILLIT</v>
       </c>
       <c r="I38" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J38" t="str">
-        <v>https://music.apple.com/us/artist/jessie-mazin/1887707056</v>
+        <v>https://music.apple.com/us/artist/illit/1734551937</v>
       </c>
       <c r="K38" t="str">
-        <v>https://music.apple.com/us/album/the-precipice/1891830323</v>
+        <v>https://music.apple.com/us/album/its-me/1887194024</v>
       </c>
       <c r="L38" t="str">
-        <v>the precipice - Jessie Mazin</v>
+        <v>It's Me - ILLIT</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="str">
-        <v>Hello Lonesome</v>
+        <v>the precipice</v>
       </c>
       <c r="B39" t="str">
         <v/>
       </c>
       <c r="C39" t="str">
-        <v>https://music.apple.com/us/song/hello-lonesome/1892466003</v>
+        <v>https://music.apple.com/us/song/the-precipice/1891830326</v>
       </c>
       <c r="D39" t="str">
         <v>2026-05-06</v>
@@ -1857,36 +1857,36 @@
         <v/>
       </c>
       <c r="F39" t="str">
-        <v>Banks Of The Trinity</v>
+        <v>untitled.jpeg - EP</v>
       </c>
       <c r="G39" t="str">
-        <v>2:58</v>
+        <v>3:52</v>
       </c>
       <c r="H39" t="str">
-        <v>Cody Johnson</v>
+        <v>Jessie Mazin</v>
       </c>
       <c r="I39" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J39" t="str">
-        <v>https://music.apple.com/us/artist/cody-johnson/331459657</v>
+        <v>https://music.apple.com/us/artist/jessie-mazin/1887707056</v>
       </c>
       <c r="K39" t="str">
-        <v>https://music.apple.com/us/album/hello-lonesome/1892465981</v>
+        <v>https://music.apple.com/us/album/the-precipice/1891830323</v>
       </c>
       <c r="L39" t="str">
-        <v>Hello Lonesome - Cody Johnson</v>
+        <v>the precipice - Jessie Mazin</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="str">
-        <v>TRIPPIN (Opera Edit)</v>
+        <v>Hello Lonesome</v>
       </c>
       <c r="B40" t="str">
         <v/>
       </c>
       <c r="C40" t="str">
-        <v>https://music.apple.com/us/song/trippin-opera-edit/6764648776</v>
+        <v>https://music.apple.com/us/song/hello-lonesome/1892466003</v>
       </c>
       <c r="D40" t="str">
         <v>2026-05-06</v>
@@ -1895,36 +1895,36 @@
         <v/>
       </c>
       <c r="F40" t="str">
-        <v>TRIPPIN (Opera Edit) - Single</v>
+        <v>Banks Of The Trinity</v>
       </c>
       <c r="G40" t="str">
-        <v>2:21</v>
+        <v>2:58</v>
       </c>
       <c r="H40" t="str">
-        <v>BUNT.</v>
+        <v>Cody Johnson</v>
       </c>
       <c r="I40" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J40" t="str">
-        <v>https://music.apple.com/us/artist/bunt/1436090348</v>
+        <v>https://music.apple.com/us/artist/cody-johnson/331459657</v>
       </c>
       <c r="K40" t="str">
-        <v>https://music.apple.com/us/album/trippin-opera-edit/1895863999</v>
+        <v>https://music.apple.com/us/album/hello-lonesome/1892465981</v>
       </c>
       <c r="L40" t="str">
-        <v>TRIPPIN (Opera Edit) - BUNT.</v>
+        <v>Hello Lonesome - Cody Johnson</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="str">
-        <v>The Mandalorian and Grogu (Boys Noize Remix) [From "Star Wars: The Mandalorian and Grogu"]</v>
+        <v>TRIPPIN (Opera Edit)</v>
       </c>
       <c r="B41" t="str">
         <v/>
       </c>
       <c r="C41" t="str">
-        <v>https://music.apple.com/us/song/the-mandalorian-and-grogu-boys-noize-remix-from-star/6764131630</v>
+        <v>https://music.apple.com/us/song/trippin-opera-edit/6764648776</v>
       </c>
       <c r="D41" t="str">
         <v>2026-05-06</v>
@@ -1933,36 +1933,36 @@
         <v/>
       </c>
       <c r="F41" t="str">
-        <v>The Mandalorian and Grogu (Boys Noize Remix) [From "Star Wars: The Mandalorian and Grogu"] - Single</v>
+        <v>TRIPPIN (Opera Edit) - Single</v>
       </c>
       <c r="G41" t="str">
-        <v>5:54</v>
+        <v>2:21</v>
       </c>
       <c r="H41" t="str">
-        <v>Ludwig Göransson</v>
+        <v>BUNT.</v>
       </c>
       <c r="I41" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J41" t="str">
-        <v>https://music.apple.com/us/artist/ludwig-g%C3%B6ransson/391832320</v>
+        <v>https://music.apple.com/us/artist/bunt/1436090348</v>
       </c>
       <c r="K41" t="str">
-        <v>https://music.apple.com/us/album/the-mandalorian-and-grogu-boys-noize-remix-from-star/1895653302</v>
+        <v>https://music.apple.com/us/album/trippin-opera-edit/1895863999</v>
       </c>
       <c r="L41" t="str">
-        <v>The Mandalorian and Grogu (Boys Noize Remix) [From "Star Wars: The Mandalorian and Grogu"] - Ludwig Göransson</v>
+        <v>TRIPPIN (Opera Edit) - BUNT.</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="str">
-        <v>Blow My Mind (CA7RIEL &amp; Paco Amoroso Version)</v>
+        <v>The Mandalorian and Grogu (Boys Noize Remix) [From "Star Wars: The Mandalorian and Grogu"]</v>
       </c>
       <c r="B42" t="str">
         <v/>
       </c>
       <c r="C42" t="str">
-        <v>https://music.apple.com/us/song/blow-my-mind-ca7riel-paco-amoroso-version/1894344140</v>
+        <v>https://music.apple.com/us/song/the-mandalorian-and-grogu-boys-noize-remix-from-star/6764131630</v>
       </c>
       <c r="D42" t="str">
         <v>2026-05-06</v>
@@ -1971,36 +1971,36 @@
         <v/>
       </c>
       <c r="F42" t="str">
-        <v>Blow My Mind (CA7RIEL &amp; Paco Amoroso Version) - Single</v>
+        <v>The Mandalorian and Grogu (Boys Noize Remix) [From "Star Wars: The Mandalorian and Grogu"] - Single</v>
       </c>
       <c r="G42" t="str">
-        <v>2:49</v>
+        <v>5:54</v>
       </c>
       <c r="H42" t="str">
-        <v>Robyn</v>
+        <v>Ludwig Göransson</v>
       </c>
       <c r="I42" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J42" t="str">
-        <v>https://music.apple.com/us/artist/robyn/535211</v>
+        <v>https://music.apple.com/us/artist/ludwig-g%C3%B6ransson/391832320</v>
       </c>
       <c r="K42" t="str">
-        <v>https://music.apple.com/us/album/blow-my-mind-ca7riel-paco-amoroso-version/1894344139</v>
+        <v>https://music.apple.com/us/album/the-mandalorian-and-grogu-boys-noize-remix-from-star/1895653302</v>
       </c>
       <c r="L42" t="str">
-        <v>Blow My Mind (CA7RIEL &amp; Paco Amoroso Version) - Robyn</v>
+        <v>The Mandalorian and Grogu (Boys Noize Remix) [From "Star Wars: The Mandalorian and Grogu"] - Ludwig Göransson</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="str">
-        <v>Bring That Body</v>
+        <v>Blow My Mind (CA7RIEL &amp; Paco Amoroso Version)</v>
       </c>
       <c r="B43" t="str">
         <v/>
       </c>
       <c r="C43" t="str">
-        <v>https://music.apple.com/us/song/bring-that-body/6764009310</v>
+        <v>https://music.apple.com/us/song/blow-my-mind-ca7riel-paco-amoroso-version/1894344140</v>
       </c>
       <c r="D43" t="str">
         <v>2026-05-06</v>
@@ -2009,36 +2009,36 @@
         <v/>
       </c>
       <c r="F43" t="str">
-        <v>Bring That Body - Single</v>
+        <v>Blow My Mind (CA7RIEL &amp; Paco Amoroso Version) - Single</v>
       </c>
       <c r="G43" t="str">
-        <v>3:34</v>
+        <v>2:49</v>
       </c>
       <c r="H43" t="str">
-        <v>The-Dream</v>
+        <v>Robyn</v>
       </c>
       <c r="I43" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J43" t="str">
-        <v>https://music.apple.com/us/artist/the-dream/259369321</v>
+        <v>https://music.apple.com/us/artist/robyn/535211</v>
       </c>
       <c r="K43" t="str">
-        <v>https://music.apple.com/us/album/bring-that-body/1895596731</v>
+        <v>https://music.apple.com/us/album/blow-my-mind-ca7riel-paco-amoroso-version/1894344139</v>
       </c>
       <c r="L43" t="str">
-        <v>Bring That Body - The-Dream</v>
+        <v>Blow My Mind (CA7RIEL &amp; Paco Amoroso Version) - Robyn</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="str">
-        <v>STAR</v>
+        <v>Bring That Body</v>
       </c>
       <c r="B44" t="str">
         <v/>
       </c>
       <c r="C44" t="str">
-        <v>https://music.apple.com/us/song/star/1891845608</v>
+        <v>https://music.apple.com/us/song/bring-that-body/6764009310</v>
       </c>
       <c r="D44" t="str">
         <v>2026-05-06</v>
@@ -2047,36 +2047,36 @@
         <v/>
       </c>
       <c r="F44" t="str">
-        <v>STAR</v>
+        <v>Bring That Body - Single</v>
       </c>
       <c r="G44" t="str">
-        <v>2:49</v>
+        <v>3:34</v>
       </c>
       <c r="H44" t="str">
-        <v>Tombochio</v>
+        <v>The-Dream</v>
       </c>
       <c r="I44" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J44" t="str">
-        <v>https://music.apple.com/us/artist/tombochio/1570164065</v>
+        <v>https://music.apple.com/us/artist/the-dream/259369321</v>
       </c>
       <c r="K44" t="str">
-        <v>https://music.apple.com/us/album/star/1891845604</v>
+        <v>https://music.apple.com/us/album/bring-that-body/1895596731</v>
       </c>
       <c r="L44" t="str">
-        <v>STAR - Tombochio</v>
+        <v>Bring That Body - The-Dream</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="str">
-        <v>What’s A Little Rain</v>
+        <v>STAR</v>
       </c>
       <c r="B45" t="str">
         <v/>
       </c>
       <c r="C45" t="str">
-        <v>https://music.apple.com/us/song/whats-a-little-rain/1885061171</v>
+        <v>https://music.apple.com/us/song/star/1891845608</v>
       </c>
       <c r="D45" t="str">
         <v>2026-05-06</v>
@@ -2085,36 +2085,36 @@
         <v/>
       </c>
       <c r="F45" t="str">
-        <v>Deep Blue</v>
+        <v>STAR</v>
       </c>
       <c r="G45" t="str">
-        <v>3:37</v>
+        <v>2:49</v>
       </c>
       <c r="H45" t="str">
-        <v>ERNEST</v>
+        <v>Tombochio</v>
       </c>
       <c r="I45" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J45" t="str">
-        <v>https://music.apple.com/us/artist/ernest/1450042443</v>
+        <v>https://music.apple.com/us/artist/tombochio/1570164065</v>
       </c>
       <c r="K45" t="str">
-        <v>https://music.apple.com/us/album/whats-a-little-rain/1885061168</v>
+        <v>https://music.apple.com/us/album/star/1891845604</v>
       </c>
       <c r="L45" t="str">
-        <v>What’s A Little Rain - ERNEST</v>
+        <v>STAR - Tombochio</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="str">
-        <v>Evergreen</v>
+        <v>What’s A Little Rain</v>
       </c>
       <c r="B46" t="str">
         <v/>
       </c>
       <c r="C46" t="str">
-        <v>https://music.apple.com/us/song/evergreen/1866700315</v>
+        <v>https://music.apple.com/us/song/whats-a-little-rain/1885061171</v>
       </c>
       <c r="D46" t="str">
         <v>2026-05-06</v>
@@ -2123,36 +2123,36 @@
         <v/>
       </c>
       <c r="F46" t="str">
-        <v>Victory Garden</v>
+        <v>Deep Blue</v>
       </c>
       <c r="G46" t="str">
-        <v>3:41</v>
+        <v>3:37</v>
       </c>
       <c r="H46" t="str">
-        <v>Young the Giant</v>
+        <v>ERNEST</v>
       </c>
       <c r="I46" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J46" t="str">
-        <v>https://music.apple.com/us/artist/young-the-giant/394582977</v>
+        <v>https://music.apple.com/us/artist/ernest/1450042443</v>
       </c>
       <c r="K46" t="str">
-        <v>https://music.apple.com/us/album/evergreen/1866700309</v>
+        <v>https://music.apple.com/us/album/whats-a-little-rain/1885061168</v>
       </c>
       <c r="L46" t="str">
-        <v>Evergreen - Young the Giant</v>
+        <v>What’s A Little Rain - ERNEST</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="str">
-        <v>She Does It Right</v>
+        <v>Evergreen</v>
       </c>
       <c r="B47" t="str">
         <v/>
       </c>
       <c r="C47" t="str">
-        <v>https://music.apple.com/us/song/she-does-it-right/1873477957</v>
+        <v>https://music.apple.com/us/song/evergreen/1866700315</v>
       </c>
       <c r="D47" t="str">
         <v>2026-05-06</v>
@@ -2161,36 +2161,36 @@
         <v/>
       </c>
       <c r="F47" t="str">
-        <v>Peaches!</v>
+        <v>Victory Garden</v>
       </c>
       <c r="G47" t="str">
-        <v>3:43</v>
+        <v>3:41</v>
       </c>
       <c r="H47" t="str">
-        <v>The Black Keys</v>
+        <v>Young the Giant</v>
       </c>
       <c r="I47" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J47" t="str">
-        <v>https://music.apple.com/us/artist/the-black-keys/5893059</v>
+        <v>https://music.apple.com/us/artist/young-the-giant/394582977</v>
       </c>
       <c r="K47" t="str">
-        <v>https://music.apple.com/us/album/she-does-it-right/1873477948</v>
+        <v>https://music.apple.com/us/album/evergreen/1866700309</v>
       </c>
       <c r="L47" t="str">
-        <v>She Does It Right - The Black Keys</v>
+        <v>Evergreen - Young the Giant</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="str">
-        <v>Punching the Flowers</v>
+        <v>She Does It Right</v>
       </c>
       <c r="B48" t="str">
         <v/>
       </c>
       <c r="C48" t="str">
-        <v>https://music.apple.com/us/song/punching-the-flowers/1878362636</v>
+        <v>https://music.apple.com/us/song/she-does-it-right/1873477957</v>
       </c>
       <c r="D48" t="str">
         <v>2026-05-06</v>
@@ -2199,36 +2199,36 @@
         <v/>
       </c>
       <c r="F48" t="str">
-        <v>I Built You A Tower</v>
+        <v>Peaches!</v>
       </c>
       <c r="G48" t="str">
-        <v>3:11</v>
+        <v>3:43</v>
       </c>
       <c r="H48" t="str">
-        <v>Death Cab for Cutie</v>
+        <v>The Black Keys</v>
       </c>
       <c r="I48" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J48" t="str">
-        <v>https://music.apple.com/us/artist/death-cab-for-cutie/5448636</v>
+        <v>https://music.apple.com/us/artist/the-black-keys/5893059</v>
       </c>
       <c r="K48" t="str">
-        <v>https://music.apple.com/us/album/punching-the-flowers/1878362451</v>
+        <v>https://music.apple.com/us/album/she-does-it-right/1873477948</v>
       </c>
       <c r="L48" t="str">
-        <v>Punching the Flowers - Death Cab for Cutie</v>
+        <v>She Does It Right - The Black Keys</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="str">
-        <v>How Did You Know</v>
+        <v>Punching the Flowers</v>
       </c>
       <c r="B49" t="str">
         <v/>
       </c>
       <c r="C49" t="str">
-        <v>https://music.apple.com/us/song/how-did-you-know/1888553137</v>
+        <v>https://music.apple.com/us/song/punching-the-flowers/1878362636</v>
       </c>
       <c r="D49" t="str">
         <v>2026-05-06</v>
@@ -2237,36 +2237,36 @@
         <v/>
       </c>
       <c r="F49" t="str">
-        <v>California Sunrise (10th Anniversary Edition)</v>
+        <v>I Built You A Tower</v>
       </c>
       <c r="G49" t="str">
-        <v>3:16</v>
+        <v>3:11</v>
       </c>
       <c r="H49" t="str">
-        <v>Jon Pardi</v>
+        <v>Death Cab for Cutie</v>
       </c>
       <c r="I49" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J49" t="str">
-        <v>https://music.apple.com/us/artist/jon-pardi/371085834</v>
+        <v>https://music.apple.com/us/artist/death-cab-for-cutie/5448636</v>
       </c>
       <c r="K49" t="str">
-        <v>https://music.apple.com/us/album/how-did-you-know/1888552935</v>
+        <v>https://music.apple.com/us/album/punching-the-flowers/1878362451</v>
       </c>
       <c r="L49" t="str">
-        <v>How Did You Know - Jon Pardi</v>
+        <v>Punching the Flowers - Death Cab for Cutie</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="str">
-        <v>Summer Breeze</v>
+        <v>How Did You Know</v>
       </c>
       <c r="B50" t="str">
         <v/>
       </c>
       <c r="C50" t="str">
-        <v>https://music.apple.com/us/song/summer-breeze/6763360727</v>
+        <v>https://music.apple.com/us/song/how-did-you-know/1888553137</v>
       </c>
       <c r="D50" t="str">
         <v>2026-05-06</v>
@@ -2275,36 +2275,36 @@
         <v/>
       </c>
       <c r="F50" t="str">
-        <v>flow state</v>
+        <v>California Sunrise (10th Anniversary Edition)</v>
       </c>
       <c r="G50" t="str">
-        <v>4:00</v>
+        <v>3:16</v>
       </c>
       <c r="H50" t="str">
-        <v>Keith Urban</v>
+        <v>Jon Pardi</v>
       </c>
       <c r="I50" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J50" t="str">
-        <v>https://music.apple.com/us/artist/keith-urban/549836</v>
+        <v>https://music.apple.com/us/artist/jon-pardi/371085834</v>
       </c>
       <c r="K50" t="str">
-        <v>https://music.apple.com/us/album/summer-breeze/1895279513</v>
+        <v>https://music.apple.com/us/album/how-did-you-know/1888552935</v>
       </c>
       <c r="L50" t="str">
-        <v>Summer Breeze - Keith Urban</v>
+        <v>How Did You Know - Jon Pardi</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="str">
-        <v>Sound of a Woman</v>
+        <v>Summer Breeze</v>
       </c>
       <c r="B51" t="str">
         <v/>
       </c>
       <c r="C51" t="str">
-        <v>https://music.apple.com/us/song/sound-of-a-woman/1859763367</v>
+        <v>https://music.apple.com/us/song/summer-breeze/6763360727</v>
       </c>
       <c r="D51" t="str">
         <v>2026-05-06</v>
@@ -2313,36 +2313,36 @@
         <v/>
       </c>
       <c r="F51" t="str">
-        <v>Sound of a Woman</v>
+        <v>flow state</v>
       </c>
       <c r="G51" t="str">
-        <v>4:27</v>
+        <v>4:00</v>
       </c>
       <c r="H51" t="str">
-        <v>Rita Wilson</v>
+        <v>Keith Urban</v>
       </c>
       <c r="I51" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J51" t="str">
-        <v>https://music.apple.com/us/artist/rita-wilson/270048575</v>
+        <v>https://music.apple.com/us/artist/keith-urban/549836</v>
       </c>
       <c r="K51" t="str">
-        <v>https://music.apple.com/us/album/sound-of-a-woman/1859763034</v>
+        <v>https://music.apple.com/us/album/summer-breeze/1895279513</v>
       </c>
       <c r="L51" t="str">
-        <v>Sound of a Woman - Rita Wilson</v>
+        <v>Summer Breeze - Keith Urban</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="str">
-        <v>My Life</v>
+        <v>Sound of a Woman</v>
       </c>
       <c r="B52" t="str">
         <v/>
       </c>
       <c r="C52" t="str">
-        <v>https://music.apple.com/us/song/my-life/1893157347</v>
+        <v>https://music.apple.com/us/song/sound-of-a-woman/1859763367</v>
       </c>
       <c r="D52" t="str">
         <v>2026-05-06</v>
@@ -2351,36 +2351,36 @@
         <v/>
       </c>
       <c r="F52" t="str">
-        <v>BERNARR.</v>
+        <v>Sound of a Woman</v>
       </c>
       <c r="G52" t="str">
-        <v>3:31</v>
+        <v>4:27</v>
       </c>
       <c r="H52" t="str">
-        <v>Durand Bernarr</v>
+        <v>Rita Wilson</v>
       </c>
       <c r="I52" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J52" t="str">
-        <v>https://music.apple.com/us/artist/durand-bernarr/584124023</v>
+        <v>https://music.apple.com/us/artist/rita-wilson/270048575</v>
       </c>
       <c r="K52" t="str">
-        <v>https://music.apple.com/us/album/my-life/1893156957</v>
+        <v>https://music.apple.com/us/album/sound-of-a-woman/1859763034</v>
       </c>
       <c r="L52" t="str">
-        <v>My Life - Durand Bernarr</v>
+        <v>Sound of a Woman - Rita Wilson</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="str">
-        <v>Ribcage</v>
+        <v>My Life</v>
       </c>
       <c r="B53" t="str">
         <v/>
       </c>
       <c r="C53" t="str">
-        <v>https://music.apple.com/us/song/ribcage/1893155593</v>
+        <v>https://music.apple.com/us/song/my-life/1893157347</v>
       </c>
       <c r="D53" t="str">
         <v>2026-05-06</v>
@@ -2389,36 +2389,36 @@
         <v/>
       </c>
       <c r="F53" t="str">
-        <v>Ribcage - Single</v>
+        <v>BERNARR.</v>
       </c>
       <c r="G53" t="str">
-        <v>3:00</v>
+        <v>3:31</v>
       </c>
       <c r="H53" t="str">
-        <v>Bella Poarch</v>
+        <v>Durand Bernarr</v>
       </c>
       <c r="I53" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J53" t="str">
-        <v>https://music.apple.com/us/artist/bella-poarch/1567245769</v>
+        <v>https://music.apple.com/us/artist/durand-bernarr/584124023</v>
       </c>
       <c r="K53" t="str">
-        <v>https://music.apple.com/us/album/ribcage/1893155591</v>
+        <v>https://music.apple.com/us/album/my-life/1893156957</v>
       </c>
       <c r="L53" t="str">
-        <v>Ribcage - Bella Poarch</v>
+        <v>My Life - Durand Bernarr</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="str">
-        <v>i loved you then</v>
+        <v>Ribcage</v>
       </c>
       <c r="B54" t="str">
         <v/>
       </c>
       <c r="C54" t="str">
-        <v>https://music.apple.com/us/song/i-loved-you-then/1878232821</v>
+        <v>https://music.apple.com/us/song/ribcage/1893155593</v>
       </c>
       <c r="D54" t="str">
         <v>2026-05-06</v>
@@ -2427,36 +2427,36 @@
         <v/>
       </c>
       <c r="F54" t="str">
-        <v>I HOPE THIS HELPS</v>
+        <v>Ribcage - Single</v>
       </c>
       <c r="G54" t="str">
-        <v>3:42</v>
+        <v>3:00</v>
       </c>
       <c r="H54" t="str">
-        <v>Alana Springsteen</v>
+        <v>Bella Poarch</v>
       </c>
       <c r="I54" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J54" t="str">
-        <v>https://music.apple.com/us/artist/alana-springsteen/1309335606</v>
+        <v>https://music.apple.com/us/artist/bella-poarch/1567245769</v>
       </c>
       <c r="K54" t="str">
-        <v>https://music.apple.com/us/album/i-loved-you-then/1878232194</v>
+        <v>https://music.apple.com/us/album/ribcage/1893155591</v>
       </c>
       <c r="L54" t="str">
-        <v>i loved you then - Alana Springsteen</v>
+        <v>Ribcage - Bella Poarch</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="str">
-        <v>I'll Let You Finish</v>
+        <v>i loved you then</v>
       </c>
       <c r="B55" t="str">
         <v/>
       </c>
       <c r="C55" t="str">
-        <v>https://music.apple.com/us/song/ill-let-you-finish/1891844342</v>
+        <v>https://music.apple.com/us/song/i-loved-you-then/1878232821</v>
       </c>
       <c r="D55" t="str">
         <v>2026-05-06</v>
@@ -2465,36 +2465,36 @@
         <v/>
       </c>
       <c r="F55" t="str">
-        <v>Fire From The Hip</v>
+        <v>I HOPE THIS HELPS</v>
       </c>
       <c r="G55" t="str">
-        <v>3:54</v>
+        <v>3:42</v>
       </c>
       <c r="H55" t="str">
-        <v>Finn Wolfhard</v>
+        <v>Alana Springsteen</v>
       </c>
       <c r="I55" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J55" t="str">
-        <v>https://music.apple.com/us/artist/finn-wolfhard/1275324142</v>
+        <v>https://music.apple.com/us/artist/alana-springsteen/1309335606</v>
       </c>
       <c r="K55" t="str">
-        <v>https://music.apple.com/us/album/ill-let-you-finish/1891844033</v>
+        <v>https://music.apple.com/us/album/i-loved-you-then/1878232194</v>
       </c>
       <c r="L55" t="str">
-        <v>I'll Let You Finish - Finn Wolfhard</v>
+        <v>i loved you then - Alana Springsteen</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="str">
-        <v>It Gets Me Through</v>
+        <v>I'll Let You Finish</v>
       </c>
       <c r="B56" t="str">
         <v/>
       </c>
       <c r="C56" t="str">
-        <v>https://music.apple.com/us/song/it-gets-me-through/1884798927</v>
+        <v>https://music.apple.com/us/song/ill-let-you-finish/1891844342</v>
       </c>
       <c r="D56" t="str">
         <v>2026-05-06</v>
@@ -2503,36 +2503,36 @@
         <v/>
       </c>
       <c r="F56" t="str">
-        <v>Original Sound (Original Motion Picture Soundtrack)</v>
+        <v>Fire From The Hip</v>
       </c>
       <c r="G56" t="str">
-        <v>2:53</v>
+        <v>3:54</v>
       </c>
       <c r="H56" t="str">
-        <v>Laura Marano</v>
+        <v>Finn Wolfhard</v>
       </c>
       <c r="I56" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J56" t="str">
-        <v>https://music.apple.com/us/artist/laura-marano/357181332</v>
+        <v>https://music.apple.com/us/artist/finn-wolfhard/1275324142</v>
       </c>
       <c r="K56" t="str">
-        <v>https://music.apple.com/us/album/it-gets-me-through/1884798598</v>
+        <v>https://music.apple.com/us/album/ill-let-you-finish/1891844033</v>
       </c>
       <c r="L56" t="str">
-        <v>It Gets Me Through - Laura Marano</v>
+        <v>I'll Let You Finish - Finn Wolfhard</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="str">
-        <v>The Author</v>
+        <v>It Gets Me Through</v>
       </c>
       <c r="B57" t="str">
         <v/>
       </c>
       <c r="C57" t="str">
-        <v>https://music.apple.com/us/song/the-author/6763327641</v>
+        <v>https://music.apple.com/us/song/it-gets-me-through/1884798927</v>
       </c>
       <c r="D57" t="str">
         <v>2026-05-06</v>
@@ -2541,36 +2541,36 @@
         <v/>
       </c>
       <c r="F57" t="str">
-        <v>The Author - Single</v>
+        <v>Original Sound (Original Motion Picture Soundtrack)</v>
       </c>
       <c r="G57" t="str">
-        <v>4:36</v>
+        <v>2:53</v>
       </c>
       <c r="H57" t="str">
-        <v>Brandon Lake</v>
+        <v>Laura Marano</v>
       </c>
       <c r="I57" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J57" t="str">
-        <v>https://music.apple.com/us/artist/brandon-lake/1050382282</v>
+        <v>https://music.apple.com/us/artist/laura-marano/357181332</v>
       </c>
       <c r="K57" t="str">
-        <v>https://music.apple.com/us/album/the-author/1895265952</v>
+        <v>https://music.apple.com/us/album/it-gets-me-through/1884798598</v>
       </c>
       <c r="L57" t="str">
-        <v>The Author - Brandon Lake</v>
+        <v>It Gets Me Through - Laura Marano</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="str">
-        <v>Want Me Back (feat. Tors)</v>
+        <v>The Author</v>
       </c>
       <c r="B58" t="str">
         <v/>
       </c>
       <c r="C58" t="str">
-        <v>https://music.apple.com/us/song/want-me-back-feat-tors/1889370756</v>
+        <v>https://music.apple.com/us/song/the-author/6763327641</v>
       </c>
       <c r="D58" t="str">
         <v>2026-05-06</v>
@@ -2579,36 +2579,36 @@
         <v/>
       </c>
       <c r="F58" t="str">
-        <v>Want Me Back (feat. Tors) - Single</v>
+        <v>The Author - Single</v>
       </c>
       <c r="G58" t="str">
-        <v>3:44</v>
+        <v>4:36</v>
       </c>
       <c r="H58" t="str">
-        <v>Trousdale</v>
+        <v>Brandon Lake</v>
       </c>
       <c r="I58" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J58" t="str">
-        <v>https://music.apple.com/us/artist/trousdale/1534241692</v>
+        <v>https://music.apple.com/us/artist/brandon-lake/1050382282</v>
       </c>
       <c r="K58" t="str">
-        <v>https://music.apple.com/us/album/want-me-back-feat-tors/1889370752</v>
+        <v>https://music.apple.com/us/album/the-author/1895265952</v>
       </c>
       <c r="L58" t="str">
-        <v>Want Me Back (feat. Tors) - Trousdale</v>
+        <v>The Author - Brandon Lake</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="str">
-        <v>RUIN</v>
+        <v>Want Me Back (feat. Tors)</v>
       </c>
       <c r="B59" t="str">
         <v/>
       </c>
       <c r="C59" t="str">
-        <v>https://music.apple.com/us/song/ruin/1886537117</v>
+        <v>https://music.apple.com/us/song/want-me-back-feat-tors/1889370756</v>
       </c>
       <c r="D59" t="str">
         <v>2026-05-06</v>
@@ -2617,36 +2617,36 @@
         <v/>
       </c>
       <c r="F59" t="str">
-        <v>ADDENDUM - EP</v>
+        <v>Want Me Back (feat. Tors) - Single</v>
       </c>
       <c r="G59" t="str">
-        <v>3:23</v>
+        <v>3:44</v>
       </c>
       <c r="H59" t="str">
-        <v>HEALTH</v>
+        <v>Trousdale</v>
       </c>
       <c r="I59" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J59" t="str">
-        <v>https://music.apple.com/us/artist/health/317478211</v>
+        <v>https://music.apple.com/us/artist/trousdale/1534241692</v>
       </c>
       <c r="K59" t="str">
-        <v>https://music.apple.com/us/album/ruin/1886536873</v>
+        <v>https://music.apple.com/us/album/want-me-back-feat-tors/1889370752</v>
       </c>
       <c r="L59" t="str">
-        <v>RUIN - HEALTH</v>
+        <v>Want Me Back (feat. Tors) - Trousdale</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="str">
-        <v>I Know I Know</v>
+        <v>RUIN</v>
       </c>
       <c r="B60" t="str">
         <v/>
       </c>
       <c r="C60" t="str">
-        <v>https://music.apple.com/us/song/i-know-i-know/1894354139</v>
+        <v>https://music.apple.com/us/song/ruin/1886537117</v>
       </c>
       <c r="D60" t="str">
         <v>2026-05-06</v>
@@ -2655,36 +2655,36 @@
         <v/>
       </c>
       <c r="F60" t="str">
-        <v>I Know I Know - Single</v>
+        <v>ADDENDUM - EP</v>
       </c>
       <c r="G60" t="str">
-        <v>2:39</v>
+        <v>3:23</v>
       </c>
       <c r="H60" t="str">
-        <v>STELLA LEFTY</v>
+        <v>HEALTH</v>
       </c>
       <c r="I60" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J60" t="str">
-        <v>https://music.apple.com/us/artist/stella-lefty/1641742186</v>
+        <v>https://music.apple.com/us/artist/health/317478211</v>
       </c>
       <c r="K60" t="str">
-        <v>https://music.apple.com/us/album/i-know-i-know/1894354136</v>
+        <v>https://music.apple.com/us/album/ruin/1886536873</v>
       </c>
       <c r="L60" t="str">
-        <v>I Know I Know - STELLA LEFTY</v>
+        <v>RUIN - HEALTH</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="str">
-        <v>Drive All Night</v>
+        <v>I Know I Know</v>
       </c>
       <c r="B61" t="str">
         <v/>
       </c>
       <c r="C61" t="str">
-        <v>https://music.apple.com/us/song/drive-all-night/6763189759</v>
+        <v>https://music.apple.com/us/song/i-know-i-know/1894354139</v>
       </c>
       <c r="D61" t="str">
         <v>2026-05-06</v>
@@ -2693,36 +2693,36 @@
         <v/>
       </c>
       <c r="F61" t="str">
-        <v>Drive All Night - Single</v>
+        <v>I Know I Know - Single</v>
       </c>
       <c r="G61" t="str">
-        <v>2:50</v>
+        <v>2:39</v>
       </c>
       <c r="H61" t="str">
-        <v>Wyatt Flores</v>
+        <v>STELLA LEFTY</v>
       </c>
       <c r="I61" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J61" t="str">
-        <v>https://music.apple.com/us/artist/wyatt-flores/1563146833</v>
+        <v>https://music.apple.com/us/artist/stella-lefty/1641742186</v>
       </c>
       <c r="K61" t="str">
-        <v>https://music.apple.com/us/album/drive-all-night/1895207255</v>
+        <v>https://music.apple.com/us/album/i-know-i-know/1894354136</v>
       </c>
       <c r="L61" t="str">
-        <v>Drive All Night - Wyatt Flores</v>
+        <v>I Know I Know - STELLA LEFTY</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="str">
-        <v>AIN'T U TIRED?</v>
+        <v>Drive All Night</v>
       </c>
       <c r="B62" t="str">
         <v/>
       </c>
       <c r="C62" t="str">
-        <v>https://music.apple.com/us/song/aint-u-tired/6763115235</v>
+        <v>https://music.apple.com/us/song/drive-all-night/6763189759</v>
       </c>
       <c r="D62" t="str">
         <v>2026-05-06</v>
@@ -2731,36 +2731,36 @@
         <v/>
       </c>
       <c r="F62" t="str">
-        <v>AIN'T U TIRED? - Single</v>
+        <v>Drive All Night - Single</v>
       </c>
       <c r="G62" t="str">
-        <v>3:41</v>
+        <v>2:50</v>
       </c>
       <c r="H62" t="str">
-        <v>Jessie Reyez</v>
+        <v>Wyatt Flores</v>
       </c>
       <c r="I62" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J62" t="str">
-        <v>https://music.apple.com/us/artist/jessie-reyez/1043591612</v>
+        <v>https://music.apple.com/us/artist/wyatt-flores/1563146833</v>
       </c>
       <c r="K62" t="str">
-        <v>https://music.apple.com/us/album/aint-u-tired/1895167276</v>
+        <v>https://music.apple.com/us/album/drive-all-night/1895207255</v>
       </c>
       <c r="L62" t="str">
-        <v>AIN'T U TIRED? - Jessie Reyez</v>
+        <v>Drive All Night - Wyatt Flores</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="str">
-        <v>Boys In Blue</v>
+        <v>AIN'T U TIRED?</v>
       </c>
       <c r="B63" t="str">
         <v/>
       </c>
       <c r="C63" t="str">
-        <v>https://music.apple.com/us/song/boys-in-blue/1892436920</v>
+        <v>https://music.apple.com/us/song/aint-u-tired/6763115235</v>
       </c>
       <c r="D63" t="str">
         <v>2026-05-06</v>
@@ -2769,36 +2769,36 @@
         <v/>
       </c>
       <c r="F63" t="str">
-        <v>Emotional Junglist</v>
+        <v>AIN'T U TIRED? - Single</v>
       </c>
       <c r="G63" t="str">
-        <v>2:33</v>
+        <v>3:41</v>
       </c>
       <c r="H63" t="str">
-        <v>Nia Archives</v>
+        <v>Jessie Reyez</v>
       </c>
       <c r="I63" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J63" t="str">
-        <v>https://music.apple.com/us/artist/nia-archives/1515978311</v>
+        <v>https://music.apple.com/us/artist/jessie-reyez/1043591612</v>
       </c>
       <c r="K63" t="str">
-        <v>https://music.apple.com/us/album/boys-in-blue/1892436329</v>
+        <v>https://music.apple.com/us/album/aint-u-tired/1895167276</v>
       </c>
       <c r="L63" t="str">
-        <v>Boys In Blue - Nia Archives</v>
+        <v>AIN'T U TIRED? - Jessie Reyez</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="str">
-        <v>Salma Hayek</v>
+        <v>Boys In Blue</v>
       </c>
       <c r="B64" t="str">
         <v/>
       </c>
       <c r="C64" t="str">
-        <v>https://music.apple.com/us/song/salma-hayek/1891815286</v>
+        <v>https://music.apple.com/us/song/boys-in-blue/1892436920</v>
       </c>
       <c r="D64" t="str">
         <v>2026-05-06</v>
@@ -2807,36 +2807,36 @@
         <v/>
       </c>
       <c r="F64" t="str">
-        <v>Salma Hayek - Single</v>
+        <v>Emotional Junglist</v>
       </c>
       <c r="G64" t="str">
-        <v>3:43</v>
+        <v>2:33</v>
       </c>
       <c r="H64" t="str">
-        <v>Luis R Conriquez</v>
+        <v>Nia Archives</v>
       </c>
       <c r="I64" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J64" t="str">
-        <v>https://music.apple.com/us/artist/luis-r-conriquez/1252271456</v>
+        <v>https://music.apple.com/us/artist/nia-archives/1515978311</v>
       </c>
       <c r="K64" t="str">
-        <v>https://music.apple.com/us/album/salma-hayek/1891815277</v>
+        <v>https://music.apple.com/us/album/boys-in-blue/1892436329</v>
       </c>
       <c r="L64" t="str">
-        <v>Salma Hayek - Luis R Conriquez</v>
+        <v>Boys In Blue - Nia Archives</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="str">
-        <v>Stubborn Mouth</v>
+        <v>Salma Hayek</v>
       </c>
       <c r="B65" t="str">
         <v/>
       </c>
       <c r="C65" t="str">
-        <v>https://music.apple.com/us/song/stubborn-mouth/1893194800</v>
+        <v>https://music.apple.com/us/song/salma-hayek/1891815286</v>
       </c>
       <c r="D65" t="str">
         <v>2026-05-06</v>
@@ -2845,36 +2845,36 @@
         <v/>
       </c>
       <c r="F65" t="str">
-        <v>Stubborn Mouth - Single</v>
+        <v>Salma Hayek - Single</v>
       </c>
       <c r="G65" t="str">
-        <v>3:02</v>
+        <v>3:43</v>
       </c>
       <c r="H65" t="str">
-        <v>Girl Tones</v>
+        <v>Luis R Conriquez</v>
       </c>
       <c r="I65" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J65" t="str">
-        <v>https://music.apple.com/us/artist/girl-tones/1761267584</v>
+        <v>https://music.apple.com/us/artist/luis-r-conriquez/1252271456</v>
       </c>
       <c r="K65" t="str">
-        <v>https://music.apple.com/us/album/stubborn-mouth/1893194649</v>
+        <v>https://music.apple.com/us/album/salma-hayek/1891815277</v>
       </c>
       <c r="L65" t="str">
-        <v>Stubborn Mouth - Girl Tones</v>
+        <v>Salma Hayek - Luis R Conriquez</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="str">
-        <v>Hallucination</v>
+        <v>Stubborn Mouth</v>
       </c>
       <c r="B66" t="str">
         <v/>
       </c>
       <c r="C66" t="str">
-        <v>https://music.apple.com/us/song/hallucination/6764110976</v>
+        <v>https://music.apple.com/us/song/stubborn-mouth/1893194800</v>
       </c>
       <c r="D66" t="str">
         <v>2026-05-06</v>
@@ -2883,36 +2883,36 @@
         <v/>
       </c>
       <c r="F66" t="str">
-        <v>Promising Young Woman - EP</v>
+        <v>Stubborn Mouth - Single</v>
       </c>
       <c r="G66" t="str">
-        <v>3:22</v>
+        <v>3:02</v>
       </c>
       <c r="H66" t="str">
-        <v>Isabel LaRosa</v>
+        <v>Girl Tones</v>
       </c>
       <c r="I66" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J66" t="str">
-        <v>https://music.apple.com/us/artist/isabel-larosa/1578296103</v>
+        <v>https://music.apple.com/us/artist/girl-tones/1761267584</v>
       </c>
       <c r="K66" t="str">
-        <v>https://music.apple.com/us/album/hallucination/1895644574</v>
+        <v>https://music.apple.com/us/album/stubborn-mouth/1893194649</v>
       </c>
       <c r="L66" t="str">
-        <v>Hallucination - Isabel LaRosa</v>
+        <v>Stubborn Mouth - Girl Tones</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="str">
-        <v>In Da Jungle</v>
+        <v>Hallucination</v>
       </c>
       <c r="B67" t="str">
         <v/>
       </c>
       <c r="C67" t="str">
-        <v>https://music.apple.com/us/song/in-da-jungle/1891136400</v>
+        <v>https://music.apple.com/us/song/hallucination/6764110976</v>
       </c>
       <c r="D67" t="str">
         <v>2026-05-06</v>
@@ -2921,36 +2921,36 @@
         <v/>
       </c>
       <c r="F67" t="str">
-        <v>In Da Jungle - Single</v>
+        <v>Promising Young Woman - EP</v>
       </c>
       <c r="G67" t="str">
-        <v>2:44</v>
+        <v>3:22</v>
       </c>
       <c r="H67" t="str">
-        <v>BLOND:ISH</v>
+        <v>Isabel LaRosa</v>
       </c>
       <c r="I67" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J67" t="str">
-        <v>https://music.apple.com/us/artist/blond-ish/394776491</v>
+        <v>https://music.apple.com/us/artist/isabel-larosa/1578296103</v>
       </c>
       <c r="K67" t="str">
-        <v>https://music.apple.com/us/album/in-da-jungle/1891136398</v>
+        <v>https://music.apple.com/us/album/hallucination/1895644574</v>
       </c>
       <c r="L67" t="str">
-        <v>In Da Jungle - BLOND:ISH</v>
+        <v>Hallucination - Isabel LaRosa</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="str">
-        <v>Fall Short</v>
+        <v>In Da Jungle</v>
       </c>
       <c r="B68" t="str">
         <v/>
       </c>
       <c r="C68" t="str">
-        <v>https://music.apple.com/us/song/fall-short/1894662749</v>
+        <v>https://music.apple.com/us/song/in-da-jungle/1891136400</v>
       </c>
       <c r="D68" t="str">
         <v>2026-05-06</v>
@@ -2959,36 +2959,36 @@
         <v/>
       </c>
       <c r="F68" t="str">
-        <v>Fall Short - Single</v>
+        <v>In Da Jungle - Single</v>
       </c>
       <c r="G68" t="str">
         <v>2:44</v>
       </c>
       <c r="H68" t="str">
-        <v>nyan</v>
+        <v>BLOND:ISH</v>
       </c>
       <c r="I68" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J68" t="str">
-        <v>https://music.apple.com/us/artist/nyan/1478138732</v>
+        <v>https://music.apple.com/us/artist/blond-ish/394776491</v>
       </c>
       <c r="K68" t="str">
-        <v>https://music.apple.com/us/album/fall-short/1894662748</v>
+        <v>https://music.apple.com/us/album/in-da-jungle/1891136398</v>
       </c>
       <c r="L68" t="str">
-        <v>Fall Short - nyan</v>
+        <v>In Da Jungle - BLOND:ISH</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="str">
-        <v>Irish Goodbye (feat. Kae Tempest)</v>
+        <v>Fall Short</v>
       </c>
       <c r="B69" t="str">
         <v/>
       </c>
       <c r="C69" t="str">
-        <v>https://music.apple.com/us/song/irish-goodbye-feat-kae-tempest/1862224205</v>
+        <v>https://music.apple.com/us/song/fall-short/1894662749</v>
       </c>
       <c r="D69" t="str">
         <v>2026-05-06</v>
@@ -2997,36 +2997,36 @@
         <v/>
       </c>
       <c r="F69" t="str">
-        <v>FENIAN</v>
+        <v>Fall Short - Single</v>
       </c>
       <c r="G69" t="str">
-        <v>3:34</v>
+        <v>2:44</v>
       </c>
       <c r="H69" t="str">
-        <v>Kneecap</v>
+        <v>nyan</v>
       </c>
       <c r="I69" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J69" t="str">
-        <v>https://music.apple.com/us/artist/kneecap/1330315811</v>
+        <v>https://music.apple.com/us/artist/nyan/1478138732</v>
       </c>
       <c r="K69" t="str">
-        <v>https://music.apple.com/us/album/irish-goodbye-feat-kae-tempest/1862223497</v>
+        <v>https://music.apple.com/us/album/fall-short/1894662748</v>
       </c>
       <c r="L69" t="str">
-        <v>Irish Goodbye (feat. Kae Tempest) - Kneecap</v>
+        <v>Fall Short - nyan</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="str">
-        <v>1989</v>
+        <v>Irish Goodbye (feat. Kae Tempest)</v>
       </c>
       <c r="B70" t="str">
         <v/>
       </c>
       <c r="C70" t="str">
-        <v>https://music.apple.com/us/song/1989/1893089382</v>
+        <v>https://music.apple.com/us/song/irish-goodbye-feat-kae-tempest/1862224205</v>
       </c>
       <c r="D70" t="str">
         <v>2026-05-06</v>
@@ -3035,36 +3035,36 @@
         <v/>
       </c>
       <c r="F70" t="str">
-        <v>1989 - Single</v>
+        <v>FENIAN</v>
       </c>
       <c r="G70" t="str">
-        <v>3:05</v>
+        <v>3:34</v>
       </c>
       <c r="H70" t="str">
-        <v>Nightly</v>
+        <v>Kneecap</v>
       </c>
       <c r="I70" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J70" t="str">
-        <v>https://music.apple.com/us/artist/nightly/352310972</v>
+        <v>https://music.apple.com/us/artist/kneecap/1330315811</v>
       </c>
       <c r="K70" t="str">
-        <v>https://music.apple.com/us/album/1989/1893089381</v>
+        <v>https://music.apple.com/us/album/irish-goodbye-feat-kae-tempest/1862223497</v>
       </c>
       <c r="L70" t="str">
-        <v>1989 - Nightly</v>
+        <v>Irish Goodbye (feat. Kae Tempest) - Kneecap</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="str">
-        <v>no more regrets</v>
+        <v>1989</v>
       </c>
       <c r="B71" t="str">
         <v/>
       </c>
       <c r="C71" t="str">
-        <v>https://music.apple.com/us/song/no-more-regrets/1893191803</v>
+        <v>https://music.apple.com/us/song/1989/1893089382</v>
       </c>
       <c r="D71" t="str">
         <v>2026-05-06</v>
@@ -3073,36 +3073,36 @@
         <v/>
       </c>
       <c r="F71" t="str">
-        <v>no more regrets - Single</v>
+        <v>1989 - Single</v>
       </c>
       <c r="G71" t="str">
-        <v>2:58</v>
+        <v>3:05</v>
       </c>
       <c r="H71" t="str">
-        <v>almost monday</v>
+        <v>Nightly</v>
       </c>
       <c r="I71" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J71" t="str">
-        <v>https://music.apple.com/us/artist/almost-monday/1300723925</v>
+        <v>https://music.apple.com/us/artist/nightly/352310972</v>
       </c>
       <c r="K71" t="str">
-        <v>https://music.apple.com/us/album/no-more-regrets/1893191802</v>
+        <v>https://music.apple.com/us/album/1989/1893089381</v>
       </c>
       <c r="L71" t="str">
-        <v>no more regrets - almost monday</v>
+        <v>1989 - Nightly</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="str">
-        <v>Drum Machine</v>
+        <v>no more regrets</v>
       </c>
       <c r="B72" t="str">
         <v/>
       </c>
       <c r="C72" t="str">
-        <v>https://music.apple.com/us/song/drum-machine/1840517102</v>
+        <v>https://music.apple.com/us/song/no-more-regrets/1893191803</v>
       </c>
       <c r="D72" t="str">
         <v>2026-05-06</v>
@@ -3111,36 +3111,36 @@
         <v/>
       </c>
       <c r="F72" t="str">
-        <v>Sweat</v>
+        <v>no more regrets - Single</v>
       </c>
       <c r="G72" t="str">
-        <v>3:16</v>
+        <v>2:58</v>
       </c>
       <c r="H72" t="str">
-        <v>Melanie C</v>
+        <v>almost monday</v>
       </c>
       <c r="I72" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J72" t="str">
-        <v>https://music.apple.com/us/artist/melanie-c/653819</v>
+        <v>https://music.apple.com/us/artist/almost-monday/1300723925</v>
       </c>
       <c r="K72" t="str">
-        <v>https://music.apple.com/us/album/drum-machine/1840516706</v>
+        <v>https://music.apple.com/us/album/no-more-regrets/1893191802</v>
       </c>
       <c r="L72" t="str">
-        <v>Drum Machine - Melanie C</v>
+        <v>no more regrets - almost monday</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="str">
-        <v>I'm Perfect</v>
+        <v>Drum Machine</v>
       </c>
       <c r="B73" t="str">
         <v/>
       </c>
       <c r="C73" t="str">
-        <v>https://music.apple.com/us/song/im-perfect/1893181359</v>
+        <v>https://music.apple.com/us/song/drum-machine/1840517102</v>
       </c>
       <c r="D73" t="str">
         <v>2026-05-06</v>
@@ -3149,36 +3149,36 @@
         <v/>
       </c>
       <c r="F73" t="str">
-        <v>I'm Perfect - Single</v>
+        <v>Sweat</v>
       </c>
       <c r="G73" t="str">
-        <v>2:36</v>
+        <v>3:16</v>
       </c>
       <c r="H73" t="str">
-        <v>Olivia O'Brien</v>
+        <v>Melanie C</v>
       </c>
       <c r="I73" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J73" t="str">
-        <v>https://music.apple.com/us/artist/olivia-obrien/1023538468</v>
+        <v>https://music.apple.com/us/artist/melanie-c/653819</v>
       </c>
       <c r="K73" t="str">
-        <v>https://music.apple.com/us/album/im-perfect/1893181351</v>
+        <v>https://music.apple.com/us/album/drum-machine/1840516706</v>
       </c>
       <c r="L73" t="str">
-        <v>I'm Perfect - Olivia O'Brien</v>
+        <v>Drum Machine - Melanie C</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="str">
-        <v>Theme for a Train Journey</v>
+        <v>I'm Perfect</v>
       </c>
       <c r="B74" t="str">
         <v/>
       </c>
       <c r="C74" t="str">
-        <v>https://music.apple.com/us/song/theme-for-a-train-journey/1880699785</v>
+        <v>https://music.apple.com/us/song/im-perfect/1893181359</v>
       </c>
       <c r="D74" t="str">
         <v>2026-05-06</v>
@@ -3187,36 +3187,36 @@
         <v/>
       </c>
       <c r="F74" t="str">
-        <v>AK Cuts: Vol 3 - EP</v>
+        <v>I'm Perfect - Single</v>
       </c>
       <c r="G74" t="str">
-        <v>5:05</v>
+        <v>2:36</v>
       </c>
       <c r="H74" t="str">
-        <v>Anish Kumar</v>
+        <v>Olivia O'Brien</v>
       </c>
       <c r="I74" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J74" t="str">
-        <v>https://music.apple.com/us/artist/anish-kumar/1510744726</v>
+        <v>https://music.apple.com/us/artist/olivia-obrien/1023538468</v>
       </c>
       <c r="K74" t="str">
-        <v>https://music.apple.com/us/album/theme-for-a-train-journey/1880699566</v>
+        <v>https://music.apple.com/us/album/im-perfect/1893181351</v>
       </c>
       <c r="L74" t="str">
-        <v>Theme for a Train Journey - Anish Kumar</v>
+        <v>I'm Perfect - Olivia O'Brien</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="str">
-        <v>Bitch You Weird</v>
+        <v>Theme for a Train Journey</v>
       </c>
       <c r="B75" t="str">
         <v/>
       </c>
       <c r="C75" t="str">
-        <v>https://music.apple.com/us/song/bitch-you-weird/6763395875</v>
+        <v>https://music.apple.com/us/song/theme-for-a-train-journey/1880699785</v>
       </c>
       <c r="D75" t="str">
         <v>2026-05-06</v>
@@ -3225,36 +3225,36 @@
         <v/>
       </c>
       <c r="F75" t="str">
-        <v>Bitch You Weird - Single</v>
+        <v>AK Cuts: Vol 3 - EP</v>
       </c>
       <c r="G75" t="str">
-        <v>2:27</v>
+        <v>5:05</v>
       </c>
       <c r="H75" t="str">
-        <v>Real Boston Richey</v>
+        <v>Anish Kumar</v>
       </c>
       <c r="I75" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J75" t="str">
-        <v>https://music.apple.com/us/artist/real-boston-richey/1595496755</v>
+        <v>https://music.apple.com/us/artist/anish-kumar/1510744726</v>
       </c>
       <c r="K75" t="str">
-        <v>https://music.apple.com/us/album/bitch-you-weird/1895294715</v>
+        <v>https://music.apple.com/us/album/theme-for-a-train-journey/1880699566</v>
       </c>
       <c r="L75" t="str">
-        <v>Bitch You Weird - Real Boston Richey</v>
+        <v>Theme for a Train Journey - Anish Kumar</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="str">
-        <v>Blackbird Rising</v>
+        <v>Bitch You Weird</v>
       </c>
       <c r="B76" t="str">
         <v/>
       </c>
       <c r="C76" t="str">
-        <v>https://music.apple.com/us/song/blackbird-rising/1887166611</v>
+        <v>https://music.apple.com/us/song/bitch-you-weird/6763395875</v>
       </c>
       <c r="D76" t="str">
         <v>2026-05-06</v>
@@ -3263,36 +3263,36 @@
         <v/>
       </c>
       <c r="F76" t="str">
-        <v>24</v>
+        <v>Bitch You Weird - Single</v>
       </c>
       <c r="G76" t="str">
-        <v>2:24</v>
+        <v>2:27</v>
       </c>
       <c r="H76" t="str">
-        <v>Alexis Ffrench</v>
+        <v>Real Boston Richey</v>
       </c>
       <c r="I76" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J76" t="str">
-        <v>https://music.apple.com/us/artist/alexis-ffrench/342515428</v>
+        <v>https://music.apple.com/us/artist/real-boston-richey/1595496755</v>
       </c>
       <c r="K76" t="str">
-        <v>https://music.apple.com/us/album/blackbird-rising/1887166427</v>
+        <v>https://music.apple.com/us/album/bitch-you-weird/1895294715</v>
       </c>
       <c r="L76" t="str">
-        <v>Blackbird Rising - Alexis Ffrench</v>
+        <v>Bitch You Weird - Real Boston Richey</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="str">
-        <v>usher in the spirit</v>
+        <v>Blackbird Rising</v>
       </c>
       <c r="B77" t="str">
         <v/>
       </c>
       <c r="C77" t="str">
-        <v>https://music.apple.com/us/song/usher-in-the-spirit/6763373678</v>
+        <v>https://music.apple.com/us/song/blackbird-rising/1887166611</v>
       </c>
       <c r="D77" t="str">
         <v>2026-05-06</v>
@@ -3301,36 +3301,36 @@
         <v/>
       </c>
       <c r="F77" t="str">
-        <v>usher in the spirit - Single</v>
+        <v>24</v>
       </c>
       <c r="G77" t="str">
-        <v>3:00</v>
+        <v>2:24</v>
       </c>
       <c r="H77" t="str">
-        <v>Aaron Cole</v>
+        <v>Alexis Ffrench</v>
       </c>
       <c r="I77" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J77" t="str">
-        <v>https://music.apple.com/us/artist/aaron-cole/507522696</v>
+        <v>https://music.apple.com/us/artist/alexis-ffrench/342515428</v>
       </c>
       <c r="K77" t="str">
-        <v>https://music.apple.com/us/album/usher-in-the-spirit/1895286256</v>
+        <v>https://music.apple.com/us/album/blackbird-rising/1887166427</v>
       </c>
       <c r="L77" t="str">
-        <v>usher in the spirit - Aaron Cole</v>
+        <v>Blackbird Rising - Alexis Ffrench</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="str">
-        <v>Moonlight</v>
+        <v>usher in the spirit</v>
       </c>
       <c r="B78" t="str">
         <v/>
       </c>
       <c r="C78" t="str">
-        <v>https://music.apple.com/us/song/moonlight/1892950791</v>
+        <v>https://music.apple.com/us/song/usher-in-the-spirit/6763373678</v>
       </c>
       <c r="D78" t="str">
         <v>2026-05-06</v>
@@ -3339,36 +3339,36 @@
         <v/>
       </c>
       <c r="F78" t="str">
-        <v>Moonlight - Single</v>
+        <v>usher in the spirit - Single</v>
       </c>
       <c r="G78" t="str">
-        <v>3:23</v>
+        <v>3:00</v>
       </c>
       <c r="H78" t="str">
-        <v>Chelsea Plank</v>
+        <v>Aaron Cole</v>
       </c>
       <c r="I78" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J78" t="str">
-        <v>https://music.apple.com/us/artist/chelsea-plank/1246169844</v>
+        <v>https://music.apple.com/us/artist/aaron-cole/507522696</v>
       </c>
       <c r="K78" t="str">
-        <v>https://music.apple.com/us/album/moonlight/1892950782</v>
+        <v>https://music.apple.com/us/album/usher-in-the-spirit/1895286256</v>
       </c>
       <c r="L78" t="str">
-        <v>Moonlight - Chelsea Plank</v>
+        <v>usher in the spirit - Aaron Cole</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="str">
-        <v>&gt;&gt;&gt;hands on me&lt;&lt;&lt;</v>
+        <v>Moonlight</v>
       </c>
       <c r="B79" t="str">
         <v/>
       </c>
       <c r="C79" t="str">
-        <v>https://music.apple.com/us/song/hands-on-me/1893960365</v>
+        <v>https://music.apple.com/us/song/moonlight/1892950791</v>
       </c>
       <c r="D79" t="str">
         <v>2026-05-06</v>
@@ -3377,36 +3377,36 @@
         <v/>
       </c>
       <c r="F79" t="str">
-        <v>&gt;&gt;&gt;hands on me&lt;&lt;&lt; - Single</v>
+        <v>Moonlight - Single</v>
       </c>
       <c r="G79" t="str">
-        <v>2:17</v>
+        <v>3:23</v>
       </c>
       <c r="H79" t="str">
-        <v>Becky Hill</v>
+        <v>Chelsea Plank</v>
       </c>
       <c r="I79" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J79" t="str">
-        <v>https://music.apple.com/us/artist/becky-hill/533839517</v>
+        <v>https://music.apple.com/us/artist/chelsea-plank/1246169844</v>
       </c>
       <c r="K79" t="str">
-        <v>https://music.apple.com/us/album/hands-on-me/1893960148</v>
+        <v>https://music.apple.com/us/album/moonlight/1892950782</v>
       </c>
       <c r="L79" t="str">
-        <v>&gt;&gt;&gt;hands on me&lt;&lt;&lt; - Becky Hill</v>
+        <v>Moonlight - Chelsea Plank</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="str">
-        <v>Closure</v>
+        <v>&gt;&gt;&gt;hands on me&lt;&lt;&lt;</v>
       </c>
       <c r="B80" t="str">
         <v/>
       </c>
       <c r="C80" t="str">
-        <v>https://music.apple.com/us/song/closure/1892418294</v>
+        <v>https://music.apple.com/us/song/hands-on-me/1893960365</v>
       </c>
       <c r="D80" t="str">
         <v>2026-05-06</v>
@@ -3415,36 +3415,36 @@
         <v/>
       </c>
       <c r="F80" t="str">
-        <v>Closure - Single</v>
+        <v>&gt;&gt;&gt;hands on me&lt;&lt;&lt; - Single</v>
       </c>
       <c r="G80" t="str">
-        <v>2:27</v>
+        <v>2:17</v>
       </c>
       <c r="H80" t="str">
-        <v>D.O.D</v>
+        <v>Becky Hill</v>
       </c>
       <c r="I80" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J80" t="str">
-        <v>https://music.apple.com/us/artist/d-o-d/444171843</v>
+        <v>https://music.apple.com/us/artist/becky-hill/533839517</v>
       </c>
       <c r="K80" t="str">
-        <v>https://music.apple.com/us/album/closure/1892418283</v>
+        <v>https://music.apple.com/us/album/hands-on-me/1893960148</v>
       </c>
       <c r="L80" t="str">
-        <v>Closure - D.O.D</v>
+        <v>&gt;&gt;&gt;hands on me&lt;&lt;&lt; - Becky Hill</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="str">
-        <v>HOTS 4 U</v>
+        <v>Closure</v>
       </c>
       <c r="B81" t="str">
         <v/>
       </c>
       <c r="C81" t="str">
-        <v>https://music.apple.com/us/song/hots-4-u/1891478541</v>
+        <v>https://music.apple.com/us/song/closure/1892418294</v>
       </c>
       <c r="D81" t="str">
         <v>2026-05-06</v>
@@ -3453,36 +3453,36 @@
         <v/>
       </c>
       <c r="F81" t="str">
-        <v>HOTS 4 U - Single</v>
+        <v>Closure - Single</v>
       </c>
       <c r="G81" t="str">
-        <v>3:34</v>
+        <v>2:27</v>
       </c>
       <c r="H81" t="str">
-        <v>Chris Lorenzo</v>
+        <v>D.O.D</v>
       </c>
       <c r="I81" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J81" t="str">
-        <v>https://music.apple.com/us/artist/chris-lorenzo/621431022</v>
+        <v>https://music.apple.com/us/artist/d-o-d/444171843</v>
       </c>
       <c r="K81" t="str">
-        <v>https://music.apple.com/us/album/hots-4-u/1891478539</v>
+        <v>https://music.apple.com/us/album/closure/1892418283</v>
       </c>
       <c r="L81" t="str">
-        <v>HOTS 4 U - Chris Lorenzo</v>
+        <v>Closure - D.O.D</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="str">
-        <v>CULE POCO (sirena_besarico_costeña)</v>
+        <v>HOTS 4 U</v>
       </c>
       <c r="B82" t="str">
         <v/>
       </c>
       <c r="C82" t="str">
-        <v>https://music.apple.com/us/song/cule-poco-sirena-besarico-coste%C3%B1a/1893480200</v>
+        <v>https://music.apple.com/us/song/hots-4-u/1891478541</v>
       </c>
       <c r="D82" t="str">
         <v>2026-05-06</v>
@@ -3491,36 +3491,36 @@
         <v/>
       </c>
       <c r="F82" t="str">
-        <v>CULE POCO (sirena_besarico_costeña) - Single</v>
+        <v>HOTS 4 U - Single</v>
       </c>
       <c r="G82" t="str">
-        <v>2:20</v>
+        <v>3:34</v>
       </c>
       <c r="H82" t="str">
-        <v>ARIA VEGA</v>
+        <v>Chris Lorenzo</v>
       </c>
       <c r="I82" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J82" t="str">
-        <v>https://music.apple.com/us/artist/aria-vega/1449328559</v>
+        <v>https://music.apple.com/us/artist/chris-lorenzo/621431022</v>
       </c>
       <c r="K82" t="str">
-        <v>https://music.apple.com/us/album/cule-poco-sirena-besarico-coste%C3%B1a/1893480124</v>
+        <v>https://music.apple.com/us/album/hots-4-u/1891478539</v>
       </c>
       <c r="L82" t="str">
-        <v>CULE POCO (sirena_besarico_costeña) - ARIA VEGA</v>
+        <v>HOTS 4 U - Chris Lorenzo</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="str">
-        <v>The Coin Toss</v>
+        <v>CULE POCO (sirena_besarico_costeña)</v>
       </c>
       <c r="B83" t="str">
         <v/>
       </c>
       <c r="C83" t="str">
-        <v>https://music.apple.com/us/song/the-coin-toss/1894872115</v>
+        <v>https://music.apple.com/us/song/cule-poco-sirena-besarico-coste%C3%B1a/1893480200</v>
       </c>
       <c r="D83" t="str">
         <v>2026-05-06</v>
@@ -3529,36 +3529,36 @@
         <v/>
       </c>
       <c r="F83" t="str">
-        <v>Roofless Records For Drop Tops: Disc 2</v>
+        <v>CULE POCO (sirena_besarico_costeña) - Single</v>
       </c>
       <c r="G83" t="str">
-        <v>2:46</v>
+        <v>2:20</v>
       </c>
       <c r="H83" t="str">
-        <v>Curren$y</v>
+        <v>ARIA VEGA</v>
       </c>
       <c r="I83" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J83" t="str">
-        <v>https://music.apple.com/us/artist/curren%24y/5914039</v>
+        <v>https://music.apple.com/us/artist/aria-vega/1449328559</v>
       </c>
       <c r="K83" t="str">
-        <v>https://music.apple.com/us/album/the-coin-toss/1894872108</v>
+        <v>https://music.apple.com/us/album/cule-poco-sirena-besarico-coste%C3%B1a/1893480124</v>
       </c>
       <c r="L83" t="str">
-        <v>The Coin Toss - Curren$y</v>
+        <v>CULE POCO (sirena_besarico_costeña) - ARIA VEGA</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="str">
-        <v>Bottles &amp; Lights</v>
+        <v>The Coin Toss</v>
       </c>
       <c r="B84" t="str">
         <v/>
       </c>
       <c r="C84" t="str">
-        <v>https://music.apple.com/us/song/bottles-lights/6763041153</v>
+        <v>https://music.apple.com/us/song/the-coin-toss/1894872115</v>
       </c>
       <c r="D84" t="str">
         <v>2026-05-06</v>
@@ -3567,36 +3567,36 @@
         <v/>
       </c>
       <c r="F84" t="str">
-        <v>Bottles &amp; Lights - Single</v>
+        <v>Roofless Records For Drop Tops: Disc 2</v>
       </c>
       <c r="G84" t="str">
-        <v>3:25</v>
+        <v>2:46</v>
       </c>
       <c r="H84" t="str">
-        <v>Chxrry</v>
+        <v>Curren$y</v>
       </c>
       <c r="I84" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J84" t="str">
-        <v>https://music.apple.com/us/artist/chxrry/1520135642</v>
+        <v>https://music.apple.com/us/artist/curren%24y/5914039</v>
       </c>
       <c r="K84" t="str">
-        <v>https://music.apple.com/us/album/bottles-lights/1895133498</v>
+        <v>https://music.apple.com/us/album/the-coin-toss/1894872108</v>
       </c>
       <c r="L84" t="str">
-        <v>Bottles &amp; Lights - Chxrry</v>
+        <v>The Coin Toss - Curren$y</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="str">
-        <v>Perfect For Me</v>
+        <v>Bottles &amp; Lights</v>
       </c>
       <c r="B85" t="str">
         <v/>
       </c>
       <c r="C85" t="str">
-        <v>https://music.apple.com/us/song/perfect-for-me/6762879981</v>
+        <v>https://music.apple.com/us/song/bottles-lights/6763041153</v>
       </c>
       <c r="D85" t="str">
         <v>2026-05-06</v>
@@ -3605,36 +3605,36 @@
         <v/>
       </c>
       <c r="F85" t="str">
-        <v>Perfect For Me - Single</v>
+        <v>Bottles &amp; Lights - Single</v>
       </c>
       <c r="G85" t="str">
-        <v>3:02</v>
+        <v>3:25</v>
       </c>
       <c r="H85" t="str">
-        <v>Jamal Roberts</v>
+        <v>Chxrry</v>
       </c>
       <c r="I85" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J85" t="str">
-        <v>https://music.apple.com/us/artist/jamal-roberts/920647552</v>
+        <v>https://music.apple.com/us/artist/chxrry/1520135642</v>
       </c>
       <c r="K85" t="str">
-        <v>https://music.apple.com/us/album/perfect-for-me/1895056299</v>
+        <v>https://music.apple.com/us/album/bottles-lights/1895133498</v>
       </c>
       <c r="L85" t="str">
-        <v>Perfect For Me - Jamal Roberts</v>
+        <v>Bottles &amp; Lights - Chxrry</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="str">
-        <v>So…</v>
+        <v>Perfect For Me</v>
       </c>
       <c r="B86" t="str">
         <v/>
       </c>
       <c r="C86" t="str">
-        <v>https://music.apple.com/us/song/so/1893162424</v>
+        <v>https://music.apple.com/us/song/perfect-for-me/6762879981</v>
       </c>
       <c r="D86" t="str">
         <v>2026-05-06</v>
@@ -3643,36 +3643,36 @@
         <v/>
       </c>
       <c r="F86" t="str">
-        <v>So… - Single</v>
+        <v>Perfect For Me - Single</v>
       </c>
       <c r="G86" t="str">
-        <v>3:16</v>
+        <v>3:02</v>
       </c>
       <c r="H86" t="str">
-        <v>Ama</v>
+        <v>Jamal Roberts</v>
       </c>
       <c r="I86" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J86" t="str">
-        <v>https://music.apple.com/us/artist/ama/1801560081</v>
+        <v>https://music.apple.com/us/artist/jamal-roberts/920647552</v>
       </c>
       <c r="K86" t="str">
-        <v>https://music.apple.com/us/album/so/1893162419</v>
+        <v>https://music.apple.com/us/album/perfect-for-me/1895056299</v>
       </c>
       <c r="L86" t="str">
-        <v>So… - Ama</v>
+        <v>Perfect For Me - Jamal Roberts</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="str">
-        <v>PASE Y PASE</v>
+        <v>So…</v>
       </c>
       <c r="B87" t="str">
         <v/>
       </c>
       <c r="C87" t="str">
-        <v>https://music.apple.com/us/song/pase-y-pase/1894076490</v>
+        <v>https://music.apple.com/us/song/so/1893162424</v>
       </c>
       <c r="D87" t="str">
         <v>2026-05-06</v>
@@ -3681,36 +3681,36 @@
         <v/>
       </c>
       <c r="F87" t="str">
-        <v>PASE Y PASE - Single</v>
+        <v>So… - Single</v>
       </c>
       <c r="G87" t="str">
-        <v>3:01</v>
+        <v>3:16</v>
       </c>
       <c r="H87" t="str">
-        <v>Tito Double P</v>
+        <v>Ama</v>
       </c>
       <c r="I87" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J87" t="str">
-        <v>https://music.apple.com/us/artist/tito-double-p/1690905306</v>
+        <v>https://music.apple.com/us/artist/ama/1801560081</v>
       </c>
       <c r="K87" t="str">
-        <v>https://music.apple.com/us/album/pase-y-pase/1894076487</v>
+        <v>https://music.apple.com/us/album/so/1893162419</v>
       </c>
       <c r="L87" t="str">
-        <v>PASE Y PASE - Tito Double P</v>
+        <v>So… - Ama</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="str">
-        <v>Agoué-Dambala (Yanvalou) 1</v>
+        <v>PASE Y PASE</v>
       </c>
       <c r="B88" t="str">
         <v/>
       </c>
       <c r="C88" t="str">
-        <v>https://music.apple.com/us/song/agou%C3%A9-dambala-yanvalou-1/1888242486</v>
+        <v>https://music.apple.com/us/song/pase-y-pase/1894076490</v>
       </c>
       <c r="D88" t="str">
         <v>2026-05-06</v>
@@ -3719,36 +3719,36 @@
         <v/>
       </c>
       <c r="F88" t="str">
-        <v>Soul Jazz Records Presents HAITIAN VODOU</v>
+        <v>PASE Y PASE - Single</v>
       </c>
       <c r="G88" t="str">
-        <v>4:13</v>
+        <v>3:01</v>
       </c>
       <c r="H88" t="str">
-        <v>Societe Absolument Guinin</v>
+        <v>Tito Double P</v>
       </c>
       <c r="I88" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J88" t="str">
-        <v>https://music.apple.com/us/artist/societe-absolument-guinin/1083463027</v>
+        <v>https://music.apple.com/us/artist/tito-double-p/1690905306</v>
       </c>
       <c r="K88" t="str">
-        <v>https://music.apple.com/us/album/agou%C3%A9-dambala-yanvalou-1/1888242483</v>
+        <v>https://music.apple.com/us/album/pase-y-pase/1894076487</v>
       </c>
       <c r="L88" t="str">
-        <v>Agoué-Dambala (Yanvalou) 1 - Societe Absolument Guinin</v>
+        <v>PASE Y PASE - Tito Double P</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="str">
-        <v>Aljahalat</v>
+        <v>Agoué-Dambala (Yanvalou) 1</v>
       </c>
       <c r="B89" t="str">
         <v/>
       </c>
       <c r="C89" t="str">
-        <v>https://music.apple.com/us/song/aljahalat/1889267983</v>
+        <v>https://music.apple.com/us/song/agou%C3%A9-dambala-yanvalou-1/1888242486</v>
       </c>
       <c r="D89" t="str">
         <v>2026-05-06</v>
@@ -3757,36 +3757,36 @@
         <v/>
       </c>
       <c r="F89" t="str">
-        <v>Aljahalat - Single</v>
+        <v>Soul Jazz Records Presents HAITIAN VODOU</v>
       </c>
       <c r="G89" t="str">
-        <v>6:12</v>
+        <v>4:13</v>
       </c>
       <c r="H89" t="str">
-        <v>Ahmed Ag Kaedy</v>
+        <v>Societe Absolument Guinin</v>
       </c>
       <c r="I89" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J89" t="str">
-        <v>https://music.apple.com/us/artist/ahmed-ag-kaedy/1445296267</v>
+        <v>https://music.apple.com/us/artist/societe-absolument-guinin/1083463027</v>
       </c>
       <c r="K89" t="str">
-        <v>https://music.apple.com/us/album/aljahalat/1889267980</v>
+        <v>https://music.apple.com/us/album/agou%C3%A9-dambala-yanvalou-1/1888242483</v>
       </c>
       <c r="L89" t="str">
-        <v>Aljahalat - Ahmed Ag Kaedy</v>
+        <v>Agoué-Dambala (Yanvalou) 1 - Societe Absolument Guinin</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="str">
-        <v>Puleza</v>
+        <v>Aljahalat</v>
       </c>
       <c r="B90" t="str">
         <v/>
       </c>
       <c r="C90" t="str">
-        <v>https://music.apple.com/us/song/puleza/1893765840</v>
+        <v>https://music.apple.com/us/song/aljahalat/1889267983</v>
       </c>
       <c r="D90" t="str">
         <v>2026-05-06</v>
@@ -3795,36 +3795,36 @@
         <v/>
       </c>
       <c r="F90" t="str">
-        <v>People of the Moon</v>
+        <v>Aljahalat - Single</v>
       </c>
       <c r="G90" t="str">
-        <v>3:47</v>
+        <v>6:12</v>
       </c>
       <c r="H90" t="str">
-        <v>Nu Genea</v>
+        <v>Ahmed Ag Kaedy</v>
       </c>
       <c r="I90" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J90" t="str">
-        <v>https://music.apple.com/us/artist/nu-genea/997053217</v>
+        <v>https://music.apple.com/us/artist/ahmed-ag-kaedy/1445296267</v>
       </c>
       <c r="K90" t="str">
-        <v>https://music.apple.com/us/album/puleza/1893765826</v>
+        <v>https://music.apple.com/us/album/aljahalat/1889267980</v>
       </c>
       <c r="L90" t="str">
-        <v>Puleza - Nu Genea</v>
+        <v>Aljahalat - Ahmed Ag Kaedy</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="str">
-        <v>Bastards</v>
+        <v>Puleza</v>
       </c>
       <c r="B91" t="str">
         <v/>
       </c>
       <c r="C91" t="str">
-        <v>https://music.apple.com/us/song/bastards/6762403102</v>
+        <v>https://music.apple.com/us/song/puleza/1893765840</v>
       </c>
       <c r="D91" t="str">
         <v>2026-05-06</v>
@@ -3833,36 +3833,36 @@
         <v/>
       </c>
       <c r="F91" t="str">
-        <v>Bunny - EP</v>
+        <v>People of the Moon</v>
       </c>
       <c r="G91" t="str">
-        <v>2:56</v>
+        <v>3:47</v>
       </c>
       <c r="H91" t="str">
-        <v>People I’ve Met</v>
+        <v>Nu Genea</v>
       </c>
       <c r="I91" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J91" t="str">
-        <v>https://music.apple.com/us/artist/people-ive-met/1853169947</v>
+        <v>https://music.apple.com/us/artist/nu-genea/997053217</v>
       </c>
       <c r="K91" t="str">
-        <v>https://music.apple.com/us/album/bastards/1894044276</v>
+        <v>https://music.apple.com/us/album/puleza/1893765826</v>
       </c>
       <c r="L91" t="str">
-        <v>Bastards - People I’ve Met</v>
+        <v>Puleza - Nu Genea</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="str">
-        <v>Crutch</v>
+        <v>Bastards</v>
       </c>
       <c r="B92" t="str">
         <v/>
       </c>
       <c r="C92" t="str">
-        <v>https://music.apple.com/us/song/crutch/6763345020</v>
+        <v>https://music.apple.com/us/song/bastards/6762403102</v>
       </c>
       <c r="D92" t="str">
         <v>2026-05-06</v>
@@ -3871,36 +3871,36 @@
         <v/>
       </c>
       <c r="F92" t="str">
-        <v>Crutch - Single</v>
+        <v>Bunny - EP</v>
       </c>
       <c r="G92" t="str">
-        <v>3:31</v>
+        <v>2:56</v>
       </c>
       <c r="H92" t="str">
-        <v>Love Spells</v>
+        <v>People I’ve Met</v>
       </c>
       <c r="I92" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J92" t="str">
-        <v>https://music.apple.com/us/artist/love-spells/1597025563</v>
+        <v>https://music.apple.com/us/artist/people-ive-met/1853169947</v>
       </c>
       <c r="K92" t="str">
-        <v>https://music.apple.com/us/album/crutch/1895274406</v>
+        <v>https://music.apple.com/us/album/bastards/1894044276</v>
       </c>
       <c r="L92" t="str">
-        <v>Crutch - Love Spells</v>
+        <v>Bastards - People I’ve Met</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="str">
-        <v>Just A Man</v>
+        <v>Crutch</v>
       </c>
       <c r="B93" t="str">
         <v/>
       </c>
       <c r="C93" t="str">
-        <v>https://music.apple.com/us/song/just-a-man/1893736206</v>
+        <v>https://music.apple.com/us/song/crutch/6763345020</v>
       </c>
       <c r="D93" t="str">
         <v>2026-05-06</v>
@@ -3909,36 +3909,36 @@
         <v/>
       </c>
       <c r="F93" t="str">
-        <v>Just A Man - Single</v>
+        <v>Crutch - Single</v>
       </c>
       <c r="G93" t="str">
-        <v>2:38</v>
+        <v>3:31</v>
       </c>
       <c r="H93" t="str">
-        <v>MOIO</v>
+        <v>Love Spells</v>
       </c>
       <c r="I93" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J93" t="str">
-        <v>https://music.apple.com/us/artist/moio/1664183608</v>
+        <v>https://music.apple.com/us/artist/love-spells/1597025563</v>
       </c>
       <c r="K93" t="str">
-        <v>https://music.apple.com/us/album/just-a-man/1893736201</v>
+        <v>https://music.apple.com/us/album/crutch/1895274406</v>
       </c>
       <c r="L93" t="str">
-        <v>Just A Man - MOIO</v>
+        <v>Crutch - Love Spells</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="str">
-        <v>Take Care Of You</v>
+        <v>Just A Man</v>
       </c>
       <c r="B94" t="str">
         <v/>
       </c>
       <c r="C94" t="str">
-        <v>https://music.apple.com/us/song/take-care-of-you/6762283983</v>
+        <v>https://music.apple.com/us/song/just-a-man/1893736206</v>
       </c>
       <c r="D94" t="str">
         <v>2026-05-06</v>
@@ -3947,36 +3947,36 @@
         <v/>
       </c>
       <c r="F94" t="str">
-        <v>Take Care Of You - Single</v>
+        <v>Just A Man - Single</v>
       </c>
       <c r="G94" t="str">
-        <v>3:51</v>
+        <v>2:38</v>
       </c>
       <c r="H94" t="str">
-        <v>Alina Baraz</v>
+        <v>MOIO</v>
       </c>
       <c r="I94" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J94" t="str">
-        <v>https://music.apple.com/us/artist/alina-baraz/757852571</v>
+        <v>https://music.apple.com/us/artist/moio/1664183608</v>
       </c>
       <c r="K94" t="str">
-        <v>https://music.apple.com/us/album/take-care-of-you/1893646113</v>
+        <v>https://music.apple.com/us/album/just-a-man/1893736201</v>
       </c>
       <c r="L94" t="str">
-        <v>Take Care Of You - Alina Baraz</v>
+        <v>Just A Man - MOIO</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="str">
-        <v>Love You More</v>
+        <v>Take Care Of You</v>
       </c>
       <c r="B95" t="str">
         <v/>
       </c>
       <c r="C95" t="str">
-        <v>https://music.apple.com/us/song/love-you-more/1889686330</v>
+        <v>https://music.apple.com/us/song/take-care-of-you/6762283983</v>
       </c>
       <c r="D95" t="str">
         <v>2026-05-06</v>
@@ -3985,36 +3985,36 @@
         <v/>
       </c>
       <c r="F95" t="str">
-        <v>Love You More - Single</v>
+        <v>Take Care Of You - Single</v>
       </c>
       <c r="G95" t="str">
-        <v>2:48</v>
+        <v>3:51</v>
       </c>
       <c r="H95" t="str">
-        <v>Rudimental</v>
+        <v>Alina Baraz</v>
       </c>
       <c r="I95" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J95" t="str">
-        <v>https://music.apple.com/us/artist/rudimental/474022504</v>
+        <v>https://music.apple.com/us/artist/alina-baraz/757852571</v>
       </c>
       <c r="K95" t="str">
-        <v>https://music.apple.com/us/album/love-you-more/1889686315</v>
+        <v>https://music.apple.com/us/album/take-care-of-you/1893646113</v>
       </c>
       <c r="L95" t="str">
-        <v>Love You More - Rudimental</v>
+        <v>Take Care Of You - Alina Baraz</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="str">
-        <v>Construct</v>
+        <v>Love You More</v>
       </c>
       <c r="B96" t="str">
         <v/>
       </c>
       <c r="C96" t="str">
-        <v>https://music.apple.com/us/song/construct/1869323374</v>
+        <v>https://music.apple.com/us/song/love-you-more/1889686330</v>
       </c>
       <c r="D96" t="str">
         <v>2026-05-06</v>
@@ -4023,36 +4023,36 @@
         <v/>
       </c>
       <c r="F96" t="str">
-        <v>ONE</v>
+        <v>Love You More - Single</v>
       </c>
       <c r="G96" t="str">
-        <v>3:57</v>
+        <v>2:48</v>
       </c>
       <c r="H96" t="str">
-        <v>Sevendust</v>
+        <v>Rudimental</v>
       </c>
       <c r="I96" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J96" t="str">
-        <v>https://music.apple.com/us/artist/sevendust/13125174</v>
+        <v>https://music.apple.com/us/artist/rudimental/474022504</v>
       </c>
       <c r="K96" t="str">
-        <v>https://music.apple.com/us/album/construct/1869323199</v>
+        <v>https://music.apple.com/us/album/love-you-more/1889686315</v>
       </c>
       <c r="L96" t="str">
-        <v>Construct - Sevendust</v>
+        <v>Love You More - Rudimental</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="str">
-        <v>As Above So Below</v>
+        <v>Construct</v>
       </c>
       <c r="B97" t="str">
         <v/>
       </c>
       <c r="C97" t="str">
-        <v>https://music.apple.com/us/song/as-above-so-below/1872651422</v>
+        <v>https://music.apple.com/us/song/construct/1869323374</v>
       </c>
       <c r="D97" t="str">
         <v>2026-05-06</v>
@@ -4061,36 +4061,36 @@
         <v/>
       </c>
       <c r="F97" t="str">
-        <v>Into Oblivion</v>
+        <v>ONE</v>
       </c>
       <c r="G97" t="str">
-        <v>4:54</v>
+        <v>3:57</v>
       </c>
       <c r="H97" t="str">
-        <v>Venom</v>
+        <v>Sevendust</v>
       </c>
       <c r="I97" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J97" t="str">
-        <v>https://music.apple.com/us/artist/venom/3222127</v>
+        <v>https://music.apple.com/us/artist/sevendust/13125174</v>
       </c>
       <c r="K97" t="str">
-        <v>https://music.apple.com/us/album/as-above-so-below/1872651243</v>
+        <v>https://music.apple.com/us/album/construct/1869323199</v>
       </c>
       <c r="L97" t="str">
-        <v>As Above So Below - Venom</v>
+        <v>Construct - Sevendust</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="str">
-        <v>Revenant</v>
+        <v>As Above So Below</v>
       </c>
       <c r="B98" t="str">
         <v/>
       </c>
       <c r="C98" t="str">
-        <v>https://music.apple.com/us/song/revenant/6763148056</v>
+        <v>https://music.apple.com/us/song/as-above-so-below/1872651422</v>
       </c>
       <c r="D98" t="str">
         <v>2026-05-06</v>
@@ -4099,36 +4099,36 @@
         <v/>
       </c>
       <c r="F98" t="str">
-        <v>A Stranger To You</v>
+        <v>Into Oblivion</v>
       </c>
       <c r="G98" t="str">
-        <v>3:31</v>
+        <v>4:54</v>
       </c>
       <c r="H98" t="str">
-        <v>Loathe</v>
+        <v>Venom</v>
       </c>
       <c r="I98" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J98" t="str">
-        <v>https://music.apple.com/us/artist/loathe/377883434</v>
+        <v>https://music.apple.com/us/artist/venom/3222127</v>
       </c>
       <c r="K98" t="str">
-        <v>https://music.apple.com/us/album/revenant/1895184628</v>
+        <v>https://music.apple.com/us/album/as-above-so-below/1872651243</v>
       </c>
       <c r="L98" t="str">
-        <v>Revenant - Loathe</v>
+        <v>As Above So Below - Venom</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="str">
-        <v>Black Box (feat. Joe Duplantier &amp; The Mystery Of The Bulgarian Voices)</v>
+        <v>Revenant</v>
       </c>
       <c r="B99" t="str">
         <v/>
       </c>
       <c r="C99" t="str">
-        <v>https://music.apple.com/us/song/black-box-feat-joe-duplantier-the-mystery-of/6762312582</v>
+        <v>https://music.apple.com/us/song/revenant/6763148056</v>
       </c>
       <c r="D99" t="str">
         <v>2026-05-06</v>
@@ -4137,36 +4137,36 @@
         <v/>
       </c>
       <c r="F99" t="str">
-        <v>Black Box (feat. Joe Duplantier &amp; The Mystery Of The Bulgarian Voices) - Single</v>
+        <v>A Stranger To You</v>
       </c>
       <c r="G99" t="str">
-        <v>4:56</v>
+        <v>3:31</v>
       </c>
       <c r="H99" t="str">
-        <v>Bear McCreary</v>
+        <v>Loathe</v>
       </c>
       <c r="I99" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J99" t="str">
-        <v>https://music.apple.com/us/artist/bear-mccreary/204012062</v>
+        <v>https://music.apple.com/us/artist/loathe/377883434</v>
       </c>
       <c r="K99" t="str">
-        <v>https://music.apple.com/us/album/black-box-feat-joe-duplantier-the-mystery-of/1893773367</v>
+        <v>https://music.apple.com/us/album/revenant/1895184628</v>
       </c>
       <c r="L99" t="str">
-        <v>Black Box (feat. Joe Duplantier &amp; The Mystery Of The Bulgarian Voices) - Bear McCreary</v>
+        <v>Revenant - Loathe</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="str">
-        <v>Power 4</v>
+        <v>Black Box (feat. Joe Duplantier &amp; The Mystery Of The Bulgarian Voices)</v>
       </c>
       <c r="B100" t="str">
         <v/>
       </c>
       <c r="C100" t="str">
-        <v>https://music.apple.com/us/song/power-4/6763647813</v>
+        <v>https://music.apple.com/us/song/black-box-feat-joe-duplantier-the-mystery-of/6762312582</v>
       </c>
       <c r="D100" t="str">
         <v>2026-05-06</v>
@@ -4175,36 +4175,36 @@
         <v/>
       </c>
       <c r="F100" t="str">
-        <v>Power 4 - Single</v>
+        <v>Black Box (feat. Joe Duplantier &amp; The Mystery Of The Bulgarian Voices) - Single</v>
       </c>
       <c r="G100" t="str">
-        <v>1:40</v>
+        <v>4:56</v>
       </c>
       <c r="H100" t="str">
-        <v>slayr</v>
+        <v>Bear McCreary</v>
       </c>
       <c r="I100" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J100" t="str">
-        <v>https://music.apple.com/us/artist/slayr/1676805496</v>
+        <v>https://music.apple.com/us/artist/bear-mccreary/204012062</v>
       </c>
       <c r="K100" t="str">
-        <v>https://music.apple.com/us/album/power-4/1895416494</v>
+        <v>https://music.apple.com/us/album/black-box-feat-joe-duplantier-the-mystery-of/1893773367</v>
       </c>
       <c r="L100" t="str">
-        <v>Power 4 - slayr</v>
+        <v>Black Box (feat. Joe Duplantier &amp; The Mystery Of The Bulgarian Voices) - Bear McCreary</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="str">
-        <v>Too Easy</v>
+        <v>Power 4</v>
       </c>
       <c r="B101" t="str">
         <v/>
       </c>
       <c r="C101" t="str">
-        <v>https://music.apple.com/us/song/too-easy/1893814702</v>
+        <v>https://music.apple.com/us/song/power-4/6763647813</v>
       </c>
       <c r="D101" t="str">
         <v>2026-05-06</v>
@@ -4213,36 +4213,36 @@
         <v/>
       </c>
       <c r="F101" t="str">
-        <v>Too Easy - Single</v>
+        <v>Power 4 - Single</v>
       </c>
       <c r="G101" t="str">
-        <v>4:14</v>
+        <v>1:40</v>
       </c>
       <c r="H101" t="str">
-        <v>tig3r lewis</v>
+        <v>slayr</v>
       </c>
       <c r="I101" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J101" t="str">
-        <v>https://music.apple.com/us/artist/tig3r-lewis/1850089834</v>
+        <v>https://music.apple.com/us/artist/slayr/1676805496</v>
       </c>
       <c r="K101" t="str">
-        <v>https://music.apple.com/us/album/too-easy/1893814697</v>
+        <v>https://music.apple.com/us/album/power-4/1895416494</v>
       </c>
       <c r="L101" t="str">
-        <v>Too Easy - tig3r lewis</v>
+        <v>Power 4 - slayr</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="str">
-        <v>If You Want It</v>
+        <v>Too Easy</v>
       </c>
       <c r="B102" t="str">
         <v/>
       </c>
       <c r="C102" t="str">
-        <v>https://music.apple.com/us/song/if-you-want-it/1892503347</v>
+        <v>https://music.apple.com/us/song/too-easy/1893814702</v>
       </c>
       <c r="D102" t="str">
         <v>2026-05-06</v>
@@ -4251,36 +4251,36 @@
         <v/>
       </c>
       <c r="F102" t="str">
-        <v>If You Want It - Single</v>
+        <v>Too Easy - Single</v>
       </c>
       <c r="G102" t="str">
-        <v>3:56</v>
+        <v>4:14</v>
       </c>
       <c r="H102" t="str">
-        <v>ALAC</v>
+        <v>tig3r lewis</v>
       </c>
       <c r="I102" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J102" t="str">
-        <v>https://music.apple.com/us/artist/alac/1885586915</v>
+        <v>https://music.apple.com/us/artist/tig3r-lewis/1850089834</v>
       </c>
       <c r="K102" t="str">
-        <v>https://music.apple.com/us/album/if-you-want-it/1892503333</v>
+        <v>https://music.apple.com/us/album/too-easy/1893814697</v>
       </c>
       <c r="L102" t="str">
-        <v>If You Want It - ALAC</v>
+        <v>Too Easy - tig3r lewis</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="str">
-        <v>Shoplifting</v>
+        <v>If You Want It</v>
       </c>
       <c r="B103" t="str">
         <v/>
       </c>
       <c r="C103" t="str">
-        <v>https://music.apple.com/us/song/shoplifting/1852812659</v>
+        <v>https://music.apple.com/us/song/if-you-want-it/1892503347</v>
       </c>
       <c r="D103" t="str">
         <v>2026-05-06</v>
@@ -4289,68 +4289,106 @@
         <v/>
       </c>
       <c r="F103" t="str">
-        <v>Theft World</v>
+        <v>If You Want It - Single</v>
       </c>
       <c r="G103" t="str">
-        <v>3:02</v>
+        <v>3:56</v>
       </c>
       <c r="H103" t="str">
-        <v>Lip Critic</v>
+        <v>ALAC</v>
       </c>
       <c r="I103" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J103" t="str">
-        <v>https://music.apple.com/us/artist/lip-critic/1458046064</v>
+        <v>https://music.apple.com/us/artist/alac/1885586915</v>
       </c>
       <c r="K103" t="str">
-        <v>https://music.apple.com/us/album/shoplifting/1852812554</v>
+        <v>https://music.apple.com/us/album/if-you-want-it/1892503333</v>
       </c>
       <c r="L103" t="str">
-        <v>Shoplifting - Lip Critic</v>
+        <v>If You Want It - ALAC</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="str">
+        <v>Shoplifting</v>
+      </c>
+      <c r="B104" t="str">
+        <v/>
+      </c>
+      <c r="C104" t="str">
+        <v>https://music.apple.com/us/song/shoplifting/1852812659</v>
+      </c>
+      <c r="D104" t="str">
+        <v>2026-05-06</v>
+      </c>
+      <c r="E104" t="str">
+        <v/>
+      </c>
+      <c r="F104" t="str">
+        <v>Theft World</v>
+      </c>
+      <c r="G104" t="str">
+        <v>3:02</v>
+      </c>
+      <c r="H104" t="str">
+        <v>Lip Critic</v>
+      </c>
+      <c r="I104" t="str">
+        <v>מוזיקה לועזית חדשה</v>
+      </c>
+      <c r="J104" t="str">
+        <v>https://music.apple.com/us/artist/lip-critic/1458046064</v>
+      </c>
+      <c r="K104" t="str">
+        <v>https://music.apple.com/us/album/shoplifting/1852812554</v>
+      </c>
+      <c r="L104" t="str">
+        <v>Shoplifting - Lip Critic</v>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="str">
         <v>Endlessly (feat. BEA1991)</v>
       </c>
-      <c r="B104" t="str">
-        <v/>
-      </c>
-      <c r="C104" t="str">
+      <c r="B105" t="str">
+        <v/>
+      </c>
+      <c r="C105" t="str">
         <v>https://music.apple.com/us/song/endlessly-feat-bea1991/1876022833</v>
       </c>
-      <c r="D104" t="str">
-        <v>2026-05-06</v>
-      </c>
-      <c r="E104" t="str">
-        <v/>
-      </c>
-      <c r="F104" t="str">
+      <c r="D105" t="str">
+        <v>2026-05-06</v>
+      </c>
+      <c r="E105" t="str">
+        <v/>
+      </c>
+      <c r="F105" t="str">
         <v>Fold</v>
       </c>
-      <c r="G104" t="str">
+      <c r="G105" t="str">
         <v>5:57</v>
       </c>
-      <c r="H104" t="str">
+      <c r="H105" t="str">
         <v>Jump Source</v>
       </c>
-      <c r="I104" t="str">
-        <v>מוזיקה לועזית חדשה</v>
-      </c>
-      <c r="J104" t="str">
+      <c r="I105" t="str">
+        <v>מוזיקה לועזית חדשה</v>
+      </c>
+      <c r="J105" t="str">
         <v>https://music.apple.com/us/artist/jump-source/1169060818</v>
       </c>
-      <c r="K104" t="str">
+      <c r="K105" t="str">
         <v>https://music.apple.com/us/album/endlessly-feat-bea1991/1876022817</v>
       </c>
-      <c r="L104" t="str">
+      <c r="L105" t="str">
         <v>Endlessly (feat. BEA1991) - Jump Source</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:L104"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:L105"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/data/tags/מוזיקה לועזית חדשה/sites/apple-music-playlist/2026-05-week01/titles.xlsx
+++ b/data/tags/מוזיקה לועזית חדשה/sites/apple-music-playlist/2026-05-week01/titles.xlsx
@@ -445,7 +445,7 @@
         <v>https://music.apple.com/us/song/therapy-at-the-club/6764050150</v>
       </c>
       <c r="D2" t="str">
-        <v>2026-05-06</v>
+        <v>2026-05-07</v>
       </c>
       <c r="E2" t="str">
         <v/>
@@ -483,7 +483,7 @@
         <v>https://music.apple.com/us/song/eurosummer-girls-trip/1894058279</v>
       </c>
       <c r="D3" t="str">
-        <v>2026-05-06</v>
+        <v>2026-05-07</v>
       </c>
       <c r="E3" t="str">
         <v/>
@@ -521,7 +521,7 @@
         <v>https://music.apple.com/us/song/shape-of-a-woman/6764429252</v>
       </c>
       <c r="D4" t="str">
-        <v>2026-05-06</v>
+        <v>2026-05-07</v>
       </c>
       <c r="E4" t="str">
         <v/>
@@ -559,7 +559,7 @@
         <v>https://music.apple.com/us/song/bring-your-love/1892545227</v>
       </c>
       <c r="D5" t="str">
-        <v>2026-05-06</v>
+        <v>2026-05-07</v>
       </c>
       <c r="E5" t="str">
         <v/>
@@ -597,7 +597,7 @@
         <v>https://music.apple.com/us/song/horses-and-divorces/1883177267</v>
       </c>
       <c r="D6" t="str">
-        <v>2026-05-06</v>
+        <v>2026-05-07</v>
       </c>
       <c r="E6" t="str">
         <v/>
@@ -635,7 +635,7 @@
         <v>https://music.apple.com/us/song/staying-still/6762758806</v>
       </c>
       <c r="D7" t="str">
-        <v>2026-05-06</v>
+        <v>2026-05-07</v>
       </c>
       <c r="E7" t="str">
         <v/>
@@ -673,7 +673,7 @@
         <v>https://music.apple.com/us/song/fine-place-to-die/6764686279</v>
       </c>
       <c r="D8" t="str">
-        <v>2026-05-06</v>
+        <v>2026-05-07</v>
       </c>
       <c r="E8" t="str">
         <v/>
@@ -711,7 +711,7 @@
         <v>https://music.apple.com/us/song/mutt/6763145178</v>
       </c>
       <c r="D9" t="str">
-        <v>2026-05-06</v>
+        <v>2026-05-07</v>
       </c>
       <c r="E9" t="str">
         <v/>
@@ -749,7 +749,7 @@
         <v>https://music.apple.com/us/song/fire-away-feat-slayyyter/1892422570</v>
       </c>
       <c r="D10" t="str">
-        <v>2026-05-06</v>
+        <v>2026-05-07</v>
       </c>
       <c r="E10" t="str">
         <v/>
@@ -787,7 +787,7 @@
         <v>https://music.apple.com/us/song/linknb/1888561848</v>
       </c>
       <c r="D11" t="str">
-        <v>2026-05-06</v>
+        <v>2026-05-07</v>
       </c>
       <c r="E11" t="str">
         <v/>
@@ -825,7 +825,7 @@
         <v>https://music.apple.com/us/song/lioness/1878649397</v>
       </c>
       <c r="D12" t="str">
-        <v>2026-05-06</v>
+        <v>2026-05-07</v>
       </c>
       <c r="E12" t="str">
         <v/>
@@ -863,7 +863,7 @@
         <v>https://music.apple.com/us/song/robotic-love/6763638857</v>
       </c>
       <c r="D13" t="str">
-        <v>2026-05-06</v>
+        <v>2026-05-07</v>
       </c>
       <c r="E13" t="str">
         <v/>
@@ -901,7 +901,7 @@
         <v>https://music.apple.com/us/song/its-ok/6763134121</v>
       </c>
       <c r="D14" t="str">
-        <v>2026-05-06</v>
+        <v>2026-05-07</v>
       </c>
       <c r="E14" t="str">
         <v/>
@@ -939,7 +939,7 @@
         <v>https://music.apple.com/us/song/promise/6763162287</v>
       </c>
       <c r="D15" t="str">
-        <v>2026-05-06</v>
+        <v>2026-05-07</v>
       </c>
       <c r="E15" t="str">
         <v/>
@@ -977,7 +977,7 @@
         <v>https://music.apple.com/us/song/cool-buzz/1880470657</v>
       </c>
       <c r="D16" t="str">
-        <v>2026-05-06</v>
+        <v>2026-05-07</v>
       </c>
       <c r="E16" t="str">
         <v/>
@@ -1015,7 +1015,7 @@
         <v>https://music.apple.com/us/song/material-lover/6764429256</v>
       </c>
       <c r="D17" t="str">
-        <v>2026-05-06</v>
+        <v>2026-05-07</v>
       </c>
       <c r="E17" t="str">
         <v/>
@@ -1053,7 +1053,7 @@
         <v>https://music.apple.com/us/song/fallin-feat-leon-thomas/6764419265</v>
       </c>
       <c r="D18" t="str">
-        <v>2026-05-06</v>
+        <v>2026-05-07</v>
       </c>
       <c r="E18" t="str">
         <v/>
@@ -1091,7 +1091,7 @@
         <v>https://music.apple.com/us/song/echo/6763379683</v>
       </c>
       <c r="D19" t="str">
-        <v>2026-05-06</v>
+        <v>2026-05-07</v>
       </c>
       <c r="E19" t="str">
         <v/>
@@ -1129,7 +1129,7 @@
         <v>https://music.apple.com/us/song/blackberry-marmalade/1887627837</v>
       </c>
       <c r="D20" t="str">
-        <v>2026-05-06</v>
+        <v>2026-05-07</v>
       </c>
       <c r="E20" t="str">
         <v/>
@@ -1167,7 +1167,7 @@
         <v>https://music.apple.com/us/song/ricky-bobby/6764406571</v>
       </c>
       <c r="D21" t="str">
-        <v>2026-05-06</v>
+        <v>2026-05-07</v>
       </c>
       <c r="E21" t="str">
         <v/>
@@ -1205,7 +1205,7 @@
         <v>https://music.apple.com/us/song/te-entiendo-remix/6763665638</v>
       </c>
       <c r="D22" t="str">
-        <v>2026-05-06</v>
+        <v>2026-05-07</v>
       </c>
       <c r="E22" t="str">
         <v/>
@@ -1243,7 +1243,7 @@
         <v>https://music.apple.com/us/song/dont-worry-baby/1894294411</v>
       </c>
       <c r="D23" t="str">
-        <v>2026-05-06</v>
+        <v>2026-05-07</v>
       </c>
       <c r="E23" t="str">
         <v/>
@@ -1281,7 +1281,7 @@
         <v>https://music.apple.com/us/song/bitch/6763622110</v>
       </c>
       <c r="D24" t="str">
-        <v>2026-05-06</v>
+        <v>2026-05-07</v>
       </c>
       <c r="E24" t="str">
         <v/>
@@ -1319,7 +1319,7 @@
         <v>https://music.apple.com/us/song/just-wanna-cry/6763414703</v>
       </c>
       <c r="D25" t="str">
-        <v>2026-05-06</v>
+        <v>2026-05-07</v>
       </c>
       <c r="E25" t="str">
         <v/>
@@ -1357,7 +1357,7 @@
         <v>https://music.apple.com/us/song/carry-the-weight/6763611647</v>
       </c>
       <c r="D26" t="str">
-        <v>2026-05-06</v>
+        <v>2026-05-07</v>
       </c>
       <c r="E26" t="str">
         <v/>
@@ -1395,7 +1395,7 @@
         <v>https://music.apple.com/us/song/prostitute/1894092341</v>
       </c>
       <c r="D27" t="str">
-        <v>2026-05-06</v>
+        <v>2026-05-07</v>
       </c>
       <c r="E27" t="str">
         <v/>
@@ -1433,7 +1433,7 @@
         <v>https://music.apple.com/us/song/im-not-joking/1872842623</v>
       </c>
       <c r="D28" t="str">
-        <v>2026-05-06</v>
+        <v>2026-05-07</v>
       </c>
       <c r="E28" t="str">
         <v/>
@@ -1471,7 +1471,7 @@
         <v>https://music.apple.com/us/song/ruca/6763671002</v>
       </c>
       <c r="D29" t="str">
-        <v>2026-05-06</v>
+        <v>2026-05-07</v>
       </c>
       <c r="E29" t="str">
         <v/>
@@ -1509,7 +1509,7 @@
         <v>https://music.apple.com/us/song/make-you-fight/1892332386</v>
       </c>
       <c r="D30" t="str">
-        <v>2026-05-06</v>
+        <v>2026-05-07</v>
       </c>
       <c r="E30" t="str">
         <v/>
@@ -1547,7 +1547,7 @@
         <v>https://music.apple.com/us/song/n0rth4evr/6763302230</v>
       </c>
       <c r="D31" t="str">
-        <v>2026-05-06</v>
+        <v>2026-05-07</v>
       </c>
       <c r="E31" t="str">
         <v/>
@@ -1585,7 +1585,7 @@
         <v>https://music.apple.com/us/song/boy-in-red/1892543110</v>
       </c>
       <c r="D32" t="str">
-        <v>2026-05-06</v>
+        <v>2026-05-07</v>
       </c>
       <c r="E32" t="str">
         <v/>
@@ -1623,7 +1623,7 @@
         <v>https://music.apple.com/us/song/ea-ea-ea/6763438376</v>
       </c>
       <c r="D33" t="str">
-        <v>2026-05-06</v>
+        <v>2026-05-07</v>
       </c>
       <c r="E33" t="str">
         <v/>
@@ -1661,7 +1661,7 @@
         <v>https://music.apple.com/us/song/just-a-man/6762944365</v>
       </c>
       <c r="D34" t="str">
-        <v>2026-05-06</v>
+        <v>2026-05-07</v>
       </c>
       <c r="E34" t="str">
         <v/>
@@ -1699,7 +1699,7 @@
         <v>https://music.apple.com/us/song/the-observer/1891982314</v>
       </c>
       <c r="D35" t="str">
-        <v>2026-05-06</v>
+        <v>2026-05-07</v>
       </c>
       <c r="E35" t="str">
         <v/>
@@ -1737,7 +1737,7 @@
         <v>https://music.apple.com/us/song/heroine/6762693177</v>
       </c>
       <c r="D36" t="str">
-        <v>2026-05-06</v>
+        <v>2026-05-07</v>
       </c>
       <c r="E36" t="str">
         <v/>
@@ -1775,7 +1775,7 @@
         <v>https://music.apple.com/us/song/do-me-right/6764667658</v>
       </c>
       <c r="D37" t="str">
-        <v>2026-05-06</v>
+        <v>2026-05-07</v>
       </c>
       <c r="E37" t="str">
         <v/>
@@ -1813,7 +1813,7 @@
         <v>https://music.apple.com/us/song/its-me/1887194026</v>
       </c>
       <c r="D38" t="str">
-        <v>2026-05-06</v>
+        <v>2026-05-07</v>
       </c>
       <c r="E38" t="str">
         <v/>
@@ -1851,7 +1851,7 @@
         <v>https://music.apple.com/us/song/the-precipice/1891830326</v>
       </c>
       <c r="D39" t="str">
-        <v>2026-05-06</v>
+        <v>2026-05-07</v>
       </c>
       <c r="E39" t="str">
         <v/>
@@ -1889,7 +1889,7 @@
         <v>https://music.apple.com/us/song/hello-lonesome/1892466003</v>
       </c>
       <c r="D40" t="str">
-        <v>2026-05-06</v>
+        <v>2026-05-07</v>
       </c>
       <c r="E40" t="str">
         <v/>
@@ -1927,7 +1927,7 @@
         <v>https://music.apple.com/us/song/trippin-opera-edit/6764648776</v>
       </c>
       <c r="D41" t="str">
-        <v>2026-05-06</v>
+        <v>2026-05-07</v>
       </c>
       <c r="E41" t="str">
         <v/>
@@ -1965,7 +1965,7 @@
         <v>https://music.apple.com/us/song/the-mandalorian-and-grogu-boys-noize-remix-from-star/6764131630</v>
       </c>
       <c r="D42" t="str">
-        <v>2026-05-06</v>
+        <v>2026-05-07</v>
       </c>
       <c r="E42" t="str">
         <v/>
@@ -2003,7 +2003,7 @@
         <v>https://music.apple.com/us/song/blow-my-mind-ca7riel-paco-amoroso-version/1894344140</v>
       </c>
       <c r="D43" t="str">
-        <v>2026-05-06</v>
+        <v>2026-05-07</v>
       </c>
       <c r="E43" t="str">
         <v/>
@@ -2041,7 +2041,7 @@
         <v>https://music.apple.com/us/song/bring-that-body/6764009310</v>
       </c>
       <c r="D44" t="str">
-        <v>2026-05-06</v>
+        <v>2026-05-07</v>
       </c>
       <c r="E44" t="str">
         <v/>
@@ -2079,7 +2079,7 @@
         <v>https://music.apple.com/us/song/star/1891845608</v>
       </c>
       <c r="D45" t="str">
-        <v>2026-05-06</v>
+        <v>2026-05-07</v>
       </c>
       <c r="E45" t="str">
         <v/>
@@ -2117,7 +2117,7 @@
         <v>https://music.apple.com/us/song/whats-a-little-rain/1885061171</v>
       </c>
       <c r="D46" t="str">
-        <v>2026-05-06</v>
+        <v>2026-05-07</v>
       </c>
       <c r="E46" t="str">
         <v/>
@@ -2155,7 +2155,7 @@
         <v>https://music.apple.com/us/song/evergreen/1866700315</v>
       </c>
       <c r="D47" t="str">
-        <v>2026-05-06</v>
+        <v>2026-05-07</v>
       </c>
       <c r="E47" t="str">
         <v/>
@@ -2193,7 +2193,7 @@
         <v>https://music.apple.com/us/song/she-does-it-right/1873477957</v>
       </c>
       <c r="D48" t="str">
-        <v>2026-05-06</v>
+        <v>2026-05-07</v>
       </c>
       <c r="E48" t="str">
         <v/>
@@ -2231,7 +2231,7 @@
         <v>https://music.apple.com/us/song/punching-the-flowers/1878362636</v>
       </c>
       <c r="D49" t="str">
-        <v>2026-05-06</v>
+        <v>2026-05-07</v>
       </c>
       <c r="E49" t="str">
         <v/>
@@ -2269,7 +2269,7 @@
         <v>https://music.apple.com/us/song/how-did-you-know/1888553137</v>
       </c>
       <c r="D50" t="str">
-        <v>2026-05-06</v>
+        <v>2026-05-07</v>
       </c>
       <c r="E50" t="str">
         <v/>
@@ -2307,7 +2307,7 @@
         <v>https://music.apple.com/us/song/summer-breeze/6763360727</v>
       </c>
       <c r="D51" t="str">
-        <v>2026-05-06</v>
+        <v>2026-05-07</v>
       </c>
       <c r="E51" t="str">
         <v/>
@@ -2345,7 +2345,7 @@
         <v>https://music.apple.com/us/song/sound-of-a-woman/1859763367</v>
       </c>
       <c r="D52" t="str">
-        <v>2026-05-06</v>
+        <v>2026-05-07</v>
       </c>
       <c r="E52" t="str">
         <v/>
@@ -2383,7 +2383,7 @@
         <v>https://music.apple.com/us/song/my-life/1893157347</v>
       </c>
       <c r="D53" t="str">
-        <v>2026-05-06</v>
+        <v>2026-05-07</v>
       </c>
       <c r="E53" t="str">
         <v/>
@@ -2421,7 +2421,7 @@
         <v>https://music.apple.com/us/song/ribcage/1893155593</v>
       </c>
       <c r="D54" t="str">
-        <v>2026-05-06</v>
+        <v>2026-05-07</v>
       </c>
       <c r="E54" t="str">
         <v/>
@@ -2459,7 +2459,7 @@
         <v>https://music.apple.com/us/song/i-loved-you-then/1878232821</v>
       </c>
       <c r="D55" t="str">
-        <v>2026-05-06</v>
+        <v>2026-05-07</v>
       </c>
       <c r="E55" t="str">
         <v/>
@@ -2497,7 +2497,7 @@
         <v>https://music.apple.com/us/song/ill-let-you-finish/1891844342</v>
       </c>
       <c r="D56" t="str">
-        <v>2026-05-06</v>
+        <v>2026-05-07</v>
       </c>
       <c r="E56" t="str">
         <v/>
@@ -2535,7 +2535,7 @@
         <v>https://music.apple.com/us/song/it-gets-me-through/1884798927</v>
       </c>
       <c r="D57" t="str">
-        <v>2026-05-06</v>
+        <v>2026-05-07</v>
       </c>
       <c r="E57" t="str">
         <v/>
@@ -2573,7 +2573,7 @@
         <v>https://music.apple.com/us/song/the-author/6763327641</v>
       </c>
       <c r="D58" t="str">
-        <v>2026-05-06</v>
+        <v>2026-05-07</v>
       </c>
       <c r="E58" t="str">
         <v/>
@@ -2611,7 +2611,7 @@
         <v>https://music.apple.com/us/song/want-me-back-feat-tors/1889370756</v>
       </c>
       <c r="D59" t="str">
-        <v>2026-05-06</v>
+        <v>2026-05-07</v>
       </c>
       <c r="E59" t="str">
         <v/>
@@ -2649,7 +2649,7 @@
         <v>https://music.apple.com/us/song/ruin/1886537117</v>
       </c>
       <c r="D60" t="str">
-        <v>2026-05-06</v>
+        <v>2026-05-07</v>
       </c>
       <c r="E60" t="str">
         <v/>
@@ -2687,7 +2687,7 @@
         <v>https://music.apple.com/us/song/i-know-i-know/1894354139</v>
       </c>
       <c r="D61" t="str">
-        <v>2026-05-06</v>
+        <v>2026-05-07</v>
       </c>
       <c r="E61" t="str">
         <v/>
@@ -2725,7 +2725,7 @@
         <v>https://music.apple.com/us/song/drive-all-night/6763189759</v>
       </c>
       <c r="D62" t="str">
-        <v>2026-05-06</v>
+        <v>2026-05-07</v>
       </c>
       <c r="E62" t="str">
         <v/>
@@ -2763,7 +2763,7 @@
         <v>https://music.apple.com/us/song/aint-u-tired/6763115235</v>
       </c>
       <c r="D63" t="str">
-        <v>2026-05-06</v>
+        <v>2026-05-07</v>
       </c>
       <c r="E63" t="str">
         <v/>
@@ -2801,7 +2801,7 @@
         <v>https://music.apple.com/us/song/boys-in-blue/1892436920</v>
       </c>
       <c r="D64" t="str">
-        <v>2026-05-06</v>
+        <v>2026-05-07</v>
       </c>
       <c r="E64" t="str">
         <v/>
@@ -2839,7 +2839,7 @@
         <v>https://music.apple.com/us/song/salma-hayek/1891815286</v>
       </c>
       <c r="D65" t="str">
-        <v>2026-05-06</v>
+        <v>2026-05-07</v>
       </c>
       <c r="E65" t="str">
         <v/>
@@ -2877,7 +2877,7 @@
         <v>https://music.apple.com/us/song/stubborn-mouth/1893194800</v>
       </c>
       <c r="D66" t="str">
-        <v>2026-05-06</v>
+        <v>2026-05-07</v>
       </c>
       <c r="E66" t="str">
         <v/>
@@ -2915,7 +2915,7 @@
         <v>https://music.apple.com/us/song/hallucination/6764110976</v>
       </c>
       <c r="D67" t="str">
-        <v>2026-05-06</v>
+        <v>2026-05-07</v>
       </c>
       <c r="E67" t="str">
         <v/>
@@ -2953,7 +2953,7 @@
         <v>https://music.apple.com/us/song/in-da-jungle/1891136400</v>
       </c>
       <c r="D68" t="str">
-        <v>2026-05-06</v>
+        <v>2026-05-07</v>
       </c>
       <c r="E68" t="str">
         <v/>
@@ -2991,7 +2991,7 @@
         <v>https://music.apple.com/us/song/fall-short/1894662749</v>
       </c>
       <c r="D69" t="str">
-        <v>2026-05-06</v>
+        <v>2026-05-07</v>
       </c>
       <c r="E69" t="str">
         <v/>
@@ -3029,7 +3029,7 @@
         <v>https://music.apple.com/us/song/irish-goodbye-feat-kae-tempest/1862224205</v>
       </c>
       <c r="D70" t="str">
-        <v>2026-05-06</v>
+        <v>2026-05-07</v>
       </c>
       <c r="E70" t="str">
         <v/>
@@ -3067,7 +3067,7 @@
         <v>https://music.apple.com/us/song/1989/1893089382</v>
       </c>
       <c r="D71" t="str">
-        <v>2026-05-06</v>
+        <v>2026-05-07</v>
       </c>
       <c r="E71" t="str">
         <v/>
@@ -3105,7 +3105,7 @@
         <v>https://music.apple.com/us/song/no-more-regrets/1893191803</v>
       </c>
       <c r="D72" t="str">
-        <v>2026-05-06</v>
+        <v>2026-05-07</v>
       </c>
       <c r="E72" t="str">
         <v/>
@@ -3143,7 +3143,7 @@
         <v>https://music.apple.com/us/song/drum-machine/1840517102</v>
       </c>
       <c r="D73" t="str">
-        <v>2026-05-06</v>
+        <v>2026-05-07</v>
       </c>
       <c r="E73" t="str">
         <v/>
@@ -3181,7 +3181,7 @@
         <v>https://music.apple.com/us/song/im-perfect/1893181359</v>
       </c>
       <c r="D74" t="str">
-        <v>2026-05-06</v>
+        <v>2026-05-07</v>
       </c>
       <c r="E74" t="str">
         <v/>
@@ -3219,7 +3219,7 @@
         <v>https://music.apple.com/us/song/theme-for-a-train-journey/1880699785</v>
       </c>
       <c r="D75" t="str">
-        <v>2026-05-06</v>
+        <v>2026-05-07</v>
       </c>
       <c r="E75" t="str">
         <v/>
@@ -3257,7 +3257,7 @@
         <v>https://music.apple.com/us/song/bitch-you-weird/6763395875</v>
       </c>
       <c r="D76" t="str">
-        <v>2026-05-06</v>
+        <v>2026-05-07</v>
       </c>
       <c r="E76" t="str">
         <v/>
@@ -3295,7 +3295,7 @@
         <v>https://music.apple.com/us/song/blackbird-rising/1887166611</v>
       </c>
       <c r="D77" t="str">
-        <v>2026-05-06</v>
+        <v>2026-05-07</v>
       </c>
       <c r="E77" t="str">
         <v/>
@@ -3333,7 +3333,7 @@
         <v>https://music.apple.com/us/song/usher-in-the-spirit/6763373678</v>
       </c>
       <c r="D78" t="str">
-        <v>2026-05-06</v>
+        <v>2026-05-07</v>
       </c>
       <c r="E78" t="str">
         <v/>
@@ -3371,7 +3371,7 @@
         <v>https://music.apple.com/us/song/moonlight/1892950791</v>
       </c>
       <c r="D79" t="str">
-        <v>2026-05-06</v>
+        <v>2026-05-07</v>
       </c>
       <c r="E79" t="str">
         <v/>
@@ -3409,7 +3409,7 @@
         <v>https://music.apple.com/us/song/hands-on-me/1893960365</v>
       </c>
       <c r="D80" t="str">
-        <v>2026-05-06</v>
+        <v>2026-05-07</v>
       </c>
       <c r="E80" t="str">
         <v/>
@@ -3447,7 +3447,7 @@
         <v>https://music.apple.com/us/song/closure/1892418294</v>
       </c>
       <c r="D81" t="str">
-        <v>2026-05-06</v>
+        <v>2026-05-07</v>
       </c>
       <c r="E81" t="str">
         <v/>
@@ -3485,7 +3485,7 @@
         <v>https://music.apple.com/us/song/hots-4-u/1891478541</v>
       </c>
       <c r="D82" t="str">
-        <v>2026-05-06</v>
+        <v>2026-05-07</v>
       </c>
       <c r="E82" t="str">
         <v/>
@@ -3523,7 +3523,7 @@
         <v>https://music.apple.com/us/song/cule-poco-sirena-besarico-coste%C3%B1a/1893480200</v>
       </c>
       <c r="D83" t="str">
-        <v>2026-05-06</v>
+        <v>2026-05-07</v>
       </c>
       <c r="E83" t="str">
         <v/>
@@ -3561,7 +3561,7 @@
         <v>https://music.apple.com/us/song/the-coin-toss/1894872115</v>
       </c>
       <c r="D84" t="str">
-        <v>2026-05-06</v>
+        <v>2026-05-07</v>
       </c>
       <c r="E84" t="str">
         <v/>
@@ -3599,7 +3599,7 @@
         <v>https://music.apple.com/us/song/bottles-lights/6763041153</v>
       </c>
       <c r="D85" t="str">
-        <v>2026-05-06</v>
+        <v>2026-05-07</v>
       </c>
       <c r="E85" t="str">
         <v/>
@@ -3637,7 +3637,7 @@
         <v>https://music.apple.com/us/song/perfect-for-me/6762879981</v>
       </c>
       <c r="D86" t="str">
-        <v>2026-05-06</v>
+        <v>2026-05-07</v>
       </c>
       <c r="E86" t="str">
         <v/>
@@ -3675,7 +3675,7 @@
         <v>https://music.apple.com/us/song/so/1893162424</v>
       </c>
       <c r="D87" t="str">
-        <v>2026-05-06</v>
+        <v>2026-05-07</v>
       </c>
       <c r="E87" t="str">
         <v/>
@@ -3713,7 +3713,7 @@
         <v>https://music.apple.com/us/song/pase-y-pase/1894076490</v>
       </c>
       <c r="D88" t="str">
-        <v>2026-05-06</v>
+        <v>2026-05-07</v>
       </c>
       <c r="E88" t="str">
         <v/>
@@ -3751,7 +3751,7 @@
         <v>https://music.apple.com/us/song/agou%C3%A9-dambala-yanvalou-1/1888242486</v>
       </c>
       <c r="D89" t="str">
-        <v>2026-05-06</v>
+        <v>2026-05-07</v>
       </c>
       <c r="E89" t="str">
         <v/>
@@ -3789,7 +3789,7 @@
         <v>https://music.apple.com/us/song/aljahalat/1889267983</v>
       </c>
       <c r="D90" t="str">
-        <v>2026-05-06</v>
+        <v>2026-05-07</v>
       </c>
       <c r="E90" t="str">
         <v/>
@@ -3827,7 +3827,7 @@
         <v>https://music.apple.com/us/song/puleza/1893765840</v>
       </c>
       <c r="D91" t="str">
-        <v>2026-05-06</v>
+        <v>2026-05-07</v>
       </c>
       <c r="E91" t="str">
         <v/>
@@ -3865,7 +3865,7 @@
         <v>https://music.apple.com/us/song/bastards/6762403102</v>
       </c>
       <c r="D92" t="str">
-        <v>2026-05-06</v>
+        <v>2026-05-07</v>
       </c>
       <c r="E92" t="str">
         <v/>
@@ -3903,7 +3903,7 @@
         <v>https://music.apple.com/us/song/crutch/6763345020</v>
       </c>
       <c r="D93" t="str">
-        <v>2026-05-06</v>
+        <v>2026-05-07</v>
       </c>
       <c r="E93" t="str">
         <v/>
@@ -3941,7 +3941,7 @@
         <v>https://music.apple.com/us/song/just-a-man/1893736206</v>
       </c>
       <c r="D94" t="str">
-        <v>2026-05-06</v>
+        <v>2026-05-07</v>
       </c>
       <c r="E94" t="str">
         <v/>
@@ -3979,7 +3979,7 @@
         <v>https://music.apple.com/us/song/take-care-of-you/6762283983</v>
       </c>
       <c r="D95" t="str">
-        <v>2026-05-06</v>
+        <v>2026-05-07</v>
       </c>
       <c r="E95" t="str">
         <v/>
@@ -4017,7 +4017,7 @@
         <v>https://music.apple.com/us/song/love-you-more/1889686330</v>
       </c>
       <c r="D96" t="str">
-        <v>2026-05-06</v>
+        <v>2026-05-07</v>
       </c>
       <c r="E96" t="str">
         <v/>
@@ -4055,7 +4055,7 @@
         <v>https://music.apple.com/us/song/construct/1869323374</v>
       </c>
       <c r="D97" t="str">
-        <v>2026-05-06</v>
+        <v>2026-05-07</v>
       </c>
       <c r="E97" t="str">
         <v/>
@@ -4093,7 +4093,7 @@
         <v>https://music.apple.com/us/song/as-above-so-below/1872651422</v>
       </c>
       <c r="D98" t="str">
-        <v>2026-05-06</v>
+        <v>2026-05-07</v>
       </c>
       <c r="E98" t="str">
         <v/>
@@ -4131,7 +4131,7 @@
         <v>https://music.apple.com/us/song/revenant/6763148056</v>
       </c>
       <c r="D99" t="str">
-        <v>2026-05-06</v>
+        <v>2026-05-07</v>
       </c>
       <c r="E99" t="str">
         <v/>
@@ -4169,7 +4169,7 @@
         <v>https://music.apple.com/us/song/black-box-feat-joe-duplantier-the-mystery-of/6762312582</v>
       </c>
       <c r="D100" t="str">
-        <v>2026-05-06</v>
+        <v>2026-05-07</v>
       </c>
       <c r="E100" t="str">
         <v/>
@@ -4207,7 +4207,7 @@
         <v>https://music.apple.com/us/song/power-4/6763647813</v>
       </c>
       <c r="D101" t="str">
-        <v>2026-05-06</v>
+        <v>2026-05-07</v>
       </c>
       <c r="E101" t="str">
         <v/>
@@ -4245,7 +4245,7 @@
         <v>https://music.apple.com/us/song/too-easy/1893814702</v>
       </c>
       <c r="D102" t="str">
-        <v>2026-05-06</v>
+        <v>2026-05-07</v>
       </c>
       <c r="E102" t="str">
         <v/>
@@ -4283,7 +4283,7 @@
         <v>https://music.apple.com/us/song/if-you-want-it/1892503347</v>
       </c>
       <c r="D103" t="str">
-        <v>2026-05-06</v>
+        <v>2026-05-07</v>
       </c>
       <c r="E103" t="str">
         <v/>
@@ -4321,7 +4321,7 @@
         <v>https://music.apple.com/us/song/shoplifting/1852812659</v>
       </c>
       <c r="D104" t="str">
-        <v>2026-05-06</v>
+        <v>2026-05-07</v>
       </c>
       <c r="E104" t="str">
         <v/>
@@ -4359,7 +4359,7 @@
         <v>https://music.apple.com/us/song/endlessly-feat-bea1991/1876022833</v>
       </c>
       <c r="D105" t="str">
-        <v>2026-05-06</v>
+        <v>2026-05-07</v>
       </c>
       <c r="E105" t="str">
         <v/>
